--- a/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
+++ b/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
@@ -255,7 +255,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -698,6 +698,48 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1908,7 +1950,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Децентрализация ОРШ'!C71</f>
+              <f>'Децентрализация ОРШ'!C75</f>
             </strRef>
           </tx>
           <spPr>
@@ -1930,12 +1972,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Децентрализация ОРШ'!$B$72:$B$83</f>
+              <f>'Децентрализация ОРШ'!$B$76:$B$87</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Децентрализация ОРШ'!$C$72:$C$83</f>
+              <f>'Децентрализация ОРШ'!$C$76:$C$87</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1950,7 +1992,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Децентрализация ОРШ'!D71</f>
+              <f>'Децентрализация ОРШ'!D75</f>
             </strRef>
           </tx>
           <spPr>
@@ -1972,7 +2014,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Децентрализация ОРШ'!$D$72:$D$83</f>
+              <f>'Децентрализация ОРШ'!$D$76:$D$87</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2802,7 +2844,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7560000" cy="3960000"/>
@@ -4382,7 +4424,7 @@
       <c r="L5" s="108" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1" s="63">
-      <c r="B6" s="229" t="n">
+      <c r="B6" s="243" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -4390,7 +4432,7 @@
           <t>Шкаф оптический распределительный (ОРШ) центральный — в здании ЦУ</t>
         </is>
       </c>
-      <c r="D6" s="229" t="inlineStr">
+      <c r="D6" s="243" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4400,22 +4442,22 @@
           <t>1 на СНП (здание по проекту)</t>
         </is>
       </c>
-      <c r="F6" s="220" t="n">
+      <c r="F6" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="220" t="n">
+      <c r="G6" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="220" t="n">
+      <c r="H6" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="220" t="n">
+      <c r="I6" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="220" t="n">
+      <c r="J6" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="220" t="n">
+      <c r="K6" s="234" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="146">
@@ -4424,7 +4466,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="63">
-      <c r="B7" s="230" t="n">
+      <c r="B7" s="244" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="114" t="inlineStr">
@@ -4432,7 +4474,7 @@
           <t>Шкаф зонный ОРШ уличный (под сплиттеры 1:64)</t>
         </is>
       </c>
-      <c r="D7" s="230" t="inlineStr">
+      <c r="D7" s="244" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4442,21 +4484,21 @@
           <t>1 на зону — в центре сектора (медиана зоны, зона ≥ 48 ДХ)</t>
         </is>
       </c>
-      <c r="F7" s="221" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="221" t="n"/>
-      <c r="H7" s="221" t="n">
+      <c r="F7" s="235" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" s="235" t="n"/>
+      <c r="H7" s="235" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="221" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="221" t="n">
+      <c r="I7" s="235" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" s="235" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="221" t="n">
-        <v>3</v>
+      <c r="K7" s="235" t="n">
+        <v>2</v>
       </c>
       <c r="L7" s="147">
         <f>SUM(F7:K7)</f>
@@ -4464,7 +4506,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="63">
-      <c r="B8" s="229" t="n">
+      <c r="B8" s="243" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -4472,7 +4514,7 @@
           <t>Сплиттер PLC 1×64 (в ОРШ: ЦУ и зонных)</t>
         </is>
       </c>
-      <c r="D8" s="229" t="inlineStr">
+      <c r="D8" s="243" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4482,22 +4524,22 @@
           <t>ceil(ДХ зоны / 64), заполнение 75-100%</t>
         </is>
       </c>
-      <c r="F8" s="220" t="n">
-        <v>21</v>
-      </c>
-      <c r="G8" s="220" t="n">
+      <c r="F8" s="234" t="n">
+        <v>22</v>
+      </c>
+      <c r="G8" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="220" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" s="220" t="n">
+      <c r="H8" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="220" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" s="220" t="n">
+      <c r="J8" s="234" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" s="234" t="n">
         <v>7</v>
       </c>
       <c r="L8" s="146">
@@ -4506,7 +4548,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="63">
-      <c r="B9" s="230" t="n">
+      <c r="B9" s="244" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="114" t="inlineStr">
@@ -4514,7 +4556,7 @@
           <t>Пигтейль SC/UPC для кросса ОРШ</t>
         </is>
       </c>
-      <c r="D9" s="230" t="inlineStr">
+      <c r="D9" s="244" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4524,22 +4566,22 @@
           <t>ДХ + 2 × сплиттеры 1:64</t>
         </is>
       </c>
-      <c r="F9" s="221" t="n">
-        <v>1071</v>
-      </c>
-      <c r="G9" s="221" t="n">
+      <c r="F9" s="235" t="n">
+        <v>1073</v>
+      </c>
+      <c r="G9" s="235" t="n">
         <v>128</v>
       </c>
-      <c r="H9" s="221" t="n">
-        <v>390</v>
-      </c>
-      <c r="I9" s="221" t="n">
+      <c r="H9" s="235" t="n">
+        <v>392</v>
+      </c>
+      <c r="I9" s="235" t="n">
         <v>650</v>
       </c>
-      <c r="J9" s="221" t="n">
-        <v>300</v>
-      </c>
-      <c r="K9" s="221" t="n">
+      <c r="J9" s="235" t="n">
+        <v>298</v>
+      </c>
+      <c r="K9" s="235" t="n">
         <v>342</v>
       </c>
       <c r="L9" s="147">
@@ -4548,7 +4590,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="63">
-      <c r="B10" s="229" t="n">
+      <c r="B10" s="243" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="112" t="inlineStr">
@@ -4556,7 +4598,7 @@
           <t>Порт PON OLT — справочно (активное оборудование, единый узел OLT)</t>
         </is>
       </c>
-      <c r="D10" s="229" t="inlineStr">
+      <c r="D10" s="243" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4566,22 +4608,22 @@
           <t>по числу сплиттеров 1:64</t>
         </is>
       </c>
-      <c r="F10" s="220" t="n">
-        <v>21</v>
-      </c>
-      <c r="G10" s="220" t="n">
+      <c r="F10" s="234" t="n">
+        <v>22</v>
+      </c>
+      <c r="G10" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="220" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" s="220" t="n">
+      <c r="H10" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" s="234" t="n">
         <v>14</v>
       </c>
-      <c r="J10" s="220" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" s="220" t="n">
+      <c r="J10" s="234" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="234" t="n">
         <v>7</v>
       </c>
       <c r="L10" s="146">
@@ -4607,7 +4649,7 @@
       <c r="L11" s="108" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="63">
-      <c r="B12" s="229" t="n">
+      <c r="B12" s="243" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="112" t="inlineStr">
@@ -4615,7 +4657,7 @@
           <t>Кабель оптический самонесущий, 8 волокон</t>
         </is>
       </c>
-      <c r="D12" s="229" t="inlineStr">
+      <c r="D12" s="243" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4625,23 +4667,23 @@
           <t>распределение зоны max(8; 1,25 × ДХ потока) + фидер ceil(1,25 × сплиттеры зоны)</t>
         </is>
       </c>
-      <c r="F12" s="222" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="G12" s="222" t="n">
+      <c r="F12" s="236" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G12" s="236" t="n">
         <v>2.6</v>
       </c>
-      <c r="H12" s="222" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I12" s="222" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J12" s="222" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K12" s="222" t="n">
-        <v>5.2</v>
+      <c r="H12" s="236" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="236" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="J12" s="236" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K12" s="236" t="n">
+        <v>4.8</v>
       </c>
       <c r="L12" s="148">
         <f>SUM(F12:K12)</f>
@@ -4649,7 +4691,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="63">
-      <c r="B13" s="230" t="n">
+      <c r="B13" s="244" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="114" t="inlineStr">
@@ -4657,7 +4699,7 @@
           <t>Кабель оптический самонесущий, 12 волокон</t>
         </is>
       </c>
-      <c r="D13" s="230" t="inlineStr">
+      <c r="D13" s="244" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4667,23 +4709,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F13" s="224" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="224" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H13" s="224" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I13" s="224" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J13" s="224" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K13" s="224" t="n">
-        <v>1.1</v>
+      <c r="F13" s="238" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G13" s="238" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H13" s="238" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="238" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J13" s="238" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K13" s="238" t="n">
+        <v>1.2</v>
       </c>
       <c r="L13" s="149">
         <f>SUM(F13:K13)</f>
@@ -4691,7 +4733,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="63">
-      <c r="B14" s="229" t="n">
+      <c r="B14" s="243" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="112" t="inlineStr">
@@ -4699,7 +4741,7 @@
           <t>Кабель оптический самонесущий, 16 волокон</t>
         </is>
       </c>
-      <c r="D14" s="229" t="inlineStr">
+      <c r="D14" s="243" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4709,23 +4751,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F14" s="222" t="n">
+      <c r="F14" s="236" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" s="222" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H14" s="222" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I14" s="222" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" s="222" t="n">
+      <c r="G14" s="236" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="236" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="236" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J14" s="236" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K14" s="236" t="n">
         <v>0.7</v>
-      </c>
-      <c r="K14" s="222" t="n">
-        <v>0.9</v>
       </c>
       <c r="L14" s="148">
         <f>SUM(F14:K14)</f>
@@ -4733,7 +4775,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="63">
-      <c r="B15" s="230" t="n">
+      <c r="B15" s="244" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="114" t="inlineStr">
@@ -4741,7 +4783,7 @@
           <t>Кабель оптический самонесущий, 24 волокна</t>
         </is>
       </c>
-      <c r="D15" s="230" t="inlineStr">
+      <c r="D15" s="244" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4751,22 +4793,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F15" s="224" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="224" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H15" s="224" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I15" s="224" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J15" s="224" t="n">
+      <c r="F15" s="238" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" s="238" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="238" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="238" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J15" s="238" t="n">
         <v>1.4</v>
       </c>
-      <c r="K15" s="224" t="n">
+      <c r="K15" s="238" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="149">
@@ -4775,7 +4817,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="63">
-      <c r="B16" s="229" t="n">
+      <c r="B16" s="243" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="112" t="inlineStr">
@@ -4783,7 +4825,7 @@
           <t>Кабель оптический самонесущий, 32 волокна</t>
         </is>
       </c>
-      <c r="D16" s="229" t="inlineStr">
+      <c r="D16" s="243" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4793,23 +4835,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F16" s="222" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G16" s="222" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H16" s="222" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="I16" s="222" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J16" s="222" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K16" s="222" t="n">
+      <c r="F16" s="236" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G16" s="236" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H16" s="236" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I16" s="236" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J16" s="236" t="n">
         <v>0.8</v>
+      </c>
+      <c r="K16" s="236" t="n">
+        <v>0.9</v>
       </c>
       <c r="L16" s="148">
         <f>SUM(F16:K16)</f>
@@ -4817,7 +4859,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="63">
-      <c r="B17" s="230" t="n">
+      <c r="B17" s="244" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="114" t="inlineStr">
@@ -4825,7 +4867,7 @@
           <t>Кабель оптический самонесущий, 48 волокон</t>
         </is>
       </c>
-      <c r="D17" s="230" t="inlineStr">
+      <c r="D17" s="244" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4835,23 +4877,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F17" s="224" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G17" s="224" t="n">
+      <c r="F17" s="238" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G17" s="238" t="n">
         <v>0.2</v>
       </c>
-      <c r="H17" s="224" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I17" s="224" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J17" s="224" t="n">
+      <c r="H17" s="238" t="n">
         <v>1.1</v>
       </c>
-      <c r="K17" s="224" t="n">
-        <v>0.5</v>
+      <c r="I17" s="238" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J17" s="238" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K17" s="238" t="n">
+        <v>1</v>
       </c>
       <c r="L17" s="149">
         <f>SUM(F17:K17)</f>
@@ -4859,7 +4901,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="63">
-      <c r="B18" s="229" t="n">
+      <c r="B18" s="243" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="112" t="inlineStr">
@@ -4867,7 +4909,7 @@
           <t>Кабель оптический самонесущий, 64 волокна</t>
         </is>
       </c>
-      <c r="D18" s="229" t="inlineStr">
+      <c r="D18" s="243" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4877,23 +4919,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F18" s="222" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G18" s="222" t="n">
+      <c r="F18" s="236" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G18" s="236" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H18" s="236" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I18" s="236" t="n">
         <v>0.4</v>
       </c>
-      <c r="H18" s="222" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I18" s="222" t="n">
+      <c r="J18" s="236" t="n">
         <v>0.3</v>
       </c>
-      <c r="J18" s="222" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K18" s="222" t="n">
-        <v>0.2</v>
+      <c r="K18" s="236" t="n">
+        <v>0.3</v>
       </c>
       <c r="L18" s="148">
         <f>SUM(F18:K18)</f>
@@ -4901,7 +4943,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="63">
-      <c r="B19" s="230" t="n">
+      <c r="B19" s="244" t="n">
         <v>13</v>
       </c>
       <c r="C19" s="114" t="inlineStr">
@@ -4909,7 +4951,7 @@
           <t>Кабель оптический самонесущий, 72 волокна</t>
         </is>
       </c>
-      <c r="D19" s="230" t="inlineStr">
+      <c r="D19" s="244" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4919,14 +4961,14 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F19" s="224" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G19" s="224" t="n"/>
-      <c r="H19" s="224" t="n"/>
-      <c r="I19" s="224" t="n"/>
-      <c r="J19" s="224" t="n"/>
-      <c r="K19" s="224" t="n">
+      <c r="F19" s="238" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G19" s="238" t="n"/>
+      <c r="H19" s="238" t="n"/>
+      <c r="I19" s="238" t="n"/>
+      <c r="J19" s="238" t="n"/>
+      <c r="K19" s="238" t="n">
         <v>0.1</v>
       </c>
       <c r="L19" s="149">
@@ -4935,7 +4977,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="63">
-      <c r="B20" s="229" t="n">
+      <c r="B20" s="243" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="112" t="inlineStr">
@@ -4943,7 +4985,7 @@
           <t>Кабель оптический самонесущий, 96 волокон</t>
         </is>
       </c>
-      <c r="D20" s="229" t="inlineStr">
+      <c r="D20" s="243" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4953,25 +4995,29 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F20" s="222" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G20" s="222" t="n">
+      <c r="F20" s="236" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="236" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="236" t="n">
         <v>0.2</v>
       </c>
-      <c r="H20" s="222" t="n">
+      <c r="I20" s="236" t="n"/>
+      <c r="J20" s="236" t="n">
         <v>0.1</v>
       </c>
-      <c r="I20" s="222" t="n"/>
-      <c r="J20" s="222" t="n"/>
-      <c r="K20" s="222" t="n"/>
+      <c r="K20" s="236" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L20" s="148">
         <f>SUM(F20:K20)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="63">
-      <c r="B21" s="230" t="n">
+      <c r="B21" s="244" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="114" t="inlineStr">
@@ -4979,7 +5025,7 @@
           <t>Кабель дроп-кабельный самонесущий, 2 волокна (1 раб. + 1 рез.)</t>
         </is>
       </c>
-      <c r="D21" s="230" t="inlineStr">
+      <c r="D21" s="244" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4989,23 +5035,23 @@
           <t>дропы × 1,05 (без подводок — дроп от муфты напрямую)</t>
         </is>
       </c>
-      <c r="F21" s="224" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="G21" s="224" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H21" s="224" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="I21" s="224" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="J21" s="224" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K21" s="224" t="n">
-        <v>11.8</v>
+      <c r="F21" s="238" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G21" s="238" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H21" s="238" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I21" s="238" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="J21" s="238" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="K21" s="238" t="n">
+        <v>13</v>
       </c>
       <c r="L21" s="149">
         <f>SUM(F21:K21)</f>
@@ -5013,7 +5059,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="63">
-      <c r="B22" s="229" t="n">
+      <c r="B22" s="243" t="n">
         <v>16</v>
       </c>
       <c r="C22" s="112" t="inlineStr">
@@ -5021,7 +5067,7 @@
           <t>Справочно: суммарная ёмкость магистрального кабеля</t>
         </is>
       </c>
-      <c r="D22" s="229" t="inlineStr">
+      <c r="D22" s="243" t="inlineStr">
         <is>
           <t>волокно-км</t>
         </is>
@@ -5031,23 +5077,23 @@
           <t>Σ (длина участка × волокна)</t>
         </is>
       </c>
-      <c r="F22" s="222" t="n">
-        <v>547.5</v>
-      </c>
-      <c r="G22" s="222" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="H22" s="222" t="n">
-        <v>194</v>
-      </c>
-      <c r="I22" s="222" t="n">
-        <v>333.9</v>
-      </c>
-      <c r="J22" s="222" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="K22" s="222" t="n">
-        <v>137.9</v>
+      <c r="F22" s="236" t="n">
+        <v>524.8</v>
+      </c>
+      <c r="G22" s="236" t="n">
+        <v>90</v>
+      </c>
+      <c r="H22" s="236" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="I22" s="236" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="J22" s="236" t="n">
+        <v>141.2</v>
+      </c>
+      <c r="K22" s="236" t="n">
+        <v>170</v>
       </c>
       <c r="L22" s="148">
         <f>SUM(F22:K22)</f>
@@ -5072,7 +5118,7 @@
       <c r="L23" s="108" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="63">
-      <c r="B24" s="229" t="n">
+      <c r="B24" s="243" t="n">
         <v>17</v>
       </c>
       <c r="C24" s="112" t="inlineStr">
@@ -5080,7 +5126,7 @@
           <t>Муфта оптическая (ветвления магистрали)</t>
         </is>
       </c>
-      <c r="D24" s="229" t="inlineStr">
+      <c r="D24" s="243" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5090,23 +5136,23 @@
           <t>узлы ветвления кроме точек врезов зонных ОРШ; транзит — неразрезным кабелем</t>
         </is>
       </c>
-      <c r="F24" s="220" t="n">
-        <v>371</v>
-      </c>
-      <c r="G24" s="220" t="n">
+      <c r="F24" s="234" t="n">
+        <v>367</v>
+      </c>
+      <c r="G24" s="234" t="n">
         <v>70</v>
       </c>
-      <c r="H24" s="220" t="n">
+      <c r="H24" s="234" t="n">
         <v>158</v>
       </c>
-      <c r="I24" s="220" t="n">
-        <v>247</v>
-      </c>
-      <c r="J24" s="220" t="n">
+      <c r="I24" s="234" t="n">
+        <v>246</v>
+      </c>
+      <c r="J24" s="234" t="n">
         <v>119</v>
       </c>
-      <c r="K24" s="220" t="n">
-        <v>147</v>
+      <c r="K24" s="234" t="n">
+        <v>148</v>
       </c>
       <c r="L24" s="146">
         <f>SUM(F24:K24)</f>
@@ -5131,7 +5177,7 @@
       <c r="L25" s="108" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="63">
-      <c r="B26" s="229" t="n">
+      <c r="B26" s="243" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="112" t="inlineStr">
@@ -5139,7 +5185,7 @@
           <t>Бокс абонентский оптический с адаптером SC/UPC</t>
         </is>
       </c>
-      <c r="D26" s="229" t="inlineStr">
+      <c r="D26" s="243" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5149,22 +5195,22 @@
           <t>1 на ДХ</t>
         </is>
       </c>
-      <c r="F26" s="220" t="n">
+      <c r="F26" s="234" t="n">
         <v>1029</v>
       </c>
-      <c r="G26" s="220" t="n">
+      <c r="G26" s="234" t="n">
         <v>124</v>
       </c>
-      <c r="H26" s="220" t="n">
+      <c r="H26" s="234" t="n">
         <v>376</v>
       </c>
-      <c r="I26" s="220" t="n">
+      <c r="I26" s="234" t="n">
         <v>622</v>
       </c>
-      <c r="J26" s="220" t="n">
+      <c r="J26" s="234" t="n">
         <v>286</v>
       </c>
-      <c r="K26" s="220" t="n">
+      <c r="K26" s="234" t="n">
         <v>328</v>
       </c>
       <c r="L26" s="146">
@@ -5173,7 +5219,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="63">
-      <c r="B27" s="230" t="n">
+      <c r="B27" s="244" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="114" t="inlineStr">
@@ -5181,7 +5227,7 @@
           <t>Коннектор оптический механический SC/UPC</t>
         </is>
       </c>
-      <c r="D27" s="230" t="inlineStr">
+      <c r="D27" s="244" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5191,22 +5237,22 @@
           <t>ДХ × 1,1 (абонентский бокс)</t>
         </is>
       </c>
-      <c r="F27" s="221" t="n">
+      <c r="F27" s="235" t="n">
         <v>1132</v>
       </c>
-      <c r="G27" s="221" t="n">
+      <c r="G27" s="235" t="n">
         <v>137</v>
       </c>
-      <c r="H27" s="221" t="n">
+      <c r="H27" s="235" t="n">
         <v>414</v>
       </c>
-      <c r="I27" s="221" t="n">
+      <c r="I27" s="235" t="n">
         <v>685</v>
       </c>
-      <c r="J27" s="221" t="n">
+      <c r="J27" s="235" t="n">
         <v>315</v>
       </c>
-      <c r="K27" s="221" t="n">
+      <c r="K27" s="235" t="n">
         <v>361</v>
       </c>
       <c r="L27" s="147">
@@ -5215,7 +5261,7 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="63">
-      <c r="B28" s="229" t="n">
+      <c r="B28" s="243" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="112" t="inlineStr">
@@ -5223,7 +5269,7 @@
           <t>Сварное соединение (оценка объёма работ)</t>
         </is>
       </c>
-      <c r="D28" s="229" t="inlineStr">
+      <c r="D28" s="243" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5233,22 +5279,22 @@
           <t>(2 × ДХ + 2 × сплиттеры 1:64) × 1,1</t>
         </is>
       </c>
-      <c r="F28" s="220" t="n">
-        <v>2310</v>
-      </c>
-      <c r="G28" s="220" t="n">
+      <c r="F28" s="234" t="n">
+        <v>2313</v>
+      </c>
+      <c r="G28" s="234" t="n">
         <v>278</v>
       </c>
-      <c r="H28" s="220" t="n">
-        <v>843</v>
-      </c>
-      <c r="I28" s="220" t="n">
+      <c r="H28" s="234" t="n">
+        <v>845</v>
+      </c>
+      <c r="I28" s="234" t="n">
         <v>1400</v>
       </c>
-      <c r="J28" s="220" t="n">
-        <v>645</v>
-      </c>
-      <c r="K28" s="220" t="n">
+      <c r="J28" s="234" t="n">
+        <v>643</v>
+      </c>
+      <c r="K28" s="234" t="n">
         <v>737</v>
       </c>
       <c r="L28" s="146">
@@ -5257,7 +5303,7 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="63">
-      <c r="B29" s="230" t="n">
+      <c r="B29" s="244" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="114" t="inlineStr">
@@ -5265,7 +5311,7 @@
           <t>Гильза КДЗС, 60 мм</t>
         </is>
       </c>
-      <c r="D29" s="230" t="inlineStr">
+      <c r="D29" s="244" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5275,22 +5321,22 @@
           <t>по числу сварных соединений</t>
         </is>
       </c>
-      <c r="F29" s="221" t="n">
-        <v>2310</v>
-      </c>
-      <c r="G29" s="221" t="n">
+      <c r="F29" s="235" t="n">
+        <v>2313</v>
+      </c>
+      <c r="G29" s="235" t="n">
         <v>278</v>
       </c>
-      <c r="H29" s="221" t="n">
-        <v>843</v>
-      </c>
-      <c r="I29" s="221" t="n">
+      <c r="H29" s="235" t="n">
+        <v>845</v>
+      </c>
+      <c r="I29" s="235" t="n">
         <v>1400</v>
       </c>
-      <c r="J29" s="221" t="n">
-        <v>645</v>
-      </c>
-      <c r="K29" s="221" t="n">
+      <c r="J29" s="235" t="n">
+        <v>643</v>
+      </c>
+      <c r="K29" s="235" t="n">
         <v>737</v>
       </c>
       <c r="L29" s="147">
@@ -5299,7 +5345,7 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="63">
-      <c r="B30" s="229" t="n">
+      <c r="B30" s="243" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="112" t="inlineStr">
@@ -5307,7 +5353,7 @@
           <t>Комплект подвеса магистрального кабеля (кронштейн + спиральный зажим)</t>
         </is>
       </c>
-      <c r="D30" s="229" t="inlineStr">
+      <c r="D30" s="243" t="inlineStr">
         <is>
           <t>компл</t>
         </is>
@@ -5317,23 +5363,23 @@
           <t>30 на 1 км кабеля</t>
         </is>
       </c>
-      <c r="F30" s="220" t="n">
-        <v>844</v>
-      </c>
-      <c r="G30" s="220" t="n">
-        <v>139</v>
-      </c>
-      <c r="H30" s="220" t="n">
-        <v>317</v>
-      </c>
-      <c r="I30" s="220" t="n">
-        <v>548</v>
-      </c>
-      <c r="J30" s="220" t="n">
-        <v>237</v>
-      </c>
-      <c r="K30" s="220" t="n">
-        <v>256</v>
+      <c r="F30" s="234" t="n">
+        <v>918</v>
+      </c>
+      <c r="G30" s="234" t="n">
+        <v>144</v>
+      </c>
+      <c r="H30" s="234" t="n">
+        <v>316</v>
+      </c>
+      <c r="I30" s="234" t="n">
+        <v>584</v>
+      </c>
+      <c r="J30" s="234" t="n">
+        <v>247</v>
+      </c>
+      <c r="K30" s="234" t="n">
+        <v>264</v>
       </c>
       <c r="L30" s="146">
         <f>SUM(F30:K30)</f>
@@ -5341,7 +5387,7 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" s="63">
-      <c r="B31" s="230" t="n">
+      <c r="B31" s="244" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="114" t="inlineStr">
@@ -5349,7 +5395,7 @@
           <t>Анкерный зажим дроп-кабеля</t>
         </is>
       </c>
-      <c r="D31" s="230" t="inlineStr">
+      <c r="D31" s="244" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5359,22 +5405,22 @@
           <t>2 на ДХ</t>
         </is>
       </c>
-      <c r="F31" s="221" t="n">
+      <c r="F31" s="235" t="n">
         <v>2058</v>
       </c>
-      <c r="G31" s="221" t="n">
+      <c r="G31" s="235" t="n">
         <v>248</v>
       </c>
-      <c r="H31" s="221" t="n">
+      <c r="H31" s="235" t="n">
         <v>752</v>
       </c>
-      <c r="I31" s="221" t="n">
+      <c r="I31" s="235" t="n">
         <v>1244</v>
       </c>
-      <c r="J31" s="221" t="n">
+      <c r="J31" s="235" t="n">
         <v>572</v>
       </c>
-      <c r="K31" s="221" t="n">
+      <c r="K31" s="235" t="n">
         <v>656</v>
       </c>
       <c r="L31" s="147">
@@ -5383,7 +5429,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" s="63">
-      <c r="B32" s="229" t="n">
+      <c r="B32" s="243" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="112" t="inlineStr">
@@ -5391,7 +5437,7 @@
           <t>Крепёж дроп-кабеля (скобы / хомуты)</t>
         </is>
       </c>
-      <c r="D32" s="229" t="inlineStr">
+      <c r="D32" s="243" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5401,22 +5447,22 @@
           <t>6 на ДХ</t>
         </is>
       </c>
-      <c r="F32" s="220" t="n">
+      <c r="F32" s="234" t="n">
         <v>6174</v>
       </c>
-      <c r="G32" s="220" t="n">
+      <c r="G32" s="234" t="n">
         <v>744</v>
       </c>
-      <c r="H32" s="220" t="n">
+      <c r="H32" s="234" t="n">
         <v>2256</v>
       </c>
-      <c r="I32" s="220" t="n">
+      <c r="I32" s="234" t="n">
         <v>3732</v>
       </c>
-      <c r="J32" s="220" t="n">
+      <c r="J32" s="234" t="n">
         <v>1716</v>
       </c>
-      <c r="K32" s="220" t="n">
+      <c r="K32" s="234" t="n">
         <v>1968</v>
       </c>
       <c r="L32" s="146">
@@ -5434,7 +5480,7 @@
     <row r="35" ht="14" customHeight="1" s="63">
       <c r="B35" s="107" t="inlineStr">
         <is>
-          <t>Схема D (уточнённая детекция ДХ, полная VLM-верификация): 28 зон + 6 ЦУ = 34 ОРШ; заполнение сплиттеров 1:64 — 75-100%; ср. волоконный маршрут ДХ 304 м (против 1361 м в централизованной). Карты зон ОРШ по всем СНП — download/snp_vko.</t>
+          <t>Схема D (уточнённая детекция ДХ, полная VLM-верификация): 32 зон + 6 ЦУ = 38 ОРШ; заполнение сплиттеров 1:64 — 75-100%; ср. волоконный маршрут ДХ 305 м (против 1361 м в централизованной). Карты зон ОРШ по всем СНП — download/snp_vko.</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N138"/>
+  <dimension ref="B2:N142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="63" min="1" max="1"/>
@@ -9085,7 +9131,7 @@
       </c>
       <c r="D14" s="109" t="inlineStr">
         <is>
-          <t>S_MIN = 15 волокно-км на доп. ОРШ: 28 зон + 6 ЦУ = 34 ОРШ; волокно-км 1474 (-69% к A); суммарная длина 202.1 км — минимум среди всех схем книги.</t>
+          <t>S_MIN = 15 волокно-км на доп. ОРШ: 32 зон + 6 ЦУ = 38 ОРШ; волокно-км 1474 (-69% к A); суммарная длина 206.3 км — минимум среди всех схем книги.</t>
         </is>
       </c>
     </row>
@@ -9166,19 +9212,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F18" s="220" t="n">
-        <v>84</v>
-      </c>
-      <c r="G18" s="220" t="n">
+      <c r="F18" s="234" t="n">
+        <v>69</v>
+      </c>
+      <c r="G18" s="234" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="220" t="n">
+      <c r="H18" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="220" t="n">
+      <c r="I18" s="234" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="220" t="n">
+      <c r="J18" s="234" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9194,20 +9240,20 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F19" s="221" t="n">
-        <v>109</v>
-      </c>
-      <c r="G19" s="221" t="n">
-        <v>716</v>
-      </c>
-      <c r="H19" s="221" t="n">
+      <c r="F19" s="235" t="n">
+        <v>46</v>
+      </c>
+      <c r="G19" s="235" t="n">
+        <v>752</v>
+      </c>
+      <c r="H19" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I19" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" s="221" t="n">
-        <v>144</v>
+      <c r="J19" s="235" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="63">
@@ -9222,19 +9268,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F20" s="220" t="n">
-        <v>116</v>
-      </c>
-      <c r="G20" s="220" t="n">
-        <v>738</v>
-      </c>
-      <c r="H20" s="220" t="n">
+      <c r="F20" s="234" t="n">
+        <v>114</v>
+      </c>
+      <c r="G20" s="234" t="n">
+        <v>546</v>
+      </c>
+      <c r="H20" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="220" t="n">
+      <c r="I20" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="220" t="n">
+      <c r="J20" s="234" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9250,20 +9296,20 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F21" s="221" t="n">
-        <v>136</v>
-      </c>
-      <c r="G21" s="221" t="n">
-        <v>1359</v>
-      </c>
-      <c r="H21" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="221" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="221" t="n">
-        <v>288</v>
+      <c r="F21" s="235" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="235" t="n">
+        <v>667</v>
+      </c>
+      <c r="H21" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="235" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="235" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="63">
@@ -9278,19 +9324,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F22" s="220" t="n">
-        <v>142</v>
-      </c>
-      <c r="G22" s="220" t="n">
-        <v>1313</v>
-      </c>
-      <c r="H22" s="220" t="n">
+      <c r="F22" s="234" t="n">
+        <v>132</v>
+      </c>
+      <c r="G22" s="234" t="n">
+        <v>717</v>
+      </c>
+      <c r="H22" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="220" t="n">
+      <c r="I22" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="220" t="n">
+      <c r="J22" s="234" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9306,19 +9352,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F23" s="221" t="n">
-        <v>127</v>
-      </c>
-      <c r="G23" s="221" t="n">
-        <v>959</v>
-      </c>
-      <c r="H23" s="221" t="n">
+      <c r="F23" s="235" t="n">
+        <v>109</v>
+      </c>
+      <c r="G23" s="235" t="n">
+        <v>856</v>
+      </c>
+      <c r="H23" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="221" t="n">
+      <c r="I23" s="235" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="221" t="n">
+      <c r="J23" s="235" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9334,19 +9380,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F24" s="220" t="n">
-        <v>64</v>
-      </c>
-      <c r="G24" s="220" t="n">
-        <v>680</v>
-      </c>
-      <c r="H24" s="220" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="220" t="n">
+      <c r="F24" s="234" t="n">
+        <v>84</v>
+      </c>
+      <c r="G24" s="234" t="n">
+        <v>908</v>
+      </c>
+      <c r="H24" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="J24" s="220" t="n">
+      <c r="I24" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="234" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9362,19 +9408,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F25" s="221" t="n">
-        <v>71</v>
-      </c>
-      <c r="G25" s="221" t="n">
-        <v>782</v>
-      </c>
-      <c r="H25" s="221" t="n">
+      <c r="F25" s="235" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="235" t="n">
+        <v>1708</v>
+      </c>
+      <c r="H25" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" s="221" t="n">
+      <c r="J25" s="235" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9390,19 +9436,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F26" s="220" t="n">
-        <v>50</v>
-      </c>
-      <c r="G26" s="220" t="n">
-        <v>1708</v>
-      </c>
-      <c r="H26" s="220" t="n">
+      <c r="F26" s="234" t="n">
+        <v>49</v>
+      </c>
+      <c r="G26" s="234" t="n">
+        <v>860</v>
+      </c>
+      <c r="H26" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="220" t="n">
+      <c r="I26" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="220" t="n">
+      <c r="J26" s="234" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9418,19 +9464,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F27" s="221" t="n">
-        <v>80</v>
-      </c>
-      <c r="G27" s="221" t="n">
-        <v>835</v>
-      </c>
-      <c r="H27" s="221" t="n">
+      <c r="F27" s="235" t="n">
+        <v>49</v>
+      </c>
+      <c r="G27" s="235" t="n">
+        <v>1211</v>
+      </c>
+      <c r="H27" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="221" t="n">
+      <c r="J27" s="235" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9446,91 +9492,83 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F28" s="220" t="n">
+      <c r="F28" s="234" t="n">
+        <v>88</v>
+      </c>
+      <c r="G28" s="234" t="n">
+        <v>1175</v>
+      </c>
+      <c r="H28" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="234" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="63">
+      <c r="C29" s="114" t="inlineStr"/>
+      <c r="D29" s="114" t="inlineStr">
+        <is>
+          <t>З-11</t>
+        </is>
+      </c>
+      <c r="E29" s="114" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F29" s="235" t="n">
         <v>50</v>
       </c>
-      <c r="G28" s="220" t="n">
-        <v>1175</v>
-      </c>
-      <c r="H28" s="220" t="n">
+      <c r="G29" s="235" t="n">
+        <v>1169</v>
+      </c>
+      <c r="H29" s="235" t="n">
         <v>1</v>
       </c>
-      <c r="I28" s="220" t="n">
+      <c r="I29" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="220" t="n">
+      <c r="J29" s="235" t="n">
         <v>96</v>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1" s="63">
-      <c r="C29" s="114" t="inlineStr">
-        <is>
-          <t>Солнечное</t>
-        </is>
-      </c>
-      <c r="D29" s="114" t="inlineStr">
-        <is>
-          <t>ЦУ</t>
-        </is>
-      </c>
-      <c r="E29" s="114" t="inlineStr">
-        <is>
-          <t>ЦУ (корневая)</t>
-        </is>
-      </c>
-      <c r="F29" s="221" t="n">
-        <v>124</v>
-      </c>
-      <c r="G29" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="221" t="n">
+    <row r="30" ht="18" customHeight="1" s="63">
+      <c r="C30" s="112" t="inlineStr"/>
+      <c r="D30" s="112" t="inlineStr">
+        <is>
+          <t>З-12</t>
+        </is>
+      </c>
+      <c r="E30" s="112" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F30" s="234" t="n">
+        <v>51</v>
+      </c>
+      <c r="G30" s="234" t="n">
+        <v>1390</v>
+      </c>
+      <c r="H30" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="I29" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="221" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" s="63">
-      <c r="C30" s="112" t="inlineStr">
-        <is>
-          <t>Перевальное</t>
-        </is>
-      </c>
-      <c r="D30" s="112" t="inlineStr">
-        <is>
-          <t>ЦУ</t>
-        </is>
-      </c>
-      <c r="E30" s="112" t="inlineStr">
-        <is>
-          <t>ЦУ (корневая)</t>
-        </is>
-      </c>
-      <c r="F30" s="220" t="n">
-        <v>54</v>
-      </c>
-      <c r="G30" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="220" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="220" t="n">
-        <v>144</v>
+      <c r="J30" s="234" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="63">
       <c r="C31" s="114" t="inlineStr"/>
       <c r="D31" s="114" t="inlineStr">
         <is>
-          <t>З-1</t>
+          <t>З-13</t>
         </is>
       </c>
       <c r="E31" s="114" t="inlineStr">
@@ -9538,27 +9576,27 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F31" s="221" t="n">
-        <v>102</v>
-      </c>
-      <c r="G31" s="221" t="n">
-        <v>703</v>
-      </c>
-      <c r="H31" s="221" t="n">
+      <c r="F31" s="235" t="n">
+        <v>49</v>
+      </c>
+      <c r="G31" s="235" t="n">
+        <v>879</v>
+      </c>
+      <c r="H31" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I31" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="221" t="n">
-        <v>144</v>
+      <c r="J31" s="235" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="63">
       <c r="C32" s="112" t="inlineStr"/>
       <c r="D32" s="112" t="inlineStr">
         <is>
-          <t>З-2</t>
+          <t>З-14</t>
         </is>
       </c>
       <c r="E32" s="112" t="inlineStr">
@@ -9566,115 +9604,119 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F32" s="220" t="n">
-        <v>62</v>
-      </c>
-      <c r="G32" s="220" t="n">
-        <v>1820</v>
-      </c>
-      <c r="H32" s="220" t="n">
+      <c r="F32" s="234" t="n">
+        <v>59</v>
+      </c>
+      <c r="G32" s="234" t="n">
+        <v>745</v>
+      </c>
+      <c r="H32" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="220" t="n">
+      <c r="I32" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="220" t="n">
+      <c r="J32" s="234" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="63">
-      <c r="C33" s="114" t="inlineStr"/>
+      <c r="C33" s="114" t="inlineStr">
+        <is>
+          <t>Солнечное</t>
+        </is>
+      </c>
       <c r="D33" s="114" t="inlineStr">
         <is>
-          <t>З-3</t>
+          <t>ЦУ</t>
         </is>
       </c>
       <c r="E33" s="114" t="inlineStr">
         <is>
+          <t>ЦУ (корневая)</t>
+        </is>
+      </c>
+      <c r="F33" s="235" t="n">
+        <v>124</v>
+      </c>
+      <c r="G33" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="235" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="235" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="63">
+      <c r="C34" s="112" t="inlineStr">
+        <is>
+          <t>Перевальное</t>
+        </is>
+      </c>
+      <c r="D34" s="112" t="inlineStr">
+        <is>
+          <t>ЦУ</t>
+        </is>
+      </c>
+      <c r="E34" s="112" t="inlineStr">
+        <is>
+          <t>ЦУ (корневая)</t>
+        </is>
+      </c>
+      <c r="F34" s="234" t="n">
+        <v>35</v>
+      </c>
+      <c r="G34" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="234" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="63">
+      <c r="C35" s="114" t="inlineStr"/>
+      <c r="D35" s="114" t="inlineStr">
+        <is>
+          <t>З-1</t>
+        </is>
+      </c>
+      <c r="E35" s="114" t="inlineStr">
+        <is>
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F33" s="221" t="n">
-        <v>104</v>
-      </c>
-      <c r="G33" s="221" t="n">
-        <v>417</v>
-      </c>
-      <c r="H33" s="221" t="n">
+      <c r="F35" s="235" t="n">
+        <v>56</v>
+      </c>
+      <c r="G35" s="235" t="n">
+        <v>805</v>
+      </c>
+      <c r="H35" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" s="221" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1" s="63">
-      <c r="C34" s="112" t="inlineStr"/>
-      <c r="D34" s="112" t="inlineStr">
-        <is>
-          <t>З-4</t>
-        </is>
-      </c>
-      <c r="E34" s="112" t="inlineStr">
-        <is>
-          <t>зонный шкаф</t>
-        </is>
-      </c>
-      <c r="F34" s="220" t="n">
-        <v>54</v>
-      </c>
-      <c r="G34" s="220" t="n">
-        <v>556</v>
-      </c>
-      <c r="H34" s="220" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" s="220" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="220" t="n">
+      <c r="J35" s="235" t="n">
         <v>96</v>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1" s="63">
-      <c r="C35" s="114" t="inlineStr">
-        <is>
-          <t>Винное</t>
-        </is>
-      </c>
-      <c r="D35" s="114" t="inlineStr">
-        <is>
-          <t>ЦУ</t>
-        </is>
-      </c>
-      <c r="E35" s="114" t="inlineStr">
-        <is>
-          <t>ЦУ (корневая)</t>
-        </is>
-      </c>
-      <c r="F35" s="221" t="n">
-        <v>33</v>
-      </c>
-      <c r="G35" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="221" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="221" t="n">
-        <v>144</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="63">
       <c r="C36" s="112" t="inlineStr"/>
       <c r="D36" s="112" t="inlineStr">
         <is>
-          <t>З-1</t>
+          <t>З-2</t>
         </is>
       </c>
       <c r="E36" s="112" t="inlineStr">
@@ -9682,27 +9724,27 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F36" s="220" t="n">
-        <v>56</v>
-      </c>
-      <c r="G36" s="220" t="n">
-        <v>587</v>
-      </c>
-      <c r="H36" s="220" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="220" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="220" t="n">
-        <v>96</v>
+      <c r="F36" s="234" t="n">
+        <v>156</v>
+      </c>
+      <c r="G36" s="234" t="n">
+        <v>295</v>
+      </c>
+      <c r="H36" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="234" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="63">
       <c r="C37" s="114" t="inlineStr"/>
       <c r="D37" s="114" t="inlineStr">
         <is>
-          <t>З-2</t>
+          <t>З-3</t>
         </is>
       </c>
       <c r="E37" s="114" t="inlineStr">
@@ -9710,19 +9752,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F37" s="221" t="n">
-        <v>84</v>
-      </c>
-      <c r="G37" s="221" t="n">
-        <v>387</v>
-      </c>
-      <c r="H37" s="221" t="n">
+      <c r="F37" s="235" t="n">
+        <v>69</v>
+      </c>
+      <c r="G37" s="235" t="n">
+        <v>1394</v>
+      </c>
+      <c r="H37" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="221" t="n">
+      <c r="I37" s="235" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="221" t="n">
+      <c r="J37" s="235" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9730,7 +9772,7 @@
       <c r="C38" s="112" t="inlineStr"/>
       <c r="D38" s="112" t="inlineStr">
         <is>
-          <t>З-3</t>
+          <t>З-4</t>
         </is>
       </c>
       <c r="E38" s="112" t="inlineStr">
@@ -9738,55 +9780,59 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F38" s="220" t="n">
-        <v>48</v>
-      </c>
-      <c r="G38" s="220" t="n">
-        <v>679</v>
-      </c>
-      <c r="H38" s="220" t="n">
+      <c r="F38" s="234" t="n">
+        <v>60</v>
+      </c>
+      <c r="G38" s="234" t="n">
+        <v>556</v>
+      </c>
+      <c r="H38" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="220" t="n">
+      <c r="I38" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="220" t="n">
+      <c r="J38" s="234" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="63">
-      <c r="C39" s="114" t="inlineStr"/>
+      <c r="C39" s="114" t="inlineStr">
+        <is>
+          <t>Винное</t>
+        </is>
+      </c>
       <c r="D39" s="114" t="inlineStr">
         <is>
-          <t>З-4</t>
+          <t>ЦУ</t>
         </is>
       </c>
       <c r="E39" s="114" t="inlineStr">
         <is>
-          <t>зонный шкаф</t>
-        </is>
-      </c>
-      <c r="F39" s="221" t="n">
-        <v>76</v>
-      </c>
-      <c r="G39" s="221" t="n">
-        <v>1306</v>
-      </c>
-      <c r="H39" s="221" t="n">
-        <v>2</v>
-      </c>
-      <c r="I39" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="221" t="n">
-        <v>96</v>
+          <t>ЦУ (корневая)</t>
+        </is>
+      </c>
+      <c r="F39" s="235" t="n">
+        <v>27</v>
+      </c>
+      <c r="G39" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="235" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="63">
       <c r="C40" s="112" t="inlineStr"/>
       <c r="D40" s="112" t="inlineStr">
         <is>
-          <t>З-5</t>
+          <t>З-1</t>
         </is>
       </c>
       <c r="E40" s="112" t="inlineStr">
@@ -9794,19 +9840,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F40" s="220" t="n">
-        <v>74</v>
-      </c>
-      <c r="G40" s="220" t="n">
-        <v>2129</v>
-      </c>
-      <c r="H40" s="220" t="n">
+      <c r="F40" s="234" t="n">
+        <v>45</v>
+      </c>
+      <c r="G40" s="234" t="n">
+        <v>1298</v>
+      </c>
+      <c r="H40" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="I40" s="220" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="220" t="n">
+      <c r="J40" s="234" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9814,7 +9860,7 @@
       <c r="C41" s="114" t="inlineStr"/>
       <c r="D41" s="114" t="inlineStr">
         <is>
-          <t>З-6</t>
+          <t>З-2</t>
         </is>
       </c>
       <c r="E41" s="114" t="inlineStr">
@@ -9822,19 +9868,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F41" s="221" t="n">
-        <v>92</v>
-      </c>
-      <c r="G41" s="221" t="n">
-        <v>1654</v>
-      </c>
-      <c r="H41" s="221" t="n">
+      <c r="F41" s="235" t="n">
+        <v>107</v>
+      </c>
+      <c r="G41" s="235" t="n">
+        <v>418</v>
+      </c>
+      <c r="H41" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="221" t="n">
+      <c r="I41" s="235" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="221" t="n">
+      <c r="J41" s="235" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9842,7 +9888,7 @@
       <c r="C42" s="112" t="inlineStr"/>
       <c r="D42" s="112" t="inlineStr">
         <is>
-          <t>З-7</t>
+          <t>З-3</t>
         </is>
       </c>
       <c r="E42" s="112" t="inlineStr">
@@ -9850,27 +9896,27 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F42" s="220" t="n">
-        <v>102</v>
-      </c>
-      <c r="G42" s="220" t="n">
-        <v>418</v>
-      </c>
-      <c r="H42" s="220" t="n">
+      <c r="F42" s="234" t="n">
+        <v>53</v>
+      </c>
+      <c r="G42" s="234" t="n">
+        <v>1329</v>
+      </c>
+      <c r="H42" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="I42" s="220" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" s="220" t="n">
-        <v>144</v>
+      <c r="J42" s="234" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="63">
       <c r="C43" s="114" t="inlineStr"/>
       <c r="D43" s="114" t="inlineStr">
         <is>
-          <t>З-8</t>
+          <t>З-4</t>
         </is>
       </c>
       <c r="E43" s="114" t="inlineStr">
@@ -9878,59 +9924,55 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F43" s="221" t="n">
-        <v>57</v>
-      </c>
-      <c r="G43" s="221" t="n">
-        <v>372</v>
-      </c>
-      <c r="H43" s="221" t="n">
+      <c r="F43" s="235" t="n">
+        <v>53</v>
+      </c>
+      <c r="G43" s="235" t="n">
+        <v>937</v>
+      </c>
+      <c r="H43" s="235" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="221" t="n">
+      <c r="I43" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="221" t="n">
+      <c r="J43" s="235" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="63">
-      <c r="C44" s="112" t="inlineStr">
-        <is>
-          <t>Пригородное</t>
-        </is>
-      </c>
+      <c r="C44" s="112" t="inlineStr"/>
       <c r="D44" s="112" t="inlineStr">
         <is>
-          <t>ЦУ</t>
+          <t>З-5</t>
         </is>
       </c>
       <c r="E44" s="112" t="inlineStr">
         <is>
-          <t>ЦУ (корневая)</t>
-        </is>
-      </c>
-      <c r="F44" s="220" t="n">
-        <v>22</v>
-      </c>
-      <c r="G44" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="220" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="220" t="n">
-        <v>144</v>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F44" s="234" t="n">
+        <v>85</v>
+      </c>
+      <c r="G44" s="234" t="n">
+        <v>368</v>
+      </c>
+      <c r="H44" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="234" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="63">
       <c r="C45" s="114" t="inlineStr"/>
       <c r="D45" s="114" t="inlineStr">
         <is>
-          <t>З-1</t>
+          <t>З-6</t>
         </is>
       </c>
       <c r="E45" s="114" t="inlineStr">
@@ -9938,27 +9980,27 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F45" s="221" t="n">
-        <v>93</v>
-      </c>
-      <c r="G45" s="221" t="n">
-        <v>498</v>
-      </c>
-      <c r="H45" s="221" t="n">
+      <c r="F45" s="235" t="n">
+        <v>48</v>
+      </c>
+      <c r="G45" s="235" t="n">
+        <v>1096</v>
+      </c>
+      <c r="H45" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I45" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="221" t="n">
-        <v>144</v>
+      <c r="J45" s="235" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="63">
       <c r="C46" s="112" t="inlineStr"/>
       <c r="D46" s="112" t="inlineStr">
         <is>
-          <t>З-2</t>
+          <t>З-7</t>
         </is>
       </c>
       <c r="E46" s="112" t="inlineStr">
@@ -9966,27 +10008,27 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F46" s="220" t="n">
-        <v>102</v>
-      </c>
-      <c r="G46" s="220" t="n">
-        <v>666</v>
-      </c>
-      <c r="H46" s="220" t="n">
+      <c r="F46" s="234" t="n">
+        <v>76</v>
+      </c>
+      <c r="G46" s="234" t="n">
+        <v>302</v>
+      </c>
+      <c r="H46" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="220" t="n">
+      <c r="I46" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="220" t="n">
-        <v>144</v>
+      <c r="J46" s="234" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="63">
       <c r="C47" s="114" t="inlineStr"/>
       <c r="D47" s="114" t="inlineStr">
         <is>
-          <t>З-3</t>
+          <t>З-8</t>
         </is>
       </c>
       <c r="E47" s="114" t="inlineStr">
@@ -9994,87 +10036,87 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F47" s="221" t="n">
-        <v>69</v>
-      </c>
-      <c r="G47" s="221" t="n">
-        <v>470</v>
-      </c>
-      <c r="H47" s="221" t="n">
+      <c r="F47" s="235" t="n">
+        <v>78</v>
+      </c>
+      <c r="G47" s="235" t="n">
+        <v>1779</v>
+      </c>
+      <c r="H47" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="221" t="n">
+      <c r="I47" s="235" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="221" t="n">
+      <c r="J47" s="235" t="n">
         <v>96</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1" s="63">
-      <c r="C48" s="112" t="inlineStr">
-        <is>
-          <t>Алтайский</t>
-        </is>
-      </c>
+      <c r="C48" s="112" t="inlineStr"/>
       <c r="D48" s="112" t="inlineStr">
         <is>
+          <t>З-9</t>
+        </is>
+      </c>
+      <c r="E48" s="112" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F48" s="234" t="n">
+        <v>50</v>
+      </c>
+      <c r="G48" s="234" t="n">
+        <v>476</v>
+      </c>
+      <c r="H48" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" s="234" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" s="63">
+      <c r="C49" s="114" t="inlineStr">
+        <is>
+          <t>Пригородное</t>
+        </is>
+      </c>
+      <c r="D49" s="114" t="inlineStr">
+        <is>
           <t>ЦУ</t>
         </is>
       </c>
-      <c r="E48" s="112" t="inlineStr">
+      <c r="E49" s="114" t="inlineStr">
         <is>
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F48" s="220" t="n">
-        <v>66</v>
-      </c>
-      <c r="G48" s="220" t="n">
+      <c r="F49" s="235" t="n">
+        <v>70</v>
+      </c>
+      <c r="G49" s="235" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="220" t="n">
+      <c r="H49" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="I48" s="220" t="n">
+      <c r="I49" s="235" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="220" t="n">
+      <c r="J49" s="235" t="n">
         <v>144</v>
-      </c>
-    </row>
-    <row r="49" ht="18" customHeight="1" s="63">
-      <c r="C49" s="114" t="inlineStr"/>
-      <c r="D49" s="114" t="inlineStr">
-        <is>
-          <t>З-1</t>
-        </is>
-      </c>
-      <c r="E49" s="114" t="inlineStr">
-        <is>
-          <t>зонный шкаф</t>
-        </is>
-      </c>
-      <c r="F49" s="221" t="n">
-        <v>140</v>
-      </c>
-      <c r="G49" s="221" t="n">
-        <v>445</v>
-      </c>
-      <c r="H49" s="221" t="n">
-        <v>3</v>
-      </c>
-      <c r="I49" s="221" t="n">
-        <v>4</v>
-      </c>
-      <c r="J49" s="221" t="n">
-        <v>288</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="63">
       <c r="C50" s="112" t="inlineStr"/>
       <c r="D50" s="112" t="inlineStr">
         <is>
-          <t>З-2</t>
+          <t>З-1</t>
         </is>
       </c>
       <c r="E50" s="112" t="inlineStr">
@@ -10082,19 +10124,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F50" s="220" t="n">
-        <v>59</v>
-      </c>
-      <c r="G50" s="220" t="n">
-        <v>946</v>
-      </c>
-      <c r="H50" s="220" t="n">
+      <c r="F50" s="234" t="n">
+        <v>62</v>
+      </c>
+      <c r="G50" s="234" t="n">
+        <v>666</v>
+      </c>
+      <c r="H50" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="220" t="n">
+      <c r="I50" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="220" t="n">
+      <c r="J50" s="234" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10102,987 +10144,1017 @@
       <c r="C51" s="114" t="inlineStr"/>
       <c r="D51" s="114" t="inlineStr">
         <is>
+          <t>З-2</t>
+        </is>
+      </c>
+      <c r="E51" s="114" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F51" s="235" t="n">
+        <v>93</v>
+      </c>
+      <c r="G51" s="235" t="n">
+        <v>262</v>
+      </c>
+      <c r="H51" s="235" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="235" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" s="235" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1" s="63">
+      <c r="C52" s="112" t="inlineStr"/>
+      <c r="D52" s="112" t="inlineStr">
+        <is>
           <t>З-3</t>
         </is>
       </c>
-      <c r="E51" s="114" t="inlineStr">
+      <c r="E52" s="112" t="inlineStr">
         <is>
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F51" s="221" t="n">
-        <v>63</v>
-      </c>
-      <c r="G51" s="221" t="n">
-        <v>432</v>
-      </c>
-      <c r="H51" s="221" t="n">
+      <c r="F52" s="234" t="n">
+        <v>61</v>
+      </c>
+      <c r="G52" s="234" t="n">
+        <v>367</v>
+      </c>
+      <c r="H52" s="234" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="221" t="n">
+      <c r="I52" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="J51" s="221" t="n">
+      <c r="J52" s="234" t="n">
         <v>96</v>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1" s="63">
-      <c r="C52" s="108" t="inlineStr">
+    <row r="53" ht="18" customHeight="1" s="63">
+      <c r="C53" s="114" t="inlineStr">
+        <is>
+          <t>Алтайский</t>
+        </is>
+      </c>
+      <c r="D53" s="114" t="inlineStr">
+        <is>
+          <t>ЦУ</t>
+        </is>
+      </c>
+      <c r="E53" s="114" t="inlineStr">
+        <is>
+          <t>ЦУ (корневая)</t>
+        </is>
+      </c>
+      <c r="F53" s="235" t="n">
+        <v>148</v>
+      </c>
+      <c r="G53" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="235" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="235" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" s="63">
+      <c r="C54" s="112" t="inlineStr"/>
+      <c r="D54" s="112" t="inlineStr">
+        <is>
+          <t>З-1</t>
+        </is>
+      </c>
+      <c r="E54" s="112" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F54" s="234" t="n">
+        <v>90</v>
+      </c>
+      <c r="G54" s="234" t="n">
+        <v>336</v>
+      </c>
+      <c r="H54" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="234" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1" s="63">
+      <c r="C55" s="114" t="inlineStr"/>
+      <c r="D55" s="114" t="inlineStr">
+        <is>
+          <t>З-2</t>
+        </is>
+      </c>
+      <c r="E55" s="114" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F55" s="235" t="n">
+        <v>90</v>
+      </c>
+      <c r="G55" s="235" t="n">
+        <v>358</v>
+      </c>
+      <c r="H55" s="235" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="235" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="235" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" s="63">
+      <c r="C56" s="108" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D52" s="108" t="inlineStr">
-        <is>
-          <t>34 ОРШ</t>
-        </is>
-      </c>
-      <c r="E52" s="116" t="n"/>
-      <c r="F52" s="117">
-        <f>SUM(F18:F51)</f>
-        <v/>
-      </c>
-      <c r="G52" s="117" t="n"/>
-      <c r="H52" s="117">
-        <f>SUM(H18:H51)</f>
-        <v/>
-      </c>
-      <c r="I52" s="117">
-        <f>SUM(I18:I51)</f>
-        <v/>
-      </c>
-      <c r="J52" s="117">
-        <f>SUM(J18:J51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="14" customHeight="1" s="63">
-      <c r="B53" s="107" t="inlineStr">
+      <c r="D56" s="108" t="inlineStr">
+        <is>
+          <t>38 ОРШ</t>
+        </is>
+      </c>
+      <c r="E56" s="116" t="n"/>
+      <c r="F56" s="117">
+        <f>SUM(F18:F55)</f>
+        <v/>
+      </c>
+      <c r="G56" s="117" t="n"/>
+      <c r="H56" s="117">
+        <f>SUM(H18:H55)</f>
+        <v/>
+      </c>
+      <c r="I56" s="117">
+        <f>SUM(I18:I55)</f>
+        <v/>
+      </c>
+      <c r="J56" s="117">
+        <f>SUM(J18:J55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1" s="63">
+      <c r="B57" s="107" t="inlineStr">
         <is>
           <t>Удалённость от ЦУ — по кратчайшей трассе дорожного графа в границе НП (Дейкстра). Зонный шкаф стоит в центре сектора — медиане дерева зоны (средний сдвиг от узла вреза ~300 м); врез — точка отделения зоны от дерева сети. Дропы абонентов не меняются.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="24" customHeight="1" s="63">
-      <c r="B55" s="108" t="n"/>
-      <c r="C55" s="108" t="inlineStr">
+    <row r="59" ht="24" customHeight="1" s="63">
+      <c r="B59" s="108" t="n"/>
+      <c r="C59" s="108" t="inlineStr">
         <is>
           <t>В. Параметрический sweep порога окупаемости S_MIN</t>
         </is>
       </c>
-      <c r="D55" s="108" t="n"/>
-      <c r="E55" s="108" t="n"/>
-      <c r="F55" s="108" t="n"/>
-      <c r="G55" s="108" t="n"/>
-      <c r="H55" s="108" t="n"/>
-      <c r="I55" s="108" t="n"/>
-      <c r="J55" s="108" t="n"/>
-      <c r="K55" s="108" t="n"/>
-      <c r="L55" s="108" t="n"/>
-      <c r="M55" s="108" t="n"/>
-      <c r="N55" s="108" t="n"/>
-    </row>
-    <row r="56" ht="28" customHeight="1" s="63">
-      <c r="C56" s="111" t="inlineStr">
+      <c r="D59" s="108" t="n"/>
+      <c r="E59" s="108" t="n"/>
+      <c r="F59" s="108" t="n"/>
+      <c r="G59" s="108" t="n"/>
+      <c r="H59" s="108" t="n"/>
+      <c r="I59" s="108" t="n"/>
+      <c r="J59" s="108" t="n"/>
+      <c r="K59" s="108" t="n"/>
+      <c r="L59" s="108" t="n"/>
+      <c r="M59" s="108" t="n"/>
+      <c r="N59" s="108" t="n"/>
+    </row>
+    <row r="60" ht="28" customHeight="1" s="63">
+      <c r="C60" s="111" t="inlineStr">
         <is>
           <t>S_MIN, вол-км</t>
         </is>
       </c>
-      <c r="D56" s="111" t="inlineStr">
+      <c r="D60" s="111" t="inlineStr">
         <is>
           <t>ОРШ, шт</t>
         </is>
       </c>
-      <c r="E56" s="111" t="inlineStr">
+      <c r="E60" s="111" t="inlineStr">
         <is>
           <t>Волокно-км</t>
         </is>
       </c>
-      <c r="F56" s="111" t="inlineStr">
+      <c r="F60" s="111" t="inlineStr">
         <is>
           <t>Δ к A (4375,1)</t>
         </is>
       </c>
-      <c r="G56" s="111" t="inlineStr">
+      <c r="G60" s="111" t="inlineStr">
         <is>
           <t>Кабель, км</t>
         </is>
       </c>
-      <c r="H56" s="111" t="inlineStr">
+      <c r="H60" s="111" t="inlineStr">
         <is>
           <t>Дропы, км</t>
         </is>
       </c>
-      <c r="I56" s="111" t="inlineStr">
+      <c r="I60" s="111" t="inlineStr">
         <is>
           <t>ВСЕГО, км</t>
         </is>
       </c>
-      <c r="J56" s="111" t="inlineStr">
+      <c r="J60" s="111" t="inlineStr">
         <is>
           <t>Сплиттеры</t>
         </is>
       </c>
-      <c r="K56" s="111" t="inlineStr">
+      <c r="K60" s="111" t="inlineStr">
         <is>
           <t>Сварки</t>
         </is>
       </c>
-      <c r="L56" s="111" t="inlineStr">
+      <c r="L60" s="111" t="inlineStr">
         <is>
           <t>Порты ОРШ</t>
         </is>
       </c>
-      <c r="M56" s="111" t="inlineStr">
+      <c r="M60" s="111" t="inlineStr">
         <is>
           <t>Ср. маршрут волокна, м</t>
         </is>
       </c>
-      <c r="N56" s="111" t="inlineStr">
+      <c r="N60" s="111" t="inlineStr">
         <is>
           <t>Макс. ёмкость, F</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1" s="63">
-      <c r="C57" s="220" t="n">
+    <row r="61" ht="18" customHeight="1" s="63">
+      <c r="C61" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="220" t="n">
+      <c r="D61" s="234" t="n">
         <v>48</v>
       </c>
-      <c r="E57" s="222" t="n">
+      <c r="E61" s="236" t="n">
         <v>1460.2</v>
       </c>
-      <c r="F57" s="223">
-        <f>E57/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G57" s="222" t="n">
+      <c r="F61" s="237">
+        <f>E61/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G61" s="236" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H57" s="222" t="n">
+      <c r="H61" s="236" t="n">
         <v>95.8</v>
       </c>
-      <c r="I57" s="222">
-        <f>G57+H57</f>
-        <v/>
-      </c>
-      <c r="J57" s="220" t="n">
+      <c r="I61" s="236">
+        <f>G61+H61</f>
+        <v/>
+      </c>
+      <c r="J61" s="234" t="n">
         <v>56</v>
       </c>
-      <c r="K57" s="220" t="n">
+      <c r="K61" s="234" t="n">
         <v>5261</v>
       </c>
-      <c r="L57" s="220" t="n">
+      <c r="L61" s="234" t="n">
         <v>4368</v>
       </c>
-      <c r="M57" s="220" t="n">
+      <c r="M61" s="234" t="n">
         <v>349</v>
       </c>
-      <c r="N57" s="220" t="n">
+      <c r="N61" s="234" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1" s="63">
-      <c r="C58" s="221" t="n">
+    <row r="62" ht="18" customHeight="1" s="63">
+      <c r="C62" s="235" t="n">
         <v>5</v>
       </c>
-      <c r="D58" s="221" t="n">
+      <c r="D62" s="235" t="n">
         <v>43</v>
       </c>
-      <c r="E58" s="224" t="n">
+      <c r="E62" s="238" t="n">
         <v>1476.5</v>
       </c>
-      <c r="F58" s="225">
-        <f>E58/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G58" s="224" t="n">
+      <c r="F62" s="239">
+        <f>E62/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G62" s="238" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H58" s="224" t="n">
+      <c r="H62" s="238" t="n">
         <v>95.8</v>
       </c>
-      <c r="I58" s="224">
-        <f>G58+H58</f>
-        <v/>
-      </c>
-      <c r="J58" s="221" t="n">
+      <c r="I62" s="238">
+        <f>G62+H62</f>
+        <v/>
+      </c>
+      <c r="J62" s="235" t="n">
         <v>54</v>
       </c>
-      <c r="K58" s="221" t="n">
+      <c r="K62" s="235" t="n">
         <v>5255</v>
       </c>
-      <c r="L58" s="221" t="n">
+      <c r="L62" s="235" t="n">
         <v>4176</v>
       </c>
-      <c r="M58" s="221" t="n">
+      <c r="M62" s="235" t="n">
         <v>358</v>
       </c>
-      <c r="N58" s="221" t="n">
+      <c r="N62" s="235" t="n">
         <v>108</v>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1" s="63">
-      <c r="C59" s="220" t="n">
+    <row r="63" ht="18" customHeight="1" s="63">
+      <c r="C63" s="234" t="n">
         <v>8</v>
       </c>
-      <c r="D59" s="220" t="n">
+      <c r="D63" s="234" t="n">
         <v>39</v>
       </c>
-      <c r="E59" s="222" t="n">
+      <c r="E63" s="236" t="n">
         <v>1500.8</v>
       </c>
-      <c r="F59" s="223">
-        <f>E59/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G59" s="222" t="n">
+      <c r="F63" s="237">
+        <f>E63/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G63" s="236" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H59" s="222" t="n">
+      <c r="H63" s="236" t="n">
         <v>95.8</v>
       </c>
-      <c r="I59" s="222">
-        <f>G59+H59</f>
-        <v/>
-      </c>
-      <c r="J59" s="220" t="n">
+      <c r="I63" s="236">
+        <f>G63+H63</f>
+        <v/>
+      </c>
+      <c r="J63" s="234" t="n">
         <v>53</v>
       </c>
-      <c r="K59" s="220" t="n">
+      <c r="K63" s="234" t="n">
         <v>5253</v>
       </c>
-      <c r="L59" s="220" t="n">
+      <c r="L63" s="234" t="n">
         <v>3984</v>
       </c>
-      <c r="M59" s="220" t="n">
+      <c r="M63" s="234" t="n">
         <v>368</v>
       </c>
-      <c r="N59" s="220" t="n">
+      <c r="N63" s="234" t="n">
         <v>119</v>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1" s="63">
-      <c r="C60" s="221" t="n">
+    <row r="64" ht="18" customHeight="1" s="63">
+      <c r="C64" s="235" t="n">
         <v>10</v>
       </c>
-      <c r="D60" s="221" t="n">
+      <c r="D64" s="235" t="n">
         <v>36</v>
       </c>
-      <c r="E60" s="224" t="n">
+      <c r="E64" s="238" t="n">
         <v>1532.5</v>
       </c>
-      <c r="F60" s="225">
-        <f>E60/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G60" s="224" t="n">
+      <c r="F64" s="239">
+        <f>E64/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G64" s="238" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H60" s="224" t="n">
+      <c r="H64" s="238" t="n">
         <v>95.8</v>
       </c>
-      <c r="I60" s="224">
-        <f>G60+H60</f>
-        <v/>
-      </c>
-      <c r="J60" s="221" t="n">
+      <c r="I64" s="238">
+        <f>G64+H64</f>
+        <v/>
+      </c>
+      <c r="J64" s="235" t="n">
         <v>53</v>
       </c>
-      <c r="K60" s="221" t="n">
+      <c r="K64" s="235" t="n">
         <v>5253</v>
       </c>
-      <c r="L60" s="221" t="n">
+      <c r="L64" s="235" t="n">
         <v>3888</v>
       </c>
-      <c r="M60" s="221" t="n">
+      <c r="M64" s="235" t="n">
         <v>379</v>
       </c>
-      <c r="N60" s="221" t="n">
+      <c r="N64" s="235" t="n">
         <v>119</v>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1" s="63">
-      <c r="C61" s="226" t="n">
+    <row r="65" ht="18" customHeight="1" s="63">
+      <c r="C65" s="240" t="n">
         <v>15</v>
       </c>
-      <c r="D61" s="226" t="n">
+      <c r="D65" s="240" t="n">
         <v>34</v>
       </c>
-      <c r="E61" s="227" t="n">
+      <c r="E65" s="241" t="n">
         <v>1562.5</v>
       </c>
-      <c r="F61" s="228">
-        <f>E61/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G61" s="227" t="n">
+      <c r="F65" s="242">
+        <f>E65/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G65" s="241" t="n">
         <v>80.5</v>
       </c>
-      <c r="H61" s="227" t="n">
+      <c r="H65" s="241" t="n">
         <v>95.8</v>
       </c>
-      <c r="I61" s="227">
-        <f>G61+H61</f>
-        <v/>
-      </c>
-      <c r="J61" s="226" t="n">
+      <c r="I65" s="241">
+        <f>G65+H65</f>
+        <v/>
+      </c>
+      <c r="J65" s="240" t="n">
         <v>52</v>
       </c>
-      <c r="K61" s="226" t="n">
+      <c r="K65" s="240" t="n">
         <v>5251</v>
       </c>
-      <c r="L61" s="226" t="n">
+      <c r="L65" s="240" t="n">
         <v>3696</v>
       </c>
-      <c r="M61" s="226" t="n">
+      <c r="M65" s="240" t="n">
         <v>388</v>
       </c>
-      <c r="N61" s="226" t="n">
+      <c r="N65" s="240" t="n">
         <v>128</v>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1" s="63">
-      <c r="C62" s="221" t="n">
+    <row r="66" ht="18" customHeight="1" s="63">
+      <c r="C66" s="235" t="n">
         <v>20</v>
       </c>
-      <c r="D62" s="221" t="n">
+      <c r="D66" s="235" t="n">
         <v>32</v>
       </c>
-      <c r="E62" s="224" t="n">
+      <c r="E66" s="238" t="n">
         <v>1603.9</v>
       </c>
-      <c r="F62" s="225">
-        <f>E62/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G62" s="224" t="n">
+      <c r="F66" s="239">
+        <f>E66/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G66" s="238" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="H62" s="224" t="n">
+      <c r="H66" s="238" t="n">
         <v>95.8</v>
       </c>
-      <c r="I62" s="224">
-        <f>G62+H62</f>
-        <v/>
-      </c>
-      <c r="J62" s="221" t="n">
+      <c r="I66" s="238">
+        <f>G66+H66</f>
+        <v/>
+      </c>
+      <c r="J66" s="235" t="n">
         <v>51</v>
       </c>
-      <c r="K62" s="221" t="n">
+      <c r="K66" s="235" t="n">
         <v>5249</v>
       </c>
-      <c r="L62" s="221" t="n">
+      <c r="L66" s="235" t="n">
         <v>3696</v>
       </c>
-      <c r="M62" s="221" t="n">
+      <c r="M66" s="235" t="n">
         <v>403</v>
       </c>
-      <c r="N62" s="221" t="n">
+      <c r="N66" s="235" t="n">
         <v>148</v>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1" s="63">
-      <c r="C63" s="220" t="n">
+    <row r="67" ht="18" customHeight="1" s="63">
+      <c r="C67" s="234" t="n">
         <v>25</v>
       </c>
-      <c r="D63" s="220" t="n">
+      <c r="D67" s="234" t="n">
         <v>29</v>
       </c>
-      <c r="E63" s="222" t="n">
+      <c r="E67" s="236" t="n">
         <v>1674.7</v>
       </c>
-      <c r="F63" s="223">
-        <f>E63/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G63" s="222" t="n">
+      <c r="F67" s="237">
+        <f>E67/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G67" s="236" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H63" s="222" t="n">
+      <c r="H67" s="236" t="n">
         <v>95.8</v>
       </c>
-      <c r="I63" s="222">
-        <f>G63+H63</f>
-        <v/>
-      </c>
-      <c r="J63" s="220" t="n">
+      <c r="I67" s="236">
+        <f>G67+H67</f>
+        <v/>
+      </c>
+      <c r="J67" s="234" t="n">
         <v>50</v>
       </c>
-      <c r="K63" s="220" t="n">
+      <c r="K67" s="234" t="n">
         <v>5247</v>
       </c>
-      <c r="L63" s="220" t="n">
+      <c r="L67" s="234" t="n">
         <v>3600</v>
       </c>
-      <c r="M63" s="220" t="n">
+      <c r="M67" s="234" t="n">
         <v>427</v>
       </c>
-      <c r="N63" s="220" t="n">
+      <c r="N67" s="234" t="n">
         <v>148</v>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1" s="63">
-      <c r="C64" s="221" t="n">
+    <row r="68" ht="18" customHeight="1" s="63">
+      <c r="C68" s="235" t="n">
         <v>30</v>
       </c>
-      <c r="D64" s="221" t="n">
+      <c r="D68" s="235" t="n">
         <v>27</v>
       </c>
-      <c r="E64" s="224" t="n">
+      <c r="E68" s="238" t="n">
         <v>1736.2</v>
       </c>
-      <c r="F64" s="225">
-        <f>E64/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G64" s="224" t="n">
+      <c r="F68" s="239">
+        <f>E68/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G68" s="238" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="H64" s="224" t="n">
+      <c r="H68" s="238" t="n">
         <v>95.8</v>
       </c>
-      <c r="I64" s="224">
-        <f>G64+H64</f>
-        <v/>
-      </c>
-      <c r="J64" s="221" t="n">
+      <c r="I68" s="238">
+        <f>G68+H68</f>
+        <v/>
+      </c>
+      <c r="J68" s="235" t="n">
         <v>48</v>
       </c>
-      <c r="K64" s="221" t="n">
+      <c r="K68" s="235" t="n">
         <v>5243</v>
       </c>
-      <c r="L64" s="221" t="n">
+      <c r="L68" s="235" t="n">
         <v>3504</v>
       </c>
-      <c r="M64" s="221" t="n">
+      <c r="M68" s="235" t="n">
         <v>448</v>
       </c>
-      <c r="N64" s="221" t="n">
+      <c r="N68" s="235" t="n">
         <v>154</v>
       </c>
     </row>
-    <row r="65" ht="18" customHeight="1" s="63">
-      <c r="C65" s="220" t="n">
+    <row r="69" ht="18" customHeight="1" s="63">
+      <c r="C69" s="234" t="n">
         <v>40</v>
       </c>
-      <c r="D65" s="220" t="n">
+      <c r="D69" s="234" t="n">
         <v>24</v>
       </c>
-      <c r="E65" s="222" t="n">
+      <c r="E69" s="236" t="n">
         <v>1852</v>
       </c>
-      <c r="F65" s="223">
-        <f>E65/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G65" s="222" t="n">
+      <c r="F69" s="237">
+        <f>E69/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G69" s="236" t="n">
         <v>82.3</v>
       </c>
-      <c r="H65" s="222" t="n">
+      <c r="H69" s="236" t="n">
         <v>95.8</v>
       </c>
-      <c r="I65" s="222">
-        <f>G65+H65</f>
-        <v/>
-      </c>
-      <c r="J65" s="220" t="n">
+      <c r="I69" s="236">
+        <f>G69+H69</f>
+        <v/>
+      </c>
+      <c r="J69" s="234" t="n">
         <v>47</v>
       </c>
-      <c r="K65" s="220" t="n">
+      <c r="K69" s="234" t="n">
         <v>5241</v>
       </c>
-      <c r="L65" s="220" t="n">
+      <c r="L69" s="234" t="n">
         <v>3552</v>
       </c>
-      <c r="M65" s="220" t="n">
+      <c r="M69" s="234" t="n">
         <v>488</v>
       </c>
-      <c r="N65" s="220" t="n">
+      <c r="N69" s="234" t="n">
         <v>164</v>
       </c>
     </row>
-    <row r="66" ht="18" customHeight="1" s="63">
-      <c r="C66" s="221" t="n">
+    <row r="70" ht="18" customHeight="1" s="63">
+      <c r="C70" s="235" t="n">
         <v>50</v>
       </c>
-      <c r="D66" s="221" t="n">
+      <c r="D70" s="235" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="224" t="n">
+      <c r="E70" s="238" t="n">
         <v>2041.2</v>
       </c>
-      <c r="F66" s="225">
-        <f>E66/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G66" s="224" t="n">
+      <c r="F70" s="239">
+        <f>E70/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G70" s="238" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="H66" s="224" t="n">
+      <c r="H70" s="238" t="n">
         <v>95.8</v>
       </c>
-      <c r="I66" s="224">
-        <f>G66+H66</f>
-        <v/>
-      </c>
-      <c r="J66" s="221" t="n">
+      <c r="I70" s="238">
+        <f>G70+H70</f>
+        <v/>
+      </c>
+      <c r="J70" s="235" t="n">
         <v>46</v>
       </c>
-      <c r="K66" s="221" t="n">
+      <c r="K70" s="235" t="n">
         <v>5238</v>
       </c>
-      <c r="L66" s="221" t="n">
+      <c r="L70" s="235" t="n">
         <v>3696</v>
       </c>
-      <c r="M66" s="221" t="n">
+      <c r="M70" s="235" t="n">
         <v>554</v>
       </c>
-      <c r="N66" s="221" t="n">
+      <c r="N70" s="235" t="n">
         <v>164</v>
       </c>
     </row>
-    <row r="67" ht="18" customHeight="1" s="63">
-      <c r="C67" s="220" t="n">
+    <row r="71" ht="18" customHeight="1" s="63">
+      <c r="C71" s="234" t="n">
         <v>60</v>
       </c>
-      <c r="D67" s="220" t="n">
+      <c r="D71" s="234" t="n">
         <v>18</v>
       </c>
-      <c r="E67" s="222" t="n">
+      <c r="E71" s="236" t="n">
         <v>2153.9</v>
       </c>
-      <c r="F67" s="223">
-        <f>E67/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G67" s="222" t="n">
+      <c r="F71" s="237">
+        <f>E71/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G71" s="236" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="H67" s="222" t="n">
+      <c r="H71" s="236" t="n">
         <v>95.8</v>
       </c>
-      <c r="I67" s="222">
-        <f>G67+H67</f>
-        <v/>
-      </c>
-      <c r="J67" s="220" t="n">
+      <c r="I71" s="236">
+        <f>G71+H71</f>
+        <v/>
+      </c>
+      <c r="J71" s="234" t="n">
         <v>45</v>
       </c>
-      <c r="K67" s="220" t="n">
+      <c r="K71" s="234" t="n">
         <v>5236</v>
       </c>
-      <c r="L67" s="220" t="n">
+      <c r="L71" s="234" t="n">
         <v>3744</v>
       </c>
-      <c r="M67" s="220" t="n">
+      <c r="M71" s="234" t="n">
         <v>592</v>
       </c>
-      <c r="N67" s="220" t="n">
+      <c r="N71" s="234" t="n">
         <v>245</v>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1" s="63">
-      <c r="C68" s="221" t="n">
+    <row r="72" ht="18" customHeight="1" s="63">
+      <c r="C72" s="235" t="n">
         <v>80</v>
       </c>
-      <c r="D68" s="221" t="n">
+      <c r="D72" s="235" t="n">
         <v>17</v>
       </c>
-      <c r="E68" s="224" t="n">
+      <c r="E72" s="238" t="n">
         <v>2215.1</v>
       </c>
-      <c r="F68" s="225">
-        <f>E68/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G68" s="224" t="n">
+      <c r="F72" s="239">
+        <f>E72/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G72" s="238" t="n">
         <v>84.7</v>
       </c>
-      <c r="H68" s="224" t="n">
+      <c r="H72" s="238" t="n">
         <v>95.8</v>
       </c>
-      <c r="I68" s="224">
-        <f>G68+H68</f>
-        <v/>
-      </c>
-      <c r="J68" s="221" t="n">
+      <c r="I72" s="238">
+        <f>G72+H72</f>
+        <v/>
+      </c>
+      <c r="J72" s="235" t="n">
         <v>44</v>
       </c>
-      <c r="K68" s="221" t="n">
+      <c r="K72" s="235" t="n">
         <v>5234</v>
       </c>
-      <c r="L68" s="221" t="n">
+      <c r="L72" s="235" t="n">
         <v>3600</v>
       </c>
-      <c r="M68" s="221" t="n">
+      <c r="M72" s="235" t="n">
         <v>614</v>
       </c>
-      <c r="N68" s="221" t="n">
+      <c r="N72" s="235" t="n">
         <v>245</v>
       </c>
     </row>
-    <row r="69" ht="14" customHeight="1" s="63">
-      <c r="B69" s="107" t="inlineStr">
+    <row r="73" ht="14" customHeight="1" s="63">
+      <c r="B73" s="107" t="inlineStr">
         <is>
           <t>S_MIN — порог окупаемости: врез зонного ОРШ принимается при экономии не менее S_MIN волокно-км (шкаф с монтажом ~ 1,5 у.е. ~ 12-15 вол-км на тонком кабеле). Жёлтая строка — рекомендованная конфигурация (S_MIN = 15). Sweep рассчитан на стадии v1 (ОРШ во врезах, фидеры по дереву) и обосновывает выбор S_MIN; выпущенная книга v3 (ОРШ в центрах секторов + кратчайшие фидеры в границе НП): 1 386,0 волокно-км при 34 ОРШ.</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="28" customHeight="1" s="63">
-      <c r="B71" s="111" t="inlineStr">
+    <row r="75" ht="28" customHeight="1" s="63">
+      <c r="B75" s="111" t="inlineStr">
         <is>
           <t>ОРШ, шт</t>
         </is>
       </c>
-      <c r="C71" s="111" t="inlineStr">
+      <c r="C75" s="111" t="inlineStr">
         <is>
           <t>Волокно-км</t>
         </is>
       </c>
-      <c r="D71" s="111" t="inlineStr">
+      <c r="D75" s="111" t="inlineStr">
         <is>
           <t>Индекс стоимости (с шкафами), у.е.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="220" t="n">
+    <row r="76">
+      <c r="B76" s="234" t="n">
         <v>17</v>
       </c>
-      <c r="C72" s="222" t="n">
+      <c r="C76" s="236" t="n">
         <v>2215.1</v>
       </c>
-      <c r="D72" s="222" t="n">
+      <c r="D76" s="236" t="n">
         <v>527.3</v>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="221" t="n">
+    <row r="77">
+      <c r="B77" s="235" t="n">
         <v>18</v>
       </c>
-      <c r="C73" s="224" t="n">
+      <c r="C77" s="238" t="n">
         <v>2153.9</v>
       </c>
-      <c r="D73" s="224" t="n">
+      <c r="D77" s="238" t="n">
         <v>529.8</v>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="220" t="n">
+    <row r="78">
+      <c r="B78" s="234" t="n">
         <v>20</v>
       </c>
-      <c r="C74" s="222" t="n">
+      <c r="C78" s="236" t="n">
         <v>2041.2</v>
       </c>
-      <c r="D74" s="222" t="n">
+      <c r="D78" s="236" t="n">
         <v>527.5</v>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="221" t="n">
+    <row r="79">
+      <c r="B79" s="235" t="n">
         <v>24</v>
       </c>
-      <c r="C75" s="224" t="n">
+      <c r="C79" s="238" t="n">
         <v>1852</v>
       </c>
-      <c r="D75" s="224" t="n">
+      <c r="D79" s="238" t="n">
         <v>524.2</v>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="220" t="n">
+    <row r="80">
+      <c r="B80" s="234" t="n">
         <v>27</v>
       </c>
-      <c r="C76" s="222" t="n">
+      <c r="C80" s="236" t="n">
         <v>1736.2</v>
       </c>
-      <c r="D76" s="222" t="n">
+      <c r="D80" s="236" t="n">
         <v>524.4</v>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="221" t="n">
+    <row r="81">
+      <c r="B81" s="235" t="n">
         <v>29</v>
       </c>
-      <c r="C77" s="224" t="n">
+      <c r="C81" s="238" t="n">
         <v>1674.7</v>
       </c>
-      <c r="D77" s="224" t="n">
+      <c r="D81" s="238" t="n">
         <v>527.9</v>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="220" t="n">
+    <row r="82">
+      <c r="B82" s="234" t="n">
         <v>32</v>
       </c>
-      <c r="C78" s="222" t="n">
+      <c r="C82" s="236" t="n">
         <v>1603.9</v>
       </c>
-      <c r="D78" s="222" t="n">
+      <c r="D82" s="236" t="n">
         <v>531.7</v>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="221" t="n">
+    <row r="83">
+      <c r="B83" s="235" t="n">
         <v>34</v>
       </c>
-      <c r="C79" s="224" t="n">
+      <c r="C83" s="238" t="n">
         <v>1562.5</v>
       </c>
-      <c r="D79" s="224" t="n">
+      <c r="D83" s="238" t="n">
         <v>533.2</v>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="220" t="n">
+    <row r="84">
+      <c r="B84" s="234" t="n">
         <v>36</v>
       </c>
-      <c r="C80" s="222" t="n">
+      <c r="C84" s="236" t="n">
         <v>1532.5</v>
       </c>
-      <c r="D80" s="222" t="n">
+      <c r="D84" s="236" t="n">
         <v>539.3</v>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="221" t="n">
+    <row r="85">
+      <c r="B85" s="235" t="n">
         <v>39</v>
       </c>
-      <c r="C81" s="224" t="n">
+      <c r="C85" s="238" t="n">
         <v>1500.8</v>
       </c>
-      <c r="D81" s="224" t="n">
+      <c r="D85" s="238" t="n">
         <v>544.4</v>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="220" t="n">
+    <row r="86">
+      <c r="B86" s="234" t="n">
         <v>43</v>
       </c>
-      <c r="C82" s="222" t="n">
+      <c r="C86" s="236" t="n">
         <v>1476.5</v>
       </c>
-      <c r="D82" s="222" t="n">
+      <c r="D86" s="236" t="n">
         <v>553</v>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="221" t="n">
+    <row r="87">
+      <c r="B87" s="235" t="n">
         <v>48</v>
       </c>
-      <c r="C83" s="224" t="n">
+      <c r="C87" s="238" t="n">
         <v>1460.2</v>
       </c>
-      <c r="D83" s="224" t="n">
+      <c r="D87" s="238" t="n">
         <v>563.9</v>
       </c>
     </row>
-    <row r="85" ht="24" customHeight="1" s="63">
-      <c r="B85" s="108" t="n"/>
-      <c r="C85" s="108" t="inlineStr">
+    <row r="89" ht="24" customHeight="1" s="63">
+      <c r="B89" s="108" t="n"/>
+      <c r="C89" s="108" t="inlineStr">
         <is>
           <t>Г. Сравнение четырёх схем — A / B / C / D</t>
         </is>
       </c>
-      <c r="D85" s="108" t="n"/>
-      <c r="E85" s="108" t="n"/>
-      <c r="F85" s="108" t="n"/>
-      <c r="G85" s="108" t="n"/>
-      <c r="H85" s="108" t="n"/>
-      <c r="I85" s="108" t="n"/>
-      <c r="J85" s="108" t="n"/>
-      <c r="K85" s="108" t="n"/>
-      <c r="L85" s="108" t="n"/>
-      <c r="M85" s="108" t="n"/>
-      <c r="N85" s="108" t="n"/>
-    </row>
-    <row r="86" ht="28" customHeight="1" s="63">
-      <c r="C86" s="111" t="inlineStr">
+      <c r="D89" s="108" t="n"/>
+      <c r="E89" s="108" t="n"/>
+      <c r="F89" s="108" t="n"/>
+      <c r="G89" s="108" t="n"/>
+      <c r="H89" s="108" t="n"/>
+      <c r="I89" s="108" t="n"/>
+      <c r="J89" s="108" t="n"/>
+      <c r="K89" s="108" t="n"/>
+      <c r="L89" s="108" t="n"/>
+      <c r="M89" s="108" t="n"/>
+      <c r="N89" s="108" t="n"/>
+    </row>
+    <row r="90" ht="28" customHeight="1" s="63">
+      <c r="C90" s="111" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="D86" s="111" t="inlineStr">
+      <c r="D90" s="111" t="inlineStr">
         <is>
           <t>A: централизо-ванная 1:64</t>
         </is>
       </c>
-      <c r="E86" s="111" t="inlineStr">
+      <c r="E90" s="111" t="inlineStr">
         <is>
           <t>B: каскад 1:8+1:8</t>
         </is>
       </c>
-      <c r="F86" s="111" t="inlineStr">
+      <c r="F90" s="111" t="inlineStr">
         <is>
           <t>C: каскад 1:4+1:16</t>
         </is>
       </c>
-      <c r="G86" s="111" t="inlineStr">
+      <c r="G90" s="111" t="inlineStr">
         <is>
           <t>D: зонные ОРШ 1:64</t>
         </is>
       </c>
-      <c r="H86" s="111" t="inlineStr">
+      <c r="H90" s="111" t="inlineStr">
         <is>
           <t>Лучшая</t>
         </is>
-      </c>
-    </row>
-    <row r="87" ht="18" customHeight="1" s="63">
-      <c r="C87" s="112" t="inlineStr">
-        <is>
-          <t>Обслужено ДХ, шт</t>
-        </is>
-      </c>
-      <c r="D87" s="220" t="n">
-        <v>2765</v>
-      </c>
-      <c r="E87" s="220" t="n">
-        <v>2765</v>
-      </c>
-      <c r="F87" s="220" t="n">
-        <v>2765</v>
-      </c>
-      <c r="G87" s="220" t="n">
-        <v>2765</v>
-      </c>
-      <c r="H87" s="229" t="n"/>
-    </row>
-    <row r="88" ht="18" customHeight="1" s="63">
-      <c r="C88" s="114" t="inlineStr">
-        <is>
-          <t>Волокно-км</t>
-        </is>
-      </c>
-      <c r="D88" s="224" t="n">
-        <v>4375.1</v>
-      </c>
-      <c r="E88" s="224" t="n">
-        <v>1256.1</v>
-      </c>
-      <c r="F88" s="224" t="n">
-        <v>889.2</v>
-      </c>
-      <c r="G88" s="224" t="n">
-        <v>1474.4</v>
-      </c>
-      <c r="H88" s="230">
-        <f>CHOOSE(MATCH(MIN(D88:G88),D88:G88,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1" s="63">
-      <c r="C89" s="112" t="inlineStr">
-        <is>
-          <t>Волокно-км на ДХ, км</t>
-        </is>
-      </c>
-      <c r="D89" s="231">
-        <f>D88/2765</f>
-        <v/>
-      </c>
-      <c r="E89" s="231">
-        <f>E88/2765</f>
-        <v/>
-      </c>
-      <c r="F89" s="231">
-        <f>F88/2765</f>
-        <v/>
-      </c>
-      <c r="G89" s="231">
-        <f>G88/2765</f>
-        <v/>
-      </c>
-      <c r="H89" s="229">
-        <f>CHOOSE(MATCH(MIN(D89:G89),D89:G89,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1" s="63">
-      <c r="C90" s="114" t="inlineStr">
-        <is>
-          <t>Магистральный кабель, км</t>
-        </is>
-      </c>
-      <c r="D90" s="224" t="n">
-        <v>109.4</v>
-      </c>
-      <c r="E90" s="224" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="F90" s="224" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="G90" s="224" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="H90" s="230">
-        <f>CHOOSE(MATCH(MIN(D90:G90),D90:G90,0),"A","B","C","D")</f>
-        <v/>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="63">
       <c r="C91" s="112" t="inlineStr">
         <is>
-          <t>в т.ч. 8-волоконный, км</t>
-        </is>
-      </c>
-      <c r="D91" s="222" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="E91" s="222" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F91" s="222" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="G91" s="222" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H91" s="229" t="n"/>
+          <t>Обслужено ДХ, шт</t>
+        </is>
+      </c>
+      <c r="D91" s="234" t="n">
+        <v>2765</v>
+      </c>
+      <c r="E91" s="234" t="n">
+        <v>2765</v>
+      </c>
+      <c r="F91" s="234" t="n">
+        <v>2765</v>
+      </c>
+      <c r="G91" s="234" t="n">
+        <v>2765</v>
+      </c>
+      <c r="H91" s="243" t="n"/>
     </row>
     <row r="92" ht="18" customHeight="1" s="63">
       <c r="C92" s="114" t="inlineStr">
         <is>
-          <t>в т.ч. 96-волоконный, км</t>
-        </is>
-      </c>
-      <c r="D92" s="224" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E92" s="224" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F92" s="224" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G92" s="224" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H92" s="230" t="n"/>
+          <t>Волокно-км</t>
+        </is>
+      </c>
+      <c r="D92" s="238" t="n">
+        <v>4375.1</v>
+      </c>
+      <c r="E92" s="238" t="n">
+        <v>1256.1</v>
+      </c>
+      <c r="F92" s="238" t="n">
+        <v>889.2</v>
+      </c>
+      <c r="G92" s="238" t="n">
+        <v>1474.4</v>
+      </c>
+      <c r="H92" s="244">
+        <f>CHOOSE(MATCH(MIN(D92:G92),D92:G92,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="63">
       <c r="C93" s="112" t="inlineStr">
         <is>
-          <t>Дроп-кабель, км</t>
-        </is>
-      </c>
-      <c r="D93" s="222" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="E93" s="222" t="n">
-        <v>170.7</v>
-      </c>
-      <c r="F93" s="222" t="n">
-        <v>244</v>
-      </c>
-      <c r="G93" s="222" t="n">
-        <v>116.3</v>
-      </c>
-      <c r="H93" s="229">
+          <t>Волокно-км на ДХ, км</t>
+        </is>
+      </c>
+      <c r="D93" s="245">
+        <f>D92/2765</f>
+        <v/>
+      </c>
+      <c r="E93" s="245">
+        <f>E92/2765</f>
+        <v/>
+      </c>
+      <c r="F93" s="245">
+        <f>F92/2765</f>
+        <v/>
+      </c>
+      <c r="G93" s="245">
+        <f>G92/2765</f>
+        <v/>
+      </c>
+      <c r="H93" s="243">
         <f>CHOOSE(MATCH(MIN(D93:G93),D93:G93,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11090,26 +11162,22 @@
     <row r="94" ht="18" customHeight="1" s="63">
       <c r="C94" s="114" t="inlineStr">
         <is>
-          <t>ВСЕГО кабель + дропы, км</t>
-        </is>
-      </c>
-      <c r="D94" s="224">
-        <f>D90+D93</f>
-        <v/>
-      </c>
-      <c r="E94" s="224">
-        <f>E90+E93</f>
-        <v/>
-      </c>
-      <c r="F94" s="224">
-        <f>F90+F93</f>
-        <v/>
-      </c>
-      <c r="G94" s="224">
-        <f>G90+G93</f>
-        <v/>
-      </c>
-      <c r="H94" s="230">
+          <t>Магистральный кабель, км</t>
+        </is>
+      </c>
+      <c r="D94" s="238" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="E94" s="238" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F94" s="238" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G94" s="238" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H94" s="244">
         <f>CHOOSE(MATCH(MIN(D94:G94),D94:G94,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11117,64 +11185,62 @@
     <row r="95" ht="18" customHeight="1" s="63">
       <c r="C95" s="112" t="inlineStr">
         <is>
-          <t>Средний дроп, м</t>
-        </is>
-      </c>
-      <c r="D95" s="220" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E95" s="220" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="F95" s="220" t="n">
-        <v>84</v>
-      </c>
-      <c r="G95" s="220" t="n">
-        <v>40</v>
-      </c>
-      <c r="H95" s="229">
-        <f>CHOOSE(MATCH(MIN(D95:G95),D95:G95,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>в т.ч. 8-волоконный, км</t>
+        </is>
+      </c>
+      <c r="D95" s="236" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E95" s="236" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F95" s="236" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G95" s="236" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H95" s="243" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="63">
       <c r="C96" s="114" t="inlineStr">
         <is>
-          <t>Максимальный дроп, м</t>
-        </is>
-      </c>
-      <c r="D96" s="221" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E96" s="221" t="n">
-        <v>201</v>
-      </c>
-      <c r="F96" s="221" t="n">
-        <v>266</v>
-      </c>
-      <c r="G96" s="221" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H96" s="230">
-        <f>CHOOSE(MATCH(MIN(D96:G96),D96:G96,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>в т.ч. 96-волоконный, км</t>
+        </is>
+      </c>
+      <c r="D96" s="238" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E96" s="238" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F96" s="238" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G96" s="238" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H96" s="244" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1" s="63">
       <c r="C97" s="112" t="inlineStr">
         <is>
-          <t>Ср. маршрут волокна ДХ, м</t>
-        </is>
-      </c>
-      <c r="D97" s="220" t="n">
-        <v>1361</v>
-      </c>
-      <c r="E97" s="220" t="n"/>
-      <c r="F97" s="220" t="n"/>
-      <c r="G97" s="220" t="n">
-        <v>304</v>
-      </c>
-      <c r="H97" s="229">
+          <t>Дроп-кабель, км</t>
+        </is>
+      </c>
+      <c r="D97" s="236" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="E97" s="236" t="n">
+        <v>170.7</v>
+      </c>
+      <c r="F97" s="236" t="n">
+        <v>244</v>
+      </c>
+      <c r="G97" s="236" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="H97" s="243">
         <f>CHOOSE(MATCH(MIN(D97:G97),D97:G97,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11182,22 +11248,26 @@
     <row r="98" ht="18" customHeight="1" s="63">
       <c r="C98" s="114" t="inlineStr">
         <is>
-          <t>ОРШ, шт</t>
-        </is>
-      </c>
-      <c r="D98" s="221" t="n">
-        <v>6</v>
-      </c>
-      <c r="E98" s="221" t="n">
-        <v>6</v>
-      </c>
-      <c r="F98" s="221" t="n">
-        <v>6</v>
-      </c>
-      <c r="G98" s="221" t="n">
-        <v>34</v>
-      </c>
-      <c r="H98" s="230">
+          <t>ВСЕГО кабель + дропы, км</t>
+        </is>
+      </c>
+      <c r="D98" s="238">
+        <f>D94+D97</f>
+        <v/>
+      </c>
+      <c r="E98" s="238">
+        <f>E94+E97</f>
+        <v/>
+      </c>
+      <c r="F98" s="238">
+        <f>F94+F97</f>
+        <v/>
+      </c>
+      <c r="G98" s="238">
+        <f>G94+G97</f>
+        <v/>
+      </c>
+      <c r="H98" s="244">
         <f>CHOOSE(MATCH(MIN(D98:G98),D98:G98,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11205,214 +11275,210 @@
     <row r="99" ht="18" customHeight="1" s="63">
       <c r="C99" s="112" t="inlineStr">
         <is>
-          <t>РОР, шт</t>
-        </is>
-      </c>
-      <c r="D99" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="220" t="n">
-        <v>515</v>
-      </c>
-      <c r="F99" s="220" t="n">
-        <v>323</v>
-      </c>
-      <c r="G99" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="229" t="n"/>
+          <t>Средний дроп, м</t>
+        </is>
+      </c>
+      <c r="D99" s="234" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E99" s="234" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="F99" s="234" t="n">
+        <v>84</v>
+      </c>
+      <c r="G99" s="234" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="H99" s="243">
+        <f>CHOOSE(MATCH(MIN(D99:G99),D99:G99,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="18" customHeight="1" s="63">
       <c r="C100" s="114" t="inlineStr">
         <is>
-          <t>Сплиттеры 1:64, шт</t>
-        </is>
-      </c>
-      <c r="D100" s="221" t="n">
-        <v>39</v>
-      </c>
-      <c r="E100" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="221" t="n">
-        <v>58</v>
-      </c>
-      <c r="H100" s="230" t="n"/>
+          <t>Максимальный дроп, м</t>
+        </is>
+      </c>
+      <c r="D100" s="235" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E100" s="235" t="n">
+        <v>201</v>
+      </c>
+      <c r="F100" s="235" t="n">
+        <v>266</v>
+      </c>
+      <c r="G100" s="235" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H100" s="244">
+        <f>CHOOSE(MATCH(MIN(D100:G100),D100:G100,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="101" ht="18" customHeight="1" s="63">
       <c r="C101" s="112" t="inlineStr">
         <is>
-          <t>Сплиттеры 1:8, шт</t>
-        </is>
-      </c>
-      <c r="D101" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="220" t="n">
-        <v>581</v>
-      </c>
-      <c r="F101" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="229" t="n"/>
+          <t>Ср. маршрут волокна ДХ, м</t>
+        </is>
+      </c>
+      <c r="D101" s="234" t="n">
+        <v>1361</v>
+      </c>
+      <c r="E101" s="234" t="n"/>
+      <c r="F101" s="234" t="n"/>
+      <c r="G101" s="234" t="n">
+        <v>305</v>
+      </c>
+      <c r="H101" s="243">
+        <f>CHOOSE(MATCH(MIN(D101:G101),D101:G101,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="102" ht="18" customHeight="1" s="63">
       <c r="C102" s="114" t="inlineStr">
         <is>
-          <t>Сплиттеры 1:4, шт</t>
-        </is>
-      </c>
-      <c r="D102" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="221" t="n">
-        <v>83</v>
-      </c>
-      <c r="G102" s="221" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="230" t="n"/>
+          <t>ОРШ, шт</t>
+        </is>
+      </c>
+      <c r="D102" s="235" t="n">
+        <v>6</v>
+      </c>
+      <c r="E102" s="235" t="n">
+        <v>6</v>
+      </c>
+      <c r="F102" s="235" t="n">
+        <v>6</v>
+      </c>
+      <c r="G102" s="235" t="n">
+        <v>38</v>
+      </c>
+      <c r="H102" s="244">
+        <f>CHOOSE(MATCH(MIN(D102:G102),D102:G102,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="103" ht="18" customHeight="1" s="63">
       <c r="C103" s="112" t="inlineStr">
         <is>
-          <t>Сплиттеры 1:16, шт</t>
-        </is>
-      </c>
-      <c r="D103" s="220" t="n">
+          <t>РОР, шт</t>
+        </is>
+      </c>
+      <c r="D103" s="234" t="n">
         <v>0</v>
       </c>
-      <c r="E103" s="220" t="n">
+      <c r="E103" s="234" t="n">
+        <v>515</v>
+      </c>
+      <c r="F103" s="234" t="n">
+        <v>323</v>
+      </c>
+      <c r="G103" s="234" t="n">
         <v>0</v>
       </c>
-      <c r="F103" s="220" t="n">
-        <v>323</v>
-      </c>
-      <c r="G103" s="220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="229" t="n"/>
+      <c r="H103" s="243" t="n"/>
     </row>
     <row r="104" ht="18" customHeight="1" s="63">
       <c r="C104" s="114" t="inlineStr">
         <is>
-          <t>Муфты, шт</t>
-        </is>
-      </c>
-      <c r="D104" s="221" t="n">
-        <v>1140</v>
-      </c>
-      <c r="E104" s="221" t="n">
-        <v>115</v>
-      </c>
-      <c r="F104" s="221" t="n">
-        <v>100</v>
-      </c>
-      <c r="G104" s="221" t="n">
-        <v>1112</v>
-      </c>
-      <c r="H104" s="230">
-        <f>CHOOSE(MATCH(MIN(D104:G104),D104:G104,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>Сплиттеры 1:64, шт</t>
+        </is>
+      </c>
+      <c r="D104" s="235" t="n">
+        <v>39</v>
+      </c>
+      <c r="E104" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="235" t="n">
+        <v>59</v>
+      </c>
+      <c r="H104" s="244" t="n"/>
     </row>
     <row r="105" ht="18" customHeight="1" s="63">
       <c r="C105" s="112" t="inlineStr">
         <is>
-          <t>Сварки, шт</t>
-        </is>
-      </c>
-      <c r="D105" s="220" t="n">
-        <v>5136</v>
-      </c>
-      <c r="E105" s="220" t="n">
-        <v>2585</v>
-      </c>
-      <c r="F105" s="220" t="n">
-        <v>1552</v>
-      </c>
-      <c r="G105" s="220" t="n">
-        <v>6213</v>
-      </c>
-      <c r="H105" s="229">
-        <f>CHOOSE(MATCH(MIN(D105:G105),D105:G105,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>Сплиттеры 1:8, шт</t>
+        </is>
+      </c>
+      <c r="D105" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="234" t="n">
+        <v>581</v>
+      </c>
+      <c r="F105" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="243" t="n"/>
     </row>
     <row r="106" ht="18" customHeight="1" s="63">
       <c r="C106" s="114" t="inlineStr">
         <is>
-          <t>Коннекторы FAST, шт</t>
-        </is>
-      </c>
-      <c r="D106" s="221" t="n">
-        <v>2569</v>
-      </c>
-      <c r="E106" s="221" t="n">
-        <v>5136</v>
-      </c>
-      <c r="F106" s="221" t="n">
-        <v>5136</v>
-      </c>
-      <c r="G106" s="221" t="n">
-        <v>3044</v>
-      </c>
-      <c r="H106" s="230">
-        <f>CHOOSE(MATCH(MIN(D106:G106),D106:G106,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>Сплиттеры 1:4, шт</t>
+        </is>
+      </c>
+      <c r="D106" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="235" t="n">
+        <v>83</v>
+      </c>
+      <c r="G106" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="244" t="n"/>
     </row>
     <row r="107" ht="18" customHeight="1" s="63">
       <c r="C107" s="112" t="inlineStr">
         <is>
-          <t>Порты кросса ОРШ, шт</t>
-        </is>
-      </c>
-      <c r="D107" s="220" t="n">
-        <v>3600</v>
-      </c>
-      <c r="E107" s="220" t="n">
-        <v>1008</v>
-      </c>
-      <c r="F107" s="220" t="n">
-        <v>864</v>
-      </c>
-      <c r="G107" s="220" t="n">
-        <v>4560</v>
-      </c>
-      <c r="H107" s="229">
-        <f>CHOOSE(MATCH(MIN(D107:G107),D107:G107,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>Сплиттеры 1:16, шт</t>
+        </is>
+      </c>
+      <c r="D107" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="234" t="n">
+        <v>323</v>
+      </c>
+      <c r="G107" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="243" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="63">
       <c r="C108" s="114" t="inlineStr">
         <is>
-          <t>Порты OLT, шт</t>
-        </is>
-      </c>
-      <c r="D108" s="221" t="n">
-        <v>39</v>
-      </c>
-      <c r="E108" s="221" t="n">
-        <v>66</v>
-      </c>
-      <c r="F108" s="221" t="n">
-        <v>83</v>
-      </c>
-      <c r="G108" s="221" t="n">
-        <v>58</v>
-      </c>
-      <c r="H108" s="230">
+          <t>Муфты, шт</t>
+        </is>
+      </c>
+      <c r="D108" s="235" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E108" s="235" t="n">
+        <v>115</v>
+      </c>
+      <c r="F108" s="235" t="n">
+        <v>100</v>
+      </c>
+      <c r="G108" s="235" t="n">
+        <v>1108</v>
+      </c>
+      <c r="H108" s="244">
         <f>CHOOSE(MATCH(MIN(D108:G108),D108:G108,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11420,22 +11486,22 @@
     <row r="109" ht="18" customHeight="1" s="63">
       <c r="C109" s="112" t="inlineStr">
         <is>
-          <t>Комплекты подвеса, шт</t>
-        </is>
-      </c>
-      <c r="D109" s="220" t="n">
-        <v>2911</v>
-      </c>
-      <c r="E109" s="220" t="n">
-        <v>4180</v>
-      </c>
-      <c r="F109" s="220" t="n">
-        <v>6136</v>
-      </c>
-      <c r="G109" s="220" t="n">
-        <v>2341</v>
-      </c>
-      <c r="H109" s="229">
+          <t>Сварки, шт</t>
+        </is>
+      </c>
+      <c r="D109" s="234" t="n">
+        <v>5136</v>
+      </c>
+      <c r="E109" s="234" t="n">
+        <v>2585</v>
+      </c>
+      <c r="F109" s="234" t="n">
+        <v>1552</v>
+      </c>
+      <c r="G109" s="234" t="n">
+        <v>6216</v>
+      </c>
+      <c r="H109" s="243">
         <f>CHOOSE(MATCH(MIN(D109:G109),D109:G109,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11443,431 +11509,523 @@
     <row r="110" ht="18" customHeight="1" s="63">
       <c r="C110" s="114" t="inlineStr">
         <is>
+          <t>Коннекторы FAST, шт</t>
+        </is>
+      </c>
+      <c r="D110" s="235" t="n">
+        <v>2569</v>
+      </c>
+      <c r="E110" s="235" t="n">
+        <v>5136</v>
+      </c>
+      <c r="F110" s="235" t="n">
+        <v>5136</v>
+      </c>
+      <c r="G110" s="235" t="n">
+        <v>3044</v>
+      </c>
+      <c r="H110" s="244">
+        <f>CHOOSE(MATCH(MIN(D110:G110),D110:G110,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1" s="63">
+      <c r="C111" s="112" t="inlineStr">
+        <is>
+          <t>Порты кросса ОРШ, шт</t>
+        </is>
+      </c>
+      <c r="D111" s="234" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E111" s="234" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F111" s="234" t="n">
+        <v>864</v>
+      </c>
+      <c r="G111" s="234" t="n">
+        <v>4752</v>
+      </c>
+      <c r="H111" s="243">
+        <f>CHOOSE(MATCH(MIN(D111:G111),D111:G111,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1" s="63">
+      <c r="C112" s="114" t="inlineStr">
+        <is>
+          <t>Порты OLT, шт</t>
+        </is>
+      </c>
+      <c r="D112" s="235" t="n">
+        <v>39</v>
+      </c>
+      <c r="E112" s="235" t="n">
+        <v>66</v>
+      </c>
+      <c r="F112" s="235" t="n">
+        <v>83</v>
+      </c>
+      <c r="G112" s="235" t="n">
+        <v>59</v>
+      </c>
+      <c r="H112" s="244">
+        <f>CHOOSE(MATCH(MIN(D112:G112),D112:G112,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1" s="63">
+      <c r="C113" s="112" t="inlineStr">
+        <is>
+          <t>Комплекты подвеса, шт</t>
+        </is>
+      </c>
+      <c r="D113" s="234" t="n">
+        <v>2911</v>
+      </c>
+      <c r="E113" s="234" t="n">
+        <v>4180</v>
+      </c>
+      <c r="F113" s="234" t="n">
+        <v>6136</v>
+      </c>
+      <c r="G113" s="234" t="n">
+        <v>2473</v>
+      </c>
+      <c r="H113" s="243">
+        <f>CHOOSE(MATCH(MIN(D113:G113),D113:G113,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1" s="63">
+      <c r="C114" s="114" t="inlineStr">
+        <is>
           <t>Доп. шкафы ОРШ (сверх 6), шт</t>
         </is>
       </c>
-      <c r="D110" s="221" t="n">
+      <c r="D114" s="235" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="221" t="n">
+      <c r="E114" s="235" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="221" t="n">
+      <c r="F114" s="235" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="221" t="n">
-        <v>28</v>
-      </c>
-      <c r="H110" s="230">
-        <f>CHOOSE(MATCH(MIN(D110:G110),D110:G110,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" ht="14" customHeight="1" s="63">
-      <c r="B111" s="107" t="inlineStr">
+      <c r="G114" s="235" t="n">
+        <v>32</v>
+      </c>
+      <c r="H114" s="244">
+        <f>CHOOSE(MATCH(MIN(D114:G114),D114:G114,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="14" customHeight="1" s="63">
+      <c r="B115" s="107" t="inlineStr">
         <is>
           <t>«Лучшая» — минимум по строке (для числа узлов и портов меньший объём работ также считается лучшим; равные значения дают первую). Ср. маршрут волокна ДХ: A/D — от ОРШ до муфты абонента; в каскадах маршрут делится на-shared участки до РОР, показатель не определён.</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="24" customHeight="1" s="63">
-      <c r="B113" s="108" t="n"/>
-      <c r="C113" s="108" t="inlineStr">
+    <row r="117" ht="24" customHeight="1" s="63">
+      <c r="B117" s="108" t="n"/>
+      <c r="C117" s="108" t="inlineStr">
         <is>
           <t>Д. Ориентировочный индекс стоимости и чувствительность к цене ёмкости</t>
         </is>
       </c>
-      <c r="D113" s="108" t="n"/>
-      <c r="E113" s="108" t="n"/>
-      <c r="F113" s="108" t="n"/>
-      <c r="G113" s="108" t="n"/>
-      <c r="H113" s="108" t="n"/>
-      <c r="I113" s="108" t="n"/>
-      <c r="J113" s="108" t="n"/>
-      <c r="K113" s="108" t="n"/>
-      <c r="L113" s="108" t="n"/>
-      <c r="M113" s="108" t="n"/>
-      <c r="N113" s="108" t="n"/>
-    </row>
-    <row r="114" ht="28" customHeight="1" s="63">
-      <c r="C114" s="111" t="inlineStr">
+      <c r="D117" s="108" t="n"/>
+      <c r="E117" s="108" t="n"/>
+      <c r="F117" s="108" t="n"/>
+      <c r="G117" s="108" t="n"/>
+      <c r="H117" s="108" t="n"/>
+      <c r="I117" s="108" t="n"/>
+      <c r="J117" s="108" t="n"/>
+      <c r="K117" s="108" t="n"/>
+      <c r="L117" s="108" t="n"/>
+      <c r="M117" s="108" t="n"/>
+      <c r="N117" s="108" t="n"/>
+    </row>
+    <row r="118" ht="28" customHeight="1" s="63">
+      <c r="C118" s="111" t="inlineStr">
         <is>
           <t>Составляющая, у.е. (1 км кабеля 8F)</t>
         </is>
       </c>
-      <c r="D114" s="111" t="inlineStr">
+      <c r="D118" s="111" t="inlineStr">
         <is>
           <t>A: централизо-ванная</t>
         </is>
       </c>
-      <c r="E114" s="111" t="inlineStr">
+      <c r="E118" s="111" t="inlineStr">
         <is>
           <t>B: каскад 1:8+1:8</t>
         </is>
       </c>
-      <c r="F114" s="111" t="inlineStr">
+      <c r="F118" s="111" t="inlineStr">
         <is>
           <t>C: каскад 1:4+1:16</t>
         </is>
       </c>
-      <c r="G114" s="111" t="inlineStr">
+      <c r="G118" s="111" t="inlineStr">
         <is>
           <t>D: зонные ОРШ</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="18" customHeight="1" s="63">
-      <c r="C115" s="112" t="inlineStr">
+    <row r="119" ht="18" customHeight="1" s="63">
+      <c r="C119" s="112" t="inlineStr">
         <is>
           <t>Кабельная продукция (магистраль)</t>
         </is>
       </c>
-      <c r="D115" s="222" t="n">
+      <c r="D119" s="236" t="n">
         <v>233</v>
       </c>
-      <c r="E115" s="222" t="n">
+      <c r="E119" s="236" t="n">
         <v>107</v>
       </c>
-      <c r="F115" s="222" t="n">
+      <c r="F119" s="236" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="G115" s="222" t="n">
-        <v>127.5</v>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1" s="63">
-      <c r="C116" s="114" t="inlineStr">
+      <c r="G119" s="236" t="n">
+        <v>132.1</v>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1" s="63">
+      <c r="C120" s="114" t="inlineStr">
         <is>
           <t>Дроп-кабели</t>
         </is>
       </c>
-      <c r="D116" s="224" t="n">
+      <c r="D120" s="238" t="n">
         <v>47.9</v>
       </c>
-      <c r="E116" s="224" t="n">
+      <c r="E120" s="238" t="n">
         <v>85.3</v>
       </c>
-      <c r="F116" s="224" t="n">
+      <c r="F120" s="238" t="n">
         <v>122</v>
       </c>
-      <c r="G116" s="224" t="n">
-        <v>58.1</v>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1" s="63">
-      <c r="C117" s="112" t="inlineStr">
+      <c r="G120" s="238" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1" s="63">
+      <c r="C121" s="112" t="inlineStr">
         <is>
           <t>Оборудование и монтаж</t>
         </is>
       </c>
-      <c r="D117" s="222" t="n">
+      <c r="D121" s="236" t="n">
         <v>315</v>
       </c>
-      <c r="E117" s="222" t="n">
+      <c r="E121" s="236" t="n">
         <v>306.2</v>
       </c>
-      <c r="F117" s="222" t="n">
+      <c r="F121" s="236" t="n">
         <v>270.8</v>
       </c>
-      <c r="G117" s="222" t="n">
-        <v>348.8</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="C118" s="108" t="inlineStr">
+      <c r="G121" s="236" t="n">
+        <v>353.8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="C122" s="108" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D118" s="132">
-        <f>SUM(D115:D117)</f>
-        <v/>
-      </c>
-      <c r="E118" s="132">
-        <f>SUM(E115:E117)</f>
-        <v/>
-      </c>
-      <c r="F118" s="132">
-        <f>SUM(F115:F117)</f>
-        <v/>
-      </c>
-      <c r="G118" s="132">
-        <f>SUM(G115:G117)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="C119" s="114" t="inlineStr">
+      <c r="D122" s="132">
+        <f>SUM(D119:D121)</f>
+        <v/>
+      </c>
+      <c r="E122" s="132">
+        <f>SUM(E119:E121)</f>
+        <v/>
+      </c>
+      <c r="F122" s="132">
+        <f>SUM(F119:F121)</f>
+        <v/>
+      </c>
+      <c r="G122" s="132">
+        <f>SUM(G119:G121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="C123" s="114" t="inlineStr">
         <is>
           <t>Доп. шкафы ОРШ (сверх базовых 6, по 1,5 у.е.)</t>
         </is>
       </c>
-      <c r="D119" s="224" t="n">
+      <c r="D123" s="238" t="n">
         <v>0</v>
       </c>
-      <c r="E119" s="224" t="n">
+      <c r="E123" s="238" t="n">
         <v>0</v>
       </c>
-      <c r="F119" s="224" t="n">
+      <c r="F123" s="238" t="n">
         <v>0</v>
       </c>
-      <c r="G119" s="224" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="C120" s="108" t="inlineStr">
+      <c r="G123" s="238" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="C124" s="108" t="inlineStr">
         <is>
           <t>ИТОГО с доп. шкафами</t>
         </is>
       </c>
-      <c r="D120" s="132">
-        <f>D118+D119</f>
-        <v/>
-      </c>
-      <c r="E120" s="132">
-        <f>E118+E119</f>
-        <v/>
-      </c>
-      <c r="F120" s="132">
-        <f>F118+F119</f>
-        <v/>
-      </c>
-      <c r="G120" s="132">
-        <f>G118+G119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="C121" s="112" t="inlineStr">
+      <c r="D124" s="132">
+        <f>D122+D123</f>
+        <v/>
+      </c>
+      <c r="E124" s="132">
+        <f>E122+E123</f>
+        <v/>
+      </c>
+      <c r="F124" s="132">
+        <f>F122+F123</f>
+        <v/>
+      </c>
+      <c r="G124" s="132">
+        <f>G122+G123</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="C125" s="112" t="inlineStr">
         <is>
           <t>Δ к лучшей схеме</t>
         </is>
       </c>
-      <c r="D121" s="223">
-        <f>D120/MIN($D$120:$G$120)-1</f>
-        <v/>
-      </c>
-      <c r="E121" s="223">
-        <f>E120/MIN($D$120:$G$120)-1</f>
-        <v/>
-      </c>
-      <c r="F121" s="223">
-        <f>F120/MIN($D$120:$G$120)-1</f>
-        <v/>
-      </c>
-      <c r="G121" s="223">
-        <f>G120/MIN($D$120:$G$120)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" ht="14" customHeight="1" s="63">
-      <c r="B122" s="107" t="inlineStr">
+      <c r="D125" s="237">
+        <f>D124/MIN($D$124:$G$124)-1</f>
+        <v/>
+      </c>
+      <c r="E125" s="237">
+        <f>E124/MIN($D$124:$G$124)-1</f>
+        <v/>
+      </c>
+      <c r="F125" s="237">
+        <f>F124/MIN($D$124:$G$124)-1</f>
+        <v/>
+      </c>
+      <c r="G125" s="237">
+        <f>G124/MIN($D$124:$G$124)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" ht="14" customHeight="1" s="63">
+      <c r="B126" s="107" t="inlineStr">
         <is>
           <t>Индекс по коэффициентам листа «Проверка волокно-км» (цена кабеля ~ (F/8)^0,5; оборудование по ориентировочным долям). Оценка для сравнения схем, не для сметы. Все схемы имеют 6 базовых ОРШ на ЦУ — в сравнении учтены только дополнительные шкафы схемы D.</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="28" customHeight="1" s="63">
-      <c r="C124" s="111" t="inlineStr">
+    <row r="128" ht="28" customHeight="1" s="63">
+      <c r="C128" s="111" t="inlineStr">
         <is>
           <t>Показатель цены k</t>
         </is>
       </c>
-      <c r="D124" s="111" t="inlineStr">
+      <c r="D128" s="111" t="inlineStr">
         <is>
           <t>A: централизо-ванная</t>
         </is>
       </c>
-      <c r="E124" s="111" t="inlineStr">
+      <c r="E128" s="111" t="inlineStr">
         <is>
           <t>B: каскад 1:8+1:8</t>
         </is>
       </c>
-      <c r="F124" s="111" t="inlineStr">
+      <c r="F128" s="111" t="inlineStr">
         <is>
           <t>C: каскад 1:4+1:16</t>
         </is>
       </c>
-      <c r="G124" s="111" t="inlineStr">
+      <c r="G128" s="111" t="inlineStr">
         <is>
           <t>D: зонные ОРШ</t>
         </is>
       </c>
-      <c r="H124" s="111" t="inlineStr">
+      <c r="H128" s="111" t="inlineStr">
         <is>
           <t>Лучшая</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="18" customHeight="1" s="63">
-      <c r="C125" s="232" t="n">
+    <row r="129" ht="18" customHeight="1" s="63">
+      <c r="C129" s="246" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="220" t="n">
+      <c r="D129" s="234" t="n">
         <v>520.2</v>
       </c>
-      <c r="E125" s="220" t="n">
+      <c r="E129" s="234" t="n">
         <v>553.4</v>
       </c>
-      <c r="F125" s="220" t="n">
+      <c r="F129" s="234" t="n">
         <v>585.9</v>
       </c>
-      <c r="G125" s="220" t="n">
-        <v>595.4</v>
-      </c>
-      <c r="H125" s="229">
-        <f>CHOOSE(MATCH(MIN(D125:G125),D125:G125,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" ht="18" customHeight="1" s="63">
-      <c r="C126" s="233" t="n">
+      <c r="G129" s="234" t="n">
+        <v>610.7</v>
+      </c>
+      <c r="H129" s="243">
+        <f>CHOOSE(MATCH(MIN(D129:G129),D129:G129,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1" s="63">
+      <c r="C130" s="247" t="n">
         <v>0.3</v>
       </c>
-      <c r="D126" s="221" t="n">
+      <c r="D130" s="235" t="n">
         <v>545.2</v>
       </c>
-      <c r="E126" s="221" t="n">
+      <c r="E130" s="235" t="n">
         <v>510.5</v>
       </c>
-      <c r="F126" s="221" t="n">
+      <c r="F130" s="235" t="n">
         <v>511.9</v>
       </c>
-      <c r="G126" s="221" t="n">
-        <v>575.8</v>
-      </c>
-      <c r="H126" s="230">
-        <f>CHOOSE(MATCH(MIN(D126:G126),D126:G126,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1" s="63">
-      <c r="C127" s="232" t="n">
+      <c r="G130" s="235" t="n">
+        <v>591.3</v>
+      </c>
+      <c r="H130" s="244">
+        <f>CHOOSE(MATCH(MIN(D130:G130),D130:G130,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1" s="63">
+      <c r="C131" s="246" t="n">
         <v>0.5</v>
       </c>
-      <c r="D127" s="220" t="n">
+      <c r="D131" s="234" t="n">
         <v>595.9</v>
       </c>
-      <c r="E127" s="220" t="n">
+      <c r="E131" s="234" t="n">
         <v>498.6</v>
       </c>
-      <c r="F127" s="220" t="n">
+      <c r="F131" s="234" t="n">
         <v>481.6</v>
       </c>
-      <c r="G127" s="220" t="n">
-        <v>576.5</v>
-      </c>
-      <c r="H127" s="229">
-        <f>CHOOSE(MATCH(MIN(D127:G127),D127:G127,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1" s="63">
-      <c r="C128" s="233" t="n">
+      <c r="G131" s="234" t="n">
+        <v>591.8</v>
+      </c>
+      <c r="H131" s="243">
+        <f>CHOOSE(MATCH(MIN(D131:G131),D131:G131,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1" s="63">
+      <c r="C132" s="247" t="n">
         <v>0.7</v>
       </c>
-      <c r="D128" s="221" t="n">
+      <c r="D132" s="235" t="n">
         <v>688</v>
       </c>
-      <c r="E128" s="221" t="n">
+      <c r="E132" s="235" t="n">
         <v>500.1</v>
       </c>
-      <c r="F128" s="221" t="n">
+      <c r="F132" s="235" t="n">
         <v>464</v>
       </c>
-      <c r="G128" s="221" t="n">
-        <v>588.5</v>
-      </c>
-      <c r="H128" s="230">
-        <f>CHOOSE(MATCH(MIN(D128:G128),D128:G128,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1" s="63">
-      <c r="C129" s="232" t="n">
+      <c r="G132" s="235" t="n">
+        <v>603.4</v>
+      </c>
+      <c r="H132" s="244">
+        <f>CHOOSE(MATCH(MIN(D132:G132),D132:G132,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1" s="63">
+      <c r="C133" s="246" t="n">
         <v>1</v>
       </c>
-      <c r="D129" s="220" t="n">
+      <c r="D133" s="234" t="n">
         <v>955</v>
       </c>
-      <c r="E129" s="220" t="n">
+      <c r="E133" s="234" t="n">
         <v>531.4</v>
       </c>
-      <c r="F129" s="220" t="n">
+      <c r="F133" s="234" t="n">
         <v>459.4</v>
       </c>
-      <c r="G129" s="220" t="n">
-        <v>632.2</v>
-      </c>
-      <c r="H129" s="229">
-        <f>CHOOSE(MATCH(MIN(D129:G129),D129:G129,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" ht="14" customHeight="1" s="63">
-      <c r="B130" s="107" t="inlineStr">
+      <c r="G133" s="234" t="n">
+        <v>645.5</v>
+      </c>
+      <c r="H133" s="243">
+        <f>CHOOSE(MATCH(MIN(D133:G133),D133:G133,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" ht="14" customHeight="1" s="63">
+      <c r="B134" s="107" t="inlineStr">
         <is>
           <t>k = 0 — цена кабеля не зависит от ёмкости; 0,5 — реалистично (√F); 1 — пропорционально волокно-км. D с доп. шкафами. При k = 0 выигрывает A (520 у.е.), при k &gt;= 0,3 — каскады; D устойчиво вторая с минимальной длиной.</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="24" customHeight="1" s="63">
-      <c r="B132" s="108" t="n"/>
-      <c r="C132" s="108" t="inlineStr">
+    <row r="136" ht="24" customHeight="1" s="63">
+      <c r="B136" s="108" t="n"/>
+      <c r="C136" s="108" t="inlineStr">
         <is>
           <t>Е. Вывод</t>
         </is>
       </c>
-      <c r="D132" s="108" t="n"/>
-      <c r="E132" s="108" t="n"/>
-      <c r="F132" s="108" t="n"/>
-      <c r="G132" s="108" t="n"/>
-      <c r="H132" s="108" t="n"/>
-      <c r="I132" s="108" t="n"/>
-      <c r="J132" s="108" t="n"/>
-      <c r="K132" s="108" t="n"/>
-      <c r="L132" s="108" t="n"/>
-      <c r="M132" s="108" t="n"/>
-      <c r="N132" s="108" t="n"/>
-    </row>
-    <row r="133" ht="36" customHeight="1" s="63">
-      <c r="B133" s="135" t="inlineStr">
+      <c r="D136" s="108" t="n"/>
+      <c r="E136" s="108" t="n"/>
+      <c r="F136" s="108" t="n"/>
+      <c r="G136" s="108" t="n"/>
+      <c r="H136" s="108" t="n"/>
+      <c r="I136" s="108" t="n"/>
+      <c r="J136" s="108" t="n"/>
+      <c r="K136" s="108" t="n"/>
+      <c r="L136" s="108" t="n"/>
+      <c r="M136" s="108" t="n"/>
+      <c r="N136" s="108" t="n"/>
+    </row>
+    <row r="137" ht="36" customHeight="1" s="63">
+      <c r="B137" s="135" t="inlineStr">
         <is>
           <t>Децентрализация работает: перенос сплиттеров из одного ОРШ села в зонные шкафы (в центрах секторов) сократил волокно-км с 4 375,1 (схема A) до 1 347,3 — на 69% — при полностью сохранённой топологии: те же муфты, те же дропы (95,8 км — минимум по всем схемам), та же трасса магистрали 73,1 км.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="50" customHeight="1" s="63">
-      <c r="B134" s="135" t="inlineStr">
-        <is>
-          <t>Схема D — лидер по суммарной длине кабельной продукции: 183,0 км (87,2 магистраль + 95,8 дропы) против 205,2 км у A, 247,2 у B, 315,1 у C и 191,2 км у «оптимума по длине» (R50). Максимальная ёмкость участка — 92 волокна против 972 у A, параллельных кабелей на участке — нет (было 2): фидеры к медианам полностью разместились в распределительных кабелях.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="50" customHeight="1" s="63">
-      <c r="B135" s="135" t="inlineStr">
-        <is>
-          <t>Цена децентрализации — оборудование: 34 ОРШ вместо 6 (28 доп. шкафов, +42 у.е.), 58 сплиттеров, 4 560 портов кросса. Индекс стоимости 524 у.е. с шкафами: на 12% дешевле централизованной (596), но на 8,9% дороже каскада C (482). Выигрыш v3 против v1-топологии (533 у.е., 1 562,5 вол-км): −215,2 вол-км волокна (−13,8%), на 2 шкафа меньше.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="36" customHeight="1" s="63">
-      <c r="B136" s="135" t="inlineStr">
-        <is>
-          <t>Чувствительность: при плоских ценах кабеля (k = 0) лучшая — A; при реалистичных k &gt;= 0,3 — каскады, D — устойчивая вторая схема (блок Д2). D выигрывает у B по стоимости за счёт коротких дропов и отсутствия параллельной прокладки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="50" customHeight="1" s="63">
-      <c r="B137" s="135" t="inlineStr">
-        <is>
-          <t>Эксплуатационный профиль D ближе к централизованной: нет РОР с полупустыми сплиттерами (заполнение зон 75-100% против 45% у C), подключение абонента и OTDR-диагностика — из зонного ОРШ (средний маршрут волокна ДХ -&gt; свой ОРШ 322 м против 1 361 м у A), портов OLT меньше, чем у каскадов (49 против 66 и 83). Плюс свой бонус: авария зонного шкафа затрагивает только свою зону, а не всё село.</t>
         </is>
       </c>
     </row>
     <row r="138" ht="50" customHeight="1" s="63">
       <c r="B138" s="135" t="inlineStr">
+        <is>
+          <t>Схема D — лидер по суммарной длине кабельной продукции: 183,0 км (87,2 магистраль + 95,8 дропы) против 205,2 км у A, 247,2 у B, 315,1 у C и 191,2 км у «оптимума по длине» (R50). Максимальная ёмкость участка — 92 волокна против 972 у A, параллельных кабелей на участке — нет (было 2): фидеры к медианам полностью разместились в распределительных кабелях.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="50" customHeight="1" s="63">
+      <c r="B139" s="135" t="inlineStr">
+        <is>
+          <t>Цена децентрализации — оборудование: 34 ОРШ вместо 6 (28 доп. шкафов, +42 у.е.), 59 сплиттеров, 4 752 порта кросса. Индекс стоимости 524 у.е. с шкафами: на 12% дешевле централизованной (596), но на 8,9% дороже каскада C (482). Выигрыш v3 против v1-топологии (533 у.е., 1 562,5 вол-км): −215,2 вол-км волокна (−13,8%), на 2 шкафа меньше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="36" customHeight="1" s="63">
+      <c r="B140" s="135" t="inlineStr">
+        <is>
+          <t>Чувствительность: при плоских ценах кабеля (k = 0) лучшая — A; при реалистичных k &gt;= 0,3 — каскады, D — устойчивая вторая схема (блок Д2). D выигрывает у B по стоимости за счёт коротких дропов и отсутствия параллельной прокладки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="50" customHeight="1" s="63">
+      <c r="B141" s="135" t="inlineStr">
+        <is>
+          <t>Эксплуатационный профиль D ближе к централизованной: нет РОР с полупустыми сплиттерами (заполнение зон 75-100% против 45% у C), подключение абонента и OTDR-диагностика — из зонного ОРШ (средний маршрут волокна ДХ -&gt; свой ОРШ 322 м против 1 361 м у A), портов OLT меньше, чем у каскадов (49 против 66 и 83). Плюс свой бонус: авария зонного шкафа затрагивает только свою зону, а не всё село.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="50" customHeight="1" s="63">
+      <c r="B142" s="135" t="inlineStr">
         <is>
           <t>Итог: если критерий — минимальное волокно и простая эксплуатация, лучшая схема D: 1 347,3 волокно-км (ниже касекада B), 183,0 км кабельной продукции, дропы 95,8 км. Если критерий — минимальная смета при реалистичных ценах, каскад 1:4+1:16 остаётся первым (482 у.е.), D — второй (524 у.е.) с минимальным волокном, централизованная — третья (596 у.е.).</t>
         </is>
@@ -11877,25 +12035,25 @@
   <mergeCells count="21">
     <mergeCell ref="B137:N137"/>
     <mergeCell ref="D10:N10"/>
-    <mergeCell ref="B133:N133"/>
+    <mergeCell ref="B139:N139"/>
+    <mergeCell ref="B142:N142"/>
     <mergeCell ref="D6:N6"/>
+    <mergeCell ref="B126:N126"/>
     <mergeCell ref="D11:N11"/>
-    <mergeCell ref="B135:N135"/>
     <mergeCell ref="B138:N138"/>
     <mergeCell ref="D13:N13"/>
     <mergeCell ref="B134:N134"/>
-    <mergeCell ref="B122:N122"/>
+    <mergeCell ref="B141:N141"/>
+    <mergeCell ref="B115:N115"/>
+    <mergeCell ref="B140:N140"/>
     <mergeCell ref="D7:N7"/>
-    <mergeCell ref="B130:N130"/>
     <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B111:N111"/>
     <mergeCell ref="D9:N9"/>
     <mergeCell ref="D12:N12"/>
-    <mergeCell ref="B136:N136"/>
     <mergeCell ref="D8:N8"/>
-    <mergeCell ref="B53:N53"/>
+    <mergeCell ref="B57:N57"/>
+    <mergeCell ref="B73:N73"/>
     <mergeCell ref="D14:N14"/>
-    <mergeCell ref="B69:N69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
+++ b/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
@@ -255,7 +255,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -698,6 +698,132 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1919,6 +2045,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1950,7 +2077,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Децентрализация ОРШ'!C75</f>
+              <f>'Децентрализация ОРШ'!C79</f>
             </strRef>
           </tx>
           <spPr>
@@ -1972,12 +2099,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Децентрализация ОРШ'!$B$76:$B$87</f>
+              <f>'Децентрализация ОРШ'!$B$80:$B$91</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Децентрализация ОРШ'!$C$76:$C$87</f>
+              <f>'Децентрализация ОРШ'!$C$80:$C$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1992,7 +2119,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Децентрализация ОРШ'!D75</f>
+              <f>'Децентрализация ОРШ'!D79</f>
             </strRef>
           </tx>
           <spPr>
@@ -2014,7 +2141,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'Децентрализация ОРШ'!$D$76:$D$87</f>
+              <f>'Децентрализация ОРШ'!$D$80:$D$91</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2093,7 +2220,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t>None</a:t>
+                <a:t/>
               </a:r>
             </a:p>
           </txPr>
@@ -2141,7 +2268,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t>None</a:t>
+                <a:t/>
               </a:r>
             </a:p>
           </txPr>
@@ -2844,7 +2971,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="7560000" cy="3960000"/>
@@ -4424,7 +4551,7 @@
       <c r="L5" s="108" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1" s="63">
-      <c r="B6" s="243" t="n">
+      <c r="B6" s="271" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -4432,7 +4559,7 @@
           <t>Шкаф оптический распределительный (ОРШ) центральный — в здании ЦУ</t>
         </is>
       </c>
-      <c r="D6" s="243" t="inlineStr">
+      <c r="D6" s="271" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4442,22 +4569,22 @@
           <t>1 на СНП (здание по проекту)</t>
         </is>
       </c>
-      <c r="F6" s="234" t="n">
+      <c r="F6" s="262" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="234" t="n">
+      <c r="G6" s="262" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="234" t="n">
+      <c r="H6" s="262" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="234" t="n">
+      <c r="I6" s="262" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="234" t="n">
+      <c r="J6" s="262" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="234" t="n">
+      <c r="K6" s="262" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="146">
@@ -4466,7 +4593,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="63">
-      <c r="B7" s="244" t="n">
+      <c r="B7" s="272" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="114" t="inlineStr">
@@ -4474,7 +4601,7 @@
           <t>Шкаф зонный ОРШ уличный (под сплиттеры 1:64)</t>
         </is>
       </c>
-      <c r="D7" s="244" t="inlineStr">
+      <c r="D7" s="272" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4484,21 +4611,21 @@
           <t>1 на зону — в центре сектора (медиана зоны, зона ≥ 48 ДХ)</t>
         </is>
       </c>
-      <c r="F7" s="235" t="n">
+      <c r="F7" s="263" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="235" t="n"/>
-      <c r="H7" s="235" t="n">
+      <c r="G7" s="263" t="n"/>
+      <c r="H7" s="263" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="235" t="n">
+      <c r="I7" s="263" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="235" t="n">
+      <c r="J7" s="263" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="235" t="n">
-        <v>2</v>
+      <c r="K7" s="263" t="n">
+        <v>6</v>
       </c>
       <c r="L7" s="147">
         <f>SUM(F7:K7)</f>
@@ -4506,7 +4633,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="63">
-      <c r="B8" s="243" t="n">
+      <c r="B8" s="271" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -4514,7 +4641,7 @@
           <t>Сплиттер PLC 1×64 (в ОРШ: ЦУ и зонных)</t>
         </is>
       </c>
-      <c r="D8" s="243" t="inlineStr">
+      <c r="D8" s="271" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4524,23 +4651,23 @@
           <t>ceil(ДХ зоны / 64), заполнение 75-100%</t>
         </is>
       </c>
-      <c r="F8" s="234" t="n">
+      <c r="F8" s="262" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="234" t="n">
+      <c r="G8" s="262" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="234" t="n">
+      <c r="H8" s="262" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="234" t="n">
+      <c r="I8" s="262" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="234" t="n">
+      <c r="J8" s="262" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="234" t="n">
-        <v>7</v>
+      <c r="K8" s="262" t="n">
+        <v>12</v>
       </c>
       <c r="L8" s="146">
         <f>SUM(F8:K8)</f>
@@ -4548,7 +4675,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="63">
-      <c r="B9" s="244" t="n">
+      <c r="B9" s="272" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="114" t="inlineStr">
@@ -4556,7 +4683,7 @@
           <t>Пигтейль SC/UPC для кросса ОРШ</t>
         </is>
       </c>
-      <c r="D9" s="244" t="inlineStr">
+      <c r="D9" s="272" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4566,23 +4693,23 @@
           <t>ДХ + 2 × сплиттеры 1:64</t>
         </is>
       </c>
-      <c r="F9" s="235" t="n">
+      <c r="F9" s="263" t="n">
         <v>1073</v>
       </c>
-      <c r="G9" s="235" t="n">
+      <c r="G9" s="263" t="n">
         <v>128</v>
       </c>
-      <c r="H9" s="235" t="n">
+      <c r="H9" s="263" t="n">
         <v>392</v>
       </c>
-      <c r="I9" s="235" t="n">
+      <c r="I9" s="263" t="n">
         <v>650</v>
       </c>
-      <c r="J9" s="235" t="n">
+      <c r="J9" s="263" t="n">
         <v>298</v>
       </c>
-      <c r="K9" s="235" t="n">
-        <v>342</v>
+      <c r="K9" s="263" t="n">
+        <v>639</v>
       </c>
       <c r="L9" s="147">
         <f>SUM(F9:K9)</f>
@@ -4590,7 +4717,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="63">
-      <c r="B10" s="243" t="n">
+      <c r="B10" s="271" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="112" t="inlineStr">
@@ -4598,7 +4725,7 @@
           <t>Порт PON OLT — справочно (активное оборудование, единый узел OLT)</t>
         </is>
       </c>
-      <c r="D10" s="243" t="inlineStr">
+      <c r="D10" s="271" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4608,23 +4735,23 @@
           <t>по числу сплиттеров 1:64</t>
         </is>
       </c>
-      <c r="F10" s="234" t="n">
+      <c r="F10" s="262" t="n">
         <v>22</v>
       </c>
-      <c r="G10" s="234" t="n">
+      <c r="G10" s="262" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="234" t="n">
+      <c r="H10" s="262" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="234" t="n">
+      <c r="I10" s="262" t="n">
         <v>14</v>
       </c>
-      <c r="J10" s="234" t="n">
+      <c r="J10" s="262" t="n">
         <v>6</v>
       </c>
-      <c r="K10" s="234" t="n">
-        <v>7</v>
+      <c r="K10" s="262" t="n">
+        <v>12</v>
       </c>
       <c r="L10" s="146">
         <f>SUM(F10:K10)</f>
@@ -4649,7 +4776,7 @@
       <c r="L11" s="108" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="63">
-      <c r="B12" s="243" t="n">
+      <c r="B12" s="271" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="112" t="inlineStr">
@@ -4657,7 +4784,7 @@
           <t>Кабель оптический самонесущий, 8 волокон</t>
         </is>
       </c>
-      <c r="D12" s="243" t="inlineStr">
+      <c r="D12" s="271" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4667,23 +4794,23 @@
           <t>распределение зоны max(8; 1,25 × ДХ потока) + фидер ceil(1,25 × сплиттеры зоны)</t>
         </is>
       </c>
-      <c r="F12" s="236" t="n">
+      <c r="F12" s="264" t="n">
         <v>16.7</v>
       </c>
-      <c r="G12" s="236" t="n">
+      <c r="G12" s="264" t="n">
         <v>2.6</v>
       </c>
-      <c r="H12" s="236" t="n">
+      <c r="H12" s="264" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="236" t="n">
+      <c r="I12" s="264" t="n">
         <v>9.9</v>
       </c>
-      <c r="J12" s="236" t="n">
+      <c r="J12" s="264" t="n">
         <v>4.5</v>
       </c>
-      <c r="K12" s="236" t="n">
-        <v>4.8</v>
+      <c r="K12" s="264" t="n">
+        <v>4</v>
       </c>
       <c r="L12" s="148">
         <f>SUM(F12:K12)</f>
@@ -4691,7 +4818,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="63">
-      <c r="B13" s="244" t="n">
+      <c r="B13" s="272" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="114" t="inlineStr">
@@ -4699,7 +4826,7 @@
           <t>Кабель оптический самонесущий, 12 волокон</t>
         </is>
       </c>
-      <c r="D13" s="244" t="inlineStr">
+      <c r="D13" s="272" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4709,23 +4836,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F13" s="238" t="n">
+      <c r="F13" s="266" t="n">
         <v>4.4</v>
       </c>
-      <c r="G13" s="238" t="n">
+      <c r="G13" s="266" t="n">
         <v>0.6</v>
       </c>
-      <c r="H13" s="238" t="n">
+      <c r="H13" s="266" t="n">
         <v>1.5</v>
       </c>
-      <c r="I13" s="238" t="n">
+      <c r="I13" s="266" t="n">
         <v>3.5</v>
       </c>
-      <c r="J13" s="238" t="n">
+      <c r="J13" s="266" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" s="238" t="n">
-        <v>1.2</v>
+      <c r="K13" s="266" t="n">
+        <v>1.3</v>
       </c>
       <c r="L13" s="149">
         <f>SUM(F13:K13)</f>
@@ -4733,7 +4860,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="63">
-      <c r="B14" s="243" t="n">
+      <c r="B14" s="271" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="112" t="inlineStr">
@@ -4741,7 +4868,7 @@
           <t>Кабель оптический самонесущий, 16 волокон</t>
         </is>
       </c>
-      <c r="D14" s="243" t="inlineStr">
+      <c r="D14" s="271" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4751,23 +4878,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F14" s="236" t="n">
+      <c r="F14" s="264" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" s="236" t="n">
+      <c r="G14" s="264" t="n">
         <v>0.5</v>
       </c>
-      <c r="H14" s="236" t="n">
+      <c r="H14" s="264" t="n">
         <v>0.5</v>
       </c>
-      <c r="I14" s="236" t="n">
+      <c r="I14" s="264" t="n">
         <v>1.6</v>
       </c>
-      <c r="J14" s="236" t="n">
+      <c r="J14" s="264" t="n">
         <v>1.3</v>
       </c>
-      <c r="K14" s="236" t="n">
-        <v>0.7</v>
+      <c r="K14" s="264" t="n">
+        <v>0.8</v>
       </c>
       <c r="L14" s="148">
         <f>SUM(F14:K14)</f>
@@ -4775,7 +4902,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="63">
-      <c r="B15" s="244" t="n">
+      <c r="B15" s="272" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="114" t="inlineStr">
@@ -4783,7 +4910,7 @@
           <t>Кабель оптический самонесущий, 24 волокна</t>
         </is>
       </c>
-      <c r="D15" s="244" t="inlineStr">
+      <c r="D15" s="272" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4793,23 +4920,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F15" s="238" t="n">
+      <c r="F15" s="266" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="238" t="n">
+      <c r="G15" s="266" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="238" t="n">
+      <c r="H15" s="266" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="238" t="n">
+      <c r="I15" s="266" t="n">
         <v>3.1</v>
       </c>
-      <c r="J15" s="238" t="n">
+      <c r="J15" s="266" t="n">
         <v>1.4</v>
       </c>
-      <c r="K15" s="238" t="n">
-        <v>1</v>
+      <c r="K15" s="266" t="n">
+        <v>1.4</v>
       </c>
       <c r="L15" s="149">
         <f>SUM(F15:K15)</f>
@@ -4817,7 +4944,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="63">
-      <c r="B16" s="243" t="n">
+      <c r="B16" s="271" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="112" t="inlineStr">
@@ -4825,7 +4952,7 @@
           <t>Кабель оптический самонесущий, 32 волокна</t>
         </is>
       </c>
-      <c r="D16" s="243" t="inlineStr">
+      <c r="D16" s="271" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4835,23 +4962,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F16" s="236" t="n">
+      <c r="F16" s="264" t="n">
         <v>2.2</v>
       </c>
-      <c r="G16" s="236" t="n">
+      <c r="G16" s="264" t="n">
         <v>0.4</v>
       </c>
-      <c r="H16" s="236" t="n">
+      <c r="H16" s="264" t="n">
         <v>1.1</v>
       </c>
-      <c r="I16" s="236" t="n">
+      <c r="I16" s="264" t="n">
         <v>1.8</v>
       </c>
-      <c r="J16" s="236" t="n">
+      <c r="J16" s="264" t="n">
         <v>0.8</v>
       </c>
-      <c r="K16" s="236" t="n">
-        <v>0.9</v>
+      <c r="K16" s="264" t="n">
+        <v>0.7</v>
       </c>
       <c r="L16" s="148">
         <f>SUM(F16:K16)</f>
@@ -4859,7 +4986,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="63">
-      <c r="B17" s="244" t="n">
+      <c r="B17" s="272" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="114" t="inlineStr">
@@ -4867,7 +4994,7 @@
           <t>Кабель оптический самонесущий, 48 волокон</t>
         </is>
       </c>
-      <c r="D17" s="244" t="inlineStr">
+      <c r="D17" s="272" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4877,23 +5004,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F17" s="238" t="n">
+      <c r="F17" s="266" t="n">
         <v>1.7</v>
       </c>
-      <c r="G17" s="238" t="n">
+      <c r="G17" s="266" t="n">
         <v>0.2</v>
       </c>
-      <c r="H17" s="238" t="n">
+      <c r="H17" s="266" t="n">
         <v>1.1</v>
       </c>
-      <c r="I17" s="238" t="n">
+      <c r="I17" s="266" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" s="238" t="n">
+      <c r="J17" s="266" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="238" t="n">
-        <v>1</v>
+      <c r="K17" s="266" t="n">
+        <v>1.1</v>
       </c>
       <c r="L17" s="149">
         <f>SUM(F17:K17)</f>
@@ -4901,7 +5028,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="63">
-      <c r="B18" s="243" t="n">
+      <c r="B18" s="271" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="112" t="inlineStr">
@@ -4909,7 +5036,7 @@
           <t>Кабель оптический самонесущий, 64 волокна</t>
         </is>
       </c>
-      <c r="D18" s="243" t="inlineStr">
+      <c r="D18" s="271" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4919,23 +5046,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F18" s="236" t="n">
+      <c r="F18" s="264" t="n">
         <v>0.7</v>
       </c>
-      <c r="G18" s="236" t="n">
+      <c r="G18" s="264" t="n">
         <v>0.3</v>
       </c>
-      <c r="H18" s="236" t="n">
+      <c r="H18" s="264" t="n">
         <v>0.5</v>
       </c>
-      <c r="I18" s="236" t="n">
+      <c r="I18" s="264" t="n">
         <v>0.4</v>
       </c>
-      <c r="J18" s="236" t="n">
+      <c r="J18" s="264" t="n">
         <v>0.3</v>
       </c>
-      <c r="K18" s="236" t="n">
-        <v>0.3</v>
+      <c r="K18" s="264" t="n">
+        <v>0.4</v>
       </c>
       <c r="L18" s="148">
         <f>SUM(F18:K18)</f>
@@ -4943,7 +5070,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="63">
-      <c r="B19" s="244" t="n">
+      <c r="B19" s="272" t="n">
         <v>13</v>
       </c>
       <c r="C19" s="114" t="inlineStr">
@@ -4951,7 +5078,7 @@
           <t>Кабель оптический самонесущий, 72 волокна</t>
         </is>
       </c>
-      <c r="D19" s="244" t="inlineStr">
+      <c r="D19" s="272" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4961,15 +5088,15 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F19" s="238" t="n">
+      <c r="F19" s="266" t="n">
         <v>0.4</v>
       </c>
-      <c r="G19" s="238" t="n"/>
-      <c r="H19" s="238" t="n"/>
-      <c r="I19" s="238" t="n"/>
-      <c r="J19" s="238" t="n"/>
-      <c r="K19" s="238" t="n">
-        <v>0.1</v>
+      <c r="G19" s="266" t="n"/>
+      <c r="H19" s="266" t="n"/>
+      <c r="I19" s="266" t="n"/>
+      <c r="J19" s="266" t="n"/>
+      <c r="K19" s="266" t="n">
+        <v>0.2</v>
       </c>
       <c r="L19" s="149">
         <f>SUM(F19:K19)</f>
@@ -4977,7 +5104,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="63">
-      <c r="B20" s="243" t="n">
+      <c r="B20" s="271" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="112" t="inlineStr">
@@ -4985,7 +5112,7 @@
           <t>Кабель оптический самонесущий, 96 волокон</t>
         </is>
       </c>
-      <c r="D20" s="243" t="inlineStr">
+      <c r="D20" s="271" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4995,21 +5122,21 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F20" s="236" t="n">
+      <c r="F20" s="264" t="n">
         <v>0.1</v>
       </c>
-      <c r="G20" s="236" t="n">
+      <c r="G20" s="264" t="n">
         <v>0.1</v>
       </c>
-      <c r="H20" s="236" t="n">
+      <c r="H20" s="264" t="n">
         <v>0.2</v>
       </c>
-      <c r="I20" s="236" t="n"/>
-      <c r="J20" s="236" t="n">
+      <c r="I20" s="264" t="n"/>
+      <c r="J20" s="264" t="n">
         <v>0.1</v>
       </c>
-      <c r="K20" s="236" t="n">
-        <v>0.2</v>
+      <c r="K20" s="264" t="n">
+        <v>0.1</v>
       </c>
       <c r="L20" s="148">
         <f>SUM(F20:K20)</f>
@@ -5017,7 +5144,7 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="63">
-      <c r="B21" s="244" t="n">
+      <c r="B21" s="272" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="114" t="inlineStr">
@@ -5025,7 +5152,7 @@
           <t>Кабель дроп-кабельный самонесущий, 2 волокна (1 раб. + 1 рез.)</t>
         </is>
       </c>
-      <c r="D21" s="244" t="inlineStr">
+      <c r="D21" s="272" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5035,23 +5162,23 @@
           <t>дропы × 1,05 (без подводок — дроп от муфты напрямую)</t>
         </is>
       </c>
-      <c r="F21" s="238" t="n">
+      <c r="F21" s="266" t="n">
         <v>41.7</v>
       </c>
-      <c r="G21" s="238" t="n">
+      <c r="G21" s="266" t="n">
         <v>5.2</v>
       </c>
-      <c r="H21" s="238" t="n">
+      <c r="H21" s="266" t="n">
         <v>15.8</v>
       </c>
-      <c r="I21" s="238" t="n">
+      <c r="I21" s="266" t="n">
         <v>27.2</v>
       </c>
-      <c r="J21" s="238" t="n">
+      <c r="J21" s="266" t="n">
         <v>12.9</v>
       </c>
-      <c r="K21" s="238" t="n">
-        <v>13</v>
+      <c r="K21" s="266" t="n">
+        <v>22.5</v>
       </c>
       <c r="L21" s="149">
         <f>SUM(F21:K21)</f>
@@ -5059,7 +5186,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="63">
-      <c r="B22" s="243" t="n">
+      <c r="B22" s="271" t="n">
         <v>16</v>
       </c>
       <c r="C22" s="112" t="inlineStr">
@@ -5067,7 +5194,7 @@
           <t>Справочно: суммарная ёмкость магистрального кабеля</t>
         </is>
       </c>
-      <c r="D22" s="243" t="inlineStr">
+      <c r="D22" s="271" t="inlineStr">
         <is>
           <t>волокно-км</t>
         </is>
@@ -5077,23 +5204,23 @@
           <t>Σ (длина участка × волокна)</t>
         </is>
       </c>
-      <c r="F22" s="236" t="n">
+      <c r="F22" s="264" t="n">
         <v>524.8</v>
       </c>
-      <c r="G22" s="236" t="n">
+      <c r="G22" s="264" t="n">
         <v>90</v>
       </c>
-      <c r="H22" s="236" t="n">
+      <c r="H22" s="264" t="n">
         <v>218.5</v>
       </c>
-      <c r="I22" s="236" t="n">
+      <c r="I22" s="264" t="n">
         <v>329.9</v>
       </c>
-      <c r="J22" s="236" t="n">
+      <c r="J22" s="264" t="n">
         <v>141.2</v>
       </c>
-      <c r="K22" s="236" t="n">
-        <v>170</v>
+      <c r="K22" s="264" t="n">
+        <v>186.7</v>
       </c>
       <c r="L22" s="148">
         <f>SUM(F22:K22)</f>
@@ -5118,7 +5245,7 @@
       <c r="L23" s="108" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="63">
-      <c r="B24" s="243" t="n">
+      <c r="B24" s="271" t="n">
         <v>17</v>
       </c>
       <c r="C24" s="112" t="inlineStr">
@@ -5126,7 +5253,7 @@
           <t>Муфта оптическая (ветвления магистрали)</t>
         </is>
       </c>
-      <c r="D24" s="243" t="inlineStr">
+      <c r="D24" s="271" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5136,23 +5263,23 @@
           <t>узлы ветвления кроме точек врезов зонных ОРШ; транзит — неразрезным кабелем</t>
         </is>
       </c>
-      <c r="F24" s="234" t="n">
+      <c r="F24" s="262" t="n">
         <v>367</v>
       </c>
-      <c r="G24" s="234" t="n">
+      <c r="G24" s="262" t="n">
         <v>70</v>
       </c>
-      <c r="H24" s="234" t="n">
+      <c r="H24" s="262" t="n">
         <v>158</v>
       </c>
-      <c r="I24" s="234" t="n">
+      <c r="I24" s="262" t="n">
         <v>246</v>
       </c>
-      <c r="J24" s="234" t="n">
+      <c r="J24" s="262" t="n">
         <v>119</v>
       </c>
-      <c r="K24" s="234" t="n">
-        <v>148</v>
+      <c r="K24" s="262" t="n">
+        <v>144</v>
       </c>
       <c r="L24" s="146">
         <f>SUM(F24:K24)</f>
@@ -5177,7 +5304,7 @@
       <c r="L25" s="108" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="63">
-      <c r="B26" s="243" t="n">
+      <c r="B26" s="271" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="112" t="inlineStr">
@@ -5185,7 +5312,7 @@
           <t>Бокс абонентский оптический с адаптером SC/UPC</t>
         </is>
       </c>
-      <c r="D26" s="243" t="inlineStr">
+      <c r="D26" s="271" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5195,23 +5322,23 @@
           <t>1 на ДХ</t>
         </is>
       </c>
-      <c r="F26" s="234" t="n">
+      <c r="F26" s="262" t="n">
         <v>1029</v>
       </c>
-      <c r="G26" s="234" t="n">
+      <c r="G26" s="262" t="n">
         <v>124</v>
       </c>
-      <c r="H26" s="234" t="n">
+      <c r="H26" s="262" t="n">
         <v>376</v>
       </c>
-      <c r="I26" s="234" t="n">
+      <c r="I26" s="262" t="n">
         <v>622</v>
       </c>
-      <c r="J26" s="234" t="n">
+      <c r="J26" s="262" t="n">
         <v>286</v>
       </c>
-      <c r="K26" s="234" t="n">
-        <v>328</v>
+      <c r="K26" s="262" t="n">
+        <v>615</v>
       </c>
       <c r="L26" s="146">
         <f>SUM(F26:K26)</f>
@@ -5219,7 +5346,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="63">
-      <c r="B27" s="244" t="n">
+      <c r="B27" s="272" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="114" t="inlineStr">
@@ -5227,7 +5354,7 @@
           <t>Коннектор оптический механический SC/UPC</t>
         </is>
       </c>
-      <c r="D27" s="244" t="inlineStr">
+      <c r="D27" s="272" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5237,23 +5364,23 @@
           <t>ДХ × 1,1 (абонентский бокс)</t>
         </is>
       </c>
-      <c r="F27" s="235" t="n">
+      <c r="F27" s="263" t="n">
         <v>1132</v>
       </c>
-      <c r="G27" s="235" t="n">
+      <c r="G27" s="263" t="n">
         <v>137</v>
       </c>
-      <c r="H27" s="235" t="n">
+      <c r="H27" s="263" t="n">
         <v>414</v>
       </c>
-      <c r="I27" s="235" t="n">
+      <c r="I27" s="263" t="n">
         <v>685</v>
       </c>
-      <c r="J27" s="235" t="n">
+      <c r="J27" s="263" t="n">
         <v>315</v>
       </c>
-      <c r="K27" s="235" t="n">
-        <v>361</v>
+      <c r="K27" s="263" t="n">
+        <v>677</v>
       </c>
       <c r="L27" s="147">
         <f>SUM(F27:K27)</f>
@@ -5261,7 +5388,7 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="63">
-      <c r="B28" s="243" t="n">
+      <c r="B28" s="271" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="112" t="inlineStr">
@@ -5269,7 +5396,7 @@
           <t>Сварное соединение (оценка объёма работ)</t>
         </is>
       </c>
-      <c r="D28" s="243" t="inlineStr">
+      <c r="D28" s="271" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5279,23 +5406,23 @@
           <t>(2 × ДХ + 2 × сплиттеры 1:64) × 1,1</t>
         </is>
       </c>
-      <c r="F28" s="234" t="n">
+      <c r="F28" s="262" t="n">
         <v>2313</v>
       </c>
-      <c r="G28" s="234" t="n">
+      <c r="G28" s="262" t="n">
         <v>278</v>
       </c>
-      <c r="H28" s="234" t="n">
+      <c r="H28" s="262" t="n">
         <v>845</v>
       </c>
-      <c r="I28" s="234" t="n">
+      <c r="I28" s="262" t="n">
         <v>1400</v>
       </c>
-      <c r="J28" s="234" t="n">
+      <c r="J28" s="262" t="n">
         <v>643</v>
       </c>
-      <c r="K28" s="234" t="n">
-        <v>737</v>
+      <c r="K28" s="262" t="n">
+        <v>1380</v>
       </c>
       <c r="L28" s="146">
         <f>SUM(F28:K28)</f>
@@ -5303,7 +5430,7 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="63">
-      <c r="B29" s="244" t="n">
+      <c r="B29" s="272" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="114" t="inlineStr">
@@ -5311,7 +5438,7 @@
           <t>Гильза КДЗС, 60 мм</t>
         </is>
       </c>
-      <c r="D29" s="244" t="inlineStr">
+      <c r="D29" s="272" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5321,23 +5448,23 @@
           <t>по числу сварных соединений</t>
         </is>
       </c>
-      <c r="F29" s="235" t="n">
+      <c r="F29" s="263" t="n">
         <v>2313</v>
       </c>
-      <c r="G29" s="235" t="n">
+      <c r="G29" s="263" t="n">
         <v>278</v>
       </c>
-      <c r="H29" s="235" t="n">
+      <c r="H29" s="263" t="n">
         <v>845</v>
       </c>
-      <c r="I29" s="235" t="n">
+      <c r="I29" s="263" t="n">
         <v>1400</v>
       </c>
-      <c r="J29" s="235" t="n">
+      <c r="J29" s="263" t="n">
         <v>643</v>
       </c>
-      <c r="K29" s="235" t="n">
-        <v>737</v>
+      <c r="K29" s="263" t="n">
+        <v>1380</v>
       </c>
       <c r="L29" s="147">
         <f>SUM(F29:K29)</f>
@@ -5345,7 +5472,7 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="63">
-      <c r="B30" s="243" t="n">
+      <c r="B30" s="271" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="112" t="inlineStr">
@@ -5353,7 +5480,7 @@
           <t>Комплект подвеса магистрального кабеля (кронштейн + спиральный зажим)</t>
         </is>
       </c>
-      <c r="D30" s="243" t="inlineStr">
+      <c r="D30" s="271" t="inlineStr">
         <is>
           <t>компл</t>
         </is>
@@ -5363,23 +5490,23 @@
           <t>30 на 1 км кабеля</t>
         </is>
       </c>
-      <c r="F30" s="234" t="n">
+      <c r="F30" s="262" t="n">
         <v>918</v>
       </c>
-      <c r="G30" s="234" t="n">
+      <c r="G30" s="262" t="n">
         <v>144</v>
       </c>
-      <c r="H30" s="234" t="n">
+      <c r="H30" s="262" t="n">
         <v>316</v>
       </c>
-      <c r="I30" s="234" t="n">
+      <c r="I30" s="262" t="n">
         <v>584</v>
       </c>
-      <c r="J30" s="234" t="n">
+      <c r="J30" s="262" t="n">
         <v>247</v>
       </c>
-      <c r="K30" s="234" t="n">
-        <v>264</v>
+      <c r="K30" s="262" t="n">
+        <v>263</v>
       </c>
       <c r="L30" s="146">
         <f>SUM(F30:K30)</f>
@@ -5387,7 +5514,7 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" s="63">
-      <c r="B31" s="244" t="n">
+      <c r="B31" s="272" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="114" t="inlineStr">
@@ -5395,7 +5522,7 @@
           <t>Анкерный зажим дроп-кабеля</t>
         </is>
       </c>
-      <c r="D31" s="244" t="inlineStr">
+      <c r="D31" s="272" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5405,23 +5532,23 @@
           <t>2 на ДХ</t>
         </is>
       </c>
-      <c r="F31" s="235" t="n">
+      <c r="F31" s="263" t="n">
         <v>2058</v>
       </c>
-      <c r="G31" s="235" t="n">
+      <c r="G31" s="263" t="n">
         <v>248</v>
       </c>
-      <c r="H31" s="235" t="n">
+      <c r="H31" s="263" t="n">
         <v>752</v>
       </c>
-      <c r="I31" s="235" t="n">
+      <c r="I31" s="263" t="n">
         <v>1244</v>
       </c>
-      <c r="J31" s="235" t="n">
+      <c r="J31" s="263" t="n">
         <v>572</v>
       </c>
-      <c r="K31" s="235" t="n">
-        <v>656</v>
+      <c r="K31" s="263" t="n">
+        <v>1230</v>
       </c>
       <c r="L31" s="147">
         <f>SUM(F31:K31)</f>
@@ -5429,7 +5556,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" s="63">
-      <c r="B32" s="243" t="n">
+      <c r="B32" s="271" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="112" t="inlineStr">
@@ -5437,7 +5564,7 @@
           <t>Крепёж дроп-кабеля (скобы / хомуты)</t>
         </is>
       </c>
-      <c r="D32" s="243" t="inlineStr">
+      <c r="D32" s="271" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5447,23 +5574,23 @@
           <t>6 на ДХ</t>
         </is>
       </c>
-      <c r="F32" s="234" t="n">
+      <c r="F32" s="262" t="n">
         <v>6174</v>
       </c>
-      <c r="G32" s="234" t="n">
+      <c r="G32" s="262" t="n">
         <v>744</v>
       </c>
-      <c r="H32" s="234" t="n">
+      <c r="H32" s="262" t="n">
         <v>2256</v>
       </c>
-      <c r="I32" s="234" t="n">
+      <c r="I32" s="262" t="n">
         <v>3732</v>
       </c>
-      <c r="J32" s="234" t="n">
+      <c r="J32" s="262" t="n">
         <v>1716</v>
       </c>
-      <c r="K32" s="234" t="n">
-        <v>1968</v>
+      <c r="K32" s="262" t="n">
+        <v>3690</v>
       </c>
       <c r="L32" s="146">
         <f>SUM(F32:K32)</f>
@@ -5480,7 +5607,7 @@
     <row r="35" ht="14" customHeight="1" s="63">
       <c r="B35" s="107" t="inlineStr">
         <is>
-          <t>Схема D (уточнённая детекция ДХ, полная VLM-верификация): 32 зон + 6 ЦУ = 38 ОРШ; заполнение сплиттеров 1:64 — 75-100%; ср. волоконный маршрут ДХ 305 м (против 1361 м в централизованной). Карты зон ОРШ по всем СНП — download/snp_vko.</t>
+          <t>Схема D (уточнённая детекция ДХ, полная VLM-верификация): 36 зон + 6 ЦУ = 42 ОРШ; заполнение сплиттеров 1:64 — 75-100%; ср. волоконный маршрут ДХ 279 м (против 1361 м в централизованной). Карты зон ОРШ по всем СНП — download/snp_vko.</t>
         </is>
       </c>
     </row>
@@ -8974,7 +9101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N142"/>
+  <dimension ref="B2:N146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="63" min="1" max="1"/>
@@ -9131,7 +9258,7 @@
       </c>
       <c r="D14" s="109" t="inlineStr">
         <is>
-          <t>S_MIN = 15 волокно-км на доп. ОРШ: 32 зон + 6 ЦУ = 38 ОРШ; волокно-км 1474 (-69% к A); суммарная длина 206.3 км — минимум среди всех схем книги.</t>
+          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1491 (-69% к A); суммарная длина 215.8 км — минимум среди всех схем книги.</t>
         </is>
       </c>
     </row>
@@ -9212,19 +9339,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F18" s="234" t="n">
+      <c r="F18" s="276" t="n">
         <v>69</v>
       </c>
-      <c r="G18" s="234" t="n">
+      <c r="G18" s="276" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="234" t="n">
+      <c r="H18" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="234" t="n">
+      <c r="I18" s="276" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="234" t="n">
+      <c r="J18" s="276" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9240,19 +9367,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F19" s="235" t="n">
+      <c r="F19" s="277" t="n">
         <v>46</v>
       </c>
-      <c r="G19" s="235" t="n">
+      <c r="G19" s="277" t="n">
         <v>752</v>
       </c>
-      <c r="H19" s="235" t="n">
+      <c r="H19" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="235" t="n">
+      <c r="I19" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="235" t="n">
+      <c r="J19" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9268,19 +9395,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F20" s="234" t="n">
+      <c r="F20" s="276" t="n">
         <v>114</v>
       </c>
-      <c r="G20" s="234" t="n">
+      <c r="G20" s="276" t="n">
         <v>546</v>
       </c>
-      <c r="H20" s="234" t="n">
+      <c r="H20" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="234" t="n">
+      <c r="I20" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="234" t="n">
+      <c r="J20" s="276" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9296,19 +9423,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F21" s="235" t="n">
+      <c r="F21" s="277" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="235" t="n">
+      <c r="G21" s="277" t="n">
         <v>667</v>
       </c>
-      <c r="H21" s="235" t="n">
+      <c r="H21" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="235" t="n">
+      <c r="I21" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="235" t="n">
+      <c r="J21" s="277" t="n">
         <v>48</v>
       </c>
     </row>
@@ -9324,19 +9451,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F22" s="234" t="n">
+      <c r="F22" s="276" t="n">
         <v>132</v>
       </c>
-      <c r="G22" s="234" t="n">
+      <c r="G22" s="276" t="n">
         <v>717</v>
       </c>
-      <c r="H22" s="234" t="n">
+      <c r="H22" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="234" t="n">
+      <c r="I22" s="276" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="234" t="n">
+      <c r="J22" s="276" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9352,19 +9479,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F23" s="235" t="n">
+      <c r="F23" s="277" t="n">
         <v>109</v>
       </c>
-      <c r="G23" s="235" t="n">
+      <c r="G23" s="277" t="n">
         <v>856</v>
       </c>
-      <c r="H23" s="235" t="n">
+      <c r="H23" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="235" t="n">
+      <c r="I23" s="277" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="235" t="n">
+      <c r="J23" s="277" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9380,19 +9507,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F24" s="234" t="n">
+      <c r="F24" s="276" t="n">
         <v>84</v>
       </c>
-      <c r="G24" s="234" t="n">
+      <c r="G24" s="276" t="n">
         <v>908</v>
       </c>
-      <c r="H24" s="234" t="n">
+      <c r="H24" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="234" t="n">
+      <c r="I24" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="234" t="n">
+      <c r="J24" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9408,19 +9535,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F25" s="235" t="n">
+      <c r="F25" s="277" t="n">
         <v>50</v>
       </c>
-      <c r="G25" s="235" t="n">
+      <c r="G25" s="277" t="n">
         <v>1708</v>
       </c>
-      <c r="H25" s="235" t="n">
+      <c r="H25" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="235" t="n">
+      <c r="I25" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="235" t="n">
+      <c r="J25" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9436,19 +9563,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F26" s="234" t="n">
+      <c r="F26" s="276" t="n">
         <v>49</v>
       </c>
-      <c r="G26" s="234" t="n">
+      <c r="G26" s="276" t="n">
         <v>860</v>
       </c>
-      <c r="H26" s="234" t="n">
+      <c r="H26" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="234" t="n">
+      <c r="I26" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="234" t="n">
+      <c r="J26" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9464,19 +9591,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F27" s="235" t="n">
+      <c r="F27" s="277" t="n">
         <v>49</v>
       </c>
-      <c r="G27" s="235" t="n">
+      <c r="G27" s="277" t="n">
         <v>1211</v>
       </c>
-      <c r="H27" s="235" t="n">
+      <c r="H27" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="235" t="n">
+      <c r="I27" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="235" t="n">
+      <c r="J27" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9492,19 +9619,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F28" s="234" t="n">
+      <c r="F28" s="276" t="n">
         <v>88</v>
       </c>
-      <c r="G28" s="234" t="n">
+      <c r="G28" s="276" t="n">
         <v>1175</v>
       </c>
-      <c r="H28" s="234" t="n">
+      <c r="H28" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="234" t="n">
+      <c r="I28" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="234" t="n">
+      <c r="J28" s="276" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9520,19 +9647,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F29" s="235" t="n">
+      <c r="F29" s="277" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="235" t="n">
+      <c r="G29" s="277" t="n">
         <v>1169</v>
       </c>
-      <c r="H29" s="235" t="n">
+      <c r="H29" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="235" t="n">
+      <c r="I29" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="235" t="n">
+      <c r="J29" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9548,19 +9675,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F30" s="234" t="n">
+      <c r="F30" s="276" t="n">
         <v>51</v>
       </c>
-      <c r="G30" s="234" t="n">
+      <c r="G30" s="276" t="n">
         <v>1390</v>
       </c>
-      <c r="H30" s="234" t="n">
+      <c r="H30" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="234" t="n">
+      <c r="I30" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="234" t="n">
+      <c r="J30" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9576,19 +9703,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F31" s="235" t="n">
+      <c r="F31" s="277" t="n">
         <v>49</v>
       </c>
-      <c r="G31" s="235" t="n">
+      <c r="G31" s="277" t="n">
         <v>879</v>
       </c>
-      <c r="H31" s="235" t="n">
+      <c r="H31" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="235" t="n">
+      <c r="I31" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="235" t="n">
+      <c r="J31" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9604,19 +9731,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F32" s="234" t="n">
+      <c r="F32" s="276" t="n">
         <v>59</v>
       </c>
-      <c r="G32" s="234" t="n">
+      <c r="G32" s="276" t="n">
         <v>745</v>
       </c>
-      <c r="H32" s="234" t="n">
+      <c r="H32" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="234" t="n">
+      <c r="I32" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="234" t="n">
+      <c r="J32" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9636,19 +9763,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F33" s="235" t="n">
+      <c r="F33" s="277" t="n">
         <v>124</v>
       </c>
-      <c r="G33" s="235" t="n">
+      <c r="G33" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="235" t="n">
+      <c r="H33" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="235" t="n">
+      <c r="I33" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="235" t="n">
+      <c r="J33" s="277" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9668,19 +9795,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F34" s="234" t="n">
+      <c r="F34" s="276" t="n">
         <v>35</v>
       </c>
-      <c r="G34" s="234" t="n">
+      <c r="G34" s="276" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="234" t="n">
+      <c r="H34" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="234" t="n">
+      <c r="I34" s="276" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="234" t="n">
+      <c r="J34" s="276" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9696,19 +9823,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F35" s="235" t="n">
+      <c r="F35" s="277" t="n">
         <v>56</v>
       </c>
-      <c r="G35" s="235" t="n">
+      <c r="G35" s="277" t="n">
         <v>805</v>
       </c>
-      <c r="H35" s="235" t="n">
+      <c r="H35" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="235" t="n">
+      <c r="I35" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="235" t="n">
+      <c r="J35" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9724,19 +9851,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F36" s="234" t="n">
+      <c r="F36" s="276" t="n">
         <v>156</v>
       </c>
-      <c r="G36" s="234" t="n">
+      <c r="G36" s="276" t="n">
         <v>295</v>
       </c>
-      <c r="H36" s="234" t="n">
+      <c r="H36" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="234" t="n">
+      <c r="I36" s="276" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="234" t="n">
+      <c r="J36" s="276" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9752,19 +9879,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F37" s="235" t="n">
+      <c r="F37" s="277" t="n">
         <v>69</v>
       </c>
-      <c r="G37" s="235" t="n">
+      <c r="G37" s="277" t="n">
         <v>1394</v>
       </c>
-      <c r="H37" s="235" t="n">
+      <c r="H37" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="235" t="n">
+      <c r="I37" s="277" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="235" t="n">
+      <c r="J37" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9780,19 +9907,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F38" s="234" t="n">
+      <c r="F38" s="276" t="n">
         <v>60</v>
       </c>
-      <c r="G38" s="234" t="n">
+      <c r="G38" s="276" t="n">
         <v>556</v>
       </c>
-      <c r="H38" s="234" t="n">
+      <c r="H38" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="234" t="n">
+      <c r="I38" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="234" t="n">
+      <c r="J38" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9812,19 +9939,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F39" s="235" t="n">
+      <c r="F39" s="277" t="n">
         <v>27</v>
       </c>
-      <c r="G39" s="235" t="n">
+      <c r="G39" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="235" t="n">
+      <c r="H39" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="235" t="n">
+      <c r="I39" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="235" t="n">
+      <c r="J39" s="277" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9840,19 +9967,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F40" s="234" t="n">
+      <c r="F40" s="276" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="234" t="n">
+      <c r="G40" s="276" t="n">
         <v>1298</v>
       </c>
-      <c r="H40" s="234" t="n">
+      <c r="H40" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="234" t="n">
+      <c r="I40" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="234" t="n">
+      <c r="J40" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9868,19 +9995,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F41" s="235" t="n">
+      <c r="F41" s="277" t="n">
         <v>107</v>
       </c>
-      <c r="G41" s="235" t="n">
+      <c r="G41" s="277" t="n">
         <v>418</v>
       </c>
-      <c r="H41" s="235" t="n">
+      <c r="H41" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="235" t="n">
+      <c r="I41" s="277" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="235" t="n">
+      <c r="J41" s="277" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9896,19 +10023,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F42" s="234" t="n">
+      <c r="F42" s="276" t="n">
         <v>53</v>
       </c>
-      <c r="G42" s="234" t="n">
+      <c r="G42" s="276" t="n">
         <v>1329</v>
       </c>
-      <c r="H42" s="234" t="n">
+      <c r="H42" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="234" t="n">
+      <c r="I42" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="234" t="n">
+      <c r="J42" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9924,19 +10051,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F43" s="235" t="n">
+      <c r="F43" s="277" t="n">
         <v>53</v>
       </c>
-      <c r="G43" s="235" t="n">
+      <c r="G43" s="277" t="n">
         <v>937</v>
       </c>
-      <c r="H43" s="235" t="n">
+      <c r="H43" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="235" t="n">
+      <c r="I43" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="235" t="n">
+      <c r="J43" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9952,19 +10079,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F44" s="234" t="n">
+      <c r="F44" s="276" t="n">
         <v>85</v>
       </c>
-      <c r="G44" s="234" t="n">
+      <c r="G44" s="276" t="n">
         <v>368</v>
       </c>
-      <c r="H44" s="234" t="n">
+      <c r="H44" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="234" t="n">
+      <c r="I44" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="234" t="n">
+      <c r="J44" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9980,19 +10107,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F45" s="235" t="n">
+      <c r="F45" s="277" t="n">
         <v>48</v>
       </c>
-      <c r="G45" s="235" t="n">
+      <c r="G45" s="277" t="n">
         <v>1096</v>
       </c>
-      <c r="H45" s="235" t="n">
+      <c r="H45" s="277" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="235" t="n">
+      <c r="I45" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="235" t="n">
+      <c r="J45" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10008,19 +10135,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F46" s="234" t="n">
+      <c r="F46" s="276" t="n">
         <v>76</v>
       </c>
-      <c r="G46" s="234" t="n">
+      <c r="G46" s="276" t="n">
         <v>302</v>
       </c>
-      <c r="H46" s="234" t="n">
+      <c r="H46" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="234" t="n">
+      <c r="I46" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="234" t="n">
+      <c r="J46" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10036,19 +10163,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F47" s="235" t="n">
+      <c r="F47" s="277" t="n">
         <v>78</v>
       </c>
-      <c r="G47" s="235" t="n">
+      <c r="G47" s="277" t="n">
         <v>1779</v>
       </c>
-      <c r="H47" s="235" t="n">
+      <c r="H47" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="235" t="n">
+      <c r="I47" s="277" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="235" t="n">
+      <c r="J47" s="277" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10064,19 +10191,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F48" s="234" t="n">
+      <c r="F48" s="276" t="n">
         <v>50</v>
       </c>
-      <c r="G48" s="234" t="n">
+      <c r="G48" s="276" t="n">
         <v>476</v>
       </c>
-      <c r="H48" s="234" t="n">
+      <c r="H48" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="234" t="n">
+      <c r="I48" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="234" t="n">
+      <c r="J48" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10096,19 +10223,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F49" s="235" t="n">
+      <c r="F49" s="277" t="n">
         <v>70</v>
       </c>
-      <c r="G49" s="235" t="n">
+      <c r="G49" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="235" t="n">
+      <c r="H49" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="I49" s="235" t="n">
+      <c r="I49" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="235" t="n">
+      <c r="J49" s="277" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10124,19 +10251,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F50" s="234" t="n">
+      <c r="F50" s="276" t="n">
         <v>62</v>
       </c>
-      <c r="G50" s="234" t="n">
+      <c r="G50" s="276" t="n">
         <v>666</v>
       </c>
-      <c r="H50" s="234" t="n">
+      <c r="H50" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="234" t="n">
+      <c r="I50" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="234" t="n">
+      <c r="J50" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10152,19 +10279,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F51" s="235" t="n">
+      <c r="F51" s="277" t="n">
         <v>93</v>
       </c>
-      <c r="G51" s="235" t="n">
+      <c r="G51" s="277" t="n">
         <v>262</v>
       </c>
-      <c r="H51" s="235" t="n">
+      <c r="H51" s="277" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="235" t="n">
+      <c r="I51" s="277" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="235" t="n">
+      <c r="J51" s="277" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10180,19 +10307,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F52" s="234" t="n">
+      <c r="F52" s="276" t="n">
         <v>61</v>
       </c>
-      <c r="G52" s="234" t="n">
+      <c r="G52" s="276" t="n">
         <v>367</v>
       </c>
-      <c r="H52" s="234" t="n">
+      <c r="H52" s="276" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="234" t="n">
+      <c r="I52" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="234" t="n">
+      <c r="J52" s="276" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10212,20 +10339,20 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F53" s="235" t="n">
-        <v>148</v>
-      </c>
-      <c r="G53" s="235" t="n">
+      <c r="F53" s="277" t="n">
+        <v>122</v>
+      </c>
+      <c r="G53" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="235" t="n">
-        <v>3</v>
-      </c>
-      <c r="I53" s="235" t="n">
+      <c r="H53" s="277" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="235" t="n">
-        <v>288</v>
+      <c r="J53" s="277" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="63">
@@ -10240,19 +10367,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F54" s="234" t="n">
-        <v>90</v>
-      </c>
-      <c r="G54" s="234" t="n">
-        <v>336</v>
-      </c>
-      <c r="H54" s="234" t="n">
+      <c r="F54" s="276" t="n">
+        <v>93</v>
+      </c>
+      <c r="G54" s="276" t="n">
+        <v>274</v>
+      </c>
+      <c r="H54" s="276" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="234" t="n">
+      <c r="I54" s="276" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="234" t="n">
+      <c r="J54" s="276" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10268,979 +10395,1005 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F55" s="235" t="n">
-        <v>90</v>
-      </c>
-      <c r="G55" s="235" t="n">
+      <c r="F55" s="277" t="n">
+        <v>121</v>
+      </c>
+      <c r="G55" s="277" t="n">
+        <v>654</v>
+      </c>
+      <c r="H55" s="277" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" s="277" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="277" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1" s="63">
+      <c r="C56" s="112" t="inlineStr"/>
+      <c r="D56" s="112" t="inlineStr">
+        <is>
+          <t>З-3</t>
+        </is>
+      </c>
+      <c r="E56" s="112" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F56" s="276" t="n">
+        <v>91</v>
+      </c>
+      <c r="G56" s="276" t="n">
+        <v>336</v>
+      </c>
+      <c r="H56" s="276" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" s="276" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" s="276" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1" s="63">
+      <c r="C57" s="114" t="inlineStr"/>
+      <c r="D57" s="114" t="inlineStr">
+        <is>
+          <t>З-4</t>
+        </is>
+      </c>
+      <c r="E57" s="114" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F57" s="277" t="n">
+        <v>59</v>
+      </c>
+      <c r="G57" s="277" t="n">
+        <v>433</v>
+      </c>
+      <c r="H57" s="277" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="277" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" s="277" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1" s="63">
+      <c r="C58" s="112" t="inlineStr"/>
+      <c r="D58" s="112" t="inlineStr">
+        <is>
+          <t>З-5</t>
+        </is>
+      </c>
+      <c r="E58" s="112" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F58" s="276" t="n">
+        <v>73</v>
+      </c>
+      <c r="G58" s="276" t="n">
+        <v>710</v>
+      </c>
+      <c r="H58" s="276" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="276" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="276" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1" s="63">
+      <c r="C59" s="114" t="inlineStr"/>
+      <c r="D59" s="114" t="inlineStr">
+        <is>
+          <t>З-6</t>
+        </is>
+      </c>
+      <c r="E59" s="114" t="inlineStr">
+        <is>
+          <t>зонный шкаф</t>
+        </is>
+      </c>
+      <c r="F59" s="277" t="n">
+        <v>56</v>
+      </c>
+      <c r="G59" s="277" t="n">
+        <v>306</v>
+      </c>
+      <c r="H59" s="277" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="277" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" s="277" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1" s="63">
+      <c r="C60" s="108" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="D60" s="108" t="inlineStr">
+        <is>
+          <t>42 ОРШ</t>
+        </is>
+      </c>
+      <c r="E60" s="116" t="n"/>
+      <c r="F60" s="117">
+        <f>SUM(F18:F59)</f>
+        <v/>
+      </c>
+      <c r="G60" s="117" t="n"/>
+      <c r="H60" s="117">
+        <f>SUM(H18:H59)</f>
+        <v/>
+      </c>
+      <c r="I60" s="117">
+        <f>SUM(I18:I59)</f>
+        <v/>
+      </c>
+      <c r="J60" s="117">
+        <f>SUM(J18:J59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="14" customHeight="1" s="63">
+      <c r="B61" s="107" t="inlineStr">
+        <is>
+          <t>Удалённость от ЦУ — по кратчайшей трассе дорожного графа в границе НП (Дейкстра). Зонный шкаф стоит в центре сектора — медиане дерева зоны (средний сдвиг от узла вреза ~300 м); врез — точка отделения зоны от дерева сети. Дропы абонентов не меняются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1" s="63">
+      <c r="B63" s="108" t="n"/>
+      <c r="C63" s="108" t="inlineStr">
+        <is>
+          <t>В. Параметрический sweep порога окупаемости S_MIN</t>
+        </is>
+      </c>
+      <c r="D63" s="108" t="n"/>
+      <c r="E63" s="108" t="n"/>
+      <c r="F63" s="108" t="n"/>
+      <c r="G63" s="108" t="n"/>
+      <c r="H63" s="108" t="n"/>
+      <c r="I63" s="108" t="n"/>
+      <c r="J63" s="108" t="n"/>
+      <c r="K63" s="108" t="n"/>
+      <c r="L63" s="108" t="n"/>
+      <c r="M63" s="108" t="n"/>
+      <c r="N63" s="108" t="n"/>
+    </row>
+    <row r="64" ht="28" customHeight="1" s="63">
+      <c r="C64" s="111" t="inlineStr">
+        <is>
+          <t>S_MIN, вол-км</t>
+        </is>
+      </c>
+      <c r="D64" s="111" t="inlineStr">
+        <is>
+          <t>ОРШ, шт</t>
+        </is>
+      </c>
+      <c r="E64" s="111" t="inlineStr">
+        <is>
+          <t>Волокно-км</t>
+        </is>
+      </c>
+      <c r="F64" s="111" t="inlineStr">
+        <is>
+          <t>Δ к A (4375,1)</t>
+        </is>
+      </c>
+      <c r="G64" s="111" t="inlineStr">
+        <is>
+          <t>Кабель, км</t>
+        </is>
+      </c>
+      <c r="H64" s="111" t="inlineStr">
+        <is>
+          <t>Дропы, км</t>
+        </is>
+      </c>
+      <c r="I64" s="111" t="inlineStr">
+        <is>
+          <t>ВСЕГО, км</t>
+        </is>
+      </c>
+      <c r="J64" s="111" t="inlineStr">
+        <is>
+          <t>Сплиттеры</t>
+        </is>
+      </c>
+      <c r="K64" s="111" t="inlineStr">
+        <is>
+          <t>Сварки</t>
+        </is>
+      </c>
+      <c r="L64" s="111" t="inlineStr">
+        <is>
+          <t>Порты ОРШ</t>
+        </is>
+      </c>
+      <c r="M64" s="111" t="inlineStr">
+        <is>
+          <t>Ср. маршрут волокна, м</t>
+        </is>
+      </c>
+      <c r="N64" s="111" t="inlineStr">
+        <is>
+          <t>Макс. ёмкость, F</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1" s="63">
+      <c r="C65" s="276" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="276" t="n">
+        <v>48</v>
+      </c>
+      <c r="E65" s="278" t="n">
+        <v>1460.2</v>
+      </c>
+      <c r="F65" s="279">
+        <f>E65/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G65" s="278" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H65" s="278" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I65" s="278">
+        <f>G65+H65</f>
+        <v/>
+      </c>
+      <c r="J65" s="276" t="n">
+        <v>56</v>
+      </c>
+      <c r="K65" s="276" t="n">
+        <v>5261</v>
+      </c>
+      <c r="L65" s="276" t="n">
+        <v>4368</v>
+      </c>
+      <c r="M65" s="276" t="n">
+        <v>349</v>
+      </c>
+      <c r="N65" s="276" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1" s="63">
+      <c r="C66" s="277" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" s="277" t="n">
+        <v>43</v>
+      </c>
+      <c r="E66" s="280" t="n">
+        <v>1476.5</v>
+      </c>
+      <c r="F66" s="281">
+        <f>E66/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G66" s="280" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H66" s="280" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I66" s="280">
+        <f>G66+H66</f>
+        <v/>
+      </c>
+      <c r="J66" s="277" t="n">
+        <v>54</v>
+      </c>
+      <c r="K66" s="277" t="n">
+        <v>5255</v>
+      </c>
+      <c r="L66" s="277" t="n">
+        <v>4176</v>
+      </c>
+      <c r="M66" s="277" t="n">
         <v>358</v>
       </c>
-      <c r="H55" s="235" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" s="235" t="n">
-        <v>3</v>
-      </c>
-      <c r="J55" s="235" t="n">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1" s="63">
-      <c r="C56" s="108" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
-      </c>
-      <c r="D56" s="108" t="inlineStr">
-        <is>
-          <t>38 ОРШ</t>
-        </is>
-      </c>
-      <c r="E56" s="116" t="n"/>
-      <c r="F56" s="117">
-        <f>SUM(F18:F55)</f>
-        <v/>
-      </c>
-      <c r="G56" s="117" t="n"/>
-      <c r="H56" s="117">
-        <f>SUM(H18:H55)</f>
-        <v/>
-      </c>
-      <c r="I56" s="117">
-        <f>SUM(I18:I55)</f>
-        <v/>
-      </c>
-      <c r="J56" s="117">
-        <f>SUM(J18:J55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="14" customHeight="1" s="63">
-      <c r="B57" s="107" t="inlineStr">
-        <is>
-          <t>Удалённость от ЦУ — по кратчайшей трассе дорожного графа в границе НП (Дейкстра). Зонный шкаф стоит в центре сектора — медиане дерева зоны (средний сдвиг от узла вреза ~300 м); врез — точка отделения зоны от дерева сети. Дропы абонентов не меняются.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="24" customHeight="1" s="63">
-      <c r="B59" s="108" t="n"/>
-      <c r="C59" s="108" t="inlineStr">
-        <is>
-          <t>В. Параметрический sweep порога окупаемости S_MIN</t>
-        </is>
-      </c>
-      <c r="D59" s="108" t="n"/>
-      <c r="E59" s="108" t="n"/>
-      <c r="F59" s="108" t="n"/>
-      <c r="G59" s="108" t="n"/>
-      <c r="H59" s="108" t="n"/>
-      <c r="I59" s="108" t="n"/>
-      <c r="J59" s="108" t="n"/>
-      <c r="K59" s="108" t="n"/>
-      <c r="L59" s="108" t="n"/>
-      <c r="M59" s="108" t="n"/>
-      <c r="N59" s="108" t="n"/>
-    </row>
-    <row r="60" ht="28" customHeight="1" s="63">
-      <c r="C60" s="111" t="inlineStr">
-        <is>
-          <t>S_MIN, вол-км</t>
-        </is>
-      </c>
-      <c r="D60" s="111" t="inlineStr">
+      <c r="N66" s="277" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1" s="63">
+      <c r="C67" s="276" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" s="276" t="n">
+        <v>39</v>
+      </c>
+      <c r="E67" s="278" t="n">
+        <v>1500.8</v>
+      </c>
+      <c r="F67" s="279">
+        <f>E67/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G67" s="278" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H67" s="278" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I67" s="278">
+        <f>G67+H67</f>
+        <v/>
+      </c>
+      <c r="J67" s="276" t="n">
+        <v>53</v>
+      </c>
+      <c r="K67" s="276" t="n">
+        <v>5253</v>
+      </c>
+      <c r="L67" s="276" t="n">
+        <v>3984</v>
+      </c>
+      <c r="M67" s="276" t="n">
+        <v>368</v>
+      </c>
+      <c r="N67" s="276" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1" s="63">
+      <c r="C68" s="277" t="n">
+        <v>10</v>
+      </c>
+      <c r="D68" s="277" t="n">
+        <v>36</v>
+      </c>
+      <c r="E68" s="280" t="n">
+        <v>1532.5</v>
+      </c>
+      <c r="F68" s="281">
+        <f>E68/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G68" s="280" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="H68" s="280" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I68" s="280">
+        <f>G68+H68</f>
+        <v/>
+      </c>
+      <c r="J68" s="277" t="n">
+        <v>53</v>
+      </c>
+      <c r="K68" s="277" t="n">
+        <v>5253</v>
+      </c>
+      <c r="L68" s="277" t="n">
+        <v>3888</v>
+      </c>
+      <c r="M68" s="277" t="n">
+        <v>379</v>
+      </c>
+      <c r="N68" s="277" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1" s="63">
+      <c r="C69" s="282" t="n">
+        <v>15</v>
+      </c>
+      <c r="D69" s="282" t="n">
+        <v>34</v>
+      </c>
+      <c r="E69" s="283" t="n">
+        <v>1562.5</v>
+      </c>
+      <c r="F69" s="284">
+        <f>E69/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G69" s="283" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="H69" s="283" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I69" s="283">
+        <f>G69+H69</f>
+        <v/>
+      </c>
+      <c r="J69" s="282" t="n">
+        <v>52</v>
+      </c>
+      <c r="K69" s="282" t="n">
+        <v>5251</v>
+      </c>
+      <c r="L69" s="282" t="n">
+        <v>3696</v>
+      </c>
+      <c r="M69" s="282" t="n">
+        <v>388</v>
+      </c>
+      <c r="N69" s="282" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" ht="18" customHeight="1" s="63">
+      <c r="C70" s="277" t="n">
+        <v>20</v>
+      </c>
+      <c r="D70" s="277" t="n">
+        <v>32</v>
+      </c>
+      <c r="E70" s="280" t="n">
+        <v>1603.9</v>
+      </c>
+      <c r="F70" s="281">
+        <f>E70/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G70" s="280" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="H70" s="280" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I70" s="280">
+        <f>G70+H70</f>
+        <v/>
+      </c>
+      <c r="J70" s="277" t="n">
+        <v>51</v>
+      </c>
+      <c r="K70" s="277" t="n">
+        <v>5249</v>
+      </c>
+      <c r="L70" s="277" t="n">
+        <v>3696</v>
+      </c>
+      <c r="M70" s="277" t="n">
+        <v>403</v>
+      </c>
+      <c r="N70" s="277" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1" s="63">
+      <c r="C71" s="276" t="n">
+        <v>25</v>
+      </c>
+      <c r="D71" s="276" t="n">
+        <v>29</v>
+      </c>
+      <c r="E71" s="278" t="n">
+        <v>1674.7</v>
+      </c>
+      <c r="F71" s="279">
+        <f>E71/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G71" s="278" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H71" s="278" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I71" s="278">
+        <f>G71+H71</f>
+        <v/>
+      </c>
+      <c r="J71" s="276" t="n">
+        <v>50</v>
+      </c>
+      <c r="K71" s="276" t="n">
+        <v>5247</v>
+      </c>
+      <c r="L71" s="276" t="n">
+        <v>3600</v>
+      </c>
+      <c r="M71" s="276" t="n">
+        <v>427</v>
+      </c>
+      <c r="N71" s="276" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1" s="63">
+      <c r="C72" s="277" t="n">
+        <v>30</v>
+      </c>
+      <c r="D72" s="277" t="n">
+        <v>27</v>
+      </c>
+      <c r="E72" s="280" t="n">
+        <v>1736.2</v>
+      </c>
+      <c r="F72" s="281">
+        <f>E72/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G72" s="280" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="H72" s="280" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I72" s="280">
+        <f>G72+H72</f>
+        <v/>
+      </c>
+      <c r="J72" s="277" t="n">
+        <v>48</v>
+      </c>
+      <c r="K72" s="277" t="n">
+        <v>5243</v>
+      </c>
+      <c r="L72" s="277" t="n">
+        <v>3504</v>
+      </c>
+      <c r="M72" s="277" t="n">
+        <v>448</v>
+      </c>
+      <c r="N72" s="277" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1" s="63">
+      <c r="C73" s="276" t="n">
+        <v>40</v>
+      </c>
+      <c r="D73" s="276" t="n">
+        <v>24</v>
+      </c>
+      <c r="E73" s="278" t="n">
+        <v>1852</v>
+      </c>
+      <c r="F73" s="279">
+        <f>E73/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G73" s="278" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="H73" s="278" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I73" s="278">
+        <f>G73+H73</f>
+        <v/>
+      </c>
+      <c r="J73" s="276" t="n">
+        <v>47</v>
+      </c>
+      <c r="K73" s="276" t="n">
+        <v>5241</v>
+      </c>
+      <c r="L73" s="276" t="n">
+        <v>3552</v>
+      </c>
+      <c r="M73" s="276" t="n">
+        <v>488</v>
+      </c>
+      <c r="N73" s="276" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1" s="63">
+      <c r="C74" s="277" t="n">
+        <v>50</v>
+      </c>
+      <c r="D74" s="277" t="n">
+        <v>20</v>
+      </c>
+      <c r="E74" s="280" t="n">
+        <v>2041.2</v>
+      </c>
+      <c r="F74" s="281">
+        <f>E74/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G74" s="280" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="H74" s="280" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I74" s="280">
+        <f>G74+H74</f>
+        <v/>
+      </c>
+      <c r="J74" s="277" t="n">
+        <v>46</v>
+      </c>
+      <c r="K74" s="277" t="n">
+        <v>5238</v>
+      </c>
+      <c r="L74" s="277" t="n">
+        <v>3696</v>
+      </c>
+      <c r="M74" s="277" t="n">
+        <v>554</v>
+      </c>
+      <c r="N74" s="277" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1" s="63">
+      <c r="C75" s="276" t="n">
+        <v>60</v>
+      </c>
+      <c r="D75" s="276" t="n">
+        <v>18</v>
+      </c>
+      <c r="E75" s="278" t="n">
+        <v>2153.9</v>
+      </c>
+      <c r="F75" s="279">
+        <f>E75/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G75" s="278" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="H75" s="278" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I75" s="278">
+        <f>G75+H75</f>
+        <v/>
+      </c>
+      <c r="J75" s="276" t="n">
+        <v>45</v>
+      </c>
+      <c r="K75" s="276" t="n">
+        <v>5236</v>
+      </c>
+      <c r="L75" s="276" t="n">
+        <v>3744</v>
+      </c>
+      <c r="M75" s="276" t="n">
+        <v>592</v>
+      </c>
+      <c r="N75" s="276" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1" s="63">
+      <c r="C76" s="277" t="n">
+        <v>80</v>
+      </c>
+      <c r="D76" s="277" t="n">
+        <v>17</v>
+      </c>
+      <c r="E76" s="280" t="n">
+        <v>2215.1</v>
+      </c>
+      <c r="F76" s="281">
+        <f>E76/4375.1-1</f>
+        <v/>
+      </c>
+      <c r="G76" s="280" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="H76" s="280" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="I76" s="280">
+        <f>G76+H76</f>
+        <v/>
+      </c>
+      <c r="J76" s="277" t="n">
+        <v>44</v>
+      </c>
+      <c r="K76" s="277" t="n">
+        <v>5234</v>
+      </c>
+      <c r="L76" s="277" t="n">
+        <v>3600</v>
+      </c>
+      <c r="M76" s="277" t="n">
+        <v>614</v>
+      </c>
+      <c r="N76" s="277" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="77" ht="14" customHeight="1" s="63">
+      <c r="B77" s="107" t="inlineStr">
+        <is>
+          <t>S_MIN — порог окупаемости: врез зонного ОРШ принимается при экономии не менее S_MIN волокно-км (шкаф с монтажом ~ 1,5 у.е. ~ 12-15 вол-км на тонком кабеле). Жёлтая строка — рекомендованная конфигурация (S_MIN = 15). Sweep рассчитан на стадии v1 (ОРШ во врезах, фидеры по дереву) и обосновывает выбор S_MIN; выпущенная книга v3 (ОРШ в центрах секторов + кратчайшие фидеры в границе НП): 1 386,0 волокно-км при 34 ОРШ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="28" customHeight="1" s="63">
+      <c r="B79" s="111" t="inlineStr">
         <is>
           <t>ОРШ, шт</t>
         </is>
       </c>
-      <c r="E60" s="111" t="inlineStr">
+      <c r="C79" s="111" t="inlineStr">
         <is>
           <t>Волокно-км</t>
         </is>
       </c>
-      <c r="F60" s="111" t="inlineStr">
-        <is>
-          <t>Δ к A (4375,1)</t>
-        </is>
-      </c>
-      <c r="G60" s="111" t="inlineStr">
-        <is>
-          <t>Кабель, км</t>
-        </is>
-      </c>
-      <c r="H60" s="111" t="inlineStr">
-        <is>
-          <t>Дропы, км</t>
-        </is>
-      </c>
-      <c r="I60" s="111" t="inlineStr">
-        <is>
-          <t>ВСЕГО, км</t>
-        </is>
-      </c>
-      <c r="J60" s="111" t="inlineStr">
-        <is>
-          <t>Сплиттеры</t>
-        </is>
-      </c>
-      <c r="K60" s="111" t="inlineStr">
-        <is>
-          <t>Сварки</t>
-        </is>
-      </c>
-      <c r="L60" s="111" t="inlineStr">
-        <is>
-          <t>Порты ОРШ</t>
-        </is>
-      </c>
-      <c r="M60" s="111" t="inlineStr">
-        <is>
-          <t>Ср. маршрут волокна, м</t>
-        </is>
-      </c>
-      <c r="N60" s="111" t="inlineStr">
-        <is>
-          <t>Макс. ёмкость, F</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1" s="63">
-      <c r="C61" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="D61" s="234" t="n">
+      <c r="D79" s="111" t="inlineStr">
+        <is>
+          <t>Индекс стоимости (с шкафами), у.е.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="262" t="n">
+        <v>17</v>
+      </c>
+      <c r="C80" s="264" t="n">
+        <v>2215.1</v>
+      </c>
+      <c r="D80" s="264" t="n">
+        <v>527.3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="263" t="n">
+        <v>18</v>
+      </c>
+      <c r="C81" s="266" t="n">
+        <v>2153.9</v>
+      </c>
+      <c r="D81" s="266" t="n">
+        <v>529.8</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="262" t="n">
+        <v>20</v>
+      </c>
+      <c r="C82" s="264" t="n">
+        <v>2041.2</v>
+      </c>
+      <c r="D82" s="264" t="n">
+        <v>527.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="263" t="n">
+        <v>24</v>
+      </c>
+      <c r="C83" s="266" t="n">
+        <v>1852</v>
+      </c>
+      <c r="D83" s="266" t="n">
+        <v>524.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="262" t="n">
+        <v>27</v>
+      </c>
+      <c r="C84" s="264" t="n">
+        <v>1736.2</v>
+      </c>
+      <c r="D84" s="264" t="n">
+        <v>524.4</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="263" t="n">
+        <v>29</v>
+      </c>
+      <c r="C85" s="266" t="n">
+        <v>1674.7</v>
+      </c>
+      <c r="D85" s="266" t="n">
+        <v>527.9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="262" t="n">
+        <v>32</v>
+      </c>
+      <c r="C86" s="264" t="n">
+        <v>1603.9</v>
+      </c>
+      <c r="D86" s="264" t="n">
+        <v>531.7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="263" t="n">
+        <v>34</v>
+      </c>
+      <c r="C87" s="266" t="n">
+        <v>1562.5</v>
+      </c>
+      <c r="D87" s="266" t="n">
+        <v>533.2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="262" t="n">
+        <v>36</v>
+      </c>
+      <c r="C88" s="264" t="n">
+        <v>1532.5</v>
+      </c>
+      <c r="D88" s="264" t="n">
+        <v>539.3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="263" t="n">
+        <v>39</v>
+      </c>
+      <c r="C89" s="266" t="n">
+        <v>1500.8</v>
+      </c>
+      <c r="D89" s="266" t="n">
+        <v>544.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="262" t="n">
+        <v>43</v>
+      </c>
+      <c r="C90" s="264" t="n">
+        <v>1476.5</v>
+      </c>
+      <c r="D90" s="264" t="n">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="263" t="n">
         <v>48</v>
       </c>
-      <c r="E61" s="236" t="n">
+      <c r="C91" s="266" t="n">
         <v>1460.2</v>
       </c>
-      <c r="F61" s="237">
-        <f>E61/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G61" s="236" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H61" s="236" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I61" s="236">
-        <f>G61+H61</f>
-        <v/>
-      </c>
-      <c r="J61" s="234" t="n">
-        <v>56</v>
-      </c>
-      <c r="K61" s="234" t="n">
-        <v>5261</v>
-      </c>
-      <c r="L61" s="234" t="n">
-        <v>4368</v>
-      </c>
-      <c r="M61" s="234" t="n">
-        <v>349</v>
-      </c>
-      <c r="N61" s="234" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1" s="63">
-      <c r="C62" s="235" t="n">
-        <v>5</v>
-      </c>
-      <c r="D62" s="235" t="n">
-        <v>43</v>
-      </c>
-      <c r="E62" s="238" t="n">
-        <v>1476.5</v>
-      </c>
-      <c r="F62" s="239">
-        <f>E62/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G62" s="238" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H62" s="238" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I62" s="238">
-        <f>G62+H62</f>
-        <v/>
-      </c>
-      <c r="J62" s="235" t="n">
-        <v>54</v>
-      </c>
-      <c r="K62" s="235" t="n">
-        <v>5255</v>
-      </c>
-      <c r="L62" s="235" t="n">
-        <v>4176</v>
-      </c>
-      <c r="M62" s="235" t="n">
-        <v>358</v>
-      </c>
-      <c r="N62" s="235" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1" s="63">
-      <c r="C63" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" s="234" t="n">
-        <v>39</v>
-      </c>
-      <c r="E63" s="236" t="n">
-        <v>1500.8</v>
-      </c>
-      <c r="F63" s="237">
-        <f>E63/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G63" s="236" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H63" s="236" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I63" s="236">
-        <f>G63+H63</f>
-        <v/>
-      </c>
-      <c r="J63" s="234" t="n">
-        <v>53</v>
-      </c>
-      <c r="K63" s="234" t="n">
-        <v>5253</v>
-      </c>
-      <c r="L63" s="234" t="n">
-        <v>3984</v>
-      </c>
-      <c r="M63" s="234" t="n">
-        <v>368</v>
-      </c>
-      <c r="N63" s="234" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="64" ht="18" customHeight="1" s="63">
-      <c r="C64" s="235" t="n">
-        <v>10</v>
-      </c>
-      <c r="D64" s="235" t="n">
-        <v>36</v>
-      </c>
-      <c r="E64" s="238" t="n">
-        <v>1532.5</v>
-      </c>
-      <c r="F64" s="239">
-        <f>E64/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G64" s="238" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="H64" s="238" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I64" s="238">
-        <f>G64+H64</f>
-        <v/>
-      </c>
-      <c r="J64" s="235" t="n">
-        <v>53</v>
-      </c>
-      <c r="K64" s="235" t="n">
-        <v>5253</v>
-      </c>
-      <c r="L64" s="235" t="n">
-        <v>3888</v>
-      </c>
-      <c r="M64" s="235" t="n">
-        <v>379</v>
-      </c>
-      <c r="N64" s="235" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="65" ht="18" customHeight="1" s="63">
-      <c r="C65" s="240" t="n">
-        <v>15</v>
-      </c>
-      <c r="D65" s="240" t="n">
-        <v>34</v>
-      </c>
-      <c r="E65" s="241" t="n">
-        <v>1562.5</v>
-      </c>
-      <c r="F65" s="242">
-        <f>E65/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G65" s="241" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="H65" s="241" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I65" s="241">
-        <f>G65+H65</f>
-        <v/>
-      </c>
-      <c r="J65" s="240" t="n">
-        <v>52</v>
-      </c>
-      <c r="K65" s="240" t="n">
-        <v>5251</v>
-      </c>
-      <c r="L65" s="240" t="n">
-        <v>3696</v>
-      </c>
-      <c r="M65" s="240" t="n">
-        <v>388</v>
-      </c>
-      <c r="N65" s="240" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" ht="18" customHeight="1" s="63">
-      <c r="C66" s="235" t="n">
-        <v>20</v>
-      </c>
-      <c r="D66" s="235" t="n">
-        <v>32</v>
-      </c>
-      <c r="E66" s="238" t="n">
-        <v>1603.9</v>
-      </c>
-      <c r="F66" s="239">
-        <f>E66/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G66" s="238" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="H66" s="238" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I66" s="238">
-        <f>G66+H66</f>
-        <v/>
-      </c>
-      <c r="J66" s="235" t="n">
-        <v>51</v>
-      </c>
-      <c r="K66" s="235" t="n">
-        <v>5249</v>
-      </c>
-      <c r="L66" s="235" t="n">
-        <v>3696</v>
-      </c>
-      <c r="M66" s="235" t="n">
-        <v>403</v>
-      </c>
-      <c r="N66" s="235" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="67" ht="18" customHeight="1" s="63">
-      <c r="C67" s="234" t="n">
-        <v>25</v>
-      </c>
-      <c r="D67" s="234" t="n">
-        <v>29</v>
-      </c>
-      <c r="E67" s="236" t="n">
-        <v>1674.7</v>
-      </c>
-      <c r="F67" s="237">
-        <f>E67/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G67" s="236" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="H67" s="236" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I67" s="236">
-        <f>G67+H67</f>
-        <v/>
-      </c>
-      <c r="J67" s="234" t="n">
-        <v>50</v>
-      </c>
-      <c r="K67" s="234" t="n">
-        <v>5247</v>
-      </c>
-      <c r="L67" s="234" t="n">
-        <v>3600</v>
-      </c>
-      <c r="M67" s="234" t="n">
-        <v>427</v>
-      </c>
-      <c r="N67" s="234" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="68" ht="18" customHeight="1" s="63">
-      <c r="C68" s="235" t="n">
-        <v>30</v>
-      </c>
-      <c r="D68" s="235" t="n">
-        <v>27</v>
-      </c>
-      <c r="E68" s="238" t="n">
-        <v>1736.2</v>
-      </c>
-      <c r="F68" s="239">
-        <f>E68/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G68" s="238" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="H68" s="238" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I68" s="238">
-        <f>G68+H68</f>
-        <v/>
-      </c>
-      <c r="J68" s="235" t="n">
-        <v>48</v>
-      </c>
-      <c r="K68" s="235" t="n">
-        <v>5243</v>
-      </c>
-      <c r="L68" s="235" t="n">
-        <v>3504</v>
-      </c>
-      <c r="M68" s="235" t="n">
-        <v>448</v>
-      </c>
-      <c r="N68" s="235" t="n">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="69" ht="18" customHeight="1" s="63">
-      <c r="C69" s="234" t="n">
-        <v>40</v>
-      </c>
-      <c r="D69" s="234" t="n">
-        <v>24</v>
-      </c>
-      <c r="E69" s="236" t="n">
-        <v>1852</v>
-      </c>
-      <c r="F69" s="237">
-        <f>E69/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G69" s="236" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="H69" s="236" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I69" s="236">
-        <f>G69+H69</f>
-        <v/>
-      </c>
-      <c r="J69" s="234" t="n">
-        <v>47</v>
-      </c>
-      <c r="K69" s="234" t="n">
-        <v>5241</v>
-      </c>
-      <c r="L69" s="234" t="n">
-        <v>3552</v>
-      </c>
-      <c r="M69" s="234" t="n">
-        <v>488</v>
-      </c>
-      <c r="N69" s="234" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1" s="63">
-      <c r="C70" s="235" t="n">
-        <v>50</v>
-      </c>
-      <c r="D70" s="235" t="n">
-        <v>20</v>
-      </c>
-      <c r="E70" s="238" t="n">
-        <v>2041.2</v>
-      </c>
-      <c r="F70" s="239">
-        <f>E70/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G70" s="238" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="H70" s="238" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I70" s="238">
-        <f>G70+H70</f>
-        <v/>
-      </c>
-      <c r="J70" s="235" t="n">
-        <v>46</v>
-      </c>
-      <c r="K70" s="235" t="n">
-        <v>5238</v>
-      </c>
-      <c r="L70" s="235" t="n">
-        <v>3696</v>
-      </c>
-      <c r="M70" s="235" t="n">
-        <v>554</v>
-      </c>
-      <c r="N70" s="235" t="n">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1" s="63">
-      <c r="C71" s="234" t="n">
-        <v>60</v>
-      </c>
-      <c r="D71" s="234" t="n">
-        <v>18</v>
-      </c>
-      <c r="E71" s="236" t="n">
-        <v>2153.9</v>
-      </c>
-      <c r="F71" s="237">
-        <f>E71/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G71" s="236" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="H71" s="236" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I71" s="236">
-        <f>G71+H71</f>
-        <v/>
-      </c>
-      <c r="J71" s="234" t="n">
-        <v>45</v>
-      </c>
-      <c r="K71" s="234" t="n">
-        <v>5236</v>
-      </c>
-      <c r="L71" s="234" t="n">
-        <v>3744</v>
-      </c>
-      <c r="M71" s="234" t="n">
-        <v>592</v>
-      </c>
-      <c r="N71" s="234" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="72" ht="18" customHeight="1" s="63">
-      <c r="C72" s="235" t="n">
-        <v>80</v>
-      </c>
-      <c r="D72" s="235" t="n">
-        <v>17</v>
-      </c>
-      <c r="E72" s="238" t="n">
-        <v>2215.1</v>
-      </c>
-      <c r="F72" s="239">
-        <f>E72/4375.1-1</f>
-        <v/>
-      </c>
-      <c r="G72" s="238" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="H72" s="238" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="I72" s="238">
-        <f>G72+H72</f>
-        <v/>
-      </c>
-      <c r="J72" s="235" t="n">
-        <v>44</v>
-      </c>
-      <c r="K72" s="235" t="n">
-        <v>5234</v>
-      </c>
-      <c r="L72" s="235" t="n">
-        <v>3600</v>
-      </c>
-      <c r="M72" s="235" t="n">
-        <v>614</v>
-      </c>
-      <c r="N72" s="235" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="73" ht="14" customHeight="1" s="63">
-      <c r="B73" s="107" t="inlineStr">
-        <is>
-          <t>S_MIN — порог окупаемости: врез зонного ОРШ принимается при экономии не менее S_MIN волокно-км (шкаф с монтажом ~ 1,5 у.е. ~ 12-15 вол-км на тонком кабеле). Жёлтая строка — рекомендованная конфигурация (S_MIN = 15). Sweep рассчитан на стадии v1 (ОРШ во врезах, фидеры по дереву) и обосновывает выбор S_MIN; выпущенная книга v3 (ОРШ в центрах секторов + кратчайшие фидеры в границе НП): 1 386,0 волокно-км при 34 ОРШ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="28" customHeight="1" s="63">
-      <c r="B75" s="111" t="inlineStr">
-        <is>
-          <t>ОРШ, шт</t>
-        </is>
-      </c>
-      <c r="C75" s="111" t="inlineStr">
-        <is>
-          <t>Волокно-км</t>
-        </is>
-      </c>
-      <c r="D75" s="111" t="inlineStr">
-        <is>
-          <t>Индекс стоимости (с шкафами), у.е.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="234" t="n">
-        <v>17</v>
-      </c>
-      <c r="C76" s="236" t="n">
-        <v>2215.1</v>
-      </c>
-      <c r="D76" s="236" t="n">
-        <v>527.3</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="235" t="n">
-        <v>18</v>
-      </c>
-      <c r="C77" s="238" t="n">
-        <v>2153.9</v>
-      </c>
-      <c r="D77" s="238" t="n">
-        <v>529.8</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="234" t="n">
-        <v>20</v>
-      </c>
-      <c r="C78" s="236" t="n">
-        <v>2041.2</v>
-      </c>
-      <c r="D78" s="236" t="n">
-        <v>527.5</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="235" t="n">
-        <v>24</v>
-      </c>
-      <c r="C79" s="238" t="n">
-        <v>1852</v>
-      </c>
-      <c r="D79" s="238" t="n">
-        <v>524.2</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="234" t="n">
-        <v>27</v>
-      </c>
-      <c r="C80" s="236" t="n">
-        <v>1736.2</v>
-      </c>
-      <c r="D80" s="236" t="n">
-        <v>524.4</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="235" t="n">
-        <v>29</v>
-      </c>
-      <c r="C81" s="238" t="n">
-        <v>1674.7</v>
-      </c>
-      <c r="D81" s="238" t="n">
-        <v>527.9</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="234" t="n">
-        <v>32</v>
-      </c>
-      <c r="C82" s="236" t="n">
-        <v>1603.9</v>
-      </c>
-      <c r="D82" s="236" t="n">
-        <v>531.7</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="235" t="n">
-        <v>34</v>
-      </c>
-      <c r="C83" s="238" t="n">
-        <v>1562.5</v>
-      </c>
-      <c r="D83" s="238" t="n">
-        <v>533.2</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="234" t="n">
-        <v>36</v>
-      </c>
-      <c r="C84" s="236" t="n">
-        <v>1532.5</v>
-      </c>
-      <c r="D84" s="236" t="n">
-        <v>539.3</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="235" t="n">
-        <v>39</v>
-      </c>
-      <c r="C85" s="238" t="n">
-        <v>1500.8</v>
-      </c>
-      <c r="D85" s="238" t="n">
-        <v>544.4</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="234" t="n">
-        <v>43</v>
-      </c>
-      <c r="C86" s="236" t="n">
-        <v>1476.5</v>
-      </c>
-      <c r="D86" s="236" t="n">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="235" t="n">
-        <v>48</v>
-      </c>
-      <c r="C87" s="238" t="n">
-        <v>1460.2</v>
-      </c>
-      <c r="D87" s="238" t="n">
+      <c r="D91" s="266" t="n">
         <v>563.9</v>
       </c>
     </row>
-    <row r="89" ht="24" customHeight="1" s="63">
-      <c r="B89" s="108" t="n"/>
-      <c r="C89" s="108" t="inlineStr">
+    <row r="93" ht="24" customHeight="1" s="63">
+      <c r="B93" s="108" t="n"/>
+      <c r="C93" s="108" t="inlineStr">
         <is>
           <t>Г. Сравнение четырёх схем — A / B / C / D</t>
         </is>
       </c>
-      <c r="D89" s="108" t="n"/>
-      <c r="E89" s="108" t="n"/>
-      <c r="F89" s="108" t="n"/>
-      <c r="G89" s="108" t="n"/>
-      <c r="H89" s="108" t="n"/>
-      <c r="I89" s="108" t="n"/>
-      <c r="J89" s="108" t="n"/>
-      <c r="K89" s="108" t="n"/>
-      <c r="L89" s="108" t="n"/>
-      <c r="M89" s="108" t="n"/>
-      <c r="N89" s="108" t="n"/>
-    </row>
-    <row r="90" ht="28" customHeight="1" s="63">
-      <c r="C90" s="111" t="inlineStr">
+      <c r="D93" s="108" t="n"/>
+      <c r="E93" s="108" t="n"/>
+      <c r="F93" s="108" t="n"/>
+      <c r="G93" s="108" t="n"/>
+      <c r="H93" s="108" t="n"/>
+      <c r="I93" s="108" t="n"/>
+      <c r="J93" s="108" t="n"/>
+      <c r="K93" s="108" t="n"/>
+      <c r="L93" s="108" t="n"/>
+      <c r="M93" s="108" t="n"/>
+      <c r="N93" s="108" t="n"/>
+    </row>
+    <row r="94" ht="28" customHeight="1" s="63">
+      <c r="C94" s="111" t="inlineStr">
         <is>
           <t>Показатель</t>
         </is>
       </c>
-      <c r="D90" s="111" t="inlineStr">
+      <c r="D94" s="111" t="inlineStr">
         <is>
           <t>A: централизо-ванная 1:64</t>
         </is>
       </c>
-      <c r="E90" s="111" t="inlineStr">
+      <c r="E94" s="111" t="inlineStr">
         <is>
           <t>B: каскад 1:8+1:8</t>
         </is>
       </c>
-      <c r="F90" s="111" t="inlineStr">
+      <c r="F94" s="111" t="inlineStr">
         <is>
           <t>C: каскад 1:4+1:16</t>
         </is>
       </c>
-      <c r="G90" s="111" t="inlineStr">
+      <c r="G94" s="111" t="inlineStr">
         <is>
           <t>D: зонные ОРШ 1:64</t>
         </is>
       </c>
-      <c r="H90" s="111" t="inlineStr">
+      <c r="H94" s="111" t="inlineStr">
         <is>
           <t>Лучшая</t>
         </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1" s="63">
-      <c r="C91" s="112" t="inlineStr">
-        <is>
-          <t>Обслужено ДХ, шт</t>
-        </is>
-      </c>
-      <c r="D91" s="234" t="n">
-        <v>2765</v>
-      </c>
-      <c r="E91" s="234" t="n">
-        <v>2765</v>
-      </c>
-      <c r="F91" s="234" t="n">
-        <v>2765</v>
-      </c>
-      <c r="G91" s="234" t="n">
-        <v>2765</v>
-      </c>
-      <c r="H91" s="243" t="n"/>
-    </row>
-    <row r="92" ht="18" customHeight="1" s="63">
-      <c r="C92" s="114" t="inlineStr">
-        <is>
-          <t>Волокно-км</t>
-        </is>
-      </c>
-      <c r="D92" s="238" t="n">
-        <v>4375.1</v>
-      </c>
-      <c r="E92" s="238" t="n">
-        <v>1256.1</v>
-      </c>
-      <c r="F92" s="238" t="n">
-        <v>889.2</v>
-      </c>
-      <c r="G92" s="238" t="n">
-        <v>1474.4</v>
-      </c>
-      <c r="H92" s="244">
-        <f>CHOOSE(MATCH(MIN(D92:G92),D92:G92,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1" s="63">
-      <c r="C93" s="112" t="inlineStr">
-        <is>
-          <t>Волокно-км на ДХ, км</t>
-        </is>
-      </c>
-      <c r="D93" s="245">
-        <f>D92/2765</f>
-        <v/>
-      </c>
-      <c r="E93" s="245">
-        <f>E92/2765</f>
-        <v/>
-      </c>
-      <c r="F93" s="245">
-        <f>F92/2765</f>
-        <v/>
-      </c>
-      <c r="G93" s="245">
-        <f>G92/2765</f>
-        <v/>
-      </c>
-      <c r="H93" s="243">
-        <f>CHOOSE(MATCH(MIN(D93:G93),D93:G93,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1" s="63">
-      <c r="C94" s="114" t="inlineStr">
-        <is>
-          <t>Магистральный кабель, км</t>
-        </is>
-      </c>
-      <c r="D94" s="238" t="n">
-        <v>109.4</v>
-      </c>
-      <c r="E94" s="238" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="F94" s="238" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="G94" s="238" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="H94" s="244">
-        <f>CHOOSE(MATCH(MIN(D94:G94),D94:G94,0),"A","B","C","D")</f>
-        <v/>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="63">
       <c r="C95" s="112" t="inlineStr">
         <is>
-          <t>в т.ч. 8-волоконный, км</t>
-        </is>
-      </c>
-      <c r="D95" s="236" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="E95" s="236" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F95" s="236" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="G95" s="236" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="H95" s="243" t="n"/>
+          <t>Обслужено ДХ, шт</t>
+        </is>
+      </c>
+      <c r="D95" s="276" t="n">
+        <v>3052</v>
+      </c>
+      <c r="E95" s="276" t="n">
+        <v>3052</v>
+      </c>
+      <c r="F95" s="276" t="n">
+        <v>3052</v>
+      </c>
+      <c r="G95" s="276" t="n">
+        <v>3052</v>
+      </c>
+      <c r="H95" s="285" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="63">
       <c r="C96" s="114" t="inlineStr">
         <is>
-          <t>в т.ч. 96-волоконный, км</t>
-        </is>
-      </c>
-      <c r="D96" s="238" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E96" s="238" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F96" s="238" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G96" s="238" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H96" s="244" t="n"/>
+          <t>Волокно-км</t>
+        </is>
+      </c>
+      <c r="D96" s="280" t="n">
+        <v>4375.1</v>
+      </c>
+      <c r="E96" s="280" t="n">
+        <v>1256.1</v>
+      </c>
+      <c r="F96" s="280" t="n">
+        <v>889.2</v>
+      </c>
+      <c r="G96" s="280" t="n">
+        <v>1491.1</v>
+      </c>
+      <c r="H96" s="286">
+        <f>CHOOSE(MATCH(MIN(D96:G96),D96:G96,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="97" ht="18" customHeight="1" s="63">
       <c r="C97" s="112" t="inlineStr">
         <is>
-          <t>Дроп-кабель, км</t>
-        </is>
-      </c>
-      <c r="D97" s="236" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="E97" s="236" t="n">
-        <v>170.7</v>
-      </c>
-      <c r="F97" s="236" t="n">
-        <v>244</v>
-      </c>
-      <c r="G97" s="236" t="n">
-        <v>115.8</v>
-      </c>
-      <c r="H97" s="243">
+          <t>Волокно-км на ДХ, км</t>
+        </is>
+      </c>
+      <c r="D97" s="287">
+        <f>D96/3052</f>
+        <v/>
+      </c>
+      <c r="E97" s="287">
+        <f>E96/3052</f>
+        <v/>
+      </c>
+      <c r="F97" s="287">
+        <f>F96/3052</f>
+        <v/>
+      </c>
+      <c r="G97" s="287">
+        <f>G96/3052</f>
+        <v/>
+      </c>
+      <c r="H97" s="285">
         <f>CHOOSE(MATCH(MIN(D97:G97),D97:G97,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11248,26 +11401,22 @@
     <row r="98" ht="18" customHeight="1" s="63">
       <c r="C98" s="114" t="inlineStr">
         <is>
-          <t>ВСЕГО кабель + дропы, км</t>
-        </is>
-      </c>
-      <c r="D98" s="238">
-        <f>D94+D97</f>
-        <v/>
-      </c>
-      <c r="E98" s="238">
-        <f>E94+E97</f>
-        <v/>
-      </c>
-      <c r="F98" s="238">
-        <f>F94+F97</f>
-        <v/>
-      </c>
-      <c r="G98" s="238">
-        <f>G94+G97</f>
-        <v/>
-      </c>
-      <c r="H98" s="244">
+          <t>Магистральный кабель, км</t>
+        </is>
+      </c>
+      <c r="D98" s="280" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="E98" s="280" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F98" s="280" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="G98" s="280" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H98" s="286">
         <f>CHOOSE(MATCH(MIN(D98:G98),D98:G98,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11275,64 +11424,62 @@
     <row r="99" ht="18" customHeight="1" s="63">
       <c r="C99" s="112" t="inlineStr">
         <is>
-          <t>Средний дроп, м</t>
-        </is>
-      </c>
-      <c r="D99" s="234" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E99" s="234" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="F99" s="234" t="n">
-        <v>84</v>
-      </c>
-      <c r="G99" s="234" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="H99" s="243">
-        <f>CHOOSE(MATCH(MIN(D99:G99),D99:G99,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>в т.ч. 8-волоконный, км</t>
+        </is>
+      </c>
+      <c r="D99" s="278" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="E99" s="278" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F99" s="278" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G99" s="278" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="H99" s="285" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1" s="63">
       <c r="C100" s="114" t="inlineStr">
         <is>
-          <t>Максимальный дроп, м</t>
-        </is>
-      </c>
-      <c r="D100" s="235" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E100" s="235" t="n">
-        <v>201</v>
-      </c>
-      <c r="F100" s="235" t="n">
-        <v>266</v>
-      </c>
-      <c r="G100" s="235" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="H100" s="244">
-        <f>CHOOSE(MATCH(MIN(D100:G100),D100:G100,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>в т.ч. 96-волоконный, км</t>
+        </is>
+      </c>
+      <c r="D100" s="280" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E100" s="280" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F100" s="280" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G100" s="280" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H100" s="286" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="63">
       <c r="C101" s="112" t="inlineStr">
         <is>
-          <t>Ср. маршрут волокна ДХ, м</t>
-        </is>
-      </c>
-      <c r="D101" s="234" t="n">
-        <v>1361</v>
-      </c>
-      <c r="E101" s="234" t="n"/>
-      <c r="F101" s="234" t="n"/>
-      <c r="G101" s="234" t="n">
-        <v>305</v>
-      </c>
-      <c r="H101" s="243">
+          <t>Дроп-кабель, км</t>
+        </is>
+      </c>
+      <c r="D101" s="278" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="E101" s="278" t="n">
+        <v>170.7</v>
+      </c>
+      <c r="F101" s="278" t="n">
+        <v>244</v>
+      </c>
+      <c r="G101" s="278" t="n">
+        <v>125.3</v>
+      </c>
+      <c r="H101" s="285">
         <f>CHOOSE(MATCH(MIN(D101:G101),D101:G101,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11340,22 +11487,26 @@
     <row r="102" ht="18" customHeight="1" s="63">
       <c r="C102" s="114" t="inlineStr">
         <is>
-          <t>ОРШ, шт</t>
-        </is>
-      </c>
-      <c r="D102" s="235" t="n">
-        <v>6</v>
-      </c>
-      <c r="E102" s="235" t="n">
-        <v>6</v>
-      </c>
-      <c r="F102" s="235" t="n">
-        <v>6</v>
-      </c>
-      <c r="G102" s="235" t="n">
-        <v>38</v>
-      </c>
-      <c r="H102" s="244">
+          <t>ВСЕГО кабель + дропы, км</t>
+        </is>
+      </c>
+      <c r="D102" s="280">
+        <f>D98+D101</f>
+        <v/>
+      </c>
+      <c r="E102" s="280">
+        <f>E98+E101</f>
+        <v/>
+      </c>
+      <c r="F102" s="280">
+        <f>F98+F101</f>
+        <v/>
+      </c>
+      <c r="G102" s="280">
+        <f>G98+G101</f>
+        <v/>
+      </c>
+      <c r="H102" s="286">
         <f>CHOOSE(MATCH(MIN(D102:G102),D102:G102,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11363,214 +11514,210 @@
     <row r="103" ht="18" customHeight="1" s="63">
       <c r="C103" s="112" t="inlineStr">
         <is>
-          <t>РОР, шт</t>
-        </is>
-      </c>
-      <c r="D103" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="234" t="n">
-        <v>515</v>
-      </c>
-      <c r="F103" s="234" t="n">
-        <v>323</v>
-      </c>
-      <c r="G103" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="243" t="n"/>
+          <t>Средний дроп, м</t>
+        </is>
+      </c>
+      <c r="D103" s="276" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E103" s="276" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F103" s="276" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="G103" s="276" t="n">
+        <v>39</v>
+      </c>
+      <c r="H103" s="285">
+        <f>CHOOSE(MATCH(MIN(D103:G103),D103:G103,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="104" ht="18" customHeight="1" s="63">
       <c r="C104" s="114" t="inlineStr">
         <is>
-          <t>Сплиттеры 1:64, шт</t>
-        </is>
-      </c>
-      <c r="D104" s="235" t="n">
-        <v>39</v>
-      </c>
-      <c r="E104" s="235" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="235" t="n">
-        <v>59</v>
-      </c>
-      <c r="H104" s="244" t="n"/>
+          <t>Максимальный дроп, м</t>
+        </is>
+      </c>
+      <c r="D104" s="277" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E104" s="277" t="n">
+        <v>201</v>
+      </c>
+      <c r="F104" s="277" t="n">
+        <v>266</v>
+      </c>
+      <c r="G104" s="277" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="H104" s="286">
+        <f>CHOOSE(MATCH(MIN(D104:G104),D104:G104,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="105" ht="18" customHeight="1" s="63">
       <c r="C105" s="112" t="inlineStr">
         <is>
-          <t>Сплиттеры 1:8, шт</t>
-        </is>
-      </c>
-      <c r="D105" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="234" t="n">
-        <v>581</v>
-      </c>
-      <c r="F105" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="243" t="n"/>
+          <t>Ср. маршрут волокна ДХ, м</t>
+        </is>
+      </c>
+      <c r="D105" s="276" t="n">
+        <v>1361</v>
+      </c>
+      <c r="E105" s="276" t="n"/>
+      <c r="F105" s="276" t="n"/>
+      <c r="G105" s="276" t="n">
+        <v>279</v>
+      </c>
+      <c r="H105" s="285">
+        <f>CHOOSE(MATCH(MIN(D105:G105),D105:G105,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="106" ht="18" customHeight="1" s="63">
       <c r="C106" s="114" t="inlineStr">
         <is>
-          <t>Сплиттеры 1:4, шт</t>
-        </is>
-      </c>
-      <c r="D106" s="235" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="235" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="235" t="n">
-        <v>83</v>
-      </c>
-      <c r="G106" s="235" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="244" t="n"/>
+          <t>ОРШ, шт</t>
+        </is>
+      </c>
+      <c r="D106" s="277" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" s="277" t="n">
+        <v>6</v>
+      </c>
+      <c r="F106" s="277" t="n">
+        <v>6</v>
+      </c>
+      <c r="G106" s="277" t="n">
+        <v>42</v>
+      </c>
+      <c r="H106" s="286">
+        <f>CHOOSE(MATCH(MIN(D106:G106),D106:G106,0),"A","B","C","D")</f>
+        <v/>
+      </c>
     </row>
     <row r="107" ht="18" customHeight="1" s="63">
       <c r="C107" s="112" t="inlineStr">
         <is>
-          <t>Сплиттеры 1:16, шт</t>
-        </is>
-      </c>
-      <c r="D107" s="234" t="n">
+          <t>РОР, шт</t>
+        </is>
+      </c>
+      <c r="D107" s="276" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="234" t="n">
+      <c r="E107" s="276" t="n">
+        <v>515</v>
+      </c>
+      <c r="F107" s="276" t="n">
+        <v>323</v>
+      </c>
+      <c r="G107" s="276" t="n">
         <v>0</v>
       </c>
-      <c r="F107" s="234" t="n">
-        <v>323</v>
-      </c>
-      <c r="G107" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="243" t="n"/>
+      <c r="H107" s="285" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="63">
       <c r="C108" s="114" t="inlineStr">
         <is>
-          <t>Муфты, шт</t>
-        </is>
-      </c>
-      <c r="D108" s="235" t="n">
-        <v>1140</v>
-      </c>
-      <c r="E108" s="235" t="n">
-        <v>115</v>
-      </c>
-      <c r="F108" s="235" t="n">
-        <v>100</v>
-      </c>
-      <c r="G108" s="235" t="n">
-        <v>1108</v>
-      </c>
-      <c r="H108" s="244">
-        <f>CHOOSE(MATCH(MIN(D108:G108),D108:G108,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>Сплиттеры 1:64, шт</t>
+        </is>
+      </c>
+      <c r="D108" s="277" t="n">
+        <v>39</v>
+      </c>
+      <c r="E108" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="277" t="n">
+        <v>64</v>
+      </c>
+      <c r="H108" s="286" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1" s="63">
       <c r="C109" s="112" t="inlineStr">
         <is>
-          <t>Сварки, шт</t>
-        </is>
-      </c>
-      <c r="D109" s="234" t="n">
-        <v>5136</v>
-      </c>
-      <c r="E109" s="234" t="n">
-        <v>2585</v>
-      </c>
-      <c r="F109" s="234" t="n">
-        <v>1552</v>
-      </c>
-      <c r="G109" s="234" t="n">
-        <v>6216</v>
-      </c>
-      <c r="H109" s="243">
-        <f>CHOOSE(MATCH(MIN(D109:G109),D109:G109,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>Сплиттеры 1:8, шт</t>
+        </is>
+      </c>
+      <c r="D109" s="276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="276" t="n">
+        <v>581</v>
+      </c>
+      <c r="F109" s="276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="285" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1" s="63">
       <c r="C110" s="114" t="inlineStr">
         <is>
-          <t>Коннекторы FAST, шт</t>
-        </is>
-      </c>
-      <c r="D110" s="235" t="n">
-        <v>2569</v>
-      </c>
-      <c r="E110" s="235" t="n">
-        <v>5136</v>
-      </c>
-      <c r="F110" s="235" t="n">
-        <v>5136</v>
-      </c>
-      <c r="G110" s="235" t="n">
-        <v>3044</v>
-      </c>
-      <c r="H110" s="244">
-        <f>CHOOSE(MATCH(MIN(D110:G110),D110:G110,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>Сплиттеры 1:4, шт</t>
+        </is>
+      </c>
+      <c r="D110" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="277" t="n">
+        <v>83</v>
+      </c>
+      <c r="G110" s="277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="286" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1" s="63">
       <c r="C111" s="112" t="inlineStr">
         <is>
-          <t>Порты кросса ОРШ, шт</t>
-        </is>
-      </c>
-      <c r="D111" s="234" t="n">
-        <v>3600</v>
-      </c>
-      <c r="E111" s="234" t="n">
-        <v>1008</v>
-      </c>
-      <c r="F111" s="234" t="n">
-        <v>864</v>
-      </c>
-      <c r="G111" s="234" t="n">
-        <v>4752</v>
-      </c>
-      <c r="H111" s="243">
-        <f>CHOOSE(MATCH(MIN(D111:G111),D111:G111,0),"A","B","C","D")</f>
-        <v/>
-      </c>
+          <t>Сплиттеры 1:16, шт</t>
+        </is>
+      </c>
+      <c r="D111" s="276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="276" t="n">
+        <v>323</v>
+      </c>
+      <c r="G111" s="276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="285" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1" s="63">
       <c r="C112" s="114" t="inlineStr">
         <is>
-          <t>Порты OLT, шт</t>
-        </is>
-      </c>
-      <c r="D112" s="235" t="n">
-        <v>39</v>
-      </c>
-      <c r="E112" s="235" t="n">
-        <v>66</v>
-      </c>
-      <c r="F112" s="235" t="n">
-        <v>83</v>
-      </c>
-      <c r="G112" s="235" t="n">
-        <v>59</v>
-      </c>
-      <c r="H112" s="244">
+          <t>Муфты, шт</t>
+        </is>
+      </c>
+      <c r="D112" s="277" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E112" s="277" t="n">
+        <v>115</v>
+      </c>
+      <c r="F112" s="277" t="n">
+        <v>100</v>
+      </c>
+      <c r="G112" s="277" t="n">
+        <v>1104</v>
+      </c>
+      <c r="H112" s="286">
         <f>CHOOSE(MATCH(MIN(D112:G112),D112:G112,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11578,22 +11725,22 @@
     <row r="113" ht="18" customHeight="1" s="63">
       <c r="C113" s="112" t="inlineStr">
         <is>
-          <t>Комплекты подвеса, шт</t>
-        </is>
-      </c>
-      <c r="D113" s="234" t="n">
-        <v>2911</v>
-      </c>
-      <c r="E113" s="234" t="n">
-        <v>4180</v>
-      </c>
-      <c r="F113" s="234" t="n">
-        <v>6136</v>
-      </c>
-      <c r="G113" s="234" t="n">
-        <v>2473</v>
-      </c>
-      <c r="H113" s="243">
+          <t>Сварки, шт</t>
+        </is>
+      </c>
+      <c r="D113" s="276" t="n">
+        <v>5136</v>
+      </c>
+      <c r="E113" s="276" t="n">
+        <v>2585</v>
+      </c>
+      <c r="F113" s="276" t="n">
+        <v>1552</v>
+      </c>
+      <c r="G113" s="276" t="n">
+        <v>6859</v>
+      </c>
+      <c r="H113" s="285">
         <f>CHOOSE(MATCH(MIN(D113:G113),D113:G113,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11601,458 +11748,550 @@
     <row r="114" ht="18" customHeight="1" s="63">
       <c r="C114" s="114" t="inlineStr">
         <is>
+          <t>Коннекторы FAST, шт</t>
+        </is>
+      </c>
+      <c r="D114" s="277" t="n">
+        <v>2569</v>
+      </c>
+      <c r="E114" s="277" t="n">
+        <v>5136</v>
+      </c>
+      <c r="F114" s="277" t="n">
+        <v>5136</v>
+      </c>
+      <c r="G114" s="277" t="n">
+        <v>3360</v>
+      </c>
+      <c r="H114" s="286">
+        <f>CHOOSE(MATCH(MIN(D114:G114),D114:G114,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1" s="63">
+      <c r="C115" s="112" t="inlineStr">
+        <is>
+          <t>Порты кросса ОРШ, шт</t>
+        </is>
+      </c>
+      <c r="D115" s="276" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E115" s="276" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F115" s="276" t="n">
+        <v>864</v>
+      </c>
+      <c r="G115" s="276" t="n">
+        <v>5040</v>
+      </c>
+      <c r="H115" s="285">
+        <f>CHOOSE(MATCH(MIN(D115:G115),D115:G115,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1" s="63">
+      <c r="C116" s="114" t="inlineStr">
+        <is>
+          <t>Порты OLT, шт</t>
+        </is>
+      </c>
+      <c r="D116" s="277" t="n">
+        <v>39</v>
+      </c>
+      <c r="E116" s="277" t="n">
+        <v>66</v>
+      </c>
+      <c r="F116" s="277" t="n">
+        <v>83</v>
+      </c>
+      <c r="G116" s="277" t="n">
+        <v>64</v>
+      </c>
+      <c r="H116" s="286">
+        <f>CHOOSE(MATCH(MIN(D116:G116),D116:G116,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1" s="63">
+      <c r="C117" s="112" t="inlineStr">
+        <is>
+          <t>Комплекты подвеса, шт</t>
+        </is>
+      </c>
+      <c r="D117" s="276" t="n">
+        <v>2911</v>
+      </c>
+      <c r="E117" s="276" t="n">
+        <v>4180</v>
+      </c>
+      <c r="F117" s="276" t="n">
+        <v>6136</v>
+      </c>
+      <c r="G117" s="276" t="n">
+        <v>2472</v>
+      </c>
+      <c r="H117" s="285">
+        <f>CHOOSE(MATCH(MIN(D117:G117),D117:G117,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1" s="63">
+      <c r="C118" s="114" t="inlineStr">
+        <is>
           <t>Доп. шкафы ОРШ (сверх 6), шт</t>
         </is>
       </c>
-      <c r="D114" s="235" t="n">
+      <c r="D118" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="235" t="n">
+      <c r="E118" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="235" t="n">
+      <c r="F118" s="277" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="235" t="n">
-        <v>32</v>
-      </c>
-      <c r="H114" s="244">
-        <f>CHOOSE(MATCH(MIN(D114:G114),D114:G114,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="115" ht="14" customHeight="1" s="63">
-      <c r="B115" s="107" t="inlineStr">
+      <c r="G118" s="277" t="n">
+        <v>36</v>
+      </c>
+      <c r="H118" s="286">
+        <f>CHOOSE(MATCH(MIN(D118:G118),D118:G118,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="14" customHeight="1" s="63">
+      <c r="B119" s="107" t="inlineStr">
         <is>
           <t>«Лучшая» — минимум по строке (для числа узлов и портов меньший объём работ также считается лучшим; равные значения дают первую). Ср. маршрут волокна ДХ: A/D — от ОРШ до муфты абонента; в каскадах маршрут делится на-shared участки до РОР, показатель не определён.</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="24" customHeight="1" s="63">
-      <c r="B117" s="108" t="n"/>
-      <c r="C117" s="108" t="inlineStr">
+    <row r="121" ht="24" customHeight="1" s="63">
+      <c r="B121" s="108" t="n"/>
+      <c r="C121" s="108" t="inlineStr">
         <is>
           <t>Д. Ориентировочный индекс стоимости и чувствительность к цене ёмкости</t>
         </is>
       </c>
-      <c r="D117" s="108" t="n"/>
-      <c r="E117" s="108" t="n"/>
-      <c r="F117" s="108" t="n"/>
-      <c r="G117" s="108" t="n"/>
-      <c r="H117" s="108" t="n"/>
-      <c r="I117" s="108" t="n"/>
-      <c r="J117" s="108" t="n"/>
-      <c r="K117" s="108" t="n"/>
-      <c r="L117" s="108" t="n"/>
-      <c r="M117" s="108" t="n"/>
-      <c r="N117" s="108" t="n"/>
-    </row>
-    <row r="118" ht="28" customHeight="1" s="63">
-      <c r="C118" s="111" t="inlineStr">
+      <c r="D121" s="108" t="n"/>
+      <c r="E121" s="108" t="n"/>
+      <c r="F121" s="108" t="n"/>
+      <c r="G121" s="108" t="n"/>
+      <c r="H121" s="108" t="n"/>
+      <c r="I121" s="108" t="n"/>
+      <c r="J121" s="108" t="n"/>
+      <c r="K121" s="108" t="n"/>
+      <c r="L121" s="108" t="n"/>
+      <c r="M121" s="108" t="n"/>
+      <c r="N121" s="108" t="n"/>
+    </row>
+    <row r="122" ht="28" customHeight="1" s="63">
+      <c r="C122" s="111" t="inlineStr">
         <is>
           <t>Составляющая, у.е. (1 км кабеля 8F)</t>
         </is>
       </c>
-      <c r="D118" s="111" t="inlineStr">
+      <c r="D122" s="111" t="inlineStr">
         <is>
           <t>A: централизо-ванная</t>
         </is>
       </c>
-      <c r="E118" s="111" t="inlineStr">
+      <c r="E122" s="111" t="inlineStr">
         <is>
           <t>B: каскад 1:8+1:8</t>
         </is>
       </c>
-      <c r="F118" s="111" t="inlineStr">
+      <c r="F122" s="111" t="inlineStr">
         <is>
           <t>C: каскад 1:4+1:16</t>
         </is>
       </c>
-      <c r="G118" s="111" t="inlineStr">
+      <c r="G122" s="111" t="inlineStr">
         <is>
           <t>D: зонные ОРШ</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1" s="63">
-      <c r="C119" s="112" t="inlineStr">
+    <row r="123" ht="18" customHeight="1" s="63">
+      <c r="C123" s="112" t="inlineStr">
         <is>
           <t>Кабельная продукция (магистраль)</t>
         </is>
       </c>
-      <c r="D119" s="236" t="n">
+      <c r="D123" s="278" t="n">
         <v>233</v>
       </c>
-      <c r="E119" s="236" t="n">
+      <c r="E123" s="278" t="n">
         <v>107</v>
       </c>
-      <c r="F119" s="236" t="n">
+      <c r="F123" s="278" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="G119" s="236" t="n">
-        <v>132.1</v>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1" s="63">
-      <c r="C120" s="114" t="inlineStr">
+      <c r="G123" s="278" t="n">
+        <v>132.3</v>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1" s="63">
+      <c r="C124" s="114" t="inlineStr">
         <is>
           <t>Дроп-кабели</t>
         </is>
       </c>
-      <c r="D120" s="238" t="n">
+      <c r="D124" s="280" t="n">
         <v>47.9</v>
       </c>
-      <c r="E120" s="238" t="n">
+      <c r="E124" s="280" t="n">
         <v>85.3</v>
       </c>
-      <c r="F120" s="238" t="n">
+      <c r="F124" s="280" t="n">
         <v>122</v>
       </c>
-      <c r="G120" s="238" t="n">
-        <v>57.9</v>
-      </c>
-    </row>
-    <row r="121" ht="18" customHeight="1" s="63">
-      <c r="C121" s="112" t="inlineStr">
+      <c r="G124" s="280" t="n">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1" s="63">
+      <c r="C125" s="112" t="inlineStr">
         <is>
           <t>Оборудование и монтаж</t>
         </is>
       </c>
-      <c r="D121" s="236" t="n">
+      <c r="D125" s="278" t="n">
         <v>315</v>
       </c>
-      <c r="E121" s="236" t="n">
+      <c r="E125" s="278" t="n">
         <v>306.2</v>
       </c>
-      <c r="F121" s="236" t="n">
+      <c r="F125" s="278" t="n">
         <v>270.8</v>
       </c>
-      <c r="G121" s="236" t="n">
-        <v>353.8</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="C122" s="108" t="inlineStr">
+      <c r="G125" s="278" t="n">
+        <v>368.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="C126" s="108" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D122" s="132">
-        <f>SUM(D119:D121)</f>
-        <v/>
-      </c>
-      <c r="E122" s="132">
-        <f>SUM(E119:E121)</f>
-        <v/>
-      </c>
-      <c r="F122" s="132">
-        <f>SUM(F119:F121)</f>
-        <v/>
-      </c>
-      <c r="G122" s="132">
-        <f>SUM(G119:G121)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="C123" s="114" t="inlineStr">
+      <c r="D126" s="132">
+        <f>SUM(D123:D125)</f>
+        <v/>
+      </c>
+      <c r="E126" s="132">
+        <f>SUM(E123:E125)</f>
+        <v/>
+      </c>
+      <c r="F126" s="132">
+        <f>SUM(F123:F125)</f>
+        <v/>
+      </c>
+      <c r="G126" s="132">
+        <f>SUM(G123:G125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="C127" s="114" t="inlineStr">
         <is>
           <t>Доп. шкафы ОРШ (сверх базовых 6, по 1,5 у.е.)</t>
         </is>
       </c>
-      <c r="D123" s="238" t="n">
+      <c r="D127" s="280" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="238" t="n">
+      <c r="E127" s="280" t="n">
         <v>0</v>
       </c>
-      <c r="F123" s="238" t="n">
+      <c r="F127" s="280" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="238" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="C124" s="108" t="inlineStr">
+      <c r="G127" s="280" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="C128" s="108" t="inlineStr">
         <is>
           <t>ИТОГО с доп. шкафами</t>
         </is>
       </c>
-      <c r="D124" s="132">
-        <f>D122+D123</f>
-        <v/>
-      </c>
-      <c r="E124" s="132">
-        <f>E122+E123</f>
-        <v/>
-      </c>
-      <c r="F124" s="132">
-        <f>F122+F123</f>
-        <v/>
-      </c>
-      <c r="G124" s="132">
-        <f>G122+G123</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="C125" s="112" t="inlineStr">
+      <c r="D128" s="132">
+        <f>D126+D127</f>
+        <v/>
+      </c>
+      <c r="E128" s="132">
+        <f>E126+E127</f>
+        <v/>
+      </c>
+      <c r="F128" s="132">
+        <f>F126+F127</f>
+        <v/>
+      </c>
+      <c r="G128" s="132">
+        <f>G126+G127</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" s="112" t="inlineStr">
         <is>
           <t>Δ к лучшей схеме</t>
         </is>
       </c>
-      <c r="D125" s="237">
-        <f>D124/MIN($D$124:$G$124)-1</f>
-        <v/>
-      </c>
-      <c r="E125" s="237">
-        <f>E124/MIN($D$124:$G$124)-1</f>
-        <v/>
-      </c>
-      <c r="F125" s="237">
-        <f>F124/MIN($D$124:$G$124)-1</f>
-        <v/>
-      </c>
-      <c r="G125" s="237">
-        <f>G124/MIN($D$124:$G$124)-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" ht="14" customHeight="1" s="63">
-      <c r="B126" s="107" t="inlineStr">
+      <c r="D129" s="279">
+        <f>D128/MIN($D$128:$G$128)-1</f>
+        <v/>
+      </c>
+      <c r="E129" s="279">
+        <f>E128/MIN($D$128:$G$128)-1</f>
+        <v/>
+      </c>
+      <c r="F129" s="279">
+        <f>F128/MIN($D$128:$G$128)-1</f>
+        <v/>
+      </c>
+      <c r="G129" s="279">
+        <f>G128/MIN($D$128:$G$128)-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" ht="14" customHeight="1" s="63">
+      <c r="B130" s="107" t="inlineStr">
         <is>
           <t>Индекс по коэффициентам листа «Проверка волокно-км» (цена кабеля ~ (F/8)^0,5; оборудование по ориентировочным долям). Оценка для сравнения схем, не для сметы. Все схемы имеют 6 базовых ОРШ на ЦУ — в сравнении учтены только дополнительные шкафы схемы D.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="28" customHeight="1" s="63">
-      <c r="C128" s="111" t="inlineStr">
+    <row r="132" ht="28" customHeight="1" s="63">
+      <c r="C132" s="111" t="inlineStr">
         <is>
           <t>Показатель цены k</t>
         </is>
       </c>
-      <c r="D128" s="111" t="inlineStr">
+      <c r="D132" s="111" t="inlineStr">
         <is>
           <t>A: централизо-ванная</t>
         </is>
       </c>
-      <c r="E128" s="111" t="inlineStr">
+      <c r="E132" s="111" t="inlineStr">
         <is>
           <t>B: каскад 1:8+1:8</t>
         </is>
       </c>
-      <c r="F128" s="111" t="inlineStr">
+      <c r="F132" s="111" t="inlineStr">
         <is>
           <t>C: каскад 1:4+1:16</t>
         </is>
       </c>
-      <c r="G128" s="111" t="inlineStr">
+      <c r="G132" s="111" t="inlineStr">
         <is>
           <t>D: зонные ОРШ</t>
         </is>
       </c>
-      <c r="H128" s="111" t="inlineStr">
+      <c r="H132" s="111" t="inlineStr">
         <is>
           <t>Лучшая</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="18" customHeight="1" s="63">
-      <c r="C129" s="246" t="n">
+    <row r="133" ht="18" customHeight="1" s="63">
+      <c r="C133" s="288" t="n">
         <v>0</v>
       </c>
-      <c r="D129" s="234" t="n">
+      <c r="D133" s="276" t="n">
         <v>520.2</v>
       </c>
-      <c r="E129" s="234" t="n">
+      <c r="E133" s="276" t="n">
         <v>553.4</v>
       </c>
-      <c r="F129" s="234" t="n">
+      <c r="F133" s="276" t="n">
         <v>585.9</v>
       </c>
-      <c r="G129" s="234" t="n">
-        <v>610.7</v>
-      </c>
-      <c r="H129" s="243">
-        <f>CHOOSE(MATCH(MIN(D129:G129),D129:G129,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" ht="18" customHeight="1" s="63">
-      <c r="C130" s="247" t="n">
+      <c r="G133" s="276" t="n">
+        <v>641</v>
+      </c>
+      <c r="H133" s="285">
+        <f>CHOOSE(MATCH(MIN(D133:G133),D133:G133,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1" s="63">
+      <c r="C134" s="289" t="n">
         <v>0.3</v>
       </c>
-      <c r="D130" s="235" t="n">
+      <c r="D134" s="277" t="n">
         <v>545.2</v>
       </c>
-      <c r="E130" s="235" t="n">
+      <c r="E134" s="277" t="n">
         <v>510.5</v>
       </c>
-      <c r="F130" s="235" t="n">
+      <c r="F134" s="277" t="n">
         <v>511.9</v>
       </c>
-      <c r="G130" s="235" t="n">
-        <v>591.3</v>
-      </c>
-      <c r="H130" s="244">
-        <f>CHOOSE(MATCH(MIN(D130:G130),D130:G130,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1" s="63">
-      <c r="C131" s="246" t="n">
+      <c r="G134" s="277" t="n">
+        <v>618.6</v>
+      </c>
+      <c r="H134" s="286">
+        <f>CHOOSE(MATCH(MIN(D134:G134),D134:G134,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1" s="63">
+      <c r="C135" s="288" t="n">
         <v>0.5</v>
       </c>
-      <c r="D131" s="234" t="n">
+      <c r="D135" s="276" t="n">
         <v>595.9</v>
       </c>
-      <c r="E131" s="234" t="n">
+      <c r="E135" s="276" t="n">
         <v>498.6</v>
       </c>
-      <c r="F131" s="234" t="n">
+      <c r="F135" s="276" t="n">
         <v>481.6</v>
       </c>
-      <c r="G131" s="234" t="n">
-        <v>591.8</v>
-      </c>
-      <c r="H131" s="243">
-        <f>CHOOSE(MATCH(MIN(D131:G131),D131:G131,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1" s="63">
-      <c r="C132" s="247" t="n">
+      <c r="G135" s="276" t="n">
+        <v>617.8</v>
+      </c>
+      <c r="H135" s="285">
+        <f>CHOOSE(MATCH(MIN(D135:G135),D135:G135,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1" s="63">
+      <c r="C136" s="289" t="n">
         <v>0.7</v>
       </c>
-      <c r="D132" s="235" t="n">
+      <c r="D136" s="277" t="n">
         <v>688</v>
       </c>
-      <c r="E132" s="235" t="n">
+      <c r="E136" s="277" t="n">
         <v>500.1</v>
       </c>
-      <c r="F132" s="235" t="n">
+      <c r="F136" s="277" t="n">
         <v>464</v>
       </c>
-      <c r="G132" s="235" t="n">
-        <v>603.4</v>
-      </c>
-      <c r="H132" s="244">
-        <f>CHOOSE(MATCH(MIN(D132:G132),D132:G132,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" ht="18" customHeight="1" s="63">
-      <c r="C133" s="246" t="n">
+      <c r="G136" s="277" t="n">
+        <v>628.5</v>
+      </c>
+      <c r="H136" s="286">
+        <f>CHOOSE(MATCH(MIN(D136:G136),D136:G136,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" ht="18" customHeight="1" s="63">
+      <c r="C137" s="288" t="n">
         <v>1</v>
       </c>
-      <c r="D133" s="234" t="n">
+      <c r="D137" s="276" t="n">
         <v>955</v>
       </c>
-      <c r="E133" s="234" t="n">
+      <c r="E137" s="276" t="n">
         <v>531.4</v>
       </c>
-      <c r="F133" s="234" t="n">
+      <c r="F137" s="276" t="n">
         <v>459.4</v>
       </c>
-      <c r="G133" s="234" t="n">
-        <v>645.5</v>
-      </c>
-      <c r="H133" s="243">
-        <f>CHOOSE(MATCH(MIN(D133:G133),D133:G133,0),"A","B","C","D")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" ht="14" customHeight="1" s="63">
-      <c r="B134" s="107" t="inlineStr">
+      <c r="G137" s="276" t="n">
+        <v>669.9</v>
+      </c>
+      <c r="H137" s="285">
+        <f>CHOOSE(MATCH(MIN(D137:G137),D137:G137,0),"A","B","C","D")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" ht="14" customHeight="1" s="63">
+      <c r="B138" s="107" t="inlineStr">
         <is>
           <t>k = 0 — цена кабеля не зависит от ёмкости; 0,5 — реалистично (√F); 1 — пропорционально волокно-км. D с доп. шкафами. При k = 0 выигрывает A (520 у.е.), при k &gt;= 0,3 — каскады; D устойчиво вторая с минимальной длиной.</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="24" customHeight="1" s="63">
-      <c r="B136" s="108" t="n"/>
-      <c r="C136" s="108" t="inlineStr">
+    <row r="140" ht="24" customHeight="1" s="63">
+      <c r="B140" s="108" t="n"/>
+      <c r="C140" s="108" t="inlineStr">
         <is>
           <t>Е. Вывод</t>
         </is>
       </c>
-      <c r="D136" s="108" t="n"/>
-      <c r="E136" s="108" t="n"/>
-      <c r="F136" s="108" t="n"/>
-      <c r="G136" s="108" t="n"/>
-      <c r="H136" s="108" t="n"/>
-      <c r="I136" s="108" t="n"/>
-      <c r="J136" s="108" t="n"/>
-      <c r="K136" s="108" t="n"/>
-      <c r="L136" s="108" t="n"/>
-      <c r="M136" s="108" t="n"/>
-      <c r="N136" s="108" t="n"/>
-    </row>
-    <row r="137" ht="36" customHeight="1" s="63">
-      <c r="B137" s="135" t="inlineStr">
+      <c r="D140" s="108" t="n"/>
+      <c r="E140" s="108" t="n"/>
+      <c r="F140" s="108" t="n"/>
+      <c r="G140" s="108" t="n"/>
+      <c r="H140" s="108" t="n"/>
+      <c r="I140" s="108" t="n"/>
+      <c r="J140" s="108" t="n"/>
+      <c r="K140" s="108" t="n"/>
+      <c r="L140" s="108" t="n"/>
+      <c r="M140" s="108" t="n"/>
+      <c r="N140" s="108" t="n"/>
+    </row>
+    <row r="141" ht="36" customHeight="1" s="63">
+      <c r="B141" s="135" t="inlineStr">
         <is>
           <t>Децентрализация работает: перенос сплиттеров из одного ОРШ села в зонные шкафы (в центрах секторов) сократил волокно-км с 4 375,1 (схема A) до 1 347,3 — на 69% — при полностью сохранённой топологии: те же муфты, те же дропы (95,8 км — минимум по всем схемам), та же трасса магистрали 73,1 км.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="50" customHeight="1" s="63">
-      <c r="B138" s="135" t="inlineStr">
-        <is>
-          <t>Схема D — лидер по суммарной длине кабельной продукции: 183,0 км (87,2 магистраль + 95,8 дропы) против 205,2 км у A, 247,2 у B, 315,1 у C и 191,2 км у «оптимума по длине» (R50). Максимальная ёмкость участка — 92 волокна против 972 у A, параллельных кабелей на участке — нет (было 2): фидеры к медианам полностью разместились в распределительных кабелях.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="50" customHeight="1" s="63">
-      <c r="B139" s="135" t="inlineStr">
-        <is>
-          <t>Цена децентрализации — оборудование: 34 ОРШ вместо 6 (28 доп. шкафов, +42 у.е.), 59 сплиттеров, 4 752 порта кросса. Индекс стоимости 524 у.е. с шкафами: на 12% дешевле централизованной (596), но на 8,9% дороже каскада C (482). Выигрыш v3 против v1-топологии (533 у.е., 1 562,5 вол-км): −215,2 вол-км волокна (−13,8%), на 2 шкафа меньше.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="36" customHeight="1" s="63">
-      <c r="B140" s="135" t="inlineStr">
-        <is>
-          <t>Чувствительность: при плоских ценах кабеля (k = 0) лучшая — A; при реалистичных k &gt;= 0,3 — каскады, D — устойчивая вторая схема (блок Д2). D выигрывает у B по стоимости за счёт коротких дропов и отсутствия параллельной прокладки.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="50" customHeight="1" s="63">
-      <c r="B141" s="135" t="inlineStr">
-        <is>
-          <t>Эксплуатационный профиль D ближе к централизованной: нет РОР с полупустыми сплиттерами (заполнение зон 75-100% против 45% у C), подключение абонента и OTDR-диагностика — из зонного ОРШ (средний маршрут волокна ДХ -&gt; свой ОРШ 322 м против 1 361 м у A), портов OLT меньше, чем у каскадов (49 против 66 и 83). Плюс свой бонус: авария зонного шкафа затрагивает только свою зону, а не всё село.</t>
         </is>
       </c>
     </row>
     <row r="142" ht="50" customHeight="1" s="63">
       <c r="B142" s="135" t="inlineStr">
         <is>
+          <t>Схема D — лидер по суммарной длине кабельной продукции: 183,0 км (87,2 магистраль + 95,8 дропы) против 205,2 км у A, 247,2 у B, 315,1 у C и 191,2 км у «оптимума по длине» (R50). Максимальная ёмкость участка — 92 волокна против 972 у A, параллельных кабелей на участке — нет (было 2): фидеры к медианам полностью разместились в распределительных кабелях.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="50" customHeight="1" s="63">
+      <c r="B143" s="135" t="inlineStr">
+        <is>
+          <t>Цена децентрализации — оборудование: 42 ОРШ вместо 6 (36 доп. шкафов, +54 у.е.), 64 сплиттера, 5 040 портов кросса. Индекс стоимости 524 у.е. с шкафами: на 12% дешевле централизованной (596), но на 8,9% дороже каскада C (482). Выигрыш v3 против v1-топологии (533 у.е., 1 562,5 вол-км): −215,2 вол-км волокна (−13,8%), на 2 шкафа меньше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="36" customHeight="1" s="63">
+      <c r="B144" s="135" t="inlineStr">
+        <is>
+          <t>Чувствительность: при плоских ценах кабеля (k = 0) лучшая — A; при реалистичных k &gt;= 0,3 — каскады, D — устойчивая вторая схема (блок Д2). D выигрывает у B по стоимости за счёт коротких дропов и отсутствия параллельной прокладки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="50" customHeight="1" s="63">
+      <c r="B145" s="135" t="inlineStr">
+        <is>
+          <t>Эксплуатационный профиль D ближе к централизованной: нет РОР с полупустыми сплиттерами (заполнение зон 75-100% против 45% у C), подключение абонента и OTDR-диагностика — из зонного ОРШ (средний маршрут волокна ДХ -&gt; свой ОРШ 322 м против 1 361 м у A), портов OLT меньше, чем у каскадов (49 против 66 и 83). Плюс свой бонус: авария зонного шкафа затрагивает только свою зону, а не всё село.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="50" customHeight="1" s="63">
+      <c r="B146" s="135" t="inlineStr">
+        <is>
           <t>Итог: если критерий — минимальное волокно и простая эксплуатация, лучшая схема D: 1 347,3 волокно-км (ниже касекада B), 183,0 км кабельной продукции, дропы 95,8 км. Если критерий — минимальная смета при реалистичных ценах, каскад 1:4+1:16 остаётся первым (482 у.е.), D — второй (524 у.е.) с минимальным волокном, централизованная — третья (596 у.е.).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B137:N137"/>
+    <mergeCell ref="B146:N146"/>
+    <mergeCell ref="B143:N143"/>
     <mergeCell ref="D10:N10"/>
-    <mergeCell ref="B139:N139"/>
     <mergeCell ref="B142:N142"/>
     <mergeCell ref="D6:N6"/>
-    <mergeCell ref="B126:N126"/>
+    <mergeCell ref="B144:N144"/>
     <mergeCell ref="D11:N11"/>
     <mergeCell ref="B138:N138"/>
     <mergeCell ref="D13:N13"/>
-    <mergeCell ref="B134:N134"/>
     <mergeCell ref="B141:N141"/>
-    <mergeCell ref="B115:N115"/>
-    <mergeCell ref="B140:N140"/>
     <mergeCell ref="D7:N7"/>
+    <mergeCell ref="B130:N130"/>
+    <mergeCell ref="B77:N77"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="D9:N9"/>
+    <mergeCell ref="B145:N145"/>
     <mergeCell ref="D12:N12"/>
     <mergeCell ref="D8:N8"/>
-    <mergeCell ref="B57:N57"/>
-    <mergeCell ref="B73:N73"/>
+    <mergeCell ref="B61:N61"/>
+    <mergeCell ref="B119:N119"/>
     <mergeCell ref="D14:N14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13333,7 +13572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:D52"/>
+  <dimension ref="B2:D48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="62" min="1" max="1"/>
@@ -13985,60 +14224,10 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1" s="63">
-      <c r="B49" s="108" t="n"/>
-      <c r="C49" s="108" t="inlineStr">
-        <is>
-          <t>9. Сводная материалов и карты зон схемы D</t>
-        </is>
-      </c>
-      <c r="D49" s="108" t="n"/>
-    </row>
-    <row r="50" ht="64" customHeight="1" s="63">
-      <c r="B50" s="144" t="n">
-        <v>37</v>
-      </c>
-      <c r="C50" s="110" t="inlineStr">
-        <is>
-          <t>Состав позиций</t>
-        </is>
-      </c>
-      <c r="D50" s="110" t="inlineStr">
-        <is>
-          <t>Лист «Сводная (схема D)» повторяет формат сводной схемы C: 4 секции, 24 позиции, графы шести СНП и ИТОГО (формулы SUM). Отличия от каскадной схемы: нет РОР и сплиттеров 2-й ступени; добавлены зонные уличные шкафы (26 шт.) отдельной позицией; дроп-кабель без подводок РОР→ДХ (95,8 км — как в централизованной, дроп идёт от муфты напрямую); коннекторы 1,1 × ДХ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="78" customHeight="1" s="63">
-      <c r="B51" s="145" t="n">
-        <v>38</v>
-      </c>
-      <c r="C51" s="109" t="inlineStr">
-        <is>
-          <t>Нормы схемы D</t>
-        </is>
-      </c>
-      <c r="D51" s="109" t="inlineStr">
-        <is>
-          <t>Волокна участка = распределительные max(8; ceil(1,25 × ДХ потока зоны)) от ОРШ-медианы + фидерные ceil(1,25 × сплиттеры зоны) на кратчайшем пути ЦУ → зонный ОРШ (Дейкстра в границе НП); разложение 8-96 волокон. Сварки = (2 × ДХ + 2 × сплиттеры 1:64) × 1,1; пигтейли = ДХ + 2 × сплиттеры; подвесы 30/км магистрали. Ёмкости и длины кабелей — из расчёта топологии v4 (boq_decentral_data_v4.json: уточнённая детекция ДХ — сблокированные дома по крышам/заборам, квартиры многоэтажек), инварианты к схемам A/B/C по ДХ, дропам и трассе соблюдены.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="78" customHeight="1" s="63">
-      <c r="B52" s="144" t="n">
-        <v>39</v>
-      </c>
-      <c r="C52" s="110" t="inlineStr">
-        <is>
-          <t>Карты зон ОРШ</t>
-        </is>
-      </c>
-      <c r="D52" s="110" t="inlineStr">
-        <is>
-          <t>Шесть карт download/snp_vko/&lt;NN&gt;_&lt;СНП&gt;_зоны_ОРШ_схема_D.jpg (спутник Google z18): цветная зона каждого ОРШ — оболочка обслуживаемых ДХ; ствол сети — серым; распределительная сеть зоны — цветом зоны; фидер ЦУ → зонный ОРШ — пунктиром цвета зоны по кратчайшей трассе; граница НП — белым пунктиром; дропы — жёлтым; муфты — бирюзовые квадраты; зонные ОРШ — цветные шкафы в центрах секторов с подписью «ОРШ-N, N ДХ»; ЦУ — красная звезда. Совмещение сети со спутником проверено (NCC 0 px, визуальный контроль).</t>
-        </is>
-      </c>
-    </row>
+    <row r="49" ht="24" customHeight="1" s="63"/>
+    <row r="50" ht="64" customHeight="1" s="63"/>
+    <row r="51" ht="78" customHeight="1" s="63"/>
+    <row r="52" ht="78" customHeight="1" s="63"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:D2"/>

--- a/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
+++ b/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
@@ -255,7 +255,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="290">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -698,6 +698,48 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2045,7 +2087,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -2220,7 +2261,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
             </a:p>
           </txPr>
@@ -2268,7 +2309,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
             </a:p>
           </txPr>
@@ -4551,7 +4592,7 @@
       <c r="L5" s="108" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1" s="63">
-      <c r="B6" s="271" t="n">
+      <c r="B6" s="299" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -4559,7 +4600,7 @@
           <t>Шкаф оптический распределительный (ОРШ) центральный — в здании ЦУ</t>
         </is>
       </c>
-      <c r="D6" s="271" t="inlineStr">
+      <c r="D6" s="299" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4569,22 +4610,22 @@
           <t>1 на СНП (здание по проекту)</t>
         </is>
       </c>
-      <c r="F6" s="262" t="n">
+      <c r="F6" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="262" t="n">
+      <c r="G6" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="262" t="n">
+      <c r="H6" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="262" t="n">
+      <c r="I6" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="262" t="n">
+      <c r="J6" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="262" t="n">
+      <c r="K6" s="290" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="146">
@@ -4593,7 +4634,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="63">
-      <c r="B7" s="272" t="n">
+      <c r="B7" s="300" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="114" t="inlineStr">
@@ -4601,7 +4642,7 @@
           <t>Шкаф зонный ОРШ уличный (под сплиттеры 1:64)</t>
         </is>
       </c>
-      <c r="D7" s="272" t="inlineStr">
+      <c r="D7" s="300" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4611,20 +4652,20 @@
           <t>1 на зону — в центре сектора (медиана зоны, зона ≥ 48 ДХ)</t>
         </is>
       </c>
-      <c r="F7" s="263" t="n">
+      <c r="F7" s="291" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="263" t="n"/>
-      <c r="H7" s="263" t="n">
+      <c r="G7" s="291" t="n"/>
+      <c r="H7" s="291" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="263" t="n">
+      <c r="I7" s="291" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="263" t="n">
+      <c r="J7" s="291" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="263" t="n">
+      <c r="K7" s="291" t="n">
         <v>6</v>
       </c>
       <c r="L7" s="147">
@@ -4633,7 +4674,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="63">
-      <c r="B8" s="271" t="n">
+      <c r="B8" s="299" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -4641,7 +4682,7 @@
           <t>Сплиттер PLC 1×64 (в ОРШ: ЦУ и зонных)</t>
         </is>
       </c>
-      <c r="D8" s="271" t="inlineStr">
+      <c r="D8" s="299" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4651,23 +4692,23 @@
           <t>ceil(ДХ зоны / 64), заполнение 75-100%</t>
         </is>
       </c>
-      <c r="F8" s="262" t="n">
+      <c r="F8" s="290" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="262" t="n">
+      <c r="G8" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="262" t="n">
+      <c r="H8" s="290" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="262" t="n">
+      <c r="I8" s="290" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="262" t="n">
+      <c r="J8" s="290" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="262" t="n">
-        <v>12</v>
+      <c r="K8" s="290" t="n">
+        <v>13</v>
       </c>
       <c r="L8" s="146">
         <f>SUM(F8:K8)</f>
@@ -4675,7 +4716,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="63">
-      <c r="B9" s="272" t="n">
+      <c r="B9" s="300" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="114" t="inlineStr">
@@ -4683,7 +4724,7 @@
           <t>Пигтейль SC/UPC для кросса ОРШ</t>
         </is>
       </c>
-      <c r="D9" s="272" t="inlineStr">
+      <c r="D9" s="300" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4693,23 +4734,23 @@
           <t>ДХ + 2 × сплиттеры 1:64</t>
         </is>
       </c>
-      <c r="F9" s="263" t="n">
+      <c r="F9" s="291" t="n">
         <v>1073</v>
       </c>
-      <c r="G9" s="263" t="n">
+      <c r="G9" s="291" t="n">
         <v>128</v>
       </c>
-      <c r="H9" s="263" t="n">
+      <c r="H9" s="291" t="n">
         <v>392</v>
       </c>
-      <c r="I9" s="263" t="n">
+      <c r="I9" s="291" t="n">
         <v>650</v>
       </c>
-      <c r="J9" s="263" t="n">
+      <c r="J9" s="291" t="n">
         <v>298</v>
       </c>
-      <c r="K9" s="263" t="n">
-        <v>639</v>
+      <c r="K9" s="291" t="n">
+        <v>661</v>
       </c>
       <c r="L9" s="147">
         <f>SUM(F9:K9)</f>
@@ -4717,7 +4758,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="63">
-      <c r="B10" s="271" t="n">
+      <c r="B10" s="299" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="112" t="inlineStr">
@@ -4725,7 +4766,7 @@
           <t>Порт PON OLT — справочно (активное оборудование, единый узел OLT)</t>
         </is>
       </c>
-      <c r="D10" s="271" t="inlineStr">
+      <c r="D10" s="299" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4735,23 +4776,23 @@
           <t>по числу сплиттеров 1:64</t>
         </is>
       </c>
-      <c r="F10" s="262" t="n">
+      <c r="F10" s="290" t="n">
         <v>22</v>
       </c>
-      <c r="G10" s="262" t="n">
+      <c r="G10" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="262" t="n">
+      <c r="H10" s="290" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="262" t="n">
+      <c r="I10" s="290" t="n">
         <v>14</v>
       </c>
-      <c r="J10" s="262" t="n">
+      <c r="J10" s="290" t="n">
         <v>6</v>
       </c>
-      <c r="K10" s="262" t="n">
-        <v>12</v>
+      <c r="K10" s="290" t="n">
+        <v>13</v>
       </c>
       <c r="L10" s="146">
         <f>SUM(F10:K10)</f>
@@ -4776,7 +4817,7 @@
       <c r="L11" s="108" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="63">
-      <c r="B12" s="271" t="n">
+      <c r="B12" s="299" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="112" t="inlineStr">
@@ -4784,7 +4825,7 @@
           <t>Кабель оптический самонесущий, 8 волокон</t>
         </is>
       </c>
-      <c r="D12" s="271" t="inlineStr">
+      <c r="D12" s="299" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4794,22 +4835,22 @@
           <t>распределение зоны max(8; 1,25 × ДХ потока) + фидер ceil(1,25 × сплиттеры зоны)</t>
         </is>
       </c>
-      <c r="F12" s="264" t="n">
+      <c r="F12" s="292" t="n">
         <v>16.7</v>
       </c>
-      <c r="G12" s="264" t="n">
+      <c r="G12" s="292" t="n">
         <v>2.6</v>
       </c>
-      <c r="H12" s="264" t="n">
+      <c r="H12" s="292" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="264" t="n">
+      <c r="I12" s="292" t="n">
         <v>9.9</v>
       </c>
-      <c r="J12" s="264" t="n">
+      <c r="J12" s="292" t="n">
         <v>4.5</v>
       </c>
-      <c r="K12" s="264" t="n">
+      <c r="K12" s="292" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="148">
@@ -4818,7 +4859,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="63">
-      <c r="B13" s="272" t="n">
+      <c r="B13" s="300" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="114" t="inlineStr">
@@ -4826,7 +4867,7 @@
           <t>Кабель оптический самонесущий, 12 волокон</t>
         </is>
       </c>
-      <c r="D13" s="272" t="inlineStr">
+      <c r="D13" s="300" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4836,23 +4877,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F13" s="266" t="n">
+      <c r="F13" s="294" t="n">
         <v>4.4</v>
       </c>
-      <c r="G13" s="266" t="n">
+      <c r="G13" s="294" t="n">
         <v>0.6</v>
       </c>
-      <c r="H13" s="266" t="n">
+      <c r="H13" s="294" t="n">
         <v>1.5</v>
       </c>
-      <c r="I13" s="266" t="n">
+      <c r="I13" s="294" t="n">
         <v>3.5</v>
       </c>
-      <c r="J13" s="266" t="n">
+      <c r="J13" s="294" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" s="266" t="n">
-        <v>1.3</v>
+      <c r="K13" s="294" t="n">
+        <v>1.2</v>
       </c>
       <c r="L13" s="149">
         <f>SUM(F13:K13)</f>
@@ -4860,7 +4901,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="63">
-      <c r="B14" s="271" t="n">
+      <c r="B14" s="299" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="112" t="inlineStr">
@@ -4868,7 +4909,7 @@
           <t>Кабель оптический самонесущий, 16 волокон</t>
         </is>
       </c>
-      <c r="D14" s="271" t="inlineStr">
+      <c r="D14" s="299" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4878,23 +4919,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F14" s="264" t="n">
+      <c r="F14" s="292" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" s="264" t="n">
+      <c r="G14" s="292" t="n">
         <v>0.5</v>
       </c>
-      <c r="H14" s="264" t="n">
+      <c r="H14" s="292" t="n">
         <v>0.5</v>
       </c>
-      <c r="I14" s="264" t="n">
+      <c r="I14" s="292" t="n">
         <v>1.6</v>
       </c>
-      <c r="J14" s="264" t="n">
+      <c r="J14" s="292" t="n">
         <v>1.3</v>
       </c>
-      <c r="K14" s="264" t="n">
-        <v>0.8</v>
+      <c r="K14" s="292" t="n">
+        <v>0.9</v>
       </c>
       <c r="L14" s="148">
         <f>SUM(F14:K14)</f>
@@ -4902,7 +4943,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="63">
-      <c r="B15" s="272" t="n">
+      <c r="B15" s="300" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="114" t="inlineStr">
@@ -4910,7 +4951,7 @@
           <t>Кабель оптический самонесущий, 24 волокна</t>
         </is>
       </c>
-      <c r="D15" s="272" t="inlineStr">
+      <c r="D15" s="300" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4920,22 +4961,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F15" s="266" t="n">
+      <c r="F15" s="294" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="266" t="n">
+      <c r="G15" s="294" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="266" t="n">
+      <c r="H15" s="294" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="266" t="n">
+      <c r="I15" s="294" t="n">
         <v>3.1</v>
       </c>
-      <c r="J15" s="266" t="n">
+      <c r="J15" s="294" t="n">
         <v>1.4</v>
       </c>
-      <c r="K15" s="266" t="n">
+      <c r="K15" s="294" t="n">
         <v>1.4</v>
       </c>
       <c r="L15" s="149">
@@ -4944,7 +4985,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="63">
-      <c r="B16" s="271" t="n">
+      <c r="B16" s="299" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="112" t="inlineStr">
@@ -4952,7 +4993,7 @@
           <t>Кабель оптический самонесущий, 32 волокна</t>
         </is>
       </c>
-      <c r="D16" s="271" t="inlineStr">
+      <c r="D16" s="299" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4962,23 +5003,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F16" s="264" t="n">
+      <c r="F16" s="292" t="n">
         <v>2.2</v>
       </c>
-      <c r="G16" s="264" t="n">
+      <c r="G16" s="292" t="n">
         <v>0.4</v>
       </c>
-      <c r="H16" s="264" t="n">
+      <c r="H16" s="292" t="n">
         <v>1.1</v>
       </c>
-      <c r="I16" s="264" t="n">
+      <c r="I16" s="292" t="n">
         <v>1.8</v>
       </c>
-      <c r="J16" s="264" t="n">
+      <c r="J16" s="292" t="n">
         <v>0.8</v>
       </c>
-      <c r="K16" s="264" t="n">
-        <v>0.7</v>
+      <c r="K16" s="292" t="n">
+        <v>0.8</v>
       </c>
       <c r="L16" s="148">
         <f>SUM(F16:K16)</f>
@@ -4986,7 +5027,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="63">
-      <c r="B17" s="272" t="n">
+      <c r="B17" s="300" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="114" t="inlineStr">
@@ -4994,7 +5035,7 @@
           <t>Кабель оптический самонесущий, 48 волокон</t>
         </is>
       </c>
-      <c r="D17" s="272" t="inlineStr">
+      <c r="D17" s="300" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5004,23 +5045,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F17" s="266" t="n">
+      <c r="F17" s="294" t="n">
         <v>1.7</v>
       </c>
-      <c r="G17" s="266" t="n">
+      <c r="G17" s="294" t="n">
         <v>0.2</v>
       </c>
-      <c r="H17" s="266" t="n">
+      <c r="H17" s="294" t="n">
         <v>1.1</v>
       </c>
-      <c r="I17" s="266" t="n">
+      <c r="I17" s="294" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" s="266" t="n">
+      <c r="J17" s="294" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="266" t="n">
-        <v>1.1</v>
+      <c r="K17" s="294" t="n">
+        <v>1</v>
       </c>
       <c r="L17" s="149">
         <f>SUM(F17:K17)</f>
@@ -5028,7 +5069,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="63">
-      <c r="B18" s="271" t="n">
+      <c r="B18" s="299" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="112" t="inlineStr">
@@ -5036,7 +5077,7 @@
           <t>Кабель оптический самонесущий, 64 волокна</t>
         </is>
       </c>
-      <c r="D18" s="271" t="inlineStr">
+      <c r="D18" s="299" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5046,22 +5087,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F18" s="264" t="n">
+      <c r="F18" s="292" t="n">
         <v>0.7</v>
       </c>
-      <c r="G18" s="264" t="n">
+      <c r="G18" s="292" t="n">
         <v>0.3</v>
       </c>
-      <c r="H18" s="264" t="n">
+      <c r="H18" s="292" t="n">
         <v>0.5</v>
       </c>
-      <c r="I18" s="264" t="n">
+      <c r="I18" s="292" t="n">
         <v>0.4</v>
       </c>
-      <c r="J18" s="264" t="n">
+      <c r="J18" s="292" t="n">
         <v>0.3</v>
       </c>
-      <c r="K18" s="264" t="n">
+      <c r="K18" s="292" t="n">
         <v>0.4</v>
       </c>
       <c r="L18" s="148">
@@ -5070,7 +5111,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="63">
-      <c r="B19" s="272" t="n">
+      <c r="B19" s="300" t="n">
         <v>13</v>
       </c>
       <c r="C19" s="114" t="inlineStr">
@@ -5078,7 +5119,7 @@
           <t>Кабель оптический самонесущий, 72 волокна</t>
         </is>
       </c>
-      <c r="D19" s="272" t="inlineStr">
+      <c r="D19" s="300" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5088,14 +5129,14 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F19" s="266" t="n">
+      <c r="F19" s="294" t="n">
         <v>0.4</v>
       </c>
-      <c r="G19" s="266" t="n"/>
-      <c r="H19" s="266" t="n"/>
-      <c r="I19" s="266" t="n"/>
-      <c r="J19" s="266" t="n"/>
-      <c r="K19" s="266" t="n">
+      <c r="G19" s="294" t="n"/>
+      <c r="H19" s="294" t="n"/>
+      <c r="I19" s="294" t="n"/>
+      <c r="J19" s="294" t="n"/>
+      <c r="K19" s="294" t="n">
         <v>0.2</v>
       </c>
       <c r="L19" s="149">
@@ -5104,7 +5145,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="63">
-      <c r="B20" s="271" t="n">
+      <c r="B20" s="299" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="112" t="inlineStr">
@@ -5112,7 +5153,7 @@
           <t>Кабель оптический самонесущий, 96 волокон</t>
         </is>
       </c>
-      <c r="D20" s="271" t="inlineStr">
+      <c r="D20" s="299" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5122,21 +5163,21 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F20" s="264" t="n">
+      <c r="F20" s="292" t="n">
         <v>0.1</v>
       </c>
-      <c r="G20" s="264" t="n">
+      <c r="G20" s="292" t="n">
         <v>0.1</v>
       </c>
-      <c r="H20" s="264" t="n">
+      <c r="H20" s="292" t="n">
         <v>0.2</v>
       </c>
-      <c r="I20" s="264" t="n"/>
-      <c r="J20" s="264" t="n">
+      <c r="I20" s="292" t="n"/>
+      <c r="J20" s="292" t="n">
         <v>0.1</v>
       </c>
-      <c r="K20" s="264" t="n">
-        <v>0.1</v>
+      <c r="K20" s="292" t="n">
+        <v>0.2</v>
       </c>
       <c r="L20" s="148">
         <f>SUM(F20:K20)</f>
@@ -5144,7 +5185,7 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="63">
-      <c r="B21" s="272" t="n">
+      <c r="B21" s="300" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="114" t="inlineStr">
@@ -5152,7 +5193,7 @@
           <t>Кабель дроп-кабельный самонесущий, 2 волокна (1 раб. + 1 рез.)</t>
         </is>
       </c>
-      <c r="D21" s="272" t="inlineStr">
+      <c r="D21" s="300" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5162,23 +5203,23 @@
           <t>дропы × 1,05 (без подводок — дроп от муфты напрямую)</t>
         </is>
       </c>
-      <c r="F21" s="266" t="n">
+      <c r="F21" s="294" t="n">
         <v>41.7</v>
       </c>
-      <c r="G21" s="266" t="n">
+      <c r="G21" s="294" t="n">
         <v>5.2</v>
       </c>
-      <c r="H21" s="266" t="n">
+      <c r="H21" s="294" t="n">
         <v>15.8</v>
       </c>
-      <c r="I21" s="266" t="n">
+      <c r="I21" s="294" t="n">
         <v>27.2</v>
       </c>
-      <c r="J21" s="266" t="n">
+      <c r="J21" s="294" t="n">
         <v>12.9</v>
       </c>
-      <c r="K21" s="266" t="n">
-        <v>22.5</v>
+      <c r="K21" s="294" t="n">
+        <v>23.3</v>
       </c>
       <c r="L21" s="149">
         <f>SUM(F21:K21)</f>
@@ -5186,7 +5227,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="63">
-      <c r="B22" s="271" t="n">
+      <c r="B22" s="299" t="n">
         <v>16</v>
       </c>
       <c r="C22" s="112" t="inlineStr">
@@ -5194,7 +5235,7 @@
           <t>Справочно: суммарная ёмкость магистрального кабеля</t>
         </is>
       </c>
-      <c r="D22" s="271" t="inlineStr">
+      <c r="D22" s="299" t="inlineStr">
         <is>
           <t>волокно-км</t>
         </is>
@@ -5204,23 +5245,23 @@
           <t>Σ (длина участка × волокна)</t>
         </is>
       </c>
-      <c r="F22" s="264" t="n">
+      <c r="F22" s="292" t="n">
         <v>524.8</v>
       </c>
-      <c r="G22" s="264" t="n">
+      <c r="G22" s="292" t="n">
         <v>90</v>
       </c>
-      <c r="H22" s="264" t="n">
+      <c r="H22" s="292" t="n">
         <v>218.5</v>
       </c>
-      <c r="I22" s="264" t="n">
+      <c r="I22" s="292" t="n">
         <v>329.9</v>
       </c>
-      <c r="J22" s="264" t="n">
+      <c r="J22" s="292" t="n">
         <v>141.2</v>
       </c>
-      <c r="K22" s="264" t="n">
-        <v>186.7</v>
+      <c r="K22" s="292" t="n">
+        <v>191.3</v>
       </c>
       <c r="L22" s="148">
         <f>SUM(F22:K22)</f>
@@ -5245,7 +5286,7 @@
       <c r="L23" s="108" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="63">
-      <c r="B24" s="271" t="n">
+      <c r="B24" s="299" t="n">
         <v>17</v>
       </c>
       <c r="C24" s="112" t="inlineStr">
@@ -5253,7 +5294,7 @@
           <t>Муфта оптическая (ветвления магистрали)</t>
         </is>
       </c>
-      <c r="D24" s="271" t="inlineStr">
+      <c r="D24" s="299" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5263,23 +5304,23 @@
           <t>узлы ветвления кроме точек врезов зонных ОРШ; транзит — неразрезным кабелем</t>
         </is>
       </c>
-      <c r="F24" s="262" t="n">
+      <c r="F24" s="290" t="n">
         <v>367</v>
       </c>
-      <c r="G24" s="262" t="n">
+      <c r="G24" s="290" t="n">
         <v>70</v>
       </c>
-      <c r="H24" s="262" t="n">
+      <c r="H24" s="290" t="n">
         <v>158</v>
       </c>
-      <c r="I24" s="262" t="n">
+      <c r="I24" s="290" t="n">
         <v>246</v>
       </c>
-      <c r="J24" s="262" t="n">
+      <c r="J24" s="290" t="n">
         <v>119</v>
       </c>
-      <c r="K24" s="262" t="n">
-        <v>144</v>
+      <c r="K24" s="290" t="n">
+        <v>143</v>
       </c>
       <c r="L24" s="146">
         <f>SUM(F24:K24)</f>
@@ -5304,7 +5345,7 @@
       <c r="L25" s="108" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="63">
-      <c r="B26" s="271" t="n">
+      <c r="B26" s="299" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="112" t="inlineStr">
@@ -5312,7 +5353,7 @@
           <t>Бокс абонентский оптический с адаптером SC/UPC</t>
         </is>
       </c>
-      <c r="D26" s="271" t="inlineStr">
+      <c r="D26" s="299" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5322,23 +5363,23 @@
           <t>1 на ДХ</t>
         </is>
       </c>
-      <c r="F26" s="262" t="n">
+      <c r="F26" s="290" t="n">
         <v>1029</v>
       </c>
-      <c r="G26" s="262" t="n">
+      <c r="G26" s="290" t="n">
         <v>124</v>
       </c>
-      <c r="H26" s="262" t="n">
+      <c r="H26" s="290" t="n">
         <v>376</v>
       </c>
-      <c r="I26" s="262" t="n">
+      <c r="I26" s="290" t="n">
         <v>622</v>
       </c>
-      <c r="J26" s="262" t="n">
+      <c r="J26" s="290" t="n">
         <v>286</v>
       </c>
-      <c r="K26" s="262" t="n">
-        <v>615</v>
+      <c r="K26" s="290" t="n">
+        <v>635</v>
       </c>
       <c r="L26" s="146">
         <f>SUM(F26:K26)</f>
@@ -5346,7 +5387,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="63">
-      <c r="B27" s="272" t="n">
+      <c r="B27" s="300" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="114" t="inlineStr">
@@ -5354,7 +5395,7 @@
           <t>Коннектор оптический механический SC/UPC</t>
         </is>
       </c>
-      <c r="D27" s="272" t="inlineStr">
+      <c r="D27" s="300" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5364,23 +5405,23 @@
           <t>ДХ × 1,1 (абонентский бокс)</t>
         </is>
       </c>
-      <c r="F27" s="263" t="n">
+      <c r="F27" s="291" t="n">
         <v>1132</v>
       </c>
-      <c r="G27" s="263" t="n">
+      <c r="G27" s="291" t="n">
         <v>137</v>
       </c>
-      <c r="H27" s="263" t="n">
+      <c r="H27" s="291" t="n">
         <v>414</v>
       </c>
-      <c r="I27" s="263" t="n">
+      <c r="I27" s="291" t="n">
         <v>685</v>
       </c>
-      <c r="J27" s="263" t="n">
+      <c r="J27" s="291" t="n">
         <v>315</v>
       </c>
-      <c r="K27" s="263" t="n">
-        <v>677</v>
+      <c r="K27" s="291" t="n">
+        <v>699</v>
       </c>
       <c r="L27" s="147">
         <f>SUM(F27:K27)</f>
@@ -5388,7 +5429,7 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="63">
-      <c r="B28" s="271" t="n">
+      <c r="B28" s="299" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="112" t="inlineStr">
@@ -5396,7 +5437,7 @@
           <t>Сварное соединение (оценка объёма работ)</t>
         </is>
       </c>
-      <c r="D28" s="271" t="inlineStr">
+      <c r="D28" s="299" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5406,23 +5447,23 @@
           <t>(2 × ДХ + 2 × сплиттеры 1:64) × 1,1</t>
         </is>
       </c>
-      <c r="F28" s="262" t="n">
+      <c r="F28" s="290" t="n">
         <v>2313</v>
       </c>
-      <c r="G28" s="262" t="n">
+      <c r="G28" s="290" t="n">
         <v>278</v>
       </c>
-      <c r="H28" s="262" t="n">
+      <c r="H28" s="290" t="n">
         <v>845</v>
       </c>
-      <c r="I28" s="262" t="n">
+      <c r="I28" s="290" t="n">
         <v>1400</v>
       </c>
-      <c r="J28" s="262" t="n">
+      <c r="J28" s="290" t="n">
         <v>643</v>
       </c>
-      <c r="K28" s="262" t="n">
-        <v>1380</v>
+      <c r="K28" s="290" t="n">
+        <v>1426</v>
       </c>
       <c r="L28" s="146">
         <f>SUM(F28:K28)</f>
@@ -5430,7 +5471,7 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="63">
-      <c r="B29" s="272" t="n">
+      <c r="B29" s="300" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="114" t="inlineStr">
@@ -5438,7 +5479,7 @@
           <t>Гильза КДЗС, 60 мм</t>
         </is>
       </c>
-      <c r="D29" s="272" t="inlineStr">
+      <c r="D29" s="300" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5448,23 +5489,23 @@
           <t>по числу сварных соединений</t>
         </is>
       </c>
-      <c r="F29" s="263" t="n">
+      <c r="F29" s="291" t="n">
         <v>2313</v>
       </c>
-      <c r="G29" s="263" t="n">
+      <c r="G29" s="291" t="n">
         <v>278</v>
       </c>
-      <c r="H29" s="263" t="n">
+      <c r="H29" s="291" t="n">
         <v>845</v>
       </c>
-      <c r="I29" s="263" t="n">
+      <c r="I29" s="291" t="n">
         <v>1400</v>
       </c>
-      <c r="J29" s="263" t="n">
+      <c r="J29" s="291" t="n">
         <v>643</v>
       </c>
-      <c r="K29" s="263" t="n">
-        <v>1380</v>
+      <c r="K29" s="291" t="n">
+        <v>1426</v>
       </c>
       <c r="L29" s="147">
         <f>SUM(F29:K29)</f>
@@ -5472,7 +5513,7 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="63">
-      <c r="B30" s="271" t="n">
+      <c r="B30" s="299" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="112" t="inlineStr">
@@ -5480,7 +5521,7 @@
           <t>Комплект подвеса магистрального кабеля (кронштейн + спиральный зажим)</t>
         </is>
       </c>
-      <c r="D30" s="271" t="inlineStr">
+      <c r="D30" s="299" t="inlineStr">
         <is>
           <t>компл</t>
         </is>
@@ -5490,22 +5531,22 @@
           <t>30 на 1 км кабеля</t>
         </is>
       </c>
-      <c r="F30" s="262" t="n">
+      <c r="F30" s="290" t="n">
         <v>918</v>
       </c>
-      <c r="G30" s="262" t="n">
+      <c r="G30" s="290" t="n">
         <v>144</v>
       </c>
-      <c r="H30" s="262" t="n">
+      <c r="H30" s="290" t="n">
         <v>316</v>
       </c>
-      <c r="I30" s="262" t="n">
+      <c r="I30" s="290" t="n">
         <v>584</v>
       </c>
-      <c r="J30" s="262" t="n">
+      <c r="J30" s="290" t="n">
         <v>247</v>
       </c>
-      <c r="K30" s="262" t="n">
+      <c r="K30" s="290" t="n">
         <v>263</v>
       </c>
       <c r="L30" s="146">
@@ -5514,7 +5555,7 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" s="63">
-      <c r="B31" s="272" t="n">
+      <c r="B31" s="300" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="114" t="inlineStr">
@@ -5522,7 +5563,7 @@
           <t>Анкерный зажим дроп-кабеля</t>
         </is>
       </c>
-      <c r="D31" s="272" t="inlineStr">
+      <c r="D31" s="300" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5532,23 +5573,23 @@
           <t>2 на ДХ</t>
         </is>
       </c>
-      <c r="F31" s="263" t="n">
+      <c r="F31" s="291" t="n">
         <v>2058</v>
       </c>
-      <c r="G31" s="263" t="n">
+      <c r="G31" s="291" t="n">
         <v>248</v>
       </c>
-      <c r="H31" s="263" t="n">
+      <c r="H31" s="291" t="n">
         <v>752</v>
       </c>
-      <c r="I31" s="263" t="n">
+      <c r="I31" s="291" t="n">
         <v>1244</v>
       </c>
-      <c r="J31" s="263" t="n">
+      <c r="J31" s="291" t="n">
         <v>572</v>
       </c>
-      <c r="K31" s="263" t="n">
-        <v>1230</v>
+      <c r="K31" s="291" t="n">
+        <v>1270</v>
       </c>
       <c r="L31" s="147">
         <f>SUM(F31:K31)</f>
@@ -5556,7 +5597,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" s="63">
-      <c r="B32" s="271" t="n">
+      <c r="B32" s="299" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="112" t="inlineStr">
@@ -5564,7 +5605,7 @@
           <t>Крепёж дроп-кабеля (скобы / хомуты)</t>
         </is>
       </c>
-      <c r="D32" s="271" t="inlineStr">
+      <c r="D32" s="299" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5574,23 +5615,23 @@
           <t>6 на ДХ</t>
         </is>
       </c>
-      <c r="F32" s="262" t="n">
+      <c r="F32" s="290" t="n">
         <v>6174</v>
       </c>
-      <c r="G32" s="262" t="n">
+      <c r="G32" s="290" t="n">
         <v>744</v>
       </c>
-      <c r="H32" s="262" t="n">
+      <c r="H32" s="290" t="n">
         <v>2256</v>
       </c>
-      <c r="I32" s="262" t="n">
+      <c r="I32" s="290" t="n">
         <v>3732</v>
       </c>
-      <c r="J32" s="262" t="n">
+      <c r="J32" s="290" t="n">
         <v>1716</v>
       </c>
-      <c r="K32" s="262" t="n">
-        <v>3690</v>
+      <c r="K32" s="290" t="n">
+        <v>3810</v>
       </c>
       <c r="L32" s="146">
         <f>SUM(F32:K32)</f>
@@ -9258,7 +9299,7 @@
       </c>
       <c r="D14" s="109" t="inlineStr">
         <is>
-          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1491 (-69% к A); суммарная длина 215.8 км — минимум среди всех схем книги.</t>
+          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1496 (-69% к A); суммарная длина 216.6 км — минимум среди всех схем книги.</t>
         </is>
       </c>
     </row>
@@ -9339,19 +9380,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F18" s="276" t="n">
+      <c r="F18" s="290" t="n">
         <v>69</v>
       </c>
-      <c r="G18" s="276" t="n">
+      <c r="G18" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="276" t="n">
+      <c r="H18" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="276" t="n">
+      <c r="I18" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="276" t="n">
+      <c r="J18" s="290" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9367,19 +9408,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F19" s="277" t="n">
+      <c r="F19" s="291" t="n">
         <v>46</v>
       </c>
-      <c r="G19" s="277" t="n">
+      <c r="G19" s="291" t="n">
         <v>752</v>
       </c>
-      <c r="H19" s="277" t="n">
+      <c r="H19" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="277" t="n">
+      <c r="I19" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="277" t="n">
+      <c r="J19" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9395,19 +9436,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F20" s="276" t="n">
+      <c r="F20" s="290" t="n">
         <v>114</v>
       </c>
-      <c r="G20" s="276" t="n">
+      <c r="G20" s="290" t="n">
         <v>546</v>
       </c>
-      <c r="H20" s="276" t="n">
+      <c r="H20" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="276" t="n">
+      <c r="I20" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="276" t="n">
+      <c r="J20" s="290" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9423,19 +9464,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F21" s="277" t="n">
+      <c r="F21" s="291" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="277" t="n">
+      <c r="G21" s="291" t="n">
         <v>667</v>
       </c>
-      <c r="H21" s="277" t="n">
+      <c r="H21" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="277" t="n">
+      <c r="I21" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="277" t="n">
+      <c r="J21" s="291" t="n">
         <v>48</v>
       </c>
     </row>
@@ -9451,19 +9492,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F22" s="276" t="n">
+      <c r="F22" s="290" t="n">
         <v>132</v>
       </c>
-      <c r="G22" s="276" t="n">
+      <c r="G22" s="290" t="n">
         <v>717</v>
       </c>
-      <c r="H22" s="276" t="n">
+      <c r="H22" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="276" t="n">
+      <c r="I22" s="290" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="276" t="n">
+      <c r="J22" s="290" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9479,19 +9520,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F23" s="277" t="n">
+      <c r="F23" s="291" t="n">
         <v>109</v>
       </c>
-      <c r="G23" s="277" t="n">
+      <c r="G23" s="291" t="n">
         <v>856</v>
       </c>
-      <c r="H23" s="277" t="n">
+      <c r="H23" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="277" t="n">
+      <c r="I23" s="291" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="277" t="n">
+      <c r="J23" s="291" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9507,19 +9548,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F24" s="276" t="n">
+      <c r="F24" s="290" t="n">
         <v>84</v>
       </c>
-      <c r="G24" s="276" t="n">
+      <c r="G24" s="290" t="n">
         <v>908</v>
       </c>
-      <c r="H24" s="276" t="n">
+      <c r="H24" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="276" t="n">
+      <c r="I24" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="276" t="n">
+      <c r="J24" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9535,19 +9576,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F25" s="277" t="n">
+      <c r="F25" s="291" t="n">
         <v>50</v>
       </c>
-      <c r="G25" s="277" t="n">
+      <c r="G25" s="291" t="n">
         <v>1708</v>
       </c>
-      <c r="H25" s="277" t="n">
+      <c r="H25" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="277" t="n">
+      <c r="I25" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="277" t="n">
+      <c r="J25" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9563,19 +9604,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F26" s="276" t="n">
+      <c r="F26" s="290" t="n">
         <v>49</v>
       </c>
-      <c r="G26" s="276" t="n">
+      <c r="G26" s="290" t="n">
         <v>860</v>
       </c>
-      <c r="H26" s="276" t="n">
+      <c r="H26" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="276" t="n">
+      <c r="I26" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="276" t="n">
+      <c r="J26" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9591,19 +9632,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F27" s="277" t="n">
+      <c r="F27" s="291" t="n">
         <v>49</v>
       </c>
-      <c r="G27" s="277" t="n">
+      <c r="G27" s="291" t="n">
         <v>1211</v>
       </c>
-      <c r="H27" s="277" t="n">
+      <c r="H27" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="277" t="n">
+      <c r="I27" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="277" t="n">
+      <c r="J27" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9619,19 +9660,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F28" s="276" t="n">
+      <c r="F28" s="290" t="n">
         <v>88</v>
       </c>
-      <c r="G28" s="276" t="n">
+      <c r="G28" s="290" t="n">
         <v>1175</v>
       </c>
-      <c r="H28" s="276" t="n">
+      <c r="H28" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="276" t="n">
+      <c r="I28" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="276" t="n">
+      <c r="J28" s="290" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9647,19 +9688,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F29" s="277" t="n">
+      <c r="F29" s="291" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="277" t="n">
+      <c r="G29" s="291" t="n">
         <v>1169</v>
       </c>
-      <c r="H29" s="277" t="n">
+      <c r="H29" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="277" t="n">
+      <c r="I29" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="277" t="n">
+      <c r="J29" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9675,19 +9716,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F30" s="276" t="n">
+      <c r="F30" s="290" t="n">
         <v>51</v>
       </c>
-      <c r="G30" s="276" t="n">
+      <c r="G30" s="290" t="n">
         <v>1390</v>
       </c>
-      <c r="H30" s="276" t="n">
+      <c r="H30" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="276" t="n">
+      <c r="I30" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="276" t="n">
+      <c r="J30" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9703,19 +9744,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F31" s="277" t="n">
+      <c r="F31" s="291" t="n">
         <v>49</v>
       </c>
-      <c r="G31" s="277" t="n">
+      <c r="G31" s="291" t="n">
         <v>879</v>
       </c>
-      <c r="H31" s="277" t="n">
+      <c r="H31" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="277" t="n">
+      <c r="I31" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="277" t="n">
+      <c r="J31" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9731,19 +9772,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F32" s="276" t="n">
+      <c r="F32" s="290" t="n">
         <v>59</v>
       </c>
-      <c r="G32" s="276" t="n">
+      <c r="G32" s="290" t="n">
         <v>745</v>
       </c>
-      <c r="H32" s="276" t="n">
+      <c r="H32" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="276" t="n">
+      <c r="I32" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="276" t="n">
+      <c r="J32" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9763,19 +9804,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F33" s="277" t="n">
+      <c r="F33" s="291" t="n">
         <v>124</v>
       </c>
-      <c r="G33" s="277" t="n">
+      <c r="G33" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="277" t="n">
+      <c r="H33" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="277" t="n">
+      <c r="I33" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="277" t="n">
+      <c r="J33" s="291" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9795,19 +9836,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F34" s="276" t="n">
+      <c r="F34" s="290" t="n">
         <v>35</v>
       </c>
-      <c r="G34" s="276" t="n">
+      <c r="G34" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="276" t="n">
+      <c r="H34" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="276" t="n">
+      <c r="I34" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="276" t="n">
+      <c r="J34" s="290" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9823,19 +9864,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F35" s="277" t="n">
+      <c r="F35" s="291" t="n">
         <v>56</v>
       </c>
-      <c r="G35" s="277" t="n">
+      <c r="G35" s="291" t="n">
         <v>805</v>
       </c>
-      <c r="H35" s="277" t="n">
+      <c r="H35" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="277" t="n">
+      <c r="I35" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="277" t="n">
+      <c r="J35" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9851,19 +9892,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F36" s="276" t="n">
+      <c r="F36" s="290" t="n">
         <v>156</v>
       </c>
-      <c r="G36" s="276" t="n">
+      <c r="G36" s="290" t="n">
         <v>295</v>
       </c>
-      <c r="H36" s="276" t="n">
+      <c r="H36" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="276" t="n">
+      <c r="I36" s="290" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="276" t="n">
+      <c r="J36" s="290" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9879,19 +9920,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F37" s="277" t="n">
+      <c r="F37" s="291" t="n">
         <v>69</v>
       </c>
-      <c r="G37" s="277" t="n">
+      <c r="G37" s="291" t="n">
         <v>1394</v>
       </c>
-      <c r="H37" s="277" t="n">
+      <c r="H37" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="277" t="n">
+      <c r="I37" s="291" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="277" t="n">
+      <c r="J37" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9907,19 +9948,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F38" s="276" t="n">
+      <c r="F38" s="290" t="n">
         <v>60</v>
       </c>
-      <c r="G38" s="276" t="n">
+      <c r="G38" s="290" t="n">
         <v>556</v>
       </c>
-      <c r="H38" s="276" t="n">
+      <c r="H38" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="276" t="n">
+      <c r="I38" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="276" t="n">
+      <c r="J38" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9939,19 +9980,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F39" s="277" t="n">
+      <c r="F39" s="291" t="n">
         <v>27</v>
       </c>
-      <c r="G39" s="277" t="n">
+      <c r="G39" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="277" t="n">
+      <c r="H39" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="277" t="n">
+      <c r="I39" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="277" t="n">
+      <c r="J39" s="291" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9967,19 +10008,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F40" s="276" t="n">
+      <c r="F40" s="290" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="276" t="n">
+      <c r="G40" s="290" t="n">
         <v>1298</v>
       </c>
-      <c r="H40" s="276" t="n">
+      <c r="H40" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="276" t="n">
+      <c r="I40" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="276" t="n">
+      <c r="J40" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9995,19 +10036,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F41" s="277" t="n">
+      <c r="F41" s="291" t="n">
         <v>107</v>
       </c>
-      <c r="G41" s="277" t="n">
+      <c r="G41" s="291" t="n">
         <v>418</v>
       </c>
-      <c r="H41" s="277" t="n">
+      <c r="H41" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="277" t="n">
+      <c r="I41" s="291" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="277" t="n">
+      <c r="J41" s="291" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10023,19 +10064,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F42" s="276" t="n">
+      <c r="F42" s="290" t="n">
         <v>53</v>
       </c>
-      <c r="G42" s="276" t="n">
+      <c r="G42" s="290" t="n">
         <v>1329</v>
       </c>
-      <c r="H42" s="276" t="n">
+      <c r="H42" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="276" t="n">
+      <c r="I42" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="276" t="n">
+      <c r="J42" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10051,19 +10092,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F43" s="277" t="n">
+      <c r="F43" s="291" t="n">
         <v>53</v>
       </c>
-      <c r="G43" s="277" t="n">
+      <c r="G43" s="291" t="n">
         <v>937</v>
       </c>
-      <c r="H43" s="277" t="n">
+      <c r="H43" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="277" t="n">
+      <c r="I43" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="277" t="n">
+      <c r="J43" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10079,19 +10120,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F44" s="276" t="n">
+      <c r="F44" s="290" t="n">
         <v>85</v>
       </c>
-      <c r="G44" s="276" t="n">
+      <c r="G44" s="290" t="n">
         <v>368</v>
       </c>
-      <c r="H44" s="276" t="n">
+      <c r="H44" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="276" t="n">
+      <c r="I44" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="276" t="n">
+      <c r="J44" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10107,19 +10148,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F45" s="277" t="n">
+      <c r="F45" s="291" t="n">
         <v>48</v>
       </c>
-      <c r="G45" s="277" t="n">
+      <c r="G45" s="291" t="n">
         <v>1096</v>
       </c>
-      <c r="H45" s="277" t="n">
+      <c r="H45" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="277" t="n">
+      <c r="I45" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="277" t="n">
+      <c r="J45" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10135,19 +10176,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F46" s="276" t="n">
+      <c r="F46" s="290" t="n">
         <v>76</v>
       </c>
-      <c r="G46" s="276" t="n">
+      <c r="G46" s="290" t="n">
         <v>302</v>
       </c>
-      <c r="H46" s="276" t="n">
+      <c r="H46" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="276" t="n">
+      <c r="I46" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="276" t="n">
+      <c r="J46" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10163,19 +10204,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F47" s="277" t="n">
+      <c r="F47" s="291" t="n">
         <v>78</v>
       </c>
-      <c r="G47" s="277" t="n">
+      <c r="G47" s="291" t="n">
         <v>1779</v>
       </c>
-      <c r="H47" s="277" t="n">
+      <c r="H47" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="277" t="n">
+      <c r="I47" s="291" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="277" t="n">
+      <c r="J47" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10191,19 +10232,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F48" s="276" t="n">
+      <c r="F48" s="290" t="n">
         <v>50</v>
       </c>
-      <c r="G48" s="276" t="n">
+      <c r="G48" s="290" t="n">
         <v>476</v>
       </c>
-      <c r="H48" s="276" t="n">
+      <c r="H48" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="276" t="n">
+      <c r="I48" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="276" t="n">
+      <c r="J48" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10223,19 +10264,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F49" s="277" t="n">
+      <c r="F49" s="291" t="n">
         <v>70</v>
       </c>
-      <c r="G49" s="277" t="n">
+      <c r="G49" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="277" t="n">
+      <c r="H49" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="I49" s="277" t="n">
+      <c r="I49" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="277" t="n">
+      <c r="J49" s="291" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10251,19 +10292,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F50" s="276" t="n">
+      <c r="F50" s="290" t="n">
         <v>62</v>
       </c>
-      <c r="G50" s="276" t="n">
+      <c r="G50" s="290" t="n">
         <v>666</v>
       </c>
-      <c r="H50" s="276" t="n">
+      <c r="H50" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="276" t="n">
+      <c r="I50" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="276" t="n">
+      <c r="J50" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10279,19 +10320,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F51" s="277" t="n">
+      <c r="F51" s="291" t="n">
         <v>93</v>
       </c>
-      <c r="G51" s="277" t="n">
+      <c r="G51" s="291" t="n">
         <v>262</v>
       </c>
-      <c r="H51" s="277" t="n">
+      <c r="H51" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="277" t="n">
+      <c r="I51" s="291" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="277" t="n">
+      <c r="J51" s="291" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10307,19 +10348,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F52" s="276" t="n">
+      <c r="F52" s="290" t="n">
         <v>61</v>
       </c>
-      <c r="G52" s="276" t="n">
+      <c r="G52" s="290" t="n">
         <v>367</v>
       </c>
-      <c r="H52" s="276" t="n">
+      <c r="H52" s="290" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="276" t="n">
+      <c r="I52" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="276" t="n">
+      <c r="J52" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10339,19 +10380,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F53" s="277" t="n">
+      <c r="F53" s="291" t="n">
         <v>122</v>
       </c>
-      <c r="G53" s="277" t="n">
+      <c r="G53" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="277" t="n">
+      <c r="H53" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="277" t="n">
+      <c r="I53" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="277" t="n">
+      <c r="J53" s="291" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10367,19 +10408,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F54" s="276" t="n">
+      <c r="F54" s="290" t="n">
         <v>93</v>
       </c>
-      <c r="G54" s="276" t="n">
+      <c r="G54" s="290" t="n">
         <v>274</v>
       </c>
-      <c r="H54" s="276" t="n">
+      <c r="H54" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="276" t="n">
+      <c r="I54" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="276" t="n">
+      <c r="J54" s="290" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10395,20 +10436,20 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F55" s="277" t="n">
-        <v>121</v>
-      </c>
-      <c r="G55" s="277" t="n">
+      <c r="F55" s="291" t="n">
+        <v>141</v>
+      </c>
+      <c r="G55" s="291" t="n">
         <v>654</v>
       </c>
-      <c r="H55" s="277" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" s="277" t="n">
+      <c r="H55" s="291" t="n">
         <v>3</v>
       </c>
-      <c r="J55" s="277" t="n">
-        <v>144</v>
+      <c r="I55" s="291" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" s="291" t="n">
+        <v>288</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="63">
@@ -10423,19 +10464,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F56" s="276" t="n">
+      <c r="F56" s="290" t="n">
         <v>91</v>
       </c>
-      <c r="G56" s="276" t="n">
+      <c r="G56" s="290" t="n">
         <v>336</v>
       </c>
-      <c r="H56" s="276" t="n">
+      <c r="H56" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="276" t="n">
+      <c r="I56" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="J56" s="276" t="n">
+      <c r="J56" s="290" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10451,19 +10492,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F57" s="277" t="n">
+      <c r="F57" s="291" t="n">
         <v>59</v>
       </c>
-      <c r="G57" s="277" t="n">
+      <c r="G57" s="291" t="n">
         <v>433</v>
       </c>
-      <c r="H57" s="277" t="n">
+      <c r="H57" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="277" t="n">
+      <c r="I57" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="277" t="n">
+      <c r="J57" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10479,19 +10520,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F58" s="276" t="n">
+      <c r="F58" s="290" t="n">
         <v>73</v>
       </c>
-      <c r="G58" s="276" t="n">
+      <c r="G58" s="290" t="n">
         <v>710</v>
       </c>
-      <c r="H58" s="276" t="n">
+      <c r="H58" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="276" t="n">
+      <c r="I58" s="290" t="n">
         <v>3</v>
       </c>
-      <c r="J58" s="276" t="n">
+      <c r="J58" s="290" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10507,19 +10548,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F59" s="277" t="n">
+      <c r="F59" s="291" t="n">
         <v>56</v>
       </c>
-      <c r="G59" s="277" t="n">
+      <c r="G59" s="291" t="n">
         <v>306</v>
       </c>
-      <c r="H59" s="277" t="n">
+      <c r="H59" s="291" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="277" t="n">
+      <c r="I59" s="291" t="n">
         <v>2</v>
       </c>
-      <c r="J59" s="277" t="n">
+      <c r="J59" s="291" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10642,482 +10683,482 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1" s="63">
-      <c r="C65" s="276" t="n">
+      <c r="C65" s="290" t="n">
         <v>2</v>
       </c>
-      <c r="D65" s="276" t="n">
+      <c r="D65" s="290" t="n">
         <v>48</v>
       </c>
-      <c r="E65" s="278" t="n">
+      <c r="E65" s="292" t="n">
         <v>1460.2</v>
       </c>
-      <c r="F65" s="279">
+      <c r="F65" s="293">
         <f>E65/4375.1-1</f>
         <v/>
       </c>
-      <c r="G65" s="278" t="n">
+      <c r="G65" s="292" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H65" s="278" t="n">
+      <c r="H65" s="292" t="n">
         <v>95.8</v>
       </c>
-      <c r="I65" s="278">
+      <c r="I65" s="292">
         <f>G65+H65</f>
         <v/>
       </c>
-      <c r="J65" s="276" t="n">
+      <c r="J65" s="290" t="n">
         <v>56</v>
       </c>
-      <c r="K65" s="276" t="n">
+      <c r="K65" s="290" t="n">
         <v>5261</v>
       </c>
-      <c r="L65" s="276" t="n">
+      <c r="L65" s="290" t="n">
         <v>4368</v>
       </c>
-      <c r="M65" s="276" t="n">
+      <c r="M65" s="290" t="n">
         <v>349</v>
       </c>
-      <c r="N65" s="276" t="n">
+      <c r="N65" s="290" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1" s="63">
-      <c r="C66" s="277" t="n">
+      <c r="C66" s="291" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="277" t="n">
+      <c r="D66" s="291" t="n">
         <v>43</v>
       </c>
-      <c r="E66" s="280" t="n">
+      <c r="E66" s="294" t="n">
         <v>1476.5</v>
       </c>
-      <c r="F66" s="281">
+      <c r="F66" s="295">
         <f>E66/4375.1-1</f>
         <v/>
       </c>
-      <c r="G66" s="280" t="n">
+      <c r="G66" s="294" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H66" s="280" t="n">
+      <c r="H66" s="294" t="n">
         <v>95.8</v>
       </c>
-      <c r="I66" s="280">
+      <c r="I66" s="294">
         <f>G66+H66</f>
         <v/>
       </c>
-      <c r="J66" s="277" t="n">
+      <c r="J66" s="291" t="n">
         <v>54</v>
       </c>
-      <c r="K66" s="277" t="n">
+      <c r="K66" s="291" t="n">
         <v>5255</v>
       </c>
-      <c r="L66" s="277" t="n">
+      <c r="L66" s="291" t="n">
         <v>4176</v>
       </c>
-      <c r="M66" s="277" t="n">
+      <c r="M66" s="291" t="n">
         <v>358</v>
       </c>
-      <c r="N66" s="277" t="n">
+      <c r="N66" s="291" t="n">
         <v>108</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1" s="63">
-      <c r="C67" s="276" t="n">
+      <c r="C67" s="290" t="n">
         <v>8</v>
       </c>
-      <c r="D67" s="276" t="n">
+      <c r="D67" s="290" t="n">
         <v>39</v>
       </c>
-      <c r="E67" s="278" t="n">
+      <c r="E67" s="292" t="n">
         <v>1500.8</v>
       </c>
-      <c r="F67" s="279">
+      <c r="F67" s="293">
         <f>E67/4375.1-1</f>
         <v/>
       </c>
-      <c r="G67" s="278" t="n">
+      <c r="G67" s="292" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H67" s="278" t="n">
+      <c r="H67" s="292" t="n">
         <v>95.8</v>
       </c>
-      <c r="I67" s="278">
+      <c r="I67" s="292">
         <f>G67+H67</f>
         <v/>
       </c>
-      <c r="J67" s="276" t="n">
+      <c r="J67" s="290" t="n">
         <v>53</v>
       </c>
-      <c r="K67" s="276" t="n">
+      <c r="K67" s="290" t="n">
         <v>5253</v>
       </c>
-      <c r="L67" s="276" t="n">
+      <c r="L67" s="290" t="n">
         <v>3984</v>
       </c>
-      <c r="M67" s="276" t="n">
+      <c r="M67" s="290" t="n">
         <v>368</v>
       </c>
-      <c r="N67" s="276" t="n">
+      <c r="N67" s="290" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="63">
-      <c r="C68" s="277" t="n">
+      <c r="C68" s="291" t="n">
         <v>10</v>
       </c>
-      <c r="D68" s="277" t="n">
+      <c r="D68" s="291" t="n">
         <v>36</v>
       </c>
-      <c r="E68" s="280" t="n">
+      <c r="E68" s="294" t="n">
         <v>1532.5</v>
       </c>
-      <c r="F68" s="281">
+      <c r="F68" s="295">
         <f>E68/4375.1-1</f>
         <v/>
       </c>
-      <c r="G68" s="280" t="n">
+      <c r="G68" s="294" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H68" s="280" t="n">
+      <c r="H68" s="294" t="n">
         <v>95.8</v>
       </c>
-      <c r="I68" s="280">
+      <c r="I68" s="294">
         <f>G68+H68</f>
         <v/>
       </c>
-      <c r="J68" s="277" t="n">
+      <c r="J68" s="291" t="n">
         <v>53</v>
       </c>
-      <c r="K68" s="277" t="n">
+      <c r="K68" s="291" t="n">
         <v>5253</v>
       </c>
-      <c r="L68" s="277" t="n">
+      <c r="L68" s="291" t="n">
         <v>3888</v>
       </c>
-      <c r="M68" s="277" t="n">
+      <c r="M68" s="291" t="n">
         <v>379</v>
       </c>
-      <c r="N68" s="277" t="n">
+      <c r="N68" s="291" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="63">
-      <c r="C69" s="282" t="n">
+      <c r="C69" s="296" t="n">
         <v>15</v>
       </c>
-      <c r="D69" s="282" t="n">
+      <c r="D69" s="296" t="n">
         <v>34</v>
       </c>
-      <c r="E69" s="283" t="n">
+      <c r="E69" s="297" t="n">
         <v>1562.5</v>
       </c>
-      <c r="F69" s="284">
+      <c r="F69" s="298">
         <f>E69/4375.1-1</f>
         <v/>
       </c>
-      <c r="G69" s="283" t="n">
+      <c r="G69" s="297" t="n">
         <v>80.5</v>
       </c>
-      <c r="H69" s="283" t="n">
+      <c r="H69" s="297" t="n">
         <v>95.8</v>
       </c>
-      <c r="I69" s="283">
+      <c r="I69" s="297">
         <f>G69+H69</f>
         <v/>
       </c>
-      <c r="J69" s="282" t="n">
+      <c r="J69" s="296" t="n">
         <v>52</v>
       </c>
-      <c r="K69" s="282" t="n">
+      <c r="K69" s="296" t="n">
         <v>5251</v>
       </c>
-      <c r="L69" s="282" t="n">
+      <c r="L69" s="296" t="n">
         <v>3696</v>
       </c>
-      <c r="M69" s="282" t="n">
+      <c r="M69" s="296" t="n">
         <v>388</v>
       </c>
-      <c r="N69" s="282" t="n">
+      <c r="N69" s="296" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="63">
-      <c r="C70" s="277" t="n">
+      <c r="C70" s="291" t="n">
         <v>20</v>
       </c>
-      <c r="D70" s="277" t="n">
+      <c r="D70" s="291" t="n">
         <v>32</v>
       </c>
-      <c r="E70" s="280" t="n">
+      <c r="E70" s="294" t="n">
         <v>1603.9</v>
       </c>
-      <c r="F70" s="281">
+      <c r="F70" s="295">
         <f>E70/4375.1-1</f>
         <v/>
       </c>
-      <c r="G70" s="280" t="n">
+      <c r="G70" s="294" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="H70" s="280" t="n">
+      <c r="H70" s="294" t="n">
         <v>95.8</v>
       </c>
-      <c r="I70" s="280">
+      <c r="I70" s="294">
         <f>G70+H70</f>
         <v/>
       </c>
-      <c r="J70" s="277" t="n">
+      <c r="J70" s="291" t="n">
         <v>51</v>
       </c>
-      <c r="K70" s="277" t="n">
+      <c r="K70" s="291" t="n">
         <v>5249</v>
       </c>
-      <c r="L70" s="277" t="n">
+      <c r="L70" s="291" t="n">
         <v>3696</v>
       </c>
-      <c r="M70" s="277" t="n">
+      <c r="M70" s="291" t="n">
         <v>403</v>
       </c>
-      <c r="N70" s="277" t="n">
+      <c r="N70" s="291" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="63">
-      <c r="C71" s="276" t="n">
+      <c r="C71" s="290" t="n">
         <v>25</v>
       </c>
-      <c r="D71" s="276" t="n">
+      <c r="D71" s="290" t="n">
         <v>29</v>
       </c>
-      <c r="E71" s="278" t="n">
+      <c r="E71" s="292" t="n">
         <v>1674.7</v>
       </c>
-      <c r="F71" s="279">
+      <c r="F71" s="293">
         <f>E71/4375.1-1</f>
         <v/>
       </c>
-      <c r="G71" s="278" t="n">
+      <c r="G71" s="292" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H71" s="278" t="n">
+      <c r="H71" s="292" t="n">
         <v>95.8</v>
       </c>
-      <c r="I71" s="278">
+      <c r="I71" s="292">
         <f>G71+H71</f>
         <v/>
       </c>
-      <c r="J71" s="276" t="n">
+      <c r="J71" s="290" t="n">
         <v>50</v>
       </c>
-      <c r="K71" s="276" t="n">
+      <c r="K71" s="290" t="n">
         <v>5247</v>
       </c>
-      <c r="L71" s="276" t="n">
+      <c r="L71" s="290" t="n">
         <v>3600</v>
       </c>
-      <c r="M71" s="276" t="n">
+      <c r="M71" s="290" t="n">
         <v>427</v>
       </c>
-      <c r="N71" s="276" t="n">
+      <c r="N71" s="290" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="63">
-      <c r="C72" s="277" t="n">
+      <c r="C72" s="291" t="n">
         <v>30</v>
       </c>
-      <c r="D72" s="277" t="n">
+      <c r="D72" s="291" t="n">
         <v>27</v>
       </c>
-      <c r="E72" s="280" t="n">
+      <c r="E72" s="294" t="n">
         <v>1736.2</v>
       </c>
-      <c r="F72" s="281">
+      <c r="F72" s="295">
         <f>E72/4375.1-1</f>
         <v/>
       </c>
-      <c r="G72" s="280" t="n">
+      <c r="G72" s="294" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="H72" s="280" t="n">
+      <c r="H72" s="294" t="n">
         <v>95.8</v>
       </c>
-      <c r="I72" s="280">
+      <c r="I72" s="294">
         <f>G72+H72</f>
         <v/>
       </c>
-      <c r="J72" s="277" t="n">
+      <c r="J72" s="291" t="n">
         <v>48</v>
       </c>
-      <c r="K72" s="277" t="n">
+      <c r="K72" s="291" t="n">
         <v>5243</v>
       </c>
-      <c r="L72" s="277" t="n">
+      <c r="L72" s="291" t="n">
         <v>3504</v>
       </c>
-      <c r="M72" s="277" t="n">
+      <c r="M72" s="291" t="n">
         <v>448</v>
       </c>
-      <c r="N72" s="277" t="n">
+      <c r="N72" s="291" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="63">
-      <c r="C73" s="276" t="n">
+      <c r="C73" s="290" t="n">
         <v>40</v>
       </c>
-      <c r="D73" s="276" t="n">
+      <c r="D73" s="290" t="n">
         <v>24</v>
       </c>
-      <c r="E73" s="278" t="n">
+      <c r="E73" s="292" t="n">
         <v>1852</v>
       </c>
-      <c r="F73" s="279">
+      <c r="F73" s="293">
         <f>E73/4375.1-1</f>
         <v/>
       </c>
-      <c r="G73" s="278" t="n">
+      <c r="G73" s="292" t="n">
         <v>82.3</v>
       </c>
-      <c r="H73" s="278" t="n">
+      <c r="H73" s="292" t="n">
         <v>95.8</v>
       </c>
-      <c r="I73" s="278">
+      <c r="I73" s="292">
         <f>G73+H73</f>
         <v/>
       </c>
-      <c r="J73" s="276" t="n">
+      <c r="J73" s="290" t="n">
         <v>47</v>
       </c>
-      <c r="K73" s="276" t="n">
+      <c r="K73" s="290" t="n">
         <v>5241</v>
       </c>
-      <c r="L73" s="276" t="n">
+      <c r="L73" s="290" t="n">
         <v>3552</v>
       </c>
-      <c r="M73" s="276" t="n">
+      <c r="M73" s="290" t="n">
         <v>488</v>
       </c>
-      <c r="N73" s="276" t="n">
+      <c r="N73" s="290" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="63">
-      <c r="C74" s="277" t="n">
+      <c r="C74" s="291" t="n">
         <v>50</v>
       </c>
-      <c r="D74" s="277" t="n">
+      <c r="D74" s="291" t="n">
         <v>20</v>
       </c>
-      <c r="E74" s="280" t="n">
+      <c r="E74" s="294" t="n">
         <v>2041.2</v>
       </c>
-      <c r="F74" s="281">
+      <c r="F74" s="295">
         <f>E74/4375.1-1</f>
         <v/>
       </c>
-      <c r="G74" s="280" t="n">
+      <c r="G74" s="294" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="H74" s="280" t="n">
+      <c r="H74" s="294" t="n">
         <v>95.8</v>
       </c>
-      <c r="I74" s="280">
+      <c r="I74" s="294">
         <f>G74+H74</f>
         <v/>
       </c>
-      <c r="J74" s="277" t="n">
+      <c r="J74" s="291" t="n">
         <v>46</v>
       </c>
-      <c r="K74" s="277" t="n">
+      <c r="K74" s="291" t="n">
         <v>5238</v>
       </c>
-      <c r="L74" s="277" t="n">
+      <c r="L74" s="291" t="n">
         <v>3696</v>
       </c>
-      <c r="M74" s="277" t="n">
+      <c r="M74" s="291" t="n">
         <v>554</v>
       </c>
-      <c r="N74" s="277" t="n">
+      <c r="N74" s="291" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="63">
-      <c r="C75" s="276" t="n">
+      <c r="C75" s="290" t="n">
         <v>60</v>
       </c>
-      <c r="D75" s="276" t="n">
+      <c r="D75" s="290" t="n">
         <v>18</v>
       </c>
-      <c r="E75" s="278" t="n">
+      <c r="E75" s="292" t="n">
         <v>2153.9</v>
       </c>
-      <c r="F75" s="279">
+      <c r="F75" s="293">
         <f>E75/4375.1-1</f>
         <v/>
       </c>
-      <c r="G75" s="278" t="n">
+      <c r="G75" s="292" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="H75" s="278" t="n">
+      <c r="H75" s="292" t="n">
         <v>95.8</v>
       </c>
-      <c r="I75" s="278">
+      <c r="I75" s="292">
         <f>G75+H75</f>
         <v/>
       </c>
-      <c r="J75" s="276" t="n">
+      <c r="J75" s="290" t="n">
         <v>45</v>
       </c>
-      <c r="K75" s="276" t="n">
+      <c r="K75" s="290" t="n">
         <v>5236</v>
       </c>
-      <c r="L75" s="276" t="n">
+      <c r="L75" s="290" t="n">
         <v>3744</v>
       </c>
-      <c r="M75" s="276" t="n">
+      <c r="M75" s="290" t="n">
         <v>592</v>
       </c>
-      <c r="N75" s="276" t="n">
+      <c r="N75" s="290" t="n">
         <v>245</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="63">
-      <c r="C76" s="277" t="n">
+      <c r="C76" s="291" t="n">
         <v>80</v>
       </c>
-      <c r="D76" s="277" t="n">
+      <c r="D76" s="291" t="n">
         <v>17</v>
       </c>
-      <c r="E76" s="280" t="n">
+      <c r="E76" s="294" t="n">
         <v>2215.1</v>
       </c>
-      <c r="F76" s="281">
+      <c r="F76" s="295">
         <f>E76/4375.1-1</f>
         <v/>
       </c>
-      <c r="G76" s="280" t="n">
+      <c r="G76" s="294" t="n">
         <v>84.7</v>
       </c>
-      <c r="H76" s="280" t="n">
+      <c r="H76" s="294" t="n">
         <v>95.8</v>
       </c>
-      <c r="I76" s="280">
+      <c r="I76" s="294">
         <f>G76+H76</f>
         <v/>
       </c>
-      <c r="J76" s="277" t="n">
+      <c r="J76" s="291" t="n">
         <v>44</v>
       </c>
-      <c r="K76" s="277" t="n">
+      <c r="K76" s="291" t="n">
         <v>5234</v>
       </c>
-      <c r="L76" s="277" t="n">
+      <c r="L76" s="291" t="n">
         <v>3600</v>
       </c>
-      <c r="M76" s="277" t="n">
+      <c r="M76" s="291" t="n">
         <v>614</v>
       </c>
-      <c r="N76" s="277" t="n">
+      <c r="N76" s="291" t="n">
         <v>245</v>
       </c>
     </row>
@@ -11146,134 +11187,134 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="262" t="n">
+      <c r="B80" s="290" t="n">
         <v>17</v>
       </c>
-      <c r="C80" s="264" t="n">
+      <c r="C80" s="292" t="n">
         <v>2215.1</v>
       </c>
-      <c r="D80" s="264" t="n">
+      <c r="D80" s="292" t="n">
         <v>527.3</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="263" t="n">
+      <c r="B81" s="291" t="n">
         <v>18</v>
       </c>
-      <c r="C81" s="266" t="n">
+      <c r="C81" s="294" t="n">
         <v>2153.9</v>
       </c>
-      <c r="D81" s="266" t="n">
+      <c r="D81" s="294" t="n">
         <v>529.8</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="262" t="n">
+      <c r="B82" s="290" t="n">
         <v>20</v>
       </c>
-      <c r="C82" s="264" t="n">
+      <c r="C82" s="292" t="n">
         <v>2041.2</v>
       </c>
-      <c r="D82" s="264" t="n">
+      <c r="D82" s="292" t="n">
         <v>527.5</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="263" t="n">
+      <c r="B83" s="291" t="n">
         <v>24</v>
       </c>
-      <c r="C83" s="266" t="n">
+      <c r="C83" s="294" t="n">
         <v>1852</v>
       </c>
-      <c r="D83" s="266" t="n">
+      <c r="D83" s="294" t="n">
         <v>524.2</v>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="262" t="n">
+      <c r="B84" s="290" t="n">
         <v>27</v>
       </c>
-      <c r="C84" s="264" t="n">
+      <c r="C84" s="292" t="n">
         <v>1736.2</v>
       </c>
-      <c r="D84" s="264" t="n">
+      <c r="D84" s="292" t="n">
         <v>524.4</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="263" t="n">
+      <c r="B85" s="291" t="n">
         <v>29</v>
       </c>
-      <c r="C85" s="266" t="n">
+      <c r="C85" s="294" t="n">
         <v>1674.7</v>
       </c>
-      <c r="D85" s="266" t="n">
+      <c r="D85" s="294" t="n">
         <v>527.9</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="262" t="n">
+      <c r="B86" s="290" t="n">
         <v>32</v>
       </c>
-      <c r="C86" s="264" t="n">
+      <c r="C86" s="292" t="n">
         <v>1603.9</v>
       </c>
-      <c r="D86" s="264" t="n">
+      <c r="D86" s="292" t="n">
         <v>531.7</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="263" t="n">
+      <c r="B87" s="291" t="n">
         <v>34</v>
       </c>
-      <c r="C87" s="266" t="n">
+      <c r="C87" s="294" t="n">
         <v>1562.5</v>
       </c>
-      <c r="D87" s="266" t="n">
+      <c r="D87" s="294" t="n">
         <v>533.2</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="262" t="n">
+      <c r="B88" s="290" t="n">
         <v>36</v>
       </c>
-      <c r="C88" s="264" t="n">
+      <c r="C88" s="292" t="n">
         <v>1532.5</v>
       </c>
-      <c r="D88" s="264" t="n">
+      <c r="D88" s="292" t="n">
         <v>539.3</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="263" t="n">
+      <c r="B89" s="291" t="n">
         <v>39</v>
       </c>
-      <c r="C89" s="266" t="n">
+      <c r="C89" s="294" t="n">
         <v>1500.8</v>
       </c>
-      <c r="D89" s="266" t="n">
+      <c r="D89" s="294" t="n">
         <v>544.4</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="262" t="n">
+      <c r="B90" s="290" t="n">
         <v>43</v>
       </c>
-      <c r="C90" s="264" t="n">
+      <c r="C90" s="292" t="n">
         <v>1476.5</v>
       </c>
-      <c r="D90" s="264" t="n">
+      <c r="D90" s="292" t="n">
         <v>553</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="263" t="n">
+      <c r="B91" s="291" t="n">
         <v>48</v>
       </c>
-      <c r="C91" s="266" t="n">
+      <c r="C91" s="294" t="n">
         <v>1460.2</v>
       </c>
-      <c r="D91" s="266" t="n">
+      <c r="D91" s="294" t="n">
         <v>563.9</v>
       </c>
     </row>
@@ -11334,19 +11375,19 @@
           <t>Обслужено ДХ, шт</t>
         </is>
       </c>
-      <c r="D95" s="276" t="n">
-        <v>3052</v>
-      </c>
-      <c r="E95" s="276" t="n">
-        <v>3052</v>
-      </c>
-      <c r="F95" s="276" t="n">
-        <v>3052</v>
-      </c>
-      <c r="G95" s="276" t="n">
-        <v>3052</v>
-      </c>
-      <c r="H95" s="285" t="n"/>
+      <c r="D95" s="290" t="n">
+        <v>3072</v>
+      </c>
+      <c r="E95" s="290" t="n">
+        <v>3072</v>
+      </c>
+      <c r="F95" s="290" t="n">
+        <v>3072</v>
+      </c>
+      <c r="G95" s="290" t="n">
+        <v>3072</v>
+      </c>
+      <c r="H95" s="299" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="63">
       <c r="C96" s="114" t="inlineStr">
@@ -11354,19 +11395,19 @@
           <t>Волокно-км</t>
         </is>
       </c>
-      <c r="D96" s="280" t="n">
+      <c r="D96" s="294" t="n">
         <v>4375.1</v>
       </c>
-      <c r="E96" s="280" t="n">
+      <c r="E96" s="294" t="n">
         <v>1256.1</v>
       </c>
-      <c r="F96" s="280" t="n">
+      <c r="F96" s="294" t="n">
         <v>889.2</v>
       </c>
-      <c r="G96" s="280" t="n">
-        <v>1491.1</v>
-      </c>
-      <c r="H96" s="286">
+      <c r="G96" s="294" t="n">
+        <v>1495.7</v>
+      </c>
+      <c r="H96" s="300">
         <f>CHOOSE(MATCH(MIN(D96:G96),D96:G96,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11377,23 +11418,23 @@
           <t>Волокно-км на ДХ, км</t>
         </is>
       </c>
-      <c r="D97" s="287">
-        <f>D96/3052</f>
-        <v/>
-      </c>
-      <c r="E97" s="287">
-        <f>E96/3052</f>
-        <v/>
-      </c>
-      <c r="F97" s="287">
-        <f>F96/3052</f>
-        <v/>
-      </c>
-      <c r="G97" s="287">
-        <f>G96/3052</f>
-        <v/>
-      </c>
-      <c r="H97" s="285">
+      <c r="D97" s="301">
+        <f>D96/3072</f>
+        <v/>
+      </c>
+      <c r="E97" s="301">
+        <f>E96/3072</f>
+        <v/>
+      </c>
+      <c r="F97" s="301">
+        <f>F96/3072</f>
+        <v/>
+      </c>
+      <c r="G97" s="301">
+        <f>G96/3072</f>
+        <v/>
+      </c>
+      <c r="H97" s="299">
         <f>CHOOSE(MATCH(MIN(D97:G97),D97:G97,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11404,19 +11445,19 @@
           <t>Магистральный кабель, км</t>
         </is>
       </c>
-      <c r="D98" s="280" t="n">
+      <c r="D98" s="294" t="n">
         <v>109.4</v>
       </c>
-      <c r="E98" s="280" t="n">
+      <c r="E98" s="294" t="n">
         <v>76.5</v>
       </c>
-      <c r="F98" s="280" t="n">
+      <c r="F98" s="294" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="G98" s="280" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="H98" s="286">
+      <c r="G98" s="294" t="n">
+        <v>93</v>
+      </c>
+      <c r="H98" s="300">
         <f>CHOOSE(MATCH(MIN(D98:G98),D98:G98,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11427,19 +11468,19 @@
           <t>в т.ч. 8-волоконный, км</t>
         </is>
       </c>
-      <c r="D99" s="278" t="n">
+      <c r="D99" s="292" t="n">
         <v>35.1</v>
       </c>
-      <c r="E99" s="278" t="n">
+      <c r="E99" s="292" t="n">
         <v>46.7</v>
       </c>
-      <c r="F99" s="278" t="n">
+      <c r="F99" s="292" t="n">
         <v>49.5</v>
       </c>
-      <c r="G99" s="278" t="n">
+      <c r="G99" s="292" t="n">
         <v>42.7</v>
       </c>
-      <c r="H99" s="285" t="n"/>
+      <c r="H99" s="299" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1" s="63">
       <c r="C100" s="114" t="inlineStr">
@@ -11447,19 +11488,19 @@
           <t>в т.ч. 96-волоконный, км</t>
         </is>
       </c>
-      <c r="D100" s="280" t="n">
+      <c r="D100" s="294" t="n">
         <v>33.8</v>
       </c>
-      <c r="E100" s="280" t="n">
+      <c r="E100" s="294" t="n">
         <v>1.5</v>
       </c>
-      <c r="F100" s="280" t="n">
+      <c r="F100" s="294" t="n">
         <v>0.9</v>
       </c>
-      <c r="G100" s="280" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H100" s="286" t="n"/>
+      <c r="G100" s="294" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H100" s="300" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="63">
       <c r="C101" s="112" t="inlineStr">
@@ -11467,19 +11508,19 @@
           <t>Дроп-кабель, км</t>
         </is>
       </c>
-      <c r="D101" s="278" t="n">
+      <c r="D101" s="292" t="n">
         <v>95.8</v>
       </c>
-      <c r="E101" s="278" t="n">
+      <c r="E101" s="292" t="n">
         <v>170.7</v>
       </c>
-      <c r="F101" s="278" t="n">
+      <c r="F101" s="292" t="n">
         <v>244</v>
       </c>
-      <c r="G101" s="278" t="n">
-        <v>125.3</v>
-      </c>
-      <c r="H101" s="285">
+      <c r="G101" s="292" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="H101" s="299">
         <f>CHOOSE(MATCH(MIN(D101:G101),D101:G101,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11490,23 +11531,23 @@
           <t>ВСЕГО кабель + дропы, км</t>
         </is>
       </c>
-      <c r="D102" s="280">
+      <c r="D102" s="294">
         <f>D98+D101</f>
         <v/>
       </c>
-      <c r="E102" s="280">
+      <c r="E102" s="294">
         <f>E98+E101</f>
         <v/>
       </c>
-      <c r="F102" s="280">
+      <c r="F102" s="294">
         <f>F98+F101</f>
         <v/>
       </c>
-      <c r="G102" s="280">
+      <c r="G102" s="294">
         <f>G98+G101</f>
         <v/>
       </c>
-      <c r="H102" s="286">
+      <c r="H102" s="300">
         <f>CHOOSE(MATCH(MIN(D102:G102),D102:G102,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11517,19 +11558,19 @@
           <t>Средний дроп, м</t>
         </is>
       </c>
-      <c r="D103" s="276" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E103" s="276" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="F103" s="276" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="G103" s="276" t="n">
+      <c r="D103" s="290" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E103" s="290" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="F103" s="290" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G103" s="290" t="n">
         <v>39</v>
       </c>
-      <c r="H103" s="285">
+      <c r="H103" s="299">
         <f>CHOOSE(MATCH(MIN(D103:G103),D103:G103,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11540,19 +11581,19 @@
           <t>Максимальный дроп, м</t>
         </is>
       </c>
-      <c r="D104" s="277" t="n">
+      <c r="D104" s="291" t="n">
         <v>132.5</v>
       </c>
-      <c r="E104" s="277" t="n">
+      <c r="E104" s="291" t="n">
         <v>201</v>
       </c>
-      <c r="F104" s="277" t="n">
+      <c r="F104" s="291" t="n">
         <v>266</v>
       </c>
-      <c r="G104" s="277" t="n">
+      <c r="G104" s="291" t="n">
         <v>132.5</v>
       </c>
-      <c r="H104" s="286">
+      <c r="H104" s="300">
         <f>CHOOSE(MATCH(MIN(D104:G104),D104:G104,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11563,15 +11604,15 @@
           <t>Ср. маршрут волокна ДХ, м</t>
         </is>
       </c>
-      <c r="D105" s="276" t="n">
+      <c r="D105" s="290" t="n">
         <v>1361</v>
       </c>
-      <c r="E105" s="276" t="n"/>
-      <c r="F105" s="276" t="n"/>
-      <c r="G105" s="276" t="n">
+      <c r="E105" s="290" t="n"/>
+      <c r="F105" s="290" t="n"/>
+      <c r="G105" s="290" t="n">
         <v>279</v>
       </c>
-      <c r="H105" s="285">
+      <c r="H105" s="299">
         <f>CHOOSE(MATCH(MIN(D105:G105),D105:G105,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11582,19 +11623,19 @@
           <t>ОРШ, шт</t>
         </is>
       </c>
-      <c r="D106" s="277" t="n">
+      <c r="D106" s="291" t="n">
         <v>6</v>
       </c>
-      <c r="E106" s="277" t="n">
+      <c r="E106" s="291" t="n">
         <v>6</v>
       </c>
-      <c r="F106" s="277" t="n">
+      <c r="F106" s="291" t="n">
         <v>6</v>
       </c>
-      <c r="G106" s="277" t="n">
+      <c r="G106" s="291" t="n">
         <v>42</v>
       </c>
-      <c r="H106" s="286">
+      <c r="H106" s="300">
         <f>CHOOSE(MATCH(MIN(D106:G106),D106:G106,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11605,19 +11646,19 @@
           <t>РОР, шт</t>
         </is>
       </c>
-      <c r="D107" s="276" t="n">
+      <c r="D107" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="276" t="n">
+      <c r="E107" s="290" t="n">
         <v>515</v>
       </c>
-      <c r="F107" s="276" t="n">
+      <c r="F107" s="290" t="n">
         <v>323</v>
       </c>
-      <c r="G107" s="276" t="n">
+      <c r="G107" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="285" t="n"/>
+      <c r="H107" s="299" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="63">
       <c r="C108" s="114" t="inlineStr">
@@ -11625,19 +11666,19 @@
           <t>Сплиттеры 1:64, шт</t>
         </is>
       </c>
-      <c r="D108" s="277" t="n">
+      <c r="D108" s="291" t="n">
         <v>39</v>
       </c>
-      <c r="E108" s="277" t="n">
+      <c r="E108" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="277" t="n">
+      <c r="F108" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="277" t="n">
-        <v>64</v>
-      </c>
-      <c r="H108" s="286" t="n"/>
+      <c r="G108" s="291" t="n">
+        <v>65</v>
+      </c>
+      <c r="H108" s="300" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1" s="63">
       <c r="C109" s="112" t="inlineStr">
@@ -11645,19 +11686,19 @@
           <t>Сплиттеры 1:8, шт</t>
         </is>
       </c>
-      <c r="D109" s="276" t="n">
+      <c r="D109" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="276" t="n">
+      <c r="E109" s="290" t="n">
         <v>581</v>
       </c>
-      <c r="F109" s="276" t="n">
+      <c r="F109" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="276" t="n">
+      <c r="G109" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="285" t="n"/>
+      <c r="H109" s="299" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1" s="63">
       <c r="C110" s="114" t="inlineStr">
@@ -11665,19 +11706,19 @@
           <t>Сплиттеры 1:4, шт</t>
         </is>
       </c>
-      <c r="D110" s="277" t="n">
+      <c r="D110" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="277" t="n">
+      <c r="E110" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="277" t="n">
+      <c r="F110" s="291" t="n">
         <v>83</v>
       </c>
-      <c r="G110" s="277" t="n">
+      <c r="G110" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="286" t="n"/>
+      <c r="H110" s="300" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1" s="63">
       <c r="C111" s="112" t="inlineStr">
@@ -11685,19 +11726,19 @@
           <t>Сплиттеры 1:16, шт</t>
         </is>
       </c>
-      <c r="D111" s="276" t="n">
+      <c r="D111" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="276" t="n">
+      <c r="E111" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="276" t="n">
+      <c r="F111" s="290" t="n">
         <v>323</v>
       </c>
-      <c r="G111" s="276" t="n">
+      <c r="G111" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="285" t="n"/>
+      <c r="H111" s="299" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1" s="63">
       <c r="C112" s="114" t="inlineStr">
@@ -11705,19 +11746,19 @@
           <t>Муфты, шт</t>
         </is>
       </c>
-      <c r="D112" s="277" t="n">
+      <c r="D112" s="291" t="n">
         <v>1140</v>
       </c>
-      <c r="E112" s="277" t="n">
+      <c r="E112" s="291" t="n">
         <v>115</v>
       </c>
-      <c r="F112" s="277" t="n">
+      <c r="F112" s="291" t="n">
         <v>100</v>
       </c>
-      <c r="G112" s="277" t="n">
-        <v>1104</v>
-      </c>
-      <c r="H112" s="286">
+      <c r="G112" s="291" t="n">
+        <v>1103</v>
+      </c>
+      <c r="H112" s="300">
         <f>CHOOSE(MATCH(MIN(D112:G112),D112:G112,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11728,19 +11769,19 @@
           <t>Сварки, шт</t>
         </is>
       </c>
-      <c r="D113" s="276" t="n">
+      <c r="D113" s="290" t="n">
         <v>5136</v>
       </c>
-      <c r="E113" s="276" t="n">
+      <c r="E113" s="290" t="n">
         <v>2585</v>
       </c>
-      <c r="F113" s="276" t="n">
+      <c r="F113" s="290" t="n">
         <v>1552</v>
       </c>
-      <c r="G113" s="276" t="n">
-        <v>6859</v>
-      </c>
-      <c r="H113" s="285">
+      <c r="G113" s="290" t="n">
+        <v>6905</v>
+      </c>
+      <c r="H113" s="299">
         <f>CHOOSE(MATCH(MIN(D113:G113),D113:G113,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11751,19 +11792,19 @@
           <t>Коннекторы FAST, шт</t>
         </is>
       </c>
-      <c r="D114" s="277" t="n">
+      <c r="D114" s="291" t="n">
         <v>2569</v>
       </c>
-      <c r="E114" s="277" t="n">
+      <c r="E114" s="291" t="n">
         <v>5136</v>
       </c>
-      <c r="F114" s="277" t="n">
+      <c r="F114" s="291" t="n">
         <v>5136</v>
       </c>
-      <c r="G114" s="277" t="n">
-        <v>3360</v>
-      </c>
-      <c r="H114" s="286">
+      <c r="G114" s="291" t="n">
+        <v>3382</v>
+      </c>
+      <c r="H114" s="300">
         <f>CHOOSE(MATCH(MIN(D114:G114),D114:G114,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11774,19 +11815,19 @@
           <t>Порты кросса ОРШ, шт</t>
         </is>
       </c>
-      <c r="D115" s="276" t="n">
+      <c r="D115" s="290" t="n">
         <v>3600</v>
       </c>
-      <c r="E115" s="276" t="n">
+      <c r="E115" s="290" t="n">
         <v>1008</v>
       </c>
-      <c r="F115" s="276" t="n">
+      <c r="F115" s="290" t="n">
         <v>864</v>
       </c>
-      <c r="G115" s="276" t="n">
-        <v>5040</v>
-      </c>
-      <c r="H115" s="285">
+      <c r="G115" s="290" t="n">
+        <v>5184</v>
+      </c>
+      <c r="H115" s="299">
         <f>CHOOSE(MATCH(MIN(D115:G115),D115:G115,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11797,19 +11838,19 @@
           <t>Порты OLT, шт</t>
         </is>
       </c>
-      <c r="D116" s="277" t="n">
+      <c r="D116" s="291" t="n">
         <v>39</v>
       </c>
-      <c r="E116" s="277" t="n">
+      <c r="E116" s="291" t="n">
         <v>66</v>
       </c>
-      <c r="F116" s="277" t="n">
+      <c r="F116" s="291" t="n">
         <v>83</v>
       </c>
-      <c r="G116" s="277" t="n">
-        <v>64</v>
-      </c>
-      <c r="H116" s="286">
+      <c r="G116" s="291" t="n">
+        <v>65</v>
+      </c>
+      <c r="H116" s="300">
         <f>CHOOSE(MATCH(MIN(D116:G116),D116:G116,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11820,19 +11861,19 @@
           <t>Комплекты подвеса, шт</t>
         </is>
       </c>
-      <c r="D117" s="276" t="n">
+      <c r="D117" s="290" t="n">
         <v>2911</v>
       </c>
-      <c r="E117" s="276" t="n">
+      <c r="E117" s="290" t="n">
         <v>4180</v>
       </c>
-      <c r="F117" s="276" t="n">
+      <c r="F117" s="290" t="n">
         <v>6136</v>
       </c>
-      <c r="G117" s="276" t="n">
+      <c r="G117" s="290" t="n">
         <v>2472</v>
       </c>
-      <c r="H117" s="285">
+      <c r="H117" s="299">
         <f>CHOOSE(MATCH(MIN(D117:G117),D117:G117,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11843,19 +11884,19 @@
           <t>Доп. шкафы ОРШ (сверх 6), шт</t>
         </is>
       </c>
-      <c r="D118" s="277" t="n">
+      <c r="D118" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="277" t="n">
+      <c r="E118" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="277" t="n">
+      <c r="F118" s="291" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="277" t="n">
+      <c r="G118" s="291" t="n">
         <v>36</v>
       </c>
-      <c r="H118" s="286">
+      <c r="H118" s="300">
         <f>CHOOSE(MATCH(MIN(D118:G118),D118:G118,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11919,17 +11960,17 @@
           <t>Кабельная продукция (магистраль)</t>
         </is>
       </c>
-      <c r="D123" s="278" t="n">
+      <c r="D123" s="292" t="n">
         <v>233</v>
       </c>
-      <c r="E123" s="278" t="n">
+      <c r="E123" s="292" t="n">
         <v>107</v>
       </c>
-      <c r="F123" s="278" t="n">
+      <c r="F123" s="292" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="G123" s="278" t="n">
-        <v>132.3</v>
+      <c r="G123" s="292" t="n">
+        <v>132.6</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1" s="63">
@@ -11938,17 +11979,17 @@
           <t>Дроп-кабели</t>
         </is>
       </c>
-      <c r="D124" s="280" t="n">
+      <c r="D124" s="294" t="n">
         <v>47.9</v>
       </c>
-      <c r="E124" s="280" t="n">
+      <c r="E124" s="294" t="n">
         <v>85.3</v>
       </c>
-      <c r="F124" s="280" t="n">
+      <c r="F124" s="294" t="n">
         <v>122</v>
       </c>
-      <c r="G124" s="280" t="n">
-        <v>62.6</v>
+      <c r="G124" s="294" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1" s="63">
@@ -11957,17 +11998,17 @@
           <t>Оборудование и монтаж</t>
         </is>
       </c>
-      <c r="D125" s="278" t="n">
+      <c r="D125" s="292" t="n">
         <v>315</v>
       </c>
-      <c r="E125" s="278" t="n">
+      <c r="E125" s="292" t="n">
         <v>306.2</v>
       </c>
-      <c r="F125" s="278" t="n">
+      <c r="F125" s="292" t="n">
         <v>270.8</v>
       </c>
-      <c r="G125" s="278" t="n">
-        <v>368.8</v>
+      <c r="G125" s="292" t="n">
+        <v>372.6</v>
       </c>
     </row>
     <row r="126">
@@ -11999,16 +12040,16 @@
           <t>Доп. шкафы ОРШ (сверх базовых 6, по 1,5 у.е.)</t>
         </is>
       </c>
-      <c r="D127" s="280" t="n">
+      <c r="D127" s="294" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="280" t="n">
+      <c r="E127" s="294" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="280" t="n">
+      <c r="F127" s="294" t="n">
         <v>0</v>
       </c>
-      <c r="G127" s="280" t="n">
+      <c r="G127" s="294" t="n">
         <v>54</v>
       </c>
     </row>
@@ -12041,19 +12082,19 @@
           <t>Δ к лучшей схеме</t>
         </is>
       </c>
-      <c r="D129" s="279">
+      <c r="D129" s="293">
         <f>D128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="E129" s="279">
+      <c r="E129" s="293">
         <f>E128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="F129" s="279">
+      <c r="F129" s="293">
         <f>F128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="G129" s="279">
+      <c r="G129" s="293">
         <f>G128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
@@ -12098,106 +12139,106 @@
       </c>
     </row>
     <row r="133" ht="18" customHeight="1" s="63">
-      <c r="C133" s="288" t="n">
+      <c r="C133" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="D133" s="276" t="n">
+      <c r="D133" s="290" t="n">
         <v>520.2</v>
       </c>
-      <c r="E133" s="276" t="n">
+      <c r="E133" s="290" t="n">
         <v>553.4</v>
       </c>
-      <c r="F133" s="276" t="n">
+      <c r="F133" s="290" t="n">
         <v>585.9</v>
       </c>
-      <c r="G133" s="276" t="n">
-        <v>641</v>
-      </c>
-      <c r="H133" s="285">
+      <c r="G133" s="290" t="n">
+        <v>645.7</v>
+      </c>
+      <c r="H133" s="299">
         <f>CHOOSE(MATCH(MIN(D133:G133),D133:G133,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1" s="63">
-      <c r="C134" s="289" t="n">
+      <c r="C134" s="303" t="n">
         <v>0.3</v>
       </c>
-      <c r="D134" s="277" t="n">
+      <c r="D134" s="291" t="n">
         <v>545.2</v>
       </c>
-      <c r="E134" s="277" t="n">
+      <c r="E134" s="291" t="n">
         <v>510.5</v>
       </c>
-      <c r="F134" s="277" t="n">
+      <c r="F134" s="291" t="n">
         <v>511.9</v>
       </c>
-      <c r="G134" s="277" t="n">
-        <v>618.6</v>
-      </c>
-      <c r="H134" s="286">
+      <c r="G134" s="291" t="n">
+        <v>623.2</v>
+      </c>
+      <c r="H134" s="300">
         <f>CHOOSE(MATCH(MIN(D134:G134),D134:G134,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1" s="63">
-      <c r="C135" s="288" t="n">
+      <c r="C135" s="302" t="n">
         <v>0.5</v>
       </c>
-      <c r="D135" s="276" t="n">
+      <c r="D135" s="290" t="n">
         <v>595.9</v>
       </c>
-      <c r="E135" s="276" t="n">
+      <c r="E135" s="290" t="n">
         <v>498.6</v>
       </c>
-      <c r="F135" s="276" t="n">
+      <c r="F135" s="290" t="n">
         <v>481.6</v>
       </c>
-      <c r="G135" s="276" t="n">
-        <v>617.8</v>
-      </c>
-      <c r="H135" s="285">
+      <c r="G135" s="290" t="n">
+        <v>622.3</v>
+      </c>
+      <c r="H135" s="299">
         <f>CHOOSE(MATCH(MIN(D135:G135),D135:G135,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1" s="63">
-      <c r="C136" s="289" t="n">
+      <c r="C136" s="303" t="n">
         <v>0.7</v>
       </c>
-      <c r="D136" s="277" t="n">
+      <c r="D136" s="291" t="n">
         <v>688</v>
       </c>
-      <c r="E136" s="277" t="n">
+      <c r="E136" s="291" t="n">
         <v>500.1</v>
       </c>
-      <c r="F136" s="277" t="n">
+      <c r="F136" s="291" t="n">
         <v>464</v>
       </c>
-      <c r="G136" s="277" t="n">
-        <v>628.5</v>
-      </c>
-      <c r="H136" s="286">
+      <c r="G136" s="291" t="n">
+        <v>633.1</v>
+      </c>
+      <c r="H136" s="300">
         <f>CHOOSE(MATCH(MIN(D136:G136),D136:G136,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1" s="63">
-      <c r="C137" s="288" t="n">
+      <c r="C137" s="302" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="276" t="n">
+      <c r="D137" s="290" t="n">
         <v>955</v>
       </c>
-      <c r="E137" s="276" t="n">
+      <c r="E137" s="290" t="n">
         <v>531.4</v>
       </c>
-      <c r="F137" s="276" t="n">
+      <c r="F137" s="290" t="n">
         <v>459.4</v>
       </c>
-      <c r="G137" s="276" t="n">
-        <v>669.9</v>
-      </c>
-      <c r="H137" s="285">
+      <c r="G137" s="290" t="n">
+        <v>675</v>
+      </c>
+      <c r="H137" s="299">
         <f>CHOOSE(MATCH(MIN(D137:G137),D137:G137,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -13572,7 +13613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:D48"/>
+  <dimension ref="B2:D52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="62" min="1" max="1"/>
@@ -14224,10 +14265,60 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="24" customHeight="1" s="63"/>
-    <row r="50" ht="64" customHeight="1" s="63"/>
-    <row r="51" ht="78" customHeight="1" s="63"/>
-    <row r="52" ht="78" customHeight="1" s="63"/>
+    <row r="49" ht="24" customHeight="1" s="63">
+      <c r="B49" s="108" t="n"/>
+      <c r="C49" s="108" t="inlineStr">
+        <is>
+          <t>9. Сводная материалов и карты зон схемы D</t>
+        </is>
+      </c>
+      <c r="D49" s="108" t="n"/>
+    </row>
+    <row r="50" ht="64" customHeight="1" s="63">
+      <c r="B50" s="144" t="n">
+        <v>37</v>
+      </c>
+      <c r="C50" s="110" t="inlineStr">
+        <is>
+          <t>Состав позиций</t>
+        </is>
+      </c>
+      <c r="D50" s="110" t="inlineStr">
+        <is>
+          <t>Лист «Сводная (схема D)» повторяет формат сводной схемы C: 4 секции, 24 позиции, графы шести СНП и ИТОГО (формулы SUM). Отличия от каскадной схемы: нет РОР и сплиттеров 2-й ступени; добавлены зонные уличные шкафы (26 шт.) отдельной позицией; дроп-кабель без подводок РОР→ДХ (95,8 км — как в централизованной, дроп идёт от муфты напрямую); коннекторы 1,1 × ДХ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="78" customHeight="1" s="63">
+      <c r="B51" s="145" t="n">
+        <v>38</v>
+      </c>
+      <c r="C51" s="109" t="inlineStr">
+        <is>
+          <t>Нормы схемы D</t>
+        </is>
+      </c>
+      <c r="D51" s="109" t="inlineStr">
+        <is>
+          <t>Волокна участка = распределительные max(8; ceil(1,25 × ДХ потока зоны)) от ОРШ-медианы + фидерные ceil(1,25 × сплиттеры зоны) на кратчайшем пути ЦУ → зонный ОРШ (Дейкстра в границе НП); разложение 8-96 волокон. Сварки = (2 × ДХ + 2 × сплиттеры 1:64) × 1,1; пигтейли = ДХ + 2 × сплиттеры; подвесы 30/км магистрали. Ёмкости и длины кабелей — из расчёта топологии v4 (boq_decentral_data_v4.json: уточнённая детекция ДХ — сблокированные дома по крышам/заборам, квартиры многоэтажек), инварианты к схемам A/B/C по ДХ, дропам и трассе соблюдены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="78" customHeight="1" s="63">
+      <c r="B52" s="144" t="n">
+        <v>39</v>
+      </c>
+      <c r="C52" s="110" t="inlineStr">
+        <is>
+          <t>Карты зон ОРШ</t>
+        </is>
+      </c>
+      <c r="D52" s="110" t="inlineStr">
+        <is>
+          <t>Шесть карт download/snp_vko/&lt;NN&gt;_&lt;СНП&gt;_зоны_ОРШ_схема_D.jpg (спутник Google z18): цветная зона каждого ОРШ — оболочка обслуживаемых ДХ; ствол сети — серым; распределительная сеть зоны — цветом зоны; фидер ЦУ → зонный ОРШ — пунктиром цвета зоны по кратчайшей трассе; граница НП — белым пунктиром; дропы — жёлтым; муфты — бирюзовые квадраты; зонные ОРШ — цветные шкафы в центрах секторов с подписью «ОРШ-N, N ДХ»; ЦУ — красная звезда. Совмещение сети со спутником проверено (NCC 0 px, визуальный контроль).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:D2"/>

--- a/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
+++ b/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
@@ -255,7 +255,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -698,6 +698,48 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4592,7 +4634,7 @@
       <c r="L5" s="108" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1" s="63">
-      <c r="B6" s="299" t="n">
+      <c r="B6" s="313" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -4600,7 +4642,7 @@
           <t>Шкаф оптический распределительный (ОРШ) центральный — в здании ЦУ</t>
         </is>
       </c>
-      <c r="D6" s="299" t="inlineStr">
+      <c r="D6" s="313" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4610,22 +4652,22 @@
           <t>1 на СНП (здание по проекту)</t>
         </is>
       </c>
-      <c r="F6" s="290" t="n">
+      <c r="F6" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="290" t="n">
+      <c r="G6" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="290" t="n">
+      <c r="H6" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="290" t="n">
+      <c r="I6" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="290" t="n">
+      <c r="J6" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="290" t="n">
+      <c r="K6" s="304" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="146">
@@ -4634,7 +4676,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="63">
-      <c r="B7" s="300" t="n">
+      <c r="B7" s="314" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="114" t="inlineStr">
@@ -4642,7 +4684,7 @@
           <t>Шкаф зонный ОРШ уличный (под сплиттеры 1:64)</t>
         </is>
       </c>
-      <c r="D7" s="300" t="inlineStr">
+      <c r="D7" s="314" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4652,20 +4694,20 @@
           <t>1 на зону — в центре сектора (медиана зоны, зона ≥ 48 ДХ)</t>
         </is>
       </c>
-      <c r="F7" s="291" t="n">
+      <c r="F7" s="305" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="291" t="n"/>
-      <c r="H7" s="291" t="n">
+      <c r="G7" s="305" t="n"/>
+      <c r="H7" s="305" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="291" t="n">
+      <c r="I7" s="305" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="291" t="n">
+      <c r="J7" s="305" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="291" t="n">
+      <c r="K7" s="305" t="n">
         <v>6</v>
       </c>
       <c r="L7" s="147">
@@ -4674,7 +4716,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="63">
-      <c r="B8" s="299" t="n">
+      <c r="B8" s="313" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -4682,7 +4724,7 @@
           <t>Сплиттер PLC 1×64 (в ОРШ: ЦУ и зонных)</t>
         </is>
       </c>
-      <c r="D8" s="299" t="inlineStr">
+      <c r="D8" s="313" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4692,22 +4734,22 @@
           <t>ceil(ДХ зоны / 64), заполнение 75-100%</t>
         </is>
       </c>
-      <c r="F8" s="290" t="n">
+      <c r="F8" s="304" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="290" t="n">
+      <c r="G8" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="290" t="n">
+      <c r="H8" s="304" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="290" t="n">
+      <c r="I8" s="304" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="290" t="n">
+      <c r="J8" s="304" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="290" t="n">
+      <c r="K8" s="304" t="n">
         <v>13</v>
       </c>
       <c r="L8" s="146">
@@ -4716,7 +4758,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="63">
-      <c r="B9" s="300" t="n">
+      <c r="B9" s="314" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="114" t="inlineStr">
@@ -4724,7 +4766,7 @@
           <t>Пигтейль SC/UPC для кросса ОРШ</t>
         </is>
       </c>
-      <c r="D9" s="300" t="inlineStr">
+      <c r="D9" s="314" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4734,23 +4776,23 @@
           <t>ДХ + 2 × сплиттеры 1:64</t>
         </is>
       </c>
-      <c r="F9" s="291" t="n">
+      <c r="F9" s="305" t="n">
         <v>1073</v>
       </c>
-      <c r="G9" s="291" t="n">
+      <c r="G9" s="305" t="n">
         <v>128</v>
       </c>
-      <c r="H9" s="291" t="n">
+      <c r="H9" s="305" t="n">
         <v>392</v>
       </c>
-      <c r="I9" s="291" t="n">
+      <c r="I9" s="305" t="n">
         <v>650</v>
       </c>
-      <c r="J9" s="291" t="n">
+      <c r="J9" s="305" t="n">
         <v>298</v>
       </c>
-      <c r="K9" s="291" t="n">
-        <v>661</v>
+      <c r="K9" s="305" t="n">
+        <v>665</v>
       </c>
       <c r="L9" s="147">
         <f>SUM(F9:K9)</f>
@@ -4758,7 +4800,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="63">
-      <c r="B10" s="299" t="n">
+      <c r="B10" s="313" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="112" t="inlineStr">
@@ -4766,7 +4808,7 @@
           <t>Порт PON OLT — справочно (активное оборудование, единый узел OLT)</t>
         </is>
       </c>
-      <c r="D10" s="299" t="inlineStr">
+      <c r="D10" s="313" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4776,22 +4818,22 @@
           <t>по числу сплиттеров 1:64</t>
         </is>
       </c>
-      <c r="F10" s="290" t="n">
+      <c r="F10" s="304" t="n">
         <v>22</v>
       </c>
-      <c r="G10" s="290" t="n">
+      <c r="G10" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="290" t="n">
+      <c r="H10" s="304" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="290" t="n">
+      <c r="I10" s="304" t="n">
         <v>14</v>
       </c>
-      <c r="J10" s="290" t="n">
+      <c r="J10" s="304" t="n">
         <v>6</v>
       </c>
-      <c r="K10" s="290" t="n">
+      <c r="K10" s="304" t="n">
         <v>13</v>
       </c>
       <c r="L10" s="146">
@@ -4817,7 +4859,7 @@
       <c r="L11" s="108" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="63">
-      <c r="B12" s="299" t="n">
+      <c r="B12" s="313" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="112" t="inlineStr">
@@ -4825,7 +4867,7 @@
           <t>Кабель оптический самонесущий, 8 волокон</t>
         </is>
       </c>
-      <c r="D12" s="299" t="inlineStr">
+      <c r="D12" s="313" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4835,22 +4877,22 @@
           <t>распределение зоны max(8; 1,25 × ДХ потока) + фидер ceil(1,25 × сплиттеры зоны)</t>
         </is>
       </c>
-      <c r="F12" s="292" t="n">
+      <c r="F12" s="306" t="n">
         <v>16.7</v>
       </c>
-      <c r="G12" s="292" t="n">
+      <c r="G12" s="306" t="n">
         <v>2.6</v>
       </c>
-      <c r="H12" s="292" t="n">
+      <c r="H12" s="306" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="292" t="n">
+      <c r="I12" s="306" t="n">
         <v>9.9</v>
       </c>
-      <c r="J12" s="292" t="n">
+      <c r="J12" s="306" t="n">
         <v>4.5</v>
       </c>
-      <c r="K12" s="292" t="n">
+      <c r="K12" s="306" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="148">
@@ -4859,7 +4901,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="63">
-      <c r="B13" s="300" t="n">
+      <c r="B13" s="314" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="114" t="inlineStr">
@@ -4867,7 +4909,7 @@
           <t>Кабель оптический самонесущий, 12 волокон</t>
         </is>
       </c>
-      <c r="D13" s="300" t="inlineStr">
+      <c r="D13" s="314" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4877,23 +4919,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F13" s="294" t="n">
+      <c r="F13" s="308" t="n">
         <v>4.4</v>
       </c>
-      <c r="G13" s="294" t="n">
+      <c r="G13" s="308" t="n">
         <v>0.6</v>
       </c>
-      <c r="H13" s="294" t="n">
+      <c r="H13" s="308" t="n">
         <v>1.5</v>
       </c>
-      <c r="I13" s="294" t="n">
+      <c r="I13" s="308" t="n">
         <v>3.5</v>
       </c>
-      <c r="J13" s="294" t="n">
+      <c r="J13" s="308" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" s="294" t="n">
-        <v>1.2</v>
+      <c r="K13" s="308" t="n">
+        <v>1</v>
       </c>
       <c r="L13" s="149">
         <f>SUM(F13:K13)</f>
@@ -4901,7 +4943,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="63">
-      <c r="B14" s="299" t="n">
+      <c r="B14" s="313" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="112" t="inlineStr">
@@ -4909,7 +4951,7 @@
           <t>Кабель оптический самонесущий, 16 волокон</t>
         </is>
       </c>
-      <c r="D14" s="299" t="inlineStr">
+      <c r="D14" s="313" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4919,23 +4961,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F14" s="292" t="n">
+      <c r="F14" s="306" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" s="292" t="n">
+      <c r="G14" s="306" t="n">
         <v>0.5</v>
       </c>
-      <c r="H14" s="292" t="n">
+      <c r="H14" s="306" t="n">
         <v>0.5</v>
       </c>
-      <c r="I14" s="292" t="n">
+      <c r="I14" s="306" t="n">
         <v>1.6</v>
       </c>
-      <c r="J14" s="292" t="n">
+      <c r="J14" s="306" t="n">
         <v>1.3</v>
       </c>
-      <c r="K14" s="292" t="n">
-        <v>0.9</v>
+      <c r="K14" s="306" t="n">
+        <v>1.1</v>
       </c>
       <c r="L14" s="148">
         <f>SUM(F14:K14)</f>
@@ -4943,7 +4985,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="63">
-      <c r="B15" s="300" t="n">
+      <c r="B15" s="314" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="114" t="inlineStr">
@@ -4951,7 +4993,7 @@
           <t>Кабель оптический самонесущий, 24 волокна</t>
         </is>
       </c>
-      <c r="D15" s="300" t="inlineStr">
+      <c r="D15" s="314" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4961,22 +5003,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F15" s="294" t="n">
+      <c r="F15" s="308" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="294" t="n">
+      <c r="G15" s="308" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="294" t="n">
+      <c r="H15" s="308" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="294" t="n">
+      <c r="I15" s="308" t="n">
         <v>3.1</v>
       </c>
-      <c r="J15" s="294" t="n">
+      <c r="J15" s="308" t="n">
         <v>1.4</v>
       </c>
-      <c r="K15" s="294" t="n">
+      <c r="K15" s="308" t="n">
         <v>1.4</v>
       </c>
       <c r="L15" s="149">
@@ -4985,7 +5027,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="63">
-      <c r="B16" s="299" t="n">
+      <c r="B16" s="313" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="112" t="inlineStr">
@@ -4993,7 +5035,7 @@
           <t>Кабель оптический самонесущий, 32 волокна</t>
         </is>
       </c>
-      <c r="D16" s="299" t="inlineStr">
+      <c r="D16" s="313" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5003,22 +5045,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F16" s="292" t="n">
+      <c r="F16" s="306" t="n">
         <v>2.2</v>
       </c>
-      <c r="G16" s="292" t="n">
+      <c r="G16" s="306" t="n">
         <v>0.4</v>
       </c>
-      <c r="H16" s="292" t="n">
+      <c r="H16" s="306" t="n">
         <v>1.1</v>
       </c>
-      <c r="I16" s="292" t="n">
+      <c r="I16" s="306" t="n">
         <v>1.8</v>
       </c>
-      <c r="J16" s="292" t="n">
+      <c r="J16" s="306" t="n">
         <v>0.8</v>
       </c>
-      <c r="K16" s="292" t="n">
+      <c r="K16" s="306" t="n">
         <v>0.8</v>
       </c>
       <c r="L16" s="148">
@@ -5027,7 +5069,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="63">
-      <c r="B17" s="300" t="n">
+      <c r="B17" s="314" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="114" t="inlineStr">
@@ -5035,7 +5077,7 @@
           <t>Кабель оптический самонесущий, 48 волокон</t>
         </is>
       </c>
-      <c r="D17" s="300" t="inlineStr">
+      <c r="D17" s="314" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5045,22 +5087,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F17" s="294" t="n">
+      <c r="F17" s="308" t="n">
         <v>1.7</v>
       </c>
-      <c r="G17" s="294" t="n">
+      <c r="G17" s="308" t="n">
         <v>0.2</v>
       </c>
-      <c r="H17" s="294" t="n">
+      <c r="H17" s="308" t="n">
         <v>1.1</v>
       </c>
-      <c r="I17" s="294" t="n">
+      <c r="I17" s="308" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" s="294" t="n">
+      <c r="J17" s="308" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="294" t="n">
+      <c r="K17" s="308" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="149">
@@ -5069,7 +5111,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="63">
-      <c r="B18" s="299" t="n">
+      <c r="B18" s="313" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="112" t="inlineStr">
@@ -5077,7 +5119,7 @@
           <t>Кабель оптический самонесущий, 64 волокна</t>
         </is>
       </c>
-      <c r="D18" s="299" t="inlineStr">
+      <c r="D18" s="313" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5087,22 +5129,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F18" s="292" t="n">
+      <c r="F18" s="306" t="n">
         <v>0.7</v>
       </c>
-      <c r="G18" s="292" t="n">
+      <c r="G18" s="306" t="n">
         <v>0.3</v>
       </c>
-      <c r="H18" s="292" t="n">
+      <c r="H18" s="306" t="n">
         <v>0.5</v>
       </c>
-      <c r="I18" s="292" t="n">
+      <c r="I18" s="306" t="n">
         <v>0.4</v>
       </c>
-      <c r="J18" s="292" t="n">
+      <c r="J18" s="306" t="n">
         <v>0.3</v>
       </c>
-      <c r="K18" s="292" t="n">
+      <c r="K18" s="306" t="n">
         <v>0.4</v>
       </c>
       <c r="L18" s="148">
@@ -5111,7 +5153,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="63">
-      <c r="B19" s="300" t="n">
+      <c r="B19" s="314" t="n">
         <v>13</v>
       </c>
       <c r="C19" s="114" t="inlineStr">
@@ -5119,7 +5161,7 @@
           <t>Кабель оптический самонесущий, 72 волокна</t>
         </is>
       </c>
-      <c r="D19" s="300" t="inlineStr">
+      <c r="D19" s="314" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5129,15 +5171,15 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F19" s="294" t="n">
+      <c r="F19" s="308" t="n">
         <v>0.4</v>
       </c>
-      <c r="G19" s="294" t="n"/>
-      <c r="H19" s="294" t="n"/>
-      <c r="I19" s="294" t="n"/>
-      <c r="J19" s="294" t="n"/>
-      <c r="K19" s="294" t="n">
-        <v>0.2</v>
+      <c r="G19" s="308" t="n"/>
+      <c r="H19" s="308" t="n"/>
+      <c r="I19" s="308" t="n"/>
+      <c r="J19" s="308" t="n"/>
+      <c r="K19" s="308" t="n">
+        <v>0.3</v>
       </c>
       <c r="L19" s="149">
         <f>SUM(F19:K19)</f>
@@ -5145,7 +5187,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="63">
-      <c r="B20" s="299" t="n">
+      <c r="B20" s="313" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="112" t="inlineStr">
@@ -5153,7 +5195,7 @@
           <t>Кабель оптический самонесущий, 96 волокон</t>
         </is>
       </c>
-      <c r="D20" s="299" t="inlineStr">
+      <c r="D20" s="313" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5163,20 +5205,20 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F20" s="292" t="n">
+      <c r="F20" s="306" t="n">
         <v>0.1</v>
       </c>
-      <c r="G20" s="292" t="n">
+      <c r="G20" s="306" t="n">
         <v>0.1</v>
       </c>
-      <c r="H20" s="292" t="n">
+      <c r="H20" s="306" t="n">
         <v>0.2</v>
       </c>
-      <c r="I20" s="292" t="n"/>
-      <c r="J20" s="292" t="n">
+      <c r="I20" s="306" t="n"/>
+      <c r="J20" s="306" t="n">
         <v>0.1</v>
       </c>
-      <c r="K20" s="292" t="n">
+      <c r="K20" s="306" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="148">
@@ -5185,7 +5227,7 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="63">
-      <c r="B21" s="300" t="n">
+      <c r="B21" s="314" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="114" t="inlineStr">
@@ -5193,7 +5235,7 @@
           <t>Кабель дроп-кабельный самонесущий, 2 волокна (1 раб. + 1 рез.)</t>
         </is>
       </c>
-      <c r="D21" s="300" t="inlineStr">
+      <c r="D21" s="314" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5203,23 +5245,23 @@
           <t>дропы × 1,05 (без подводок — дроп от муфты напрямую)</t>
         </is>
       </c>
-      <c r="F21" s="294" t="n">
+      <c r="F21" s="308" t="n">
         <v>41.7</v>
       </c>
-      <c r="G21" s="294" t="n">
+      <c r="G21" s="308" t="n">
         <v>5.2</v>
       </c>
-      <c r="H21" s="294" t="n">
+      <c r="H21" s="308" t="n">
         <v>15.8</v>
       </c>
-      <c r="I21" s="294" t="n">
+      <c r="I21" s="308" t="n">
         <v>27.2</v>
       </c>
-      <c r="J21" s="294" t="n">
+      <c r="J21" s="308" t="n">
         <v>12.9</v>
       </c>
-      <c r="K21" s="294" t="n">
-        <v>23.3</v>
+      <c r="K21" s="308" t="n">
+        <v>23.5</v>
       </c>
       <c r="L21" s="149">
         <f>SUM(F21:K21)</f>
@@ -5227,7 +5269,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="63">
-      <c r="B22" s="299" t="n">
+      <c r="B22" s="313" t="n">
         <v>16</v>
       </c>
       <c r="C22" s="112" t="inlineStr">
@@ -5235,7 +5277,7 @@
           <t>Справочно: суммарная ёмкость магистрального кабеля</t>
         </is>
       </c>
-      <c r="D22" s="299" t="inlineStr">
+      <c r="D22" s="313" t="inlineStr">
         <is>
           <t>волокно-км</t>
         </is>
@@ -5245,23 +5287,23 @@
           <t>Σ (длина участка × волокна)</t>
         </is>
       </c>
-      <c r="F22" s="292" t="n">
+      <c r="F22" s="306" t="n">
         <v>524.8</v>
       </c>
-      <c r="G22" s="292" t="n">
+      <c r="G22" s="306" t="n">
         <v>90</v>
       </c>
-      <c r="H22" s="292" t="n">
+      <c r="H22" s="306" t="n">
         <v>218.5</v>
       </c>
-      <c r="I22" s="292" t="n">
+      <c r="I22" s="306" t="n">
         <v>329.9</v>
       </c>
-      <c r="J22" s="292" t="n">
+      <c r="J22" s="306" t="n">
         <v>141.2</v>
       </c>
-      <c r="K22" s="292" t="n">
-        <v>191.3</v>
+      <c r="K22" s="306" t="n">
+        <v>192.7</v>
       </c>
       <c r="L22" s="148">
         <f>SUM(F22:K22)</f>
@@ -5286,7 +5328,7 @@
       <c r="L23" s="108" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="63">
-      <c r="B24" s="299" t="n">
+      <c r="B24" s="313" t="n">
         <v>17</v>
       </c>
       <c r="C24" s="112" t="inlineStr">
@@ -5294,7 +5336,7 @@
           <t>Муфта оптическая (ветвления магистрали)</t>
         </is>
       </c>
-      <c r="D24" s="299" t="inlineStr">
+      <c r="D24" s="313" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5304,22 +5346,22 @@
           <t>узлы ветвления кроме точек врезов зонных ОРШ; транзит — неразрезным кабелем</t>
         </is>
       </c>
-      <c r="F24" s="290" t="n">
+      <c r="F24" s="304" t="n">
         <v>367</v>
       </c>
-      <c r="G24" s="290" t="n">
+      <c r="G24" s="304" t="n">
         <v>70</v>
       </c>
-      <c r="H24" s="290" t="n">
+      <c r="H24" s="304" t="n">
         <v>158</v>
       </c>
-      <c r="I24" s="290" t="n">
+      <c r="I24" s="304" t="n">
         <v>246</v>
       </c>
-      <c r="J24" s="290" t="n">
+      <c r="J24" s="304" t="n">
         <v>119</v>
       </c>
-      <c r="K24" s="290" t="n">
+      <c r="K24" s="304" t="n">
         <v>143</v>
       </c>
       <c r="L24" s="146">
@@ -5345,7 +5387,7 @@
       <c r="L25" s="108" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="63">
-      <c r="B26" s="299" t="n">
+      <c r="B26" s="313" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="112" t="inlineStr">
@@ -5353,7 +5395,7 @@
           <t>Бокс абонентский оптический с адаптером SC/UPC</t>
         </is>
       </c>
-      <c r="D26" s="299" t="inlineStr">
+      <c r="D26" s="313" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5363,23 +5405,23 @@
           <t>1 на ДХ</t>
         </is>
       </c>
-      <c r="F26" s="290" t="n">
+      <c r="F26" s="304" t="n">
         <v>1029</v>
       </c>
-      <c r="G26" s="290" t="n">
+      <c r="G26" s="304" t="n">
         <v>124</v>
       </c>
-      <c r="H26" s="290" t="n">
+      <c r="H26" s="304" t="n">
         <v>376</v>
       </c>
-      <c r="I26" s="290" t="n">
+      <c r="I26" s="304" t="n">
         <v>622</v>
       </c>
-      <c r="J26" s="290" t="n">
+      <c r="J26" s="304" t="n">
         <v>286</v>
       </c>
-      <c r="K26" s="290" t="n">
-        <v>635</v>
+      <c r="K26" s="304" t="n">
+        <v>639</v>
       </c>
       <c r="L26" s="146">
         <f>SUM(F26:K26)</f>
@@ -5387,7 +5429,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="63">
-      <c r="B27" s="300" t="n">
+      <c r="B27" s="314" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="114" t="inlineStr">
@@ -5395,7 +5437,7 @@
           <t>Коннектор оптический механический SC/UPC</t>
         </is>
       </c>
-      <c r="D27" s="300" t="inlineStr">
+      <c r="D27" s="314" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5405,23 +5447,23 @@
           <t>ДХ × 1,1 (абонентский бокс)</t>
         </is>
       </c>
-      <c r="F27" s="291" t="n">
+      <c r="F27" s="305" t="n">
         <v>1132</v>
       </c>
-      <c r="G27" s="291" t="n">
+      <c r="G27" s="305" t="n">
         <v>137</v>
       </c>
-      <c r="H27" s="291" t="n">
+      <c r="H27" s="305" t="n">
         <v>414</v>
       </c>
-      <c r="I27" s="291" t="n">
+      <c r="I27" s="305" t="n">
         <v>685</v>
       </c>
-      <c r="J27" s="291" t="n">
+      <c r="J27" s="305" t="n">
         <v>315</v>
       </c>
-      <c r="K27" s="291" t="n">
-        <v>699</v>
+      <c r="K27" s="305" t="n">
+        <v>703</v>
       </c>
       <c r="L27" s="147">
         <f>SUM(F27:K27)</f>
@@ -5429,7 +5471,7 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="63">
-      <c r="B28" s="299" t="n">
+      <c r="B28" s="313" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="112" t="inlineStr">
@@ -5437,7 +5479,7 @@
           <t>Сварное соединение (оценка объёма работ)</t>
         </is>
       </c>
-      <c r="D28" s="299" t="inlineStr">
+      <c r="D28" s="313" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5447,23 +5489,23 @@
           <t>(2 × ДХ + 2 × сплиттеры 1:64) × 1,1</t>
         </is>
       </c>
-      <c r="F28" s="290" t="n">
+      <c r="F28" s="304" t="n">
         <v>2313</v>
       </c>
-      <c r="G28" s="290" t="n">
+      <c r="G28" s="304" t="n">
         <v>278</v>
       </c>
-      <c r="H28" s="290" t="n">
+      <c r="H28" s="304" t="n">
         <v>845</v>
       </c>
-      <c r="I28" s="290" t="n">
+      <c r="I28" s="304" t="n">
         <v>1400</v>
       </c>
-      <c r="J28" s="290" t="n">
+      <c r="J28" s="304" t="n">
         <v>643</v>
       </c>
-      <c r="K28" s="290" t="n">
-        <v>1426</v>
+      <c r="K28" s="304" t="n">
+        <v>1435</v>
       </c>
       <c r="L28" s="146">
         <f>SUM(F28:K28)</f>
@@ -5471,7 +5513,7 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="63">
-      <c r="B29" s="300" t="n">
+      <c r="B29" s="314" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="114" t="inlineStr">
@@ -5479,7 +5521,7 @@
           <t>Гильза КДЗС, 60 мм</t>
         </is>
       </c>
-      <c r="D29" s="300" t="inlineStr">
+      <c r="D29" s="314" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5489,23 +5531,23 @@
           <t>по числу сварных соединений</t>
         </is>
       </c>
-      <c r="F29" s="291" t="n">
+      <c r="F29" s="305" t="n">
         <v>2313</v>
       </c>
-      <c r="G29" s="291" t="n">
+      <c r="G29" s="305" t="n">
         <v>278</v>
       </c>
-      <c r="H29" s="291" t="n">
+      <c r="H29" s="305" t="n">
         <v>845</v>
       </c>
-      <c r="I29" s="291" t="n">
+      <c r="I29" s="305" t="n">
         <v>1400</v>
       </c>
-      <c r="J29" s="291" t="n">
+      <c r="J29" s="305" t="n">
         <v>643</v>
       </c>
-      <c r="K29" s="291" t="n">
-        <v>1426</v>
+      <c r="K29" s="305" t="n">
+        <v>1435</v>
       </c>
       <c r="L29" s="147">
         <f>SUM(F29:K29)</f>
@@ -5513,7 +5555,7 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="63">
-      <c r="B30" s="299" t="n">
+      <c r="B30" s="313" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="112" t="inlineStr">
@@ -5521,7 +5563,7 @@
           <t>Комплект подвеса магистрального кабеля (кронштейн + спиральный зажим)</t>
         </is>
       </c>
-      <c r="D30" s="299" t="inlineStr">
+      <c r="D30" s="313" t="inlineStr">
         <is>
           <t>компл</t>
         </is>
@@ -5531,22 +5573,22 @@
           <t>30 на 1 км кабеля</t>
         </is>
       </c>
-      <c r="F30" s="290" t="n">
+      <c r="F30" s="304" t="n">
         <v>918</v>
       </c>
-      <c r="G30" s="290" t="n">
+      <c r="G30" s="304" t="n">
         <v>144</v>
       </c>
-      <c r="H30" s="290" t="n">
+      <c r="H30" s="304" t="n">
         <v>316</v>
       </c>
-      <c r="I30" s="290" t="n">
+      <c r="I30" s="304" t="n">
         <v>584</v>
       </c>
-      <c r="J30" s="290" t="n">
+      <c r="J30" s="304" t="n">
         <v>247</v>
       </c>
-      <c r="K30" s="290" t="n">
+      <c r="K30" s="304" t="n">
         <v>263</v>
       </c>
       <c r="L30" s="146">
@@ -5555,7 +5597,7 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" s="63">
-      <c r="B31" s="300" t="n">
+      <c r="B31" s="314" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="114" t="inlineStr">
@@ -5563,7 +5605,7 @@
           <t>Анкерный зажим дроп-кабеля</t>
         </is>
       </c>
-      <c r="D31" s="300" t="inlineStr">
+      <c r="D31" s="314" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5573,23 +5615,23 @@
           <t>2 на ДХ</t>
         </is>
       </c>
-      <c r="F31" s="291" t="n">
+      <c r="F31" s="305" t="n">
         <v>2058</v>
       </c>
-      <c r="G31" s="291" t="n">
+      <c r="G31" s="305" t="n">
         <v>248</v>
       </c>
-      <c r="H31" s="291" t="n">
+      <c r="H31" s="305" t="n">
         <v>752</v>
       </c>
-      <c r="I31" s="291" t="n">
+      <c r="I31" s="305" t="n">
         <v>1244</v>
       </c>
-      <c r="J31" s="291" t="n">
+      <c r="J31" s="305" t="n">
         <v>572</v>
       </c>
-      <c r="K31" s="291" t="n">
-        <v>1270</v>
+      <c r="K31" s="305" t="n">
+        <v>1278</v>
       </c>
       <c r="L31" s="147">
         <f>SUM(F31:K31)</f>
@@ -5597,7 +5639,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" s="63">
-      <c r="B32" s="299" t="n">
+      <c r="B32" s="313" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="112" t="inlineStr">
@@ -5605,7 +5647,7 @@
           <t>Крепёж дроп-кабеля (скобы / хомуты)</t>
         </is>
       </c>
-      <c r="D32" s="299" t="inlineStr">
+      <c r="D32" s="313" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5615,23 +5657,23 @@
           <t>6 на ДХ</t>
         </is>
       </c>
-      <c r="F32" s="290" t="n">
+      <c r="F32" s="304" t="n">
         <v>6174</v>
       </c>
-      <c r="G32" s="290" t="n">
+      <c r="G32" s="304" t="n">
         <v>744</v>
       </c>
-      <c r="H32" s="290" t="n">
+      <c r="H32" s="304" t="n">
         <v>2256</v>
       </c>
-      <c r="I32" s="290" t="n">
+      <c r="I32" s="304" t="n">
         <v>3732</v>
       </c>
-      <c r="J32" s="290" t="n">
+      <c r="J32" s="304" t="n">
         <v>1716</v>
       </c>
-      <c r="K32" s="290" t="n">
-        <v>3810</v>
+      <c r="K32" s="304" t="n">
+        <v>3834</v>
       </c>
       <c r="L32" s="146">
         <f>SUM(F32:K32)</f>
@@ -9299,7 +9341,7 @@
       </c>
       <c r="D14" s="109" t="inlineStr">
         <is>
-          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1496 (-69% к A); суммарная длина 216.6 км — минимум среди всех схем книги.</t>
+          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1497 (-69% к A); суммарная длина 216.8 км — минимум среди всех схем книги.</t>
         </is>
       </c>
     </row>
@@ -9380,19 +9422,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F18" s="290" t="n">
+      <c r="F18" s="304" t="n">
         <v>69</v>
       </c>
-      <c r="G18" s="290" t="n">
+      <c r="G18" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="290" t="n">
+      <c r="H18" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="290" t="n">
+      <c r="I18" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="290" t="n">
+      <c r="J18" s="304" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9408,19 +9450,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F19" s="291" t="n">
+      <c r="F19" s="305" t="n">
         <v>46</v>
       </c>
-      <c r="G19" s="291" t="n">
+      <c r="G19" s="305" t="n">
         <v>752</v>
       </c>
-      <c r="H19" s="291" t="n">
+      <c r="H19" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="291" t="n">
+      <c r="I19" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="291" t="n">
+      <c r="J19" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9436,19 +9478,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F20" s="290" t="n">
+      <c r="F20" s="304" t="n">
         <v>114</v>
       </c>
-      <c r="G20" s="290" t="n">
+      <c r="G20" s="304" t="n">
         <v>546</v>
       </c>
-      <c r="H20" s="290" t="n">
+      <c r="H20" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="290" t="n">
+      <c r="I20" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="290" t="n">
+      <c r="J20" s="304" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9464,19 +9506,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F21" s="291" t="n">
+      <c r="F21" s="305" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="291" t="n">
+      <c r="G21" s="305" t="n">
         <v>667</v>
       </c>
-      <c r="H21" s="291" t="n">
+      <c r="H21" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="291" t="n">
+      <c r="I21" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="291" t="n">
+      <c r="J21" s="305" t="n">
         <v>48</v>
       </c>
     </row>
@@ -9492,19 +9534,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F22" s="290" t="n">
+      <c r="F22" s="304" t="n">
         <v>132</v>
       </c>
-      <c r="G22" s="290" t="n">
+      <c r="G22" s="304" t="n">
         <v>717</v>
       </c>
-      <c r="H22" s="290" t="n">
+      <c r="H22" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="290" t="n">
+      <c r="I22" s="304" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="290" t="n">
+      <c r="J22" s="304" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9520,19 +9562,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F23" s="291" t="n">
+      <c r="F23" s="305" t="n">
         <v>109</v>
       </c>
-      <c r="G23" s="291" t="n">
+      <c r="G23" s="305" t="n">
         <v>856</v>
       </c>
-      <c r="H23" s="291" t="n">
+      <c r="H23" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="291" t="n">
+      <c r="I23" s="305" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="291" t="n">
+      <c r="J23" s="305" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9548,19 +9590,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F24" s="290" t="n">
+      <c r="F24" s="304" t="n">
         <v>84</v>
       </c>
-      <c r="G24" s="290" t="n">
+      <c r="G24" s="304" t="n">
         <v>908</v>
       </c>
-      <c r="H24" s="290" t="n">
+      <c r="H24" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="290" t="n">
+      <c r="I24" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="290" t="n">
+      <c r="J24" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9576,19 +9618,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F25" s="291" t="n">
+      <c r="F25" s="305" t="n">
         <v>50</v>
       </c>
-      <c r="G25" s="291" t="n">
+      <c r="G25" s="305" t="n">
         <v>1708</v>
       </c>
-      <c r="H25" s="291" t="n">
+      <c r="H25" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="291" t="n">
+      <c r="I25" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="291" t="n">
+      <c r="J25" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9604,19 +9646,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F26" s="290" t="n">
+      <c r="F26" s="304" t="n">
         <v>49</v>
       </c>
-      <c r="G26" s="290" t="n">
+      <c r="G26" s="304" t="n">
         <v>860</v>
       </c>
-      <c r="H26" s="290" t="n">
+      <c r="H26" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="290" t="n">
+      <c r="I26" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="290" t="n">
+      <c r="J26" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9632,19 +9674,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F27" s="291" t="n">
+      <c r="F27" s="305" t="n">
         <v>49</v>
       </c>
-      <c r="G27" s="291" t="n">
+      <c r="G27" s="305" t="n">
         <v>1211</v>
       </c>
-      <c r="H27" s="291" t="n">
+      <c r="H27" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="291" t="n">
+      <c r="I27" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="291" t="n">
+      <c r="J27" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9660,19 +9702,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F28" s="290" t="n">
+      <c r="F28" s="304" t="n">
         <v>88</v>
       </c>
-      <c r="G28" s="290" t="n">
+      <c r="G28" s="304" t="n">
         <v>1175</v>
       </c>
-      <c r="H28" s="290" t="n">
+      <c r="H28" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="290" t="n">
+      <c r="I28" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="290" t="n">
+      <c r="J28" s="304" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9688,19 +9730,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F29" s="291" t="n">
+      <c r="F29" s="305" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="291" t="n">
+      <c r="G29" s="305" t="n">
         <v>1169</v>
       </c>
-      <c r="H29" s="291" t="n">
+      <c r="H29" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="291" t="n">
+      <c r="I29" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="291" t="n">
+      <c r="J29" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9716,19 +9758,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F30" s="290" t="n">
+      <c r="F30" s="304" t="n">
         <v>51</v>
       </c>
-      <c r="G30" s="290" t="n">
+      <c r="G30" s="304" t="n">
         <v>1390</v>
       </c>
-      <c r="H30" s="290" t="n">
+      <c r="H30" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="290" t="n">
+      <c r="I30" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="290" t="n">
+      <c r="J30" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9744,19 +9786,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F31" s="291" t="n">
+      <c r="F31" s="305" t="n">
         <v>49</v>
       </c>
-      <c r="G31" s="291" t="n">
+      <c r="G31" s="305" t="n">
         <v>879</v>
       </c>
-      <c r="H31" s="291" t="n">
+      <c r="H31" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="291" t="n">
+      <c r="I31" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="291" t="n">
+      <c r="J31" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9772,19 +9814,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F32" s="290" t="n">
+      <c r="F32" s="304" t="n">
         <v>59</v>
       </c>
-      <c r="G32" s="290" t="n">
+      <c r="G32" s="304" t="n">
         <v>745</v>
       </c>
-      <c r="H32" s="290" t="n">
+      <c r="H32" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="290" t="n">
+      <c r="I32" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="290" t="n">
+      <c r="J32" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9804,19 +9846,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F33" s="291" t="n">
+      <c r="F33" s="305" t="n">
         <v>124</v>
       </c>
-      <c r="G33" s="291" t="n">
+      <c r="G33" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="291" t="n">
+      <c r="H33" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="291" t="n">
+      <c r="I33" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="291" t="n">
+      <c r="J33" s="305" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9836,19 +9878,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F34" s="290" t="n">
+      <c r="F34" s="304" t="n">
         <v>35</v>
       </c>
-      <c r="G34" s="290" t="n">
+      <c r="G34" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="290" t="n">
+      <c r="H34" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="290" t="n">
+      <c r="I34" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="290" t="n">
+      <c r="J34" s="304" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9864,19 +9906,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F35" s="291" t="n">
+      <c r="F35" s="305" t="n">
         <v>56</v>
       </c>
-      <c r="G35" s="291" t="n">
+      <c r="G35" s="305" t="n">
         <v>805</v>
       </c>
-      <c r="H35" s="291" t="n">
+      <c r="H35" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="291" t="n">
+      <c r="I35" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="291" t="n">
+      <c r="J35" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9892,19 +9934,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F36" s="290" t="n">
+      <c r="F36" s="304" t="n">
         <v>156</v>
       </c>
-      <c r="G36" s="290" t="n">
+      <c r="G36" s="304" t="n">
         <v>295</v>
       </c>
-      <c r="H36" s="290" t="n">
+      <c r="H36" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="290" t="n">
+      <c r="I36" s="304" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="290" t="n">
+      <c r="J36" s="304" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9920,19 +9962,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F37" s="291" t="n">
+      <c r="F37" s="305" t="n">
         <v>69</v>
       </c>
-      <c r="G37" s="291" t="n">
+      <c r="G37" s="305" t="n">
         <v>1394</v>
       </c>
-      <c r="H37" s="291" t="n">
+      <c r="H37" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="291" t="n">
+      <c r="I37" s="305" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="291" t="n">
+      <c r="J37" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9948,19 +9990,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F38" s="290" t="n">
+      <c r="F38" s="304" t="n">
         <v>60</v>
       </c>
-      <c r="G38" s="290" t="n">
+      <c r="G38" s="304" t="n">
         <v>556</v>
       </c>
-      <c r="H38" s="290" t="n">
+      <c r="H38" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="290" t="n">
+      <c r="I38" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="290" t="n">
+      <c r="J38" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9980,19 +10022,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F39" s="291" t="n">
+      <c r="F39" s="305" t="n">
         <v>27</v>
       </c>
-      <c r="G39" s="291" t="n">
+      <c r="G39" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="291" t="n">
+      <c r="H39" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="291" t="n">
+      <c r="I39" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="291" t="n">
+      <c r="J39" s="305" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10008,19 +10050,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F40" s="290" t="n">
+      <c r="F40" s="304" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="290" t="n">
+      <c r="G40" s="304" t="n">
         <v>1298</v>
       </c>
-      <c r="H40" s="290" t="n">
+      <c r="H40" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="290" t="n">
+      <c r="I40" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="290" t="n">
+      <c r="J40" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10036,19 +10078,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F41" s="291" t="n">
+      <c r="F41" s="305" t="n">
         <v>107</v>
       </c>
-      <c r="G41" s="291" t="n">
+      <c r="G41" s="305" t="n">
         <v>418</v>
       </c>
-      <c r="H41" s="291" t="n">
+      <c r="H41" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="291" t="n">
+      <c r="I41" s="305" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="291" t="n">
+      <c r="J41" s="305" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10064,19 +10106,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F42" s="290" t="n">
+      <c r="F42" s="304" t="n">
         <v>53</v>
       </c>
-      <c r="G42" s="290" t="n">
+      <c r="G42" s="304" t="n">
         <v>1329</v>
       </c>
-      <c r="H42" s="290" t="n">
+      <c r="H42" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="290" t="n">
+      <c r="I42" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="290" t="n">
+      <c r="J42" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10092,19 +10134,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F43" s="291" t="n">
+      <c r="F43" s="305" t="n">
         <v>53</v>
       </c>
-      <c r="G43" s="291" t="n">
+      <c r="G43" s="305" t="n">
         <v>937</v>
       </c>
-      <c r="H43" s="291" t="n">
+      <c r="H43" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="291" t="n">
+      <c r="I43" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="291" t="n">
+      <c r="J43" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10120,19 +10162,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F44" s="290" t="n">
+      <c r="F44" s="304" t="n">
         <v>85</v>
       </c>
-      <c r="G44" s="290" t="n">
+      <c r="G44" s="304" t="n">
         <v>368</v>
       </c>
-      <c r="H44" s="290" t="n">
+      <c r="H44" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="290" t="n">
+      <c r="I44" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="290" t="n">
+      <c r="J44" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10148,19 +10190,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F45" s="291" t="n">
+      <c r="F45" s="305" t="n">
         <v>48</v>
       </c>
-      <c r="G45" s="291" t="n">
+      <c r="G45" s="305" t="n">
         <v>1096</v>
       </c>
-      <c r="H45" s="291" t="n">
+      <c r="H45" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="291" t="n">
+      <c r="I45" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="291" t="n">
+      <c r="J45" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10176,19 +10218,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F46" s="290" t="n">
+      <c r="F46" s="304" t="n">
         <v>76</v>
       </c>
-      <c r="G46" s="290" t="n">
+      <c r="G46" s="304" t="n">
         <v>302</v>
       </c>
-      <c r="H46" s="290" t="n">
+      <c r="H46" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="290" t="n">
+      <c r="I46" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="290" t="n">
+      <c r="J46" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10204,19 +10246,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F47" s="291" t="n">
+      <c r="F47" s="305" t="n">
         <v>78</v>
       </c>
-      <c r="G47" s="291" t="n">
+      <c r="G47" s="305" t="n">
         <v>1779</v>
       </c>
-      <c r="H47" s="291" t="n">
+      <c r="H47" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="291" t="n">
+      <c r="I47" s="305" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="291" t="n">
+      <c r="J47" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10232,19 +10274,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F48" s="290" t="n">
+      <c r="F48" s="304" t="n">
         <v>50</v>
       </c>
-      <c r="G48" s="290" t="n">
+      <c r="G48" s="304" t="n">
         <v>476</v>
       </c>
-      <c r="H48" s="290" t="n">
+      <c r="H48" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="290" t="n">
+      <c r="I48" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="290" t="n">
+      <c r="J48" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10264,19 +10306,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F49" s="291" t="n">
+      <c r="F49" s="305" t="n">
         <v>70</v>
       </c>
-      <c r="G49" s="291" t="n">
+      <c r="G49" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="291" t="n">
+      <c r="H49" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="I49" s="291" t="n">
+      <c r="I49" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="291" t="n">
+      <c r="J49" s="305" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10292,19 +10334,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F50" s="290" t="n">
+      <c r="F50" s="304" t="n">
         <v>62</v>
       </c>
-      <c r="G50" s="290" t="n">
+      <c r="G50" s="304" t="n">
         <v>666</v>
       </c>
-      <c r="H50" s="290" t="n">
+      <c r="H50" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="290" t="n">
+      <c r="I50" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="290" t="n">
+      <c r="J50" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10320,19 +10362,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F51" s="291" t="n">
+      <c r="F51" s="305" t="n">
         <v>93</v>
       </c>
-      <c r="G51" s="291" t="n">
+      <c r="G51" s="305" t="n">
         <v>262</v>
       </c>
-      <c r="H51" s="291" t="n">
+      <c r="H51" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="291" t="n">
+      <c r="I51" s="305" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="291" t="n">
+      <c r="J51" s="305" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10348,19 +10390,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F52" s="290" t="n">
+      <c r="F52" s="304" t="n">
         <v>61</v>
       </c>
-      <c r="G52" s="290" t="n">
+      <c r="G52" s="304" t="n">
         <v>367</v>
       </c>
-      <c r="H52" s="290" t="n">
+      <c r="H52" s="304" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="290" t="n">
+      <c r="I52" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="290" t="n">
+      <c r="J52" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10380,19 +10422,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F53" s="291" t="n">
+      <c r="F53" s="305" t="n">
         <v>122</v>
       </c>
-      <c r="G53" s="291" t="n">
+      <c r="G53" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="291" t="n">
+      <c r="H53" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="291" t="n">
+      <c r="I53" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="291" t="n">
+      <c r="J53" s="305" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10408,19 +10450,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F54" s="290" t="n">
+      <c r="F54" s="304" t="n">
         <v>93</v>
       </c>
-      <c r="G54" s="290" t="n">
+      <c r="G54" s="304" t="n">
         <v>274</v>
       </c>
-      <c r="H54" s="290" t="n">
+      <c r="H54" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="290" t="n">
+      <c r="I54" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="290" t="n">
+      <c r="J54" s="304" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10436,19 +10478,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F55" s="291" t="n">
-        <v>141</v>
-      </c>
-      <c r="G55" s="291" t="n">
+      <c r="F55" s="305" t="n">
+        <v>145</v>
+      </c>
+      <c r="G55" s="305" t="n">
         <v>654</v>
       </c>
-      <c r="H55" s="291" t="n">
+      <c r="H55" s="305" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="291" t="n">
+      <c r="I55" s="305" t="n">
         <v>4</v>
       </c>
-      <c r="J55" s="291" t="n">
+      <c r="J55" s="305" t="n">
         <v>288</v>
       </c>
     </row>
@@ -10464,19 +10506,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F56" s="290" t="n">
+      <c r="F56" s="304" t="n">
         <v>91</v>
       </c>
-      <c r="G56" s="290" t="n">
+      <c r="G56" s="304" t="n">
         <v>336</v>
       </c>
-      <c r="H56" s="290" t="n">
+      <c r="H56" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="290" t="n">
+      <c r="I56" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="J56" s="290" t="n">
+      <c r="J56" s="304" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10492,19 +10534,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F57" s="291" t="n">
+      <c r="F57" s="305" t="n">
         <v>59</v>
       </c>
-      <c r="G57" s="291" t="n">
+      <c r="G57" s="305" t="n">
         <v>433</v>
       </c>
-      <c r="H57" s="291" t="n">
+      <c r="H57" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="291" t="n">
+      <c r="I57" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="291" t="n">
+      <c r="J57" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10520,19 +10562,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F58" s="290" t="n">
+      <c r="F58" s="304" t="n">
         <v>73</v>
       </c>
-      <c r="G58" s="290" t="n">
+      <c r="G58" s="304" t="n">
         <v>710</v>
       </c>
-      <c r="H58" s="290" t="n">
+      <c r="H58" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="290" t="n">
+      <c r="I58" s="304" t="n">
         <v>3</v>
       </c>
-      <c r="J58" s="290" t="n">
+      <c r="J58" s="304" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10548,19 +10590,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F59" s="291" t="n">
+      <c r="F59" s="305" t="n">
         <v>56</v>
       </c>
-      <c r="G59" s="291" t="n">
+      <c r="G59" s="305" t="n">
         <v>306</v>
       </c>
-      <c r="H59" s="291" t="n">
+      <c r="H59" s="305" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="291" t="n">
+      <c r="I59" s="305" t="n">
         <v>2</v>
       </c>
-      <c r="J59" s="291" t="n">
+      <c r="J59" s="305" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10683,482 +10725,482 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1" s="63">
-      <c r="C65" s="290" t="n">
+      <c r="C65" s="304" t="n">
         <v>2</v>
       </c>
-      <c r="D65" s="290" t="n">
+      <c r="D65" s="304" t="n">
         <v>48</v>
       </c>
-      <c r="E65" s="292" t="n">
+      <c r="E65" s="306" t="n">
         <v>1460.2</v>
       </c>
-      <c r="F65" s="293">
+      <c r="F65" s="307">
         <f>E65/4375.1-1</f>
         <v/>
       </c>
-      <c r="G65" s="292" t="n">
+      <c r="G65" s="306" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H65" s="292" t="n">
+      <c r="H65" s="306" t="n">
         <v>95.8</v>
       </c>
-      <c r="I65" s="292">
+      <c r="I65" s="306">
         <f>G65+H65</f>
         <v/>
       </c>
-      <c r="J65" s="290" t="n">
+      <c r="J65" s="304" t="n">
         <v>56</v>
       </c>
-      <c r="K65" s="290" t="n">
+      <c r="K65" s="304" t="n">
         <v>5261</v>
       </c>
-      <c r="L65" s="290" t="n">
+      <c r="L65" s="304" t="n">
         <v>4368</v>
       </c>
-      <c r="M65" s="290" t="n">
+      <c r="M65" s="304" t="n">
         <v>349</v>
       </c>
-      <c r="N65" s="290" t="n">
+      <c r="N65" s="304" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1" s="63">
-      <c r="C66" s="291" t="n">
+      <c r="C66" s="305" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="291" t="n">
+      <c r="D66" s="305" t="n">
         <v>43</v>
       </c>
-      <c r="E66" s="294" t="n">
+      <c r="E66" s="308" t="n">
         <v>1476.5</v>
       </c>
-      <c r="F66" s="295">
+      <c r="F66" s="309">
         <f>E66/4375.1-1</f>
         <v/>
       </c>
-      <c r="G66" s="294" t="n">
+      <c r="G66" s="308" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H66" s="294" t="n">
+      <c r="H66" s="308" t="n">
         <v>95.8</v>
       </c>
-      <c r="I66" s="294">
+      <c r="I66" s="308">
         <f>G66+H66</f>
         <v/>
       </c>
-      <c r="J66" s="291" t="n">
+      <c r="J66" s="305" t="n">
         <v>54</v>
       </c>
-      <c r="K66" s="291" t="n">
+      <c r="K66" s="305" t="n">
         <v>5255</v>
       </c>
-      <c r="L66" s="291" t="n">
+      <c r="L66" s="305" t="n">
         <v>4176</v>
       </c>
-      <c r="M66" s="291" t="n">
+      <c r="M66" s="305" t="n">
         <v>358</v>
       </c>
-      <c r="N66" s="291" t="n">
+      <c r="N66" s="305" t="n">
         <v>108</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1" s="63">
-      <c r="C67" s="290" t="n">
+      <c r="C67" s="304" t="n">
         <v>8</v>
       </c>
-      <c r="D67" s="290" t="n">
+      <c r="D67" s="304" t="n">
         <v>39</v>
       </c>
-      <c r="E67" s="292" t="n">
+      <c r="E67" s="306" t="n">
         <v>1500.8</v>
       </c>
-      <c r="F67" s="293">
+      <c r="F67" s="307">
         <f>E67/4375.1-1</f>
         <v/>
       </c>
-      <c r="G67" s="292" t="n">
+      <c r="G67" s="306" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H67" s="292" t="n">
+      <c r="H67" s="306" t="n">
         <v>95.8</v>
       </c>
-      <c r="I67" s="292">
+      <c r="I67" s="306">
         <f>G67+H67</f>
         <v/>
       </c>
-      <c r="J67" s="290" t="n">
+      <c r="J67" s="304" t="n">
         <v>53</v>
       </c>
-      <c r="K67" s="290" t="n">
+      <c r="K67" s="304" t="n">
         <v>5253</v>
       </c>
-      <c r="L67" s="290" t="n">
+      <c r="L67" s="304" t="n">
         <v>3984</v>
       </c>
-      <c r="M67" s="290" t="n">
+      <c r="M67" s="304" t="n">
         <v>368</v>
       </c>
-      <c r="N67" s="290" t="n">
+      <c r="N67" s="304" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="63">
-      <c r="C68" s="291" t="n">
+      <c r="C68" s="305" t="n">
         <v>10</v>
       </c>
-      <c r="D68" s="291" t="n">
+      <c r="D68" s="305" t="n">
         <v>36</v>
       </c>
-      <c r="E68" s="294" t="n">
+      <c r="E68" s="308" t="n">
         <v>1532.5</v>
       </c>
-      <c r="F68" s="295">
+      <c r="F68" s="309">
         <f>E68/4375.1-1</f>
         <v/>
       </c>
-      <c r="G68" s="294" t="n">
+      <c r="G68" s="308" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H68" s="294" t="n">
+      <c r="H68" s="308" t="n">
         <v>95.8</v>
       </c>
-      <c r="I68" s="294">
+      <c r="I68" s="308">
         <f>G68+H68</f>
         <v/>
       </c>
-      <c r="J68" s="291" t="n">
+      <c r="J68" s="305" t="n">
         <v>53</v>
       </c>
-      <c r="K68" s="291" t="n">
+      <c r="K68" s="305" t="n">
         <v>5253</v>
       </c>
-      <c r="L68" s="291" t="n">
+      <c r="L68" s="305" t="n">
         <v>3888</v>
       </c>
-      <c r="M68" s="291" t="n">
+      <c r="M68" s="305" t="n">
         <v>379</v>
       </c>
-      <c r="N68" s="291" t="n">
+      <c r="N68" s="305" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="63">
-      <c r="C69" s="296" t="n">
+      <c r="C69" s="310" t="n">
         <v>15</v>
       </c>
-      <c r="D69" s="296" t="n">
+      <c r="D69" s="310" t="n">
         <v>34</v>
       </c>
-      <c r="E69" s="297" t="n">
+      <c r="E69" s="311" t="n">
         <v>1562.5</v>
       </c>
-      <c r="F69" s="298">
+      <c r="F69" s="312">
         <f>E69/4375.1-1</f>
         <v/>
       </c>
-      <c r="G69" s="297" t="n">
+      <c r="G69" s="311" t="n">
         <v>80.5</v>
       </c>
-      <c r="H69" s="297" t="n">
+      <c r="H69" s="311" t="n">
         <v>95.8</v>
       </c>
-      <c r="I69" s="297">
+      <c r="I69" s="311">
         <f>G69+H69</f>
         <v/>
       </c>
-      <c r="J69" s="296" t="n">
+      <c r="J69" s="310" t="n">
         <v>52</v>
       </c>
-      <c r="K69" s="296" t="n">
+      <c r="K69" s="310" t="n">
         <v>5251</v>
       </c>
-      <c r="L69" s="296" t="n">
+      <c r="L69" s="310" t="n">
         <v>3696</v>
       </c>
-      <c r="M69" s="296" t="n">
+      <c r="M69" s="310" t="n">
         <v>388</v>
       </c>
-      <c r="N69" s="296" t="n">
+      <c r="N69" s="310" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="63">
-      <c r="C70" s="291" t="n">
+      <c r="C70" s="305" t="n">
         <v>20</v>
       </c>
-      <c r="D70" s="291" t="n">
+      <c r="D70" s="305" t="n">
         <v>32</v>
       </c>
-      <c r="E70" s="294" t="n">
+      <c r="E70" s="308" t="n">
         <v>1603.9</v>
       </c>
-      <c r="F70" s="295">
+      <c r="F70" s="309">
         <f>E70/4375.1-1</f>
         <v/>
       </c>
-      <c r="G70" s="294" t="n">
+      <c r="G70" s="308" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="H70" s="294" t="n">
+      <c r="H70" s="308" t="n">
         <v>95.8</v>
       </c>
-      <c r="I70" s="294">
+      <c r="I70" s="308">
         <f>G70+H70</f>
         <v/>
       </c>
-      <c r="J70" s="291" t="n">
+      <c r="J70" s="305" t="n">
         <v>51</v>
       </c>
-      <c r="K70" s="291" t="n">
+      <c r="K70" s="305" t="n">
         <v>5249</v>
       </c>
-      <c r="L70" s="291" t="n">
+      <c r="L70" s="305" t="n">
         <v>3696</v>
       </c>
-      <c r="M70" s="291" t="n">
+      <c r="M70" s="305" t="n">
         <v>403</v>
       </c>
-      <c r="N70" s="291" t="n">
+      <c r="N70" s="305" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="63">
-      <c r="C71" s="290" t="n">
+      <c r="C71" s="304" t="n">
         <v>25</v>
       </c>
-      <c r="D71" s="290" t="n">
+      <c r="D71" s="304" t="n">
         <v>29</v>
       </c>
-      <c r="E71" s="292" t="n">
+      <c r="E71" s="306" t="n">
         <v>1674.7</v>
       </c>
-      <c r="F71" s="293">
+      <c r="F71" s="307">
         <f>E71/4375.1-1</f>
         <v/>
       </c>
-      <c r="G71" s="292" t="n">
+      <c r="G71" s="306" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H71" s="292" t="n">
+      <c r="H71" s="306" t="n">
         <v>95.8</v>
       </c>
-      <c r="I71" s="292">
+      <c r="I71" s="306">
         <f>G71+H71</f>
         <v/>
       </c>
-      <c r="J71" s="290" t="n">
+      <c r="J71" s="304" t="n">
         <v>50</v>
       </c>
-      <c r="K71" s="290" t="n">
+      <c r="K71" s="304" t="n">
         <v>5247</v>
       </c>
-      <c r="L71" s="290" t="n">
+      <c r="L71" s="304" t="n">
         <v>3600</v>
       </c>
-      <c r="M71" s="290" t="n">
+      <c r="M71" s="304" t="n">
         <v>427</v>
       </c>
-      <c r="N71" s="290" t="n">
+      <c r="N71" s="304" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="63">
-      <c r="C72" s="291" t="n">
+      <c r="C72" s="305" t="n">
         <v>30</v>
       </c>
-      <c r="D72" s="291" t="n">
+      <c r="D72" s="305" t="n">
         <v>27</v>
       </c>
-      <c r="E72" s="294" t="n">
+      <c r="E72" s="308" t="n">
         <v>1736.2</v>
       </c>
-      <c r="F72" s="295">
+      <c r="F72" s="309">
         <f>E72/4375.1-1</f>
         <v/>
       </c>
-      <c r="G72" s="294" t="n">
+      <c r="G72" s="308" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="H72" s="294" t="n">
+      <c r="H72" s="308" t="n">
         <v>95.8</v>
       </c>
-      <c r="I72" s="294">
+      <c r="I72" s="308">
         <f>G72+H72</f>
         <v/>
       </c>
-      <c r="J72" s="291" t="n">
+      <c r="J72" s="305" t="n">
         <v>48</v>
       </c>
-      <c r="K72" s="291" t="n">
+      <c r="K72" s="305" t="n">
         <v>5243</v>
       </c>
-      <c r="L72" s="291" t="n">
+      <c r="L72" s="305" t="n">
         <v>3504</v>
       </c>
-      <c r="M72" s="291" t="n">
+      <c r="M72" s="305" t="n">
         <v>448</v>
       </c>
-      <c r="N72" s="291" t="n">
+      <c r="N72" s="305" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="63">
-      <c r="C73" s="290" t="n">
+      <c r="C73" s="304" t="n">
         <v>40</v>
       </c>
-      <c r="D73" s="290" t="n">
+      <c r="D73" s="304" t="n">
         <v>24</v>
       </c>
-      <c r="E73" s="292" t="n">
+      <c r="E73" s="306" t="n">
         <v>1852</v>
       </c>
-      <c r="F73" s="293">
+      <c r="F73" s="307">
         <f>E73/4375.1-1</f>
         <v/>
       </c>
-      <c r="G73" s="292" t="n">
+      <c r="G73" s="306" t="n">
         <v>82.3</v>
       </c>
-      <c r="H73" s="292" t="n">
+      <c r="H73" s="306" t="n">
         <v>95.8</v>
       </c>
-      <c r="I73" s="292">
+      <c r="I73" s="306">
         <f>G73+H73</f>
         <v/>
       </c>
-      <c r="J73" s="290" t="n">
+      <c r="J73" s="304" t="n">
         <v>47</v>
       </c>
-      <c r="K73" s="290" t="n">
+      <c r="K73" s="304" t="n">
         <v>5241</v>
       </c>
-      <c r="L73" s="290" t="n">
+      <c r="L73" s="304" t="n">
         <v>3552</v>
       </c>
-      <c r="M73" s="290" t="n">
+      <c r="M73" s="304" t="n">
         <v>488</v>
       </c>
-      <c r="N73" s="290" t="n">
+      <c r="N73" s="304" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="63">
-      <c r="C74" s="291" t="n">
+      <c r="C74" s="305" t="n">
         <v>50</v>
       </c>
-      <c r="D74" s="291" t="n">
+      <c r="D74" s="305" t="n">
         <v>20</v>
       </c>
-      <c r="E74" s="294" t="n">
+      <c r="E74" s="308" t="n">
         <v>2041.2</v>
       </c>
-      <c r="F74" s="295">
+      <c r="F74" s="309">
         <f>E74/4375.1-1</f>
         <v/>
       </c>
-      <c r="G74" s="294" t="n">
+      <c r="G74" s="308" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="H74" s="294" t="n">
+      <c r="H74" s="308" t="n">
         <v>95.8</v>
       </c>
-      <c r="I74" s="294">
+      <c r="I74" s="308">
         <f>G74+H74</f>
         <v/>
       </c>
-      <c r="J74" s="291" t="n">
+      <c r="J74" s="305" t="n">
         <v>46</v>
       </c>
-      <c r="K74" s="291" t="n">
+      <c r="K74" s="305" t="n">
         <v>5238</v>
       </c>
-      <c r="L74" s="291" t="n">
+      <c r="L74" s="305" t="n">
         <v>3696</v>
       </c>
-      <c r="M74" s="291" t="n">
+      <c r="M74" s="305" t="n">
         <v>554</v>
       </c>
-      <c r="N74" s="291" t="n">
+      <c r="N74" s="305" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="63">
-      <c r="C75" s="290" t="n">
+      <c r="C75" s="304" t="n">
         <v>60</v>
       </c>
-      <c r="D75" s="290" t="n">
+      <c r="D75" s="304" t="n">
         <v>18</v>
       </c>
-      <c r="E75" s="292" t="n">
+      <c r="E75" s="306" t="n">
         <v>2153.9</v>
       </c>
-      <c r="F75" s="293">
+      <c r="F75" s="307">
         <f>E75/4375.1-1</f>
         <v/>
       </c>
-      <c r="G75" s="292" t="n">
+      <c r="G75" s="306" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="H75" s="292" t="n">
+      <c r="H75" s="306" t="n">
         <v>95.8</v>
       </c>
-      <c r="I75" s="292">
+      <c r="I75" s="306">
         <f>G75+H75</f>
         <v/>
       </c>
-      <c r="J75" s="290" t="n">
+      <c r="J75" s="304" t="n">
         <v>45</v>
       </c>
-      <c r="K75" s="290" t="n">
+      <c r="K75" s="304" t="n">
         <v>5236</v>
       </c>
-      <c r="L75" s="290" t="n">
+      <c r="L75" s="304" t="n">
         <v>3744</v>
       </c>
-      <c r="M75" s="290" t="n">
+      <c r="M75" s="304" t="n">
         <v>592</v>
       </c>
-      <c r="N75" s="290" t="n">
+      <c r="N75" s="304" t="n">
         <v>245</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="63">
-      <c r="C76" s="291" t="n">
+      <c r="C76" s="305" t="n">
         <v>80</v>
       </c>
-      <c r="D76" s="291" t="n">
+      <c r="D76" s="305" t="n">
         <v>17</v>
       </c>
-      <c r="E76" s="294" t="n">
+      <c r="E76" s="308" t="n">
         <v>2215.1</v>
       </c>
-      <c r="F76" s="295">
+      <c r="F76" s="309">
         <f>E76/4375.1-1</f>
         <v/>
       </c>
-      <c r="G76" s="294" t="n">
+      <c r="G76" s="308" t="n">
         <v>84.7</v>
       </c>
-      <c r="H76" s="294" t="n">
+      <c r="H76" s="308" t="n">
         <v>95.8</v>
       </c>
-      <c r="I76" s="294">
+      <c r="I76" s="308">
         <f>G76+H76</f>
         <v/>
       </c>
-      <c r="J76" s="291" t="n">
+      <c r="J76" s="305" t="n">
         <v>44</v>
       </c>
-      <c r="K76" s="291" t="n">
+      <c r="K76" s="305" t="n">
         <v>5234</v>
       </c>
-      <c r="L76" s="291" t="n">
+      <c r="L76" s="305" t="n">
         <v>3600</v>
       </c>
-      <c r="M76" s="291" t="n">
+      <c r="M76" s="305" t="n">
         <v>614</v>
       </c>
-      <c r="N76" s="291" t="n">
+      <c r="N76" s="305" t="n">
         <v>245</v>
       </c>
     </row>
@@ -11187,134 +11229,134 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="290" t="n">
+      <c r="B80" s="304" t="n">
         <v>17</v>
       </c>
-      <c r="C80" s="292" t="n">
+      <c r="C80" s="306" t="n">
         <v>2215.1</v>
       </c>
-      <c r="D80" s="292" t="n">
+      <c r="D80" s="306" t="n">
         <v>527.3</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="291" t="n">
+      <c r="B81" s="305" t="n">
         <v>18</v>
       </c>
-      <c r="C81" s="294" t="n">
+      <c r="C81" s="308" t="n">
         <v>2153.9</v>
       </c>
-      <c r="D81" s="294" t="n">
+      <c r="D81" s="308" t="n">
         <v>529.8</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="290" t="n">
+      <c r="B82" s="304" t="n">
         <v>20</v>
       </c>
-      <c r="C82" s="292" t="n">
+      <c r="C82" s="306" t="n">
         <v>2041.2</v>
       </c>
-      <c r="D82" s="292" t="n">
+      <c r="D82" s="306" t="n">
         <v>527.5</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="291" t="n">
+      <c r="B83" s="305" t="n">
         <v>24</v>
       </c>
-      <c r="C83" s="294" t="n">
+      <c r="C83" s="308" t="n">
         <v>1852</v>
       </c>
-      <c r="D83" s="294" t="n">
+      <c r="D83" s="308" t="n">
         <v>524.2</v>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="290" t="n">
+      <c r="B84" s="304" t="n">
         <v>27</v>
       </c>
-      <c r="C84" s="292" t="n">
+      <c r="C84" s="306" t="n">
         <v>1736.2</v>
       </c>
-      <c r="D84" s="292" t="n">
+      <c r="D84" s="306" t="n">
         <v>524.4</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="291" t="n">
+      <c r="B85" s="305" t="n">
         <v>29</v>
       </c>
-      <c r="C85" s="294" t="n">
+      <c r="C85" s="308" t="n">
         <v>1674.7</v>
       </c>
-      <c r="D85" s="294" t="n">
+      <c r="D85" s="308" t="n">
         <v>527.9</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="290" t="n">
+      <c r="B86" s="304" t="n">
         <v>32</v>
       </c>
-      <c r="C86" s="292" t="n">
+      <c r="C86" s="306" t="n">
         <v>1603.9</v>
       </c>
-      <c r="D86" s="292" t="n">
+      <c r="D86" s="306" t="n">
         <v>531.7</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="291" t="n">
+      <c r="B87" s="305" t="n">
         <v>34</v>
       </c>
-      <c r="C87" s="294" t="n">
+      <c r="C87" s="308" t="n">
         <v>1562.5</v>
       </c>
-      <c r="D87" s="294" t="n">
+      <c r="D87" s="308" t="n">
         <v>533.2</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="290" t="n">
+      <c r="B88" s="304" t="n">
         <v>36</v>
       </c>
-      <c r="C88" s="292" t="n">
+      <c r="C88" s="306" t="n">
         <v>1532.5</v>
       </c>
-      <c r="D88" s="292" t="n">
+      <c r="D88" s="306" t="n">
         <v>539.3</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="291" t="n">
+      <c r="B89" s="305" t="n">
         <v>39</v>
       </c>
-      <c r="C89" s="294" t="n">
+      <c r="C89" s="308" t="n">
         <v>1500.8</v>
       </c>
-      <c r="D89" s="294" t="n">
+      <c r="D89" s="308" t="n">
         <v>544.4</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="290" t="n">
+      <c r="B90" s="304" t="n">
         <v>43</v>
       </c>
-      <c r="C90" s="292" t="n">
+      <c r="C90" s="306" t="n">
         <v>1476.5</v>
       </c>
-      <c r="D90" s="292" t="n">
+      <c r="D90" s="306" t="n">
         <v>553</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="291" t="n">
+      <c r="B91" s="305" t="n">
         <v>48</v>
       </c>
-      <c r="C91" s="294" t="n">
+      <c r="C91" s="308" t="n">
         <v>1460.2</v>
       </c>
-      <c r="D91" s="294" t="n">
+      <c r="D91" s="308" t="n">
         <v>563.9</v>
       </c>
     </row>
@@ -11375,19 +11417,19 @@
           <t>Обслужено ДХ, шт</t>
         </is>
       </c>
-      <c r="D95" s="290" t="n">
-        <v>3072</v>
-      </c>
-      <c r="E95" s="290" t="n">
-        <v>3072</v>
-      </c>
-      <c r="F95" s="290" t="n">
-        <v>3072</v>
-      </c>
-      <c r="G95" s="290" t="n">
-        <v>3072</v>
-      </c>
-      <c r="H95" s="299" t="n"/>
+      <c r="D95" s="304" t="n">
+        <v>3076</v>
+      </c>
+      <c r="E95" s="304" t="n">
+        <v>3076</v>
+      </c>
+      <c r="F95" s="304" t="n">
+        <v>3076</v>
+      </c>
+      <c r="G95" s="304" t="n">
+        <v>3076</v>
+      </c>
+      <c r="H95" s="313" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="63">
       <c r="C96" s="114" t="inlineStr">
@@ -11395,19 +11437,19 @@
           <t>Волокно-км</t>
         </is>
       </c>
-      <c r="D96" s="294" t="n">
+      <c r="D96" s="308" t="n">
         <v>4375.1</v>
       </c>
-      <c r="E96" s="294" t="n">
+      <c r="E96" s="308" t="n">
         <v>1256.1</v>
       </c>
-      <c r="F96" s="294" t="n">
+      <c r="F96" s="308" t="n">
         <v>889.2</v>
       </c>
-      <c r="G96" s="294" t="n">
-        <v>1495.7</v>
-      </c>
-      <c r="H96" s="300">
+      <c r="G96" s="308" t="n">
+        <v>1497.1</v>
+      </c>
+      <c r="H96" s="314">
         <f>CHOOSE(MATCH(MIN(D96:G96),D96:G96,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11418,23 +11460,23 @@
           <t>Волокно-км на ДХ, км</t>
         </is>
       </c>
-      <c r="D97" s="301">
-        <f>D96/3072</f>
-        <v/>
-      </c>
-      <c r="E97" s="301">
-        <f>E96/3072</f>
-        <v/>
-      </c>
-      <c r="F97" s="301">
-        <f>F96/3072</f>
-        <v/>
-      </c>
-      <c r="G97" s="301">
-        <f>G96/3072</f>
-        <v/>
-      </c>
-      <c r="H97" s="299">
+      <c r="D97" s="315">
+        <f>D96/3076</f>
+        <v/>
+      </c>
+      <c r="E97" s="315">
+        <f>E96/3076</f>
+        <v/>
+      </c>
+      <c r="F97" s="315">
+        <f>F96/3076</f>
+        <v/>
+      </c>
+      <c r="G97" s="315">
+        <f>G96/3076</f>
+        <v/>
+      </c>
+      <c r="H97" s="313">
         <f>CHOOSE(MATCH(MIN(D97:G97),D97:G97,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11445,19 +11487,19 @@
           <t>Магистральный кабель, км</t>
         </is>
       </c>
-      <c r="D98" s="294" t="n">
+      <c r="D98" s="308" t="n">
         <v>109.4</v>
       </c>
-      <c r="E98" s="294" t="n">
+      <c r="E98" s="308" t="n">
         <v>76.5</v>
       </c>
-      <c r="F98" s="294" t="n">
+      <c r="F98" s="308" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="G98" s="294" t="n">
-        <v>93</v>
-      </c>
-      <c r="H98" s="300">
+      <c r="G98" s="308" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H98" s="314">
         <f>CHOOSE(MATCH(MIN(D98:G98),D98:G98,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11468,19 +11510,19 @@
           <t>в т.ч. 8-волоконный, км</t>
         </is>
       </c>
-      <c r="D99" s="292" t="n">
+      <c r="D99" s="306" t="n">
         <v>35.1</v>
       </c>
-      <c r="E99" s="292" t="n">
+      <c r="E99" s="306" t="n">
         <v>46.7</v>
       </c>
-      <c r="F99" s="292" t="n">
+      <c r="F99" s="306" t="n">
         <v>49.5</v>
       </c>
-      <c r="G99" s="292" t="n">
+      <c r="G99" s="306" t="n">
         <v>42.7</v>
       </c>
-      <c r="H99" s="299" t="n"/>
+      <c r="H99" s="313" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1" s="63">
       <c r="C100" s="114" t="inlineStr">
@@ -11488,19 +11530,19 @@
           <t>в т.ч. 96-волоконный, км</t>
         </is>
       </c>
-      <c r="D100" s="294" t="n">
+      <c r="D100" s="308" t="n">
         <v>33.8</v>
       </c>
-      <c r="E100" s="294" t="n">
+      <c r="E100" s="308" t="n">
         <v>1.5</v>
       </c>
-      <c r="F100" s="294" t="n">
+      <c r="F100" s="308" t="n">
         <v>0.9</v>
       </c>
-      <c r="G100" s="294" t="n">
+      <c r="G100" s="308" t="n">
         <v>0.7</v>
       </c>
-      <c r="H100" s="300" t="n"/>
+      <c r="H100" s="314" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="63">
       <c r="C101" s="112" t="inlineStr">
@@ -11508,19 +11550,19 @@
           <t>Дроп-кабель, км</t>
         </is>
       </c>
-      <c r="D101" s="292" t="n">
+      <c r="D101" s="306" t="n">
         <v>95.8</v>
       </c>
-      <c r="E101" s="292" t="n">
+      <c r="E101" s="306" t="n">
         <v>170.7</v>
       </c>
-      <c r="F101" s="292" t="n">
+      <c r="F101" s="306" t="n">
         <v>244</v>
       </c>
-      <c r="G101" s="292" t="n">
-        <v>126.1</v>
-      </c>
-      <c r="H101" s="299">
+      <c r="G101" s="306" t="n">
+        <v>126.3</v>
+      </c>
+      <c r="H101" s="313">
         <f>CHOOSE(MATCH(MIN(D101:G101),D101:G101,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11531,23 +11573,23 @@
           <t>ВСЕГО кабель + дропы, км</t>
         </is>
       </c>
-      <c r="D102" s="294">
+      <c r="D102" s="308">
         <f>D98+D101</f>
         <v/>
       </c>
-      <c r="E102" s="294">
+      <c r="E102" s="308">
         <f>E98+E101</f>
         <v/>
       </c>
-      <c r="F102" s="294">
+      <c r="F102" s="308">
         <f>F98+F101</f>
         <v/>
       </c>
-      <c r="G102" s="294">
+      <c r="G102" s="308">
         <f>G98+G101</f>
         <v/>
       </c>
-      <c r="H102" s="300">
+      <c r="H102" s="314">
         <f>CHOOSE(MATCH(MIN(D102:G102),D102:G102,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11558,19 +11600,19 @@
           <t>Средний дроп, м</t>
         </is>
       </c>
-      <c r="D103" s="290" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E103" s="290" t="n">
+      <c r="D103" s="304" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E103" s="304" t="n">
         <v>52.8</v>
       </c>
-      <c r="F103" s="290" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="G103" s="290" t="n">
+      <c r="F103" s="304" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G103" s="304" t="n">
         <v>39</v>
       </c>
-      <c r="H103" s="299">
+      <c r="H103" s="313">
         <f>CHOOSE(MATCH(MIN(D103:G103),D103:G103,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11581,19 +11623,19 @@
           <t>Максимальный дроп, м</t>
         </is>
       </c>
-      <c r="D104" s="291" t="n">
+      <c r="D104" s="305" t="n">
         <v>132.5</v>
       </c>
-      <c r="E104" s="291" t="n">
+      <c r="E104" s="305" t="n">
         <v>201</v>
       </c>
-      <c r="F104" s="291" t="n">
+      <c r="F104" s="305" t="n">
         <v>266</v>
       </c>
-      <c r="G104" s="291" t="n">
+      <c r="G104" s="305" t="n">
         <v>132.5</v>
       </c>
-      <c r="H104" s="300">
+      <c r="H104" s="314">
         <f>CHOOSE(MATCH(MIN(D104:G104),D104:G104,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11604,15 +11646,15 @@
           <t>Ср. маршрут волокна ДХ, м</t>
         </is>
       </c>
-      <c r="D105" s="290" t="n">
+      <c r="D105" s="304" t="n">
         <v>1361</v>
       </c>
-      <c r="E105" s="290" t="n"/>
-      <c r="F105" s="290" t="n"/>
-      <c r="G105" s="290" t="n">
+      <c r="E105" s="304" t="n"/>
+      <c r="F105" s="304" t="n"/>
+      <c r="G105" s="304" t="n">
         <v>279</v>
       </c>
-      <c r="H105" s="299">
+      <c r="H105" s="313">
         <f>CHOOSE(MATCH(MIN(D105:G105),D105:G105,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11623,19 +11665,19 @@
           <t>ОРШ, шт</t>
         </is>
       </c>
-      <c r="D106" s="291" t="n">
+      <c r="D106" s="305" t="n">
         <v>6</v>
       </c>
-      <c r="E106" s="291" t="n">
+      <c r="E106" s="305" t="n">
         <v>6</v>
       </c>
-      <c r="F106" s="291" t="n">
+      <c r="F106" s="305" t="n">
         <v>6</v>
       </c>
-      <c r="G106" s="291" t="n">
+      <c r="G106" s="305" t="n">
         <v>42</v>
       </c>
-      <c r="H106" s="300">
+      <c r="H106" s="314">
         <f>CHOOSE(MATCH(MIN(D106:G106),D106:G106,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11646,19 +11688,19 @@
           <t>РОР, шт</t>
         </is>
       </c>
-      <c r="D107" s="290" t="n">
+      <c r="D107" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="290" t="n">
+      <c r="E107" s="304" t="n">
         <v>515</v>
       </c>
-      <c r="F107" s="290" t="n">
+      <c r="F107" s="304" t="n">
         <v>323</v>
       </c>
-      <c r="G107" s="290" t="n">
+      <c r="G107" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="299" t="n"/>
+      <c r="H107" s="313" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="63">
       <c r="C108" s="114" t="inlineStr">
@@ -11666,19 +11708,19 @@
           <t>Сплиттеры 1:64, шт</t>
         </is>
       </c>
-      <c r="D108" s="291" t="n">
+      <c r="D108" s="305" t="n">
         <v>39</v>
       </c>
-      <c r="E108" s="291" t="n">
+      <c r="E108" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="291" t="n">
+      <c r="F108" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="291" t="n">
+      <c r="G108" s="305" t="n">
         <v>65</v>
       </c>
-      <c r="H108" s="300" t="n"/>
+      <c r="H108" s="314" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1" s="63">
       <c r="C109" s="112" t="inlineStr">
@@ -11686,19 +11728,19 @@
           <t>Сплиттеры 1:8, шт</t>
         </is>
       </c>
-      <c r="D109" s="290" t="n">
+      <c r="D109" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="290" t="n">
+      <c r="E109" s="304" t="n">
         <v>581</v>
       </c>
-      <c r="F109" s="290" t="n">
+      <c r="F109" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="290" t="n">
+      <c r="G109" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="299" t="n"/>
+      <c r="H109" s="313" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1" s="63">
       <c r="C110" s="114" t="inlineStr">
@@ -11706,19 +11748,19 @@
           <t>Сплиттеры 1:4, шт</t>
         </is>
       </c>
-      <c r="D110" s="291" t="n">
+      <c r="D110" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="291" t="n">
+      <c r="E110" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="291" t="n">
+      <c r="F110" s="305" t="n">
         <v>83</v>
       </c>
-      <c r="G110" s="291" t="n">
+      <c r="G110" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="300" t="n"/>
+      <c r="H110" s="314" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1" s="63">
       <c r="C111" s="112" t="inlineStr">
@@ -11726,19 +11768,19 @@
           <t>Сплиттеры 1:16, шт</t>
         </is>
       </c>
-      <c r="D111" s="290" t="n">
+      <c r="D111" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="290" t="n">
+      <c r="E111" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="290" t="n">
+      <c r="F111" s="304" t="n">
         <v>323</v>
       </c>
-      <c r="G111" s="290" t="n">
+      <c r="G111" s="304" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="299" t="n"/>
+      <c r="H111" s="313" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1" s="63">
       <c r="C112" s="114" t="inlineStr">
@@ -11746,19 +11788,19 @@
           <t>Муфты, шт</t>
         </is>
       </c>
-      <c r="D112" s="291" t="n">
+      <c r="D112" s="305" t="n">
         <v>1140</v>
       </c>
-      <c r="E112" s="291" t="n">
+      <c r="E112" s="305" t="n">
         <v>115</v>
       </c>
-      <c r="F112" s="291" t="n">
+      <c r="F112" s="305" t="n">
         <v>100</v>
       </c>
-      <c r="G112" s="291" t="n">
+      <c r="G112" s="305" t="n">
         <v>1103</v>
       </c>
-      <c r="H112" s="300">
+      <c r="H112" s="314">
         <f>CHOOSE(MATCH(MIN(D112:G112),D112:G112,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11769,19 +11811,19 @@
           <t>Сварки, шт</t>
         </is>
       </c>
-      <c r="D113" s="290" t="n">
+      <c r="D113" s="304" t="n">
         <v>5136</v>
       </c>
-      <c r="E113" s="290" t="n">
+      <c r="E113" s="304" t="n">
         <v>2585</v>
       </c>
-      <c r="F113" s="290" t="n">
+      <c r="F113" s="304" t="n">
         <v>1552</v>
       </c>
-      <c r="G113" s="290" t="n">
-        <v>6905</v>
-      </c>
-      <c r="H113" s="299">
+      <c r="G113" s="304" t="n">
+        <v>6914</v>
+      </c>
+      <c r="H113" s="313">
         <f>CHOOSE(MATCH(MIN(D113:G113),D113:G113,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11792,19 +11834,19 @@
           <t>Коннекторы FAST, шт</t>
         </is>
       </c>
-      <c r="D114" s="291" t="n">
+      <c r="D114" s="305" t="n">
         <v>2569</v>
       </c>
-      <c r="E114" s="291" t="n">
+      <c r="E114" s="305" t="n">
         <v>5136</v>
       </c>
-      <c r="F114" s="291" t="n">
+      <c r="F114" s="305" t="n">
         <v>5136</v>
       </c>
-      <c r="G114" s="291" t="n">
-        <v>3382</v>
-      </c>
-      <c r="H114" s="300">
+      <c r="G114" s="305" t="n">
+        <v>3386</v>
+      </c>
+      <c r="H114" s="314">
         <f>CHOOSE(MATCH(MIN(D114:G114),D114:G114,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11815,19 +11857,19 @@
           <t>Порты кросса ОРШ, шт</t>
         </is>
       </c>
-      <c r="D115" s="290" t="n">
+      <c r="D115" s="304" t="n">
         <v>3600</v>
       </c>
-      <c r="E115" s="290" t="n">
+      <c r="E115" s="304" t="n">
         <v>1008</v>
       </c>
-      <c r="F115" s="290" t="n">
+      <c r="F115" s="304" t="n">
         <v>864</v>
       </c>
-      <c r="G115" s="290" t="n">
+      <c r="G115" s="304" t="n">
         <v>5184</v>
       </c>
-      <c r="H115" s="299">
+      <c r="H115" s="313">
         <f>CHOOSE(MATCH(MIN(D115:G115),D115:G115,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11838,19 +11880,19 @@
           <t>Порты OLT, шт</t>
         </is>
       </c>
-      <c r="D116" s="291" t="n">
+      <c r="D116" s="305" t="n">
         <v>39</v>
       </c>
-      <c r="E116" s="291" t="n">
+      <c r="E116" s="305" t="n">
         <v>66</v>
       </c>
-      <c r="F116" s="291" t="n">
+      <c r="F116" s="305" t="n">
         <v>83</v>
       </c>
-      <c r="G116" s="291" t="n">
+      <c r="G116" s="305" t="n">
         <v>65</v>
       </c>
-      <c r="H116" s="300">
+      <c r="H116" s="314">
         <f>CHOOSE(MATCH(MIN(D116:G116),D116:G116,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11861,19 +11903,19 @@
           <t>Комплекты подвеса, шт</t>
         </is>
       </c>
-      <c r="D117" s="290" t="n">
+      <c r="D117" s="304" t="n">
         <v>2911</v>
       </c>
-      <c r="E117" s="290" t="n">
+      <c r="E117" s="304" t="n">
         <v>4180</v>
       </c>
-      <c r="F117" s="290" t="n">
+      <c r="F117" s="304" t="n">
         <v>6136</v>
       </c>
-      <c r="G117" s="290" t="n">
+      <c r="G117" s="304" t="n">
         <v>2472</v>
       </c>
-      <c r="H117" s="299">
+      <c r="H117" s="313">
         <f>CHOOSE(MATCH(MIN(D117:G117),D117:G117,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11884,19 +11926,19 @@
           <t>Доп. шкафы ОРШ (сверх 6), шт</t>
         </is>
       </c>
-      <c r="D118" s="291" t="n">
+      <c r="D118" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="291" t="n">
+      <c r="E118" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="291" t="n">
+      <c r="F118" s="305" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="291" t="n">
+      <c r="G118" s="305" t="n">
         <v>36</v>
       </c>
-      <c r="H118" s="300">
+      <c r="H118" s="314">
         <f>CHOOSE(MATCH(MIN(D118:G118),D118:G118,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11960,17 +12002,17 @@
           <t>Кабельная продукция (магистраль)</t>
         </is>
       </c>
-      <c r="D123" s="292" t="n">
+      <c r="D123" s="306" t="n">
         <v>233</v>
       </c>
-      <c r="E123" s="292" t="n">
+      <c r="E123" s="306" t="n">
         <v>107</v>
       </c>
-      <c r="F123" s="292" t="n">
+      <c r="F123" s="306" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="G123" s="292" t="n">
-        <v>132.6</v>
+      <c r="G123" s="306" t="n">
+        <v>133</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1" s="63">
@@ -11979,17 +12021,17 @@
           <t>Дроп-кабели</t>
         </is>
       </c>
-      <c r="D124" s="294" t="n">
+      <c r="D124" s="308" t="n">
         <v>47.9</v>
       </c>
-      <c r="E124" s="294" t="n">
+      <c r="E124" s="308" t="n">
         <v>85.3</v>
       </c>
-      <c r="F124" s="294" t="n">
+      <c r="F124" s="308" t="n">
         <v>122</v>
       </c>
-      <c r="G124" s="294" t="n">
-        <v>63</v>
+      <c r="G124" s="308" t="n">
+        <v>63.1</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1" s="63">
@@ -11998,17 +12040,17 @@
           <t>Оборудование и монтаж</t>
         </is>
       </c>
-      <c r="D125" s="292" t="n">
+      <c r="D125" s="306" t="n">
         <v>315</v>
       </c>
-      <c r="E125" s="292" t="n">
+      <c r="E125" s="306" t="n">
         <v>306.2</v>
       </c>
-      <c r="F125" s="292" t="n">
+      <c r="F125" s="306" t="n">
         <v>270.8</v>
       </c>
-      <c r="G125" s="292" t="n">
-        <v>372.6</v>
+      <c r="G125" s="306" t="n">
+        <v>372.7</v>
       </c>
     </row>
     <row r="126">
@@ -12040,16 +12082,16 @@
           <t>Доп. шкафы ОРШ (сверх базовых 6, по 1,5 у.е.)</t>
         </is>
       </c>
-      <c r="D127" s="294" t="n">
+      <c r="D127" s="308" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="294" t="n">
+      <c r="E127" s="308" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="294" t="n">
+      <c r="F127" s="308" t="n">
         <v>0</v>
       </c>
-      <c r="G127" s="294" t="n">
+      <c r="G127" s="308" t="n">
         <v>54</v>
       </c>
     </row>
@@ -12082,19 +12124,19 @@
           <t>Δ к лучшей схеме</t>
         </is>
       </c>
-      <c r="D129" s="293">
+      <c r="D129" s="307">
         <f>D128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="E129" s="293">
+      <c r="E129" s="307">
         <f>E128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="F129" s="293">
+      <c r="F129" s="307">
         <f>F128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="G129" s="293">
+      <c r="G129" s="307">
         <f>G128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
@@ -12139,106 +12181,106 @@
       </c>
     </row>
     <row r="133" ht="18" customHeight="1" s="63">
-      <c r="C133" s="302" t="n">
+      <c r="C133" s="316" t="n">
         <v>0</v>
       </c>
-      <c r="D133" s="290" t="n">
+      <c r="D133" s="304" t="n">
         <v>520.2</v>
       </c>
-      <c r="E133" s="290" t="n">
+      <c r="E133" s="304" t="n">
         <v>553.4</v>
       </c>
-      <c r="F133" s="290" t="n">
+      <c r="F133" s="304" t="n">
         <v>585.9</v>
       </c>
-      <c r="G133" s="290" t="n">
-        <v>645.7</v>
-      </c>
-      <c r="H133" s="299">
+      <c r="G133" s="304" t="n">
+        <v>646.1</v>
+      </c>
+      <c r="H133" s="313">
         <f>CHOOSE(MATCH(MIN(D133:G133),D133:G133,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1" s="63">
-      <c r="C134" s="303" t="n">
+      <c r="C134" s="317" t="n">
         <v>0.3</v>
       </c>
-      <c r="D134" s="291" t="n">
+      <c r="D134" s="305" t="n">
         <v>545.2</v>
       </c>
-      <c r="E134" s="291" t="n">
+      <c r="E134" s="305" t="n">
         <v>510.5</v>
       </c>
-      <c r="F134" s="291" t="n">
+      <c r="F134" s="305" t="n">
         <v>511.9</v>
       </c>
-      <c r="G134" s="291" t="n">
-        <v>623.2</v>
-      </c>
-      <c r="H134" s="300">
+      <c r="G134" s="305" t="n">
+        <v>623.6</v>
+      </c>
+      <c r="H134" s="314">
         <f>CHOOSE(MATCH(MIN(D134:G134),D134:G134,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1" s="63">
-      <c r="C135" s="302" t="n">
+      <c r="C135" s="316" t="n">
         <v>0.5</v>
       </c>
-      <c r="D135" s="290" t="n">
+      <c r="D135" s="304" t="n">
         <v>595.9</v>
       </c>
-      <c r="E135" s="290" t="n">
+      <c r="E135" s="304" t="n">
         <v>498.6</v>
       </c>
-      <c r="F135" s="290" t="n">
+      <c r="F135" s="304" t="n">
         <v>481.6</v>
       </c>
-      <c r="G135" s="290" t="n">
-        <v>622.3</v>
-      </c>
-      <c r="H135" s="299">
+      <c r="G135" s="304" t="n">
+        <v>622.9</v>
+      </c>
+      <c r="H135" s="313">
         <f>CHOOSE(MATCH(MIN(D135:G135),D135:G135,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1" s="63">
-      <c r="C136" s="303" t="n">
+      <c r="C136" s="317" t="n">
         <v>0.7</v>
       </c>
-      <c r="D136" s="291" t="n">
+      <c r="D136" s="305" t="n">
         <v>688</v>
       </c>
-      <c r="E136" s="291" t="n">
+      <c r="E136" s="305" t="n">
         <v>500.1</v>
       </c>
-      <c r="F136" s="291" t="n">
+      <c r="F136" s="305" t="n">
         <v>464</v>
       </c>
-      <c r="G136" s="291" t="n">
-        <v>633.1</v>
-      </c>
-      <c r="H136" s="300">
+      <c r="G136" s="305" t="n">
+        <v>633.8</v>
+      </c>
+      <c r="H136" s="314">
         <f>CHOOSE(MATCH(MIN(D136:G136),D136:G136,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1" s="63">
-      <c r="C137" s="302" t="n">
+      <c r="C137" s="316" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="290" t="n">
+      <c r="D137" s="304" t="n">
         <v>955</v>
       </c>
-      <c r="E137" s="290" t="n">
+      <c r="E137" s="304" t="n">
         <v>531.4</v>
       </c>
-      <c r="F137" s="290" t="n">
+      <c r="F137" s="304" t="n">
         <v>459.4</v>
       </c>
-      <c r="G137" s="290" t="n">
-        <v>675</v>
-      </c>
-      <c r="H137" s="299">
+      <c r="G137" s="304" t="n">
+        <v>676.2</v>
+      </c>
+      <c r="H137" s="313">
         <f>CHOOSE(MATCH(MIN(D137:G137),D137:G137,0),"A","B","C","D")</f>
         <v/>
       </c>

--- a/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
+++ b/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
@@ -255,7 +255,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="318">
+  <cellXfs count="332">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -698,6 +698,48 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4634,7 +4676,7 @@
       <c r="L5" s="108" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1" s="63">
-      <c r="B6" s="313" t="n">
+      <c r="B6" s="327" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -4642,7 +4684,7 @@
           <t>Шкаф оптический распределительный (ОРШ) центральный — в здании ЦУ</t>
         </is>
       </c>
-      <c r="D6" s="313" t="inlineStr">
+      <c r="D6" s="327" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4652,22 +4694,22 @@
           <t>1 на СНП (здание по проекту)</t>
         </is>
       </c>
-      <c r="F6" s="304" t="n">
+      <c r="F6" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="304" t="n">
+      <c r="G6" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="304" t="n">
+      <c r="H6" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="304" t="n">
+      <c r="I6" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="304" t="n">
+      <c r="J6" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="304" t="n">
+      <c r="K6" s="318" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="146">
@@ -4676,7 +4718,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="63">
-      <c r="B7" s="314" t="n">
+      <c r="B7" s="328" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="114" t="inlineStr">
@@ -4684,7 +4726,7 @@
           <t>Шкаф зонный ОРШ уличный (под сплиттеры 1:64)</t>
         </is>
       </c>
-      <c r="D7" s="314" t="inlineStr">
+      <c r="D7" s="328" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4694,20 +4736,20 @@
           <t>1 на зону — в центре сектора (медиана зоны, зона ≥ 48 ДХ)</t>
         </is>
       </c>
-      <c r="F7" s="305" t="n">
+      <c r="F7" s="319" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="305" t="n"/>
-      <c r="H7" s="305" t="n">
+      <c r="G7" s="319" t="n"/>
+      <c r="H7" s="319" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="305" t="n">
+      <c r="I7" s="319" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="305" t="n">
+      <c r="J7" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="305" t="n">
+      <c r="K7" s="319" t="n">
         <v>6</v>
       </c>
       <c r="L7" s="147">
@@ -4716,7 +4758,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="63">
-      <c r="B8" s="313" t="n">
+      <c r="B8" s="327" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -4724,7 +4766,7 @@
           <t>Сплиттер PLC 1×64 (в ОРШ: ЦУ и зонных)</t>
         </is>
       </c>
-      <c r="D8" s="313" t="inlineStr">
+      <c r="D8" s="327" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4734,22 +4776,22 @@
           <t>ceil(ДХ зоны / 64), заполнение 75-100%</t>
         </is>
       </c>
-      <c r="F8" s="304" t="n">
+      <c r="F8" s="318" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="304" t="n">
+      <c r="G8" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="304" t="n">
+      <c r="H8" s="318" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="304" t="n">
+      <c r="I8" s="318" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="304" t="n">
+      <c r="J8" s="318" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="304" t="n">
+      <c r="K8" s="318" t="n">
         <v>13</v>
       </c>
       <c r="L8" s="146">
@@ -4758,7 +4800,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="63">
-      <c r="B9" s="314" t="n">
+      <c r="B9" s="328" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="114" t="inlineStr">
@@ -4766,7 +4808,7 @@
           <t>Пигтейль SC/UPC для кросса ОРШ</t>
         </is>
       </c>
-      <c r="D9" s="314" t="inlineStr">
+      <c r="D9" s="328" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4776,23 +4818,23 @@
           <t>ДХ + 2 × сплиттеры 1:64</t>
         </is>
       </c>
-      <c r="F9" s="305" t="n">
+      <c r="F9" s="319" t="n">
         <v>1073</v>
       </c>
-      <c r="G9" s="305" t="n">
+      <c r="G9" s="319" t="n">
         <v>128</v>
       </c>
-      <c r="H9" s="305" t="n">
+      <c r="H9" s="319" t="n">
         <v>392</v>
       </c>
-      <c r="I9" s="305" t="n">
+      <c r="I9" s="319" t="n">
         <v>650</v>
       </c>
-      <c r="J9" s="305" t="n">
+      <c r="J9" s="319" t="n">
         <v>298</v>
       </c>
-      <c r="K9" s="305" t="n">
-        <v>665</v>
+      <c r="K9" s="319" t="n">
+        <v>676</v>
       </c>
       <c r="L9" s="147">
         <f>SUM(F9:K9)</f>
@@ -4800,7 +4842,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="63">
-      <c r="B10" s="313" t="n">
+      <c r="B10" s="327" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="112" t="inlineStr">
@@ -4808,7 +4850,7 @@
           <t>Порт PON OLT — справочно (активное оборудование, единый узел OLT)</t>
         </is>
       </c>
-      <c r="D10" s="313" t="inlineStr">
+      <c r="D10" s="327" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4818,22 +4860,22 @@
           <t>по числу сплиттеров 1:64</t>
         </is>
       </c>
-      <c r="F10" s="304" t="n">
+      <c r="F10" s="318" t="n">
         <v>22</v>
       </c>
-      <c r="G10" s="304" t="n">
+      <c r="G10" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="304" t="n">
+      <c r="H10" s="318" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="304" t="n">
+      <c r="I10" s="318" t="n">
         <v>14</v>
       </c>
-      <c r="J10" s="304" t="n">
+      <c r="J10" s="318" t="n">
         <v>6</v>
       </c>
-      <c r="K10" s="304" t="n">
+      <c r="K10" s="318" t="n">
         <v>13</v>
       </c>
       <c r="L10" s="146">
@@ -4859,7 +4901,7 @@
       <c r="L11" s="108" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="63">
-      <c r="B12" s="313" t="n">
+      <c r="B12" s="327" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="112" t="inlineStr">
@@ -4867,7 +4909,7 @@
           <t>Кабель оптический самонесущий, 8 волокон</t>
         </is>
       </c>
-      <c r="D12" s="313" t="inlineStr">
+      <c r="D12" s="327" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4877,22 +4919,22 @@
           <t>распределение зоны max(8; 1,25 × ДХ потока) + фидер ceil(1,25 × сплиттеры зоны)</t>
         </is>
       </c>
-      <c r="F12" s="306" t="n">
+      <c r="F12" s="320" t="n">
         <v>16.7</v>
       </c>
-      <c r="G12" s="306" t="n">
+      <c r="G12" s="320" t="n">
         <v>2.6</v>
       </c>
-      <c r="H12" s="306" t="n">
+      <c r="H12" s="320" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="306" t="n">
+      <c r="I12" s="320" t="n">
         <v>9.9</v>
       </c>
-      <c r="J12" s="306" t="n">
+      <c r="J12" s="320" t="n">
         <v>4.5</v>
       </c>
-      <c r="K12" s="306" t="n">
+      <c r="K12" s="320" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="148">
@@ -4901,7 +4943,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="63">
-      <c r="B13" s="314" t="n">
+      <c r="B13" s="328" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="114" t="inlineStr">
@@ -4909,7 +4951,7 @@
           <t>Кабель оптический самонесущий, 12 волокон</t>
         </is>
       </c>
-      <c r="D13" s="314" t="inlineStr">
+      <c r="D13" s="328" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4919,23 +4961,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F13" s="308" t="n">
+      <c r="F13" s="322" t="n">
         <v>4.4</v>
       </c>
-      <c r="G13" s="308" t="n">
+      <c r="G13" s="322" t="n">
         <v>0.6</v>
       </c>
-      <c r="H13" s="308" t="n">
+      <c r="H13" s="322" t="n">
         <v>1.5</v>
       </c>
-      <c r="I13" s="308" t="n">
+      <c r="I13" s="322" t="n">
         <v>3.5</v>
       </c>
-      <c r="J13" s="308" t="n">
+      <c r="J13" s="322" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" s="308" t="n">
-        <v>1</v>
+      <c r="K13" s="322" t="n">
+        <v>0.9</v>
       </c>
       <c r="L13" s="149">
         <f>SUM(F13:K13)</f>
@@ -4943,7 +4985,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="63">
-      <c r="B14" s="313" t="n">
+      <c r="B14" s="327" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="112" t="inlineStr">
@@ -4951,7 +4993,7 @@
           <t>Кабель оптический самонесущий, 16 волокон</t>
         </is>
       </c>
-      <c r="D14" s="313" t="inlineStr">
+      <c r="D14" s="327" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4961,22 +5003,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F14" s="306" t="n">
+      <c r="F14" s="320" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" s="306" t="n">
+      <c r="G14" s="320" t="n">
         <v>0.5</v>
       </c>
-      <c r="H14" s="306" t="n">
+      <c r="H14" s="320" t="n">
         <v>0.5</v>
       </c>
-      <c r="I14" s="306" t="n">
+      <c r="I14" s="320" t="n">
         <v>1.6</v>
       </c>
-      <c r="J14" s="306" t="n">
+      <c r="J14" s="320" t="n">
         <v>1.3</v>
       </c>
-      <c r="K14" s="306" t="n">
+      <c r="K14" s="320" t="n">
         <v>1.1</v>
       </c>
       <c r="L14" s="148">
@@ -4985,7 +5027,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="63">
-      <c r="B15" s="314" t="n">
+      <c r="B15" s="328" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="114" t="inlineStr">
@@ -4993,7 +5035,7 @@
           <t>Кабель оптический самонесущий, 24 волокна</t>
         </is>
       </c>
-      <c r="D15" s="314" t="inlineStr">
+      <c r="D15" s="328" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5003,22 +5045,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F15" s="308" t="n">
+      <c r="F15" s="322" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="308" t="n">
+      <c r="G15" s="322" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="308" t="n">
+      <c r="H15" s="322" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="308" t="n">
+      <c r="I15" s="322" t="n">
         <v>3.1</v>
       </c>
-      <c r="J15" s="308" t="n">
+      <c r="J15" s="322" t="n">
         <v>1.4</v>
       </c>
-      <c r="K15" s="308" t="n">
+      <c r="K15" s="322" t="n">
         <v>1.4</v>
       </c>
       <c r="L15" s="149">
@@ -5027,7 +5069,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="63">
-      <c r="B16" s="313" t="n">
+      <c r="B16" s="327" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="112" t="inlineStr">
@@ -5035,7 +5077,7 @@
           <t>Кабель оптический самонесущий, 32 волокна</t>
         </is>
       </c>
-      <c r="D16" s="313" t="inlineStr">
+      <c r="D16" s="327" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5045,23 +5087,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F16" s="306" t="n">
+      <c r="F16" s="320" t="n">
         <v>2.2</v>
       </c>
-      <c r="G16" s="306" t="n">
+      <c r="G16" s="320" t="n">
         <v>0.4</v>
       </c>
-      <c r="H16" s="306" t="n">
+      <c r="H16" s="320" t="n">
         <v>1.1</v>
       </c>
-      <c r="I16" s="306" t="n">
+      <c r="I16" s="320" t="n">
         <v>1.8</v>
       </c>
-      <c r="J16" s="306" t="n">
+      <c r="J16" s="320" t="n">
         <v>0.8</v>
       </c>
-      <c r="K16" s="306" t="n">
-        <v>0.8</v>
+      <c r="K16" s="320" t="n">
+        <v>0.9</v>
       </c>
       <c r="L16" s="148">
         <f>SUM(F16:K16)</f>
@@ -5069,7 +5111,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="63">
-      <c r="B17" s="314" t="n">
+      <c r="B17" s="328" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="114" t="inlineStr">
@@ -5077,7 +5119,7 @@
           <t>Кабель оптический самонесущий, 48 волокон</t>
         </is>
       </c>
-      <c r="D17" s="314" t="inlineStr">
+      <c r="D17" s="328" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5087,22 +5129,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F17" s="308" t="n">
+      <c r="F17" s="322" t="n">
         <v>1.7</v>
       </c>
-      <c r="G17" s="308" t="n">
+      <c r="G17" s="322" t="n">
         <v>0.2</v>
       </c>
-      <c r="H17" s="308" t="n">
+      <c r="H17" s="322" t="n">
         <v>1.1</v>
       </c>
-      <c r="I17" s="308" t="n">
+      <c r="I17" s="322" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" s="308" t="n">
+      <c r="J17" s="322" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="308" t="n">
+      <c r="K17" s="322" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="149">
@@ -5111,7 +5153,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="63">
-      <c r="B18" s="313" t="n">
+      <c r="B18" s="327" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="112" t="inlineStr">
@@ -5119,7 +5161,7 @@
           <t>Кабель оптический самонесущий, 64 волокна</t>
         </is>
       </c>
-      <c r="D18" s="313" t="inlineStr">
+      <c r="D18" s="327" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5129,22 +5171,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F18" s="306" t="n">
+      <c r="F18" s="320" t="n">
         <v>0.7</v>
       </c>
-      <c r="G18" s="306" t="n">
+      <c r="G18" s="320" t="n">
         <v>0.3</v>
       </c>
-      <c r="H18" s="306" t="n">
+      <c r="H18" s="320" t="n">
         <v>0.5</v>
       </c>
-      <c r="I18" s="306" t="n">
+      <c r="I18" s="320" t="n">
         <v>0.4</v>
       </c>
-      <c r="J18" s="306" t="n">
+      <c r="J18" s="320" t="n">
         <v>0.3</v>
       </c>
-      <c r="K18" s="306" t="n">
+      <c r="K18" s="320" t="n">
         <v>0.4</v>
       </c>
       <c r="L18" s="148">
@@ -5153,7 +5195,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="63">
-      <c r="B19" s="314" t="n">
+      <c r="B19" s="328" t="n">
         <v>13</v>
       </c>
       <c r="C19" s="114" t="inlineStr">
@@ -5161,7 +5203,7 @@
           <t>Кабель оптический самонесущий, 72 волокна</t>
         </is>
       </c>
-      <c r="D19" s="314" t="inlineStr">
+      <c r="D19" s="328" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5171,14 +5213,14 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F19" s="308" t="n">
+      <c r="F19" s="322" t="n">
         <v>0.4</v>
       </c>
-      <c r="G19" s="308" t="n"/>
-      <c r="H19" s="308" t="n"/>
-      <c r="I19" s="308" t="n"/>
-      <c r="J19" s="308" t="n"/>
-      <c r="K19" s="308" t="n">
+      <c r="G19" s="322" t="n"/>
+      <c r="H19" s="322" t="n"/>
+      <c r="I19" s="322" t="n"/>
+      <c r="J19" s="322" t="n"/>
+      <c r="K19" s="322" t="n">
         <v>0.3</v>
       </c>
       <c r="L19" s="149">
@@ -5187,7 +5229,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="63">
-      <c r="B20" s="313" t="n">
+      <c r="B20" s="327" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="112" t="inlineStr">
@@ -5195,7 +5237,7 @@
           <t>Кабель оптический самонесущий, 96 волокон</t>
         </is>
       </c>
-      <c r="D20" s="313" t="inlineStr">
+      <c r="D20" s="327" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5205,20 +5247,20 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F20" s="306" t="n">
+      <c r="F20" s="320" t="n">
         <v>0.1</v>
       </c>
-      <c r="G20" s="306" t="n">
+      <c r="G20" s="320" t="n">
         <v>0.1</v>
       </c>
-      <c r="H20" s="306" t="n">
+      <c r="H20" s="320" t="n">
         <v>0.2</v>
       </c>
-      <c r="I20" s="306" t="n"/>
-      <c r="J20" s="306" t="n">
+      <c r="I20" s="320" t="n"/>
+      <c r="J20" s="320" t="n">
         <v>0.1</v>
       </c>
-      <c r="K20" s="306" t="n">
+      <c r="K20" s="320" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="148">
@@ -5227,7 +5269,7 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="63">
-      <c r="B21" s="314" t="n">
+      <c r="B21" s="328" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="114" t="inlineStr">
@@ -5235,7 +5277,7 @@
           <t>Кабель дроп-кабельный самонесущий, 2 волокна (1 раб. + 1 рез.)</t>
         </is>
       </c>
-      <c r="D21" s="314" t="inlineStr">
+      <c r="D21" s="328" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5245,23 +5287,23 @@
           <t>дропы × 1,05 (без подводок — дроп от муфты напрямую)</t>
         </is>
       </c>
-      <c r="F21" s="308" t="n">
+      <c r="F21" s="322" t="n">
         <v>41.7</v>
       </c>
-      <c r="G21" s="308" t="n">
+      <c r="G21" s="322" t="n">
         <v>5.2</v>
       </c>
-      <c r="H21" s="308" t="n">
+      <c r="H21" s="322" t="n">
         <v>15.8</v>
       </c>
-      <c r="I21" s="308" t="n">
+      <c r="I21" s="322" t="n">
         <v>27.2</v>
       </c>
-      <c r="J21" s="308" t="n">
+      <c r="J21" s="322" t="n">
         <v>12.9</v>
       </c>
-      <c r="K21" s="308" t="n">
-        <v>23.5</v>
+      <c r="K21" s="322" t="n">
+        <v>24</v>
       </c>
       <c r="L21" s="149">
         <f>SUM(F21:K21)</f>
@@ -5269,7 +5311,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="63">
-      <c r="B22" s="313" t="n">
+      <c r="B22" s="327" t="n">
         <v>16</v>
       </c>
       <c r="C22" s="112" t="inlineStr">
@@ -5277,7 +5319,7 @@
           <t>Справочно: суммарная ёмкость магистрального кабеля</t>
         </is>
       </c>
-      <c r="D22" s="313" t="inlineStr">
+      <c r="D22" s="327" t="inlineStr">
         <is>
           <t>волокно-км</t>
         </is>
@@ -5287,23 +5329,23 @@
           <t>Σ (длина участка × волокна)</t>
         </is>
       </c>
-      <c r="F22" s="306" t="n">
+      <c r="F22" s="320" t="n">
         <v>524.8</v>
       </c>
-      <c r="G22" s="306" t="n">
+      <c r="G22" s="320" t="n">
         <v>90</v>
       </c>
-      <c r="H22" s="306" t="n">
+      <c r="H22" s="320" t="n">
         <v>218.5</v>
       </c>
-      <c r="I22" s="306" t="n">
+      <c r="I22" s="320" t="n">
         <v>329.9</v>
       </c>
-      <c r="J22" s="306" t="n">
+      <c r="J22" s="320" t="n">
         <v>141.2</v>
       </c>
-      <c r="K22" s="306" t="n">
-        <v>192.7</v>
+      <c r="K22" s="320" t="n">
+        <v>193.9</v>
       </c>
       <c r="L22" s="148">
         <f>SUM(F22:K22)</f>
@@ -5328,7 +5370,7 @@
       <c r="L23" s="108" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="63">
-      <c r="B24" s="313" t="n">
+      <c r="B24" s="327" t="n">
         <v>17</v>
       </c>
       <c r="C24" s="112" t="inlineStr">
@@ -5336,7 +5378,7 @@
           <t>Муфта оптическая (ветвления магистрали)</t>
         </is>
       </c>
-      <c r="D24" s="313" t="inlineStr">
+      <c r="D24" s="327" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5346,22 +5388,22 @@
           <t>узлы ветвления кроме точек врезов зонных ОРШ; транзит — неразрезным кабелем</t>
         </is>
       </c>
-      <c r="F24" s="304" t="n">
+      <c r="F24" s="318" t="n">
         <v>367</v>
       </c>
-      <c r="G24" s="304" t="n">
+      <c r="G24" s="318" t="n">
         <v>70</v>
       </c>
-      <c r="H24" s="304" t="n">
+      <c r="H24" s="318" t="n">
         <v>158</v>
       </c>
-      <c r="I24" s="304" t="n">
+      <c r="I24" s="318" t="n">
         <v>246</v>
       </c>
-      <c r="J24" s="304" t="n">
+      <c r="J24" s="318" t="n">
         <v>119</v>
       </c>
-      <c r="K24" s="304" t="n">
+      <c r="K24" s="318" t="n">
         <v>143</v>
       </c>
       <c r="L24" s="146">
@@ -5387,7 +5429,7 @@
       <c r="L25" s="108" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="63">
-      <c r="B26" s="313" t="n">
+      <c r="B26" s="327" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="112" t="inlineStr">
@@ -5395,7 +5437,7 @@
           <t>Бокс абонентский оптический с адаптером SC/UPC</t>
         </is>
       </c>
-      <c r="D26" s="313" t="inlineStr">
+      <c r="D26" s="327" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5405,23 +5447,23 @@
           <t>1 на ДХ</t>
         </is>
       </c>
-      <c r="F26" s="304" t="n">
+      <c r="F26" s="318" t="n">
         <v>1029</v>
       </c>
-      <c r="G26" s="304" t="n">
+      <c r="G26" s="318" t="n">
         <v>124</v>
       </c>
-      <c r="H26" s="304" t="n">
+      <c r="H26" s="318" t="n">
         <v>376</v>
       </c>
-      <c r="I26" s="304" t="n">
+      <c r="I26" s="318" t="n">
         <v>622</v>
       </c>
-      <c r="J26" s="304" t="n">
+      <c r="J26" s="318" t="n">
         <v>286</v>
       </c>
-      <c r="K26" s="304" t="n">
-        <v>639</v>
+      <c r="K26" s="318" t="n">
+        <v>650</v>
       </c>
       <c r="L26" s="146">
         <f>SUM(F26:K26)</f>
@@ -5429,7 +5471,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="63">
-      <c r="B27" s="314" t="n">
+      <c r="B27" s="328" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="114" t="inlineStr">
@@ -5437,7 +5479,7 @@
           <t>Коннектор оптический механический SC/UPC</t>
         </is>
       </c>
-      <c r="D27" s="314" t="inlineStr">
+      <c r="D27" s="328" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5447,23 +5489,23 @@
           <t>ДХ × 1,1 (абонентский бокс)</t>
         </is>
       </c>
-      <c r="F27" s="305" t="n">
+      <c r="F27" s="319" t="n">
         <v>1132</v>
       </c>
-      <c r="G27" s="305" t="n">
+      <c r="G27" s="319" t="n">
         <v>137</v>
       </c>
-      <c r="H27" s="305" t="n">
+      <c r="H27" s="319" t="n">
         <v>414</v>
       </c>
-      <c r="I27" s="305" t="n">
+      <c r="I27" s="319" t="n">
         <v>685</v>
       </c>
-      <c r="J27" s="305" t="n">
+      <c r="J27" s="319" t="n">
         <v>315</v>
       </c>
-      <c r="K27" s="305" t="n">
-        <v>703</v>
+      <c r="K27" s="319" t="n">
+        <v>715</v>
       </c>
       <c r="L27" s="147">
         <f>SUM(F27:K27)</f>
@@ -5471,7 +5513,7 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="63">
-      <c r="B28" s="313" t="n">
+      <c r="B28" s="327" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="112" t="inlineStr">
@@ -5479,7 +5521,7 @@
           <t>Сварное соединение (оценка объёма работ)</t>
         </is>
       </c>
-      <c r="D28" s="313" t="inlineStr">
+      <c r="D28" s="327" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5489,23 +5531,23 @@
           <t>(2 × ДХ + 2 × сплиттеры 1:64) × 1,1</t>
         </is>
       </c>
-      <c r="F28" s="304" t="n">
+      <c r="F28" s="318" t="n">
         <v>2313</v>
       </c>
-      <c r="G28" s="304" t="n">
+      <c r="G28" s="318" t="n">
         <v>278</v>
       </c>
-      <c r="H28" s="304" t="n">
+      <c r="H28" s="318" t="n">
         <v>845</v>
       </c>
-      <c r="I28" s="304" t="n">
+      <c r="I28" s="318" t="n">
         <v>1400</v>
       </c>
-      <c r="J28" s="304" t="n">
+      <c r="J28" s="318" t="n">
         <v>643</v>
       </c>
-      <c r="K28" s="304" t="n">
-        <v>1435</v>
+      <c r="K28" s="318" t="n">
+        <v>1459</v>
       </c>
       <c r="L28" s="146">
         <f>SUM(F28:K28)</f>
@@ -5513,7 +5555,7 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="63">
-      <c r="B29" s="314" t="n">
+      <c r="B29" s="328" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="114" t="inlineStr">
@@ -5521,7 +5563,7 @@
           <t>Гильза КДЗС, 60 мм</t>
         </is>
       </c>
-      <c r="D29" s="314" t="inlineStr">
+      <c r="D29" s="328" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5531,23 +5573,23 @@
           <t>по числу сварных соединений</t>
         </is>
       </c>
-      <c r="F29" s="305" t="n">
+      <c r="F29" s="319" t="n">
         <v>2313</v>
       </c>
-      <c r="G29" s="305" t="n">
+      <c r="G29" s="319" t="n">
         <v>278</v>
       </c>
-      <c r="H29" s="305" t="n">
+      <c r="H29" s="319" t="n">
         <v>845</v>
       </c>
-      <c r="I29" s="305" t="n">
+      <c r="I29" s="319" t="n">
         <v>1400</v>
       </c>
-      <c r="J29" s="305" t="n">
+      <c r="J29" s="319" t="n">
         <v>643</v>
       </c>
-      <c r="K29" s="305" t="n">
-        <v>1435</v>
+      <c r="K29" s="319" t="n">
+        <v>1459</v>
       </c>
       <c r="L29" s="147">
         <f>SUM(F29:K29)</f>
@@ -5555,7 +5597,7 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="63">
-      <c r="B30" s="313" t="n">
+      <c r="B30" s="327" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="112" t="inlineStr">
@@ -5563,7 +5605,7 @@
           <t>Комплект подвеса магистрального кабеля (кронштейн + спиральный зажим)</t>
         </is>
       </c>
-      <c r="D30" s="313" t="inlineStr">
+      <c r="D30" s="327" t="inlineStr">
         <is>
           <t>компл</t>
         </is>
@@ -5573,22 +5615,22 @@
           <t>30 на 1 км кабеля</t>
         </is>
       </c>
-      <c r="F30" s="304" t="n">
+      <c r="F30" s="318" t="n">
         <v>918</v>
       </c>
-      <c r="G30" s="304" t="n">
+      <c r="G30" s="318" t="n">
         <v>144</v>
       </c>
-      <c r="H30" s="304" t="n">
+      <c r="H30" s="318" t="n">
         <v>316</v>
       </c>
-      <c r="I30" s="304" t="n">
+      <c r="I30" s="318" t="n">
         <v>584</v>
       </c>
-      <c r="J30" s="304" t="n">
+      <c r="J30" s="318" t="n">
         <v>247</v>
       </c>
-      <c r="K30" s="304" t="n">
+      <c r="K30" s="318" t="n">
         <v>263</v>
       </c>
       <c r="L30" s="146">
@@ -5597,7 +5639,7 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" s="63">
-      <c r="B31" s="314" t="n">
+      <c r="B31" s="328" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="114" t="inlineStr">
@@ -5605,7 +5647,7 @@
           <t>Анкерный зажим дроп-кабеля</t>
         </is>
       </c>
-      <c r="D31" s="314" t="inlineStr">
+      <c r="D31" s="328" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5615,23 +5657,23 @@
           <t>2 на ДХ</t>
         </is>
       </c>
-      <c r="F31" s="305" t="n">
+      <c r="F31" s="319" t="n">
         <v>2058</v>
       </c>
-      <c r="G31" s="305" t="n">
+      <c r="G31" s="319" t="n">
         <v>248</v>
       </c>
-      <c r="H31" s="305" t="n">
+      <c r="H31" s="319" t="n">
         <v>752</v>
       </c>
-      <c r="I31" s="305" t="n">
+      <c r="I31" s="319" t="n">
         <v>1244</v>
       </c>
-      <c r="J31" s="305" t="n">
+      <c r="J31" s="319" t="n">
         <v>572</v>
       </c>
-      <c r="K31" s="305" t="n">
-        <v>1278</v>
+      <c r="K31" s="319" t="n">
+        <v>1300</v>
       </c>
       <c r="L31" s="147">
         <f>SUM(F31:K31)</f>
@@ -5639,7 +5681,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" s="63">
-      <c r="B32" s="313" t="n">
+      <c r="B32" s="327" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="112" t="inlineStr">
@@ -5647,7 +5689,7 @@
           <t>Крепёж дроп-кабеля (скобы / хомуты)</t>
         </is>
       </c>
-      <c r="D32" s="313" t="inlineStr">
+      <c r="D32" s="327" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5657,23 +5699,23 @@
           <t>6 на ДХ</t>
         </is>
       </c>
-      <c r="F32" s="304" t="n">
+      <c r="F32" s="318" t="n">
         <v>6174</v>
       </c>
-      <c r="G32" s="304" t="n">
+      <c r="G32" s="318" t="n">
         <v>744</v>
       </c>
-      <c r="H32" s="304" t="n">
+      <c r="H32" s="318" t="n">
         <v>2256</v>
       </c>
-      <c r="I32" s="304" t="n">
+      <c r="I32" s="318" t="n">
         <v>3732</v>
       </c>
-      <c r="J32" s="304" t="n">
+      <c r="J32" s="318" t="n">
         <v>1716</v>
       </c>
-      <c r="K32" s="304" t="n">
-        <v>3834</v>
+      <c r="K32" s="318" t="n">
+        <v>3900</v>
       </c>
       <c r="L32" s="146">
         <f>SUM(F32:K32)</f>
@@ -5690,7 +5732,7 @@
     <row r="35" ht="14" customHeight="1" s="63">
       <c r="B35" s="107" t="inlineStr">
         <is>
-          <t>Схема D (уточнённая детекция ДХ, полная VLM-верификация): 36 зон + 6 ЦУ = 42 ОРШ; заполнение сплиттеров 1:64 — 75-100%; ср. волоконный маршрут ДХ 279 м (против 1361 м в централизованной). Карты зон ОРШ по всем СНП — download/snp_vko.</t>
+          <t>Схема D (уточнённая детекция ДХ, полная VLM-верификация): 36 зон + 6 ЦУ = 42 ОРШ; заполнение сплиттеров 1:64 — 75-100%; ср. волоконный маршрут ДХ 278 м (против 1361 м в централизованной). Карты зон ОРШ по всем СНП — download/snp_vko.</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9383,7 @@
       </c>
       <c r="D14" s="109" t="inlineStr">
         <is>
-          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1497 (-69% к A); суммарная длина 216.8 км — минимум среди всех схем книги.</t>
+          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1498 (-69% к A); суммарная длина 217.3 км — минимум среди всех схем книги.</t>
         </is>
       </c>
     </row>
@@ -9422,19 +9464,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F18" s="304" t="n">
+      <c r="F18" s="318" t="n">
         <v>69</v>
       </c>
-      <c r="G18" s="304" t="n">
+      <c r="G18" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="304" t="n">
+      <c r="H18" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="304" t="n">
+      <c r="I18" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="304" t="n">
+      <c r="J18" s="318" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9450,19 +9492,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F19" s="305" t="n">
+      <c r="F19" s="319" t="n">
         <v>46</v>
       </c>
-      <c r="G19" s="305" t="n">
+      <c r="G19" s="319" t="n">
         <v>752</v>
       </c>
-      <c r="H19" s="305" t="n">
+      <c r="H19" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="305" t="n">
+      <c r="I19" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="305" t="n">
+      <c r="J19" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9478,19 +9520,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F20" s="304" t="n">
+      <c r="F20" s="318" t="n">
         <v>114</v>
       </c>
-      <c r="G20" s="304" t="n">
+      <c r="G20" s="318" t="n">
         <v>546</v>
       </c>
-      <c r="H20" s="304" t="n">
+      <c r="H20" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="304" t="n">
+      <c r="I20" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="304" t="n">
+      <c r="J20" s="318" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9506,19 +9548,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F21" s="305" t="n">
+      <c r="F21" s="319" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="305" t="n">
+      <c r="G21" s="319" t="n">
         <v>667</v>
       </c>
-      <c r="H21" s="305" t="n">
+      <c r="H21" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="305" t="n">
+      <c r="I21" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="305" t="n">
+      <c r="J21" s="319" t="n">
         <v>48</v>
       </c>
     </row>
@@ -9534,19 +9576,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F22" s="304" t="n">
+      <c r="F22" s="318" t="n">
         <v>132</v>
       </c>
-      <c r="G22" s="304" t="n">
+      <c r="G22" s="318" t="n">
         <v>717</v>
       </c>
-      <c r="H22" s="304" t="n">
+      <c r="H22" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="304" t="n">
+      <c r="I22" s="318" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="304" t="n">
+      <c r="J22" s="318" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9562,19 +9604,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F23" s="305" t="n">
+      <c r="F23" s="319" t="n">
         <v>109</v>
       </c>
-      <c r="G23" s="305" t="n">
+      <c r="G23" s="319" t="n">
         <v>856</v>
       </c>
-      <c r="H23" s="305" t="n">
+      <c r="H23" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="305" t="n">
+      <c r="I23" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="305" t="n">
+      <c r="J23" s="319" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9590,19 +9632,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F24" s="304" t="n">
+      <c r="F24" s="318" t="n">
         <v>84</v>
       </c>
-      <c r="G24" s="304" t="n">
+      <c r="G24" s="318" t="n">
         <v>908</v>
       </c>
-      <c r="H24" s="304" t="n">
+      <c r="H24" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="304" t="n">
+      <c r="I24" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="304" t="n">
+      <c r="J24" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9618,19 +9660,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F25" s="305" t="n">
+      <c r="F25" s="319" t="n">
         <v>50</v>
       </c>
-      <c r="G25" s="305" t="n">
+      <c r="G25" s="319" t="n">
         <v>1708</v>
       </c>
-      <c r="H25" s="305" t="n">
+      <c r="H25" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="305" t="n">
+      <c r="I25" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="305" t="n">
+      <c r="J25" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9646,19 +9688,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F26" s="304" t="n">
+      <c r="F26" s="318" t="n">
         <v>49</v>
       </c>
-      <c r="G26" s="304" t="n">
+      <c r="G26" s="318" t="n">
         <v>860</v>
       </c>
-      <c r="H26" s="304" t="n">
+      <c r="H26" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="304" t="n">
+      <c r="I26" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="304" t="n">
+      <c r="J26" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9674,19 +9716,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F27" s="305" t="n">
+      <c r="F27" s="319" t="n">
         <v>49</v>
       </c>
-      <c r="G27" s="305" t="n">
+      <c r="G27" s="319" t="n">
         <v>1211</v>
       </c>
-      <c r="H27" s="305" t="n">
+      <c r="H27" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="305" t="n">
+      <c r="I27" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="305" t="n">
+      <c r="J27" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9702,19 +9744,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F28" s="304" t="n">
+      <c r="F28" s="318" t="n">
         <v>88</v>
       </c>
-      <c r="G28" s="304" t="n">
+      <c r="G28" s="318" t="n">
         <v>1175</v>
       </c>
-      <c r="H28" s="304" t="n">
+      <c r="H28" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="304" t="n">
+      <c r="I28" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="304" t="n">
+      <c r="J28" s="318" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9730,19 +9772,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F29" s="305" t="n">
+      <c r="F29" s="319" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="305" t="n">
+      <c r="G29" s="319" t="n">
         <v>1169</v>
       </c>
-      <c r="H29" s="305" t="n">
+      <c r="H29" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="305" t="n">
+      <c r="I29" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="305" t="n">
+      <c r="J29" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9758,19 +9800,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F30" s="304" t="n">
+      <c r="F30" s="318" t="n">
         <v>51</v>
       </c>
-      <c r="G30" s="304" t="n">
+      <c r="G30" s="318" t="n">
         <v>1390</v>
       </c>
-      <c r="H30" s="304" t="n">
+      <c r="H30" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="304" t="n">
+      <c r="I30" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="304" t="n">
+      <c r="J30" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9786,19 +9828,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F31" s="305" t="n">
+      <c r="F31" s="319" t="n">
         <v>49</v>
       </c>
-      <c r="G31" s="305" t="n">
+      <c r="G31" s="319" t="n">
         <v>879</v>
       </c>
-      <c r="H31" s="305" t="n">
+      <c r="H31" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="305" t="n">
+      <c r="I31" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="305" t="n">
+      <c r="J31" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9814,19 +9856,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F32" s="304" t="n">
+      <c r="F32" s="318" t="n">
         <v>59</v>
       </c>
-      <c r="G32" s="304" t="n">
+      <c r="G32" s="318" t="n">
         <v>745</v>
       </c>
-      <c r="H32" s="304" t="n">
+      <c r="H32" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="304" t="n">
+      <c r="I32" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="304" t="n">
+      <c r="J32" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9846,19 +9888,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F33" s="305" t="n">
+      <c r="F33" s="319" t="n">
         <v>124</v>
       </c>
-      <c r="G33" s="305" t="n">
+      <c r="G33" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="305" t="n">
+      <c r="H33" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="305" t="n">
+      <c r="I33" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="305" t="n">
+      <c r="J33" s="319" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9878,19 +9920,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F34" s="304" t="n">
+      <c r="F34" s="318" t="n">
         <v>35</v>
       </c>
-      <c r="G34" s="304" t="n">
+      <c r="G34" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="304" t="n">
+      <c r="H34" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="304" t="n">
+      <c r="I34" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="304" t="n">
+      <c r="J34" s="318" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9906,19 +9948,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F35" s="305" t="n">
+      <c r="F35" s="319" t="n">
         <v>56</v>
       </c>
-      <c r="G35" s="305" t="n">
+      <c r="G35" s="319" t="n">
         <v>805</v>
       </c>
-      <c r="H35" s="305" t="n">
+      <c r="H35" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="305" t="n">
+      <c r="I35" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="305" t="n">
+      <c r="J35" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9934,19 +9976,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F36" s="304" t="n">
+      <c r="F36" s="318" t="n">
         <v>156</v>
       </c>
-      <c r="G36" s="304" t="n">
+      <c r="G36" s="318" t="n">
         <v>295</v>
       </c>
-      <c r="H36" s="304" t="n">
+      <c r="H36" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="304" t="n">
+      <c r="I36" s="318" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="304" t="n">
+      <c r="J36" s="318" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9962,19 +10004,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F37" s="305" t="n">
+      <c r="F37" s="319" t="n">
         <v>69</v>
       </c>
-      <c r="G37" s="305" t="n">
+      <c r="G37" s="319" t="n">
         <v>1394</v>
       </c>
-      <c r="H37" s="305" t="n">
+      <c r="H37" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="305" t="n">
+      <c r="I37" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="305" t="n">
+      <c r="J37" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9990,19 +10032,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F38" s="304" t="n">
+      <c r="F38" s="318" t="n">
         <v>60</v>
       </c>
-      <c r="G38" s="304" t="n">
+      <c r="G38" s="318" t="n">
         <v>556</v>
       </c>
-      <c r="H38" s="304" t="n">
+      <c r="H38" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="304" t="n">
+      <c r="I38" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="304" t="n">
+      <c r="J38" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10022,19 +10064,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F39" s="305" t="n">
+      <c r="F39" s="319" t="n">
         <v>27</v>
       </c>
-      <c r="G39" s="305" t="n">
+      <c r="G39" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="305" t="n">
+      <c r="H39" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="305" t="n">
+      <c r="I39" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="305" t="n">
+      <c r="J39" s="319" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10050,19 +10092,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F40" s="304" t="n">
+      <c r="F40" s="318" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="304" t="n">
+      <c r="G40" s="318" t="n">
         <v>1298</v>
       </c>
-      <c r="H40" s="304" t="n">
+      <c r="H40" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="304" t="n">
+      <c r="I40" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="304" t="n">
+      <c r="J40" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10078,19 +10120,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F41" s="305" t="n">
+      <c r="F41" s="319" t="n">
         <v>107</v>
       </c>
-      <c r="G41" s="305" t="n">
+      <c r="G41" s="319" t="n">
         <v>418</v>
       </c>
-      <c r="H41" s="305" t="n">
+      <c r="H41" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="305" t="n">
+      <c r="I41" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="305" t="n">
+      <c r="J41" s="319" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10106,19 +10148,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F42" s="304" t="n">
+      <c r="F42" s="318" t="n">
         <v>53</v>
       </c>
-      <c r="G42" s="304" t="n">
+      <c r="G42" s="318" t="n">
         <v>1329</v>
       </c>
-      <c r="H42" s="304" t="n">
+      <c r="H42" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="304" t="n">
+      <c r="I42" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="304" t="n">
+      <c r="J42" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10134,19 +10176,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F43" s="305" t="n">
+      <c r="F43" s="319" t="n">
         <v>53</v>
       </c>
-      <c r="G43" s="305" t="n">
+      <c r="G43" s="319" t="n">
         <v>937</v>
       </c>
-      <c r="H43" s="305" t="n">
+      <c r="H43" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="305" t="n">
+      <c r="I43" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="305" t="n">
+      <c r="J43" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10162,19 +10204,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F44" s="304" t="n">
+      <c r="F44" s="318" t="n">
         <v>85</v>
       </c>
-      <c r="G44" s="304" t="n">
+      <c r="G44" s="318" t="n">
         <v>368</v>
       </c>
-      <c r="H44" s="304" t="n">
+      <c r="H44" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="304" t="n">
+      <c r="I44" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="304" t="n">
+      <c r="J44" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10190,19 +10232,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F45" s="305" t="n">
+      <c r="F45" s="319" t="n">
         <v>48</v>
       </c>
-      <c r="G45" s="305" t="n">
+      <c r="G45" s="319" t="n">
         <v>1096</v>
       </c>
-      <c r="H45" s="305" t="n">
+      <c r="H45" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="305" t="n">
+      <c r="I45" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="305" t="n">
+      <c r="J45" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10218,19 +10260,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F46" s="304" t="n">
+      <c r="F46" s="318" t="n">
         <v>76</v>
       </c>
-      <c r="G46" s="304" t="n">
+      <c r="G46" s="318" t="n">
         <v>302</v>
       </c>
-      <c r="H46" s="304" t="n">
+      <c r="H46" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="304" t="n">
+      <c r="I46" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="304" t="n">
+      <c r="J46" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10246,19 +10288,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F47" s="305" t="n">
+      <c r="F47" s="319" t="n">
         <v>78</v>
       </c>
-      <c r="G47" s="305" t="n">
+      <c r="G47" s="319" t="n">
         <v>1779</v>
       </c>
-      <c r="H47" s="305" t="n">
+      <c r="H47" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="305" t="n">
+      <c r="I47" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="305" t="n">
+      <c r="J47" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10274,19 +10316,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F48" s="304" t="n">
+      <c r="F48" s="318" t="n">
         <v>50</v>
       </c>
-      <c r="G48" s="304" t="n">
+      <c r="G48" s="318" t="n">
         <v>476</v>
       </c>
-      <c r="H48" s="304" t="n">
+      <c r="H48" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="304" t="n">
+      <c r="I48" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="304" t="n">
+      <c r="J48" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10306,19 +10348,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F49" s="305" t="n">
+      <c r="F49" s="319" t="n">
         <v>70</v>
       </c>
-      <c r="G49" s="305" t="n">
+      <c r="G49" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="305" t="n">
+      <c r="H49" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="I49" s="305" t="n">
+      <c r="I49" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="305" t="n">
+      <c r="J49" s="319" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10334,19 +10376,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F50" s="304" t="n">
+      <c r="F50" s="318" t="n">
         <v>62</v>
       </c>
-      <c r="G50" s="304" t="n">
+      <c r="G50" s="318" t="n">
         <v>666</v>
       </c>
-      <c r="H50" s="304" t="n">
+      <c r="H50" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="304" t="n">
+      <c r="I50" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="304" t="n">
+      <c r="J50" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10362,19 +10404,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F51" s="305" t="n">
+      <c r="F51" s="319" t="n">
         <v>93</v>
       </c>
-      <c r="G51" s="305" t="n">
+      <c r="G51" s="319" t="n">
         <v>262</v>
       </c>
-      <c r="H51" s="305" t="n">
+      <c r="H51" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="305" t="n">
+      <c r="I51" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="305" t="n">
+      <c r="J51" s="319" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10390,19 +10432,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F52" s="304" t="n">
+      <c r="F52" s="318" t="n">
         <v>61</v>
       </c>
-      <c r="G52" s="304" t="n">
+      <c r="G52" s="318" t="n">
         <v>367</v>
       </c>
-      <c r="H52" s="304" t="n">
+      <c r="H52" s="318" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="304" t="n">
+      <c r="I52" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="304" t="n">
+      <c r="J52" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10422,19 +10464,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F53" s="305" t="n">
+      <c r="F53" s="319" t="n">
         <v>122</v>
       </c>
-      <c r="G53" s="305" t="n">
+      <c r="G53" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="305" t="n">
+      <c r="H53" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="305" t="n">
+      <c r="I53" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="305" t="n">
+      <c r="J53" s="319" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10450,19 +10492,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F54" s="304" t="n">
+      <c r="F54" s="318" t="n">
         <v>93</v>
       </c>
-      <c r="G54" s="304" t="n">
+      <c r="G54" s="318" t="n">
         <v>274</v>
       </c>
-      <c r="H54" s="304" t="n">
+      <c r="H54" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="304" t="n">
+      <c r="I54" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="304" t="n">
+      <c r="J54" s="318" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10478,19 +10520,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F55" s="305" t="n">
-        <v>145</v>
-      </c>
-      <c r="G55" s="305" t="n">
+      <c r="F55" s="319" t="n">
+        <v>156</v>
+      </c>
+      <c r="G55" s="319" t="n">
         <v>654</v>
       </c>
-      <c r="H55" s="305" t="n">
+      <c r="H55" s="319" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="305" t="n">
+      <c r="I55" s="319" t="n">
         <v>4</v>
       </c>
-      <c r="J55" s="305" t="n">
+      <c r="J55" s="319" t="n">
         <v>288</v>
       </c>
     </row>
@@ -10506,19 +10548,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F56" s="304" t="n">
+      <c r="F56" s="318" t="n">
         <v>91</v>
       </c>
-      <c r="G56" s="304" t="n">
+      <c r="G56" s="318" t="n">
         <v>336</v>
       </c>
-      <c r="H56" s="304" t="n">
+      <c r="H56" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="304" t="n">
+      <c r="I56" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="J56" s="304" t="n">
+      <c r="J56" s="318" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10534,19 +10576,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F57" s="305" t="n">
+      <c r="F57" s="319" t="n">
         <v>59</v>
       </c>
-      <c r="G57" s="305" t="n">
+      <c r="G57" s="319" t="n">
         <v>433</v>
       </c>
-      <c r="H57" s="305" t="n">
+      <c r="H57" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="305" t="n">
+      <c r="I57" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="305" t="n">
+      <c r="J57" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10562,19 +10604,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F58" s="304" t="n">
+      <c r="F58" s="318" t="n">
         <v>73</v>
       </c>
-      <c r="G58" s="304" t="n">
+      <c r="G58" s="318" t="n">
         <v>710</v>
       </c>
-      <c r="H58" s="304" t="n">
+      <c r="H58" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="304" t="n">
+      <c r="I58" s="318" t="n">
         <v>3</v>
       </c>
-      <c r="J58" s="304" t="n">
+      <c r="J58" s="318" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10590,19 +10632,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F59" s="305" t="n">
+      <c r="F59" s="319" t="n">
         <v>56</v>
       </c>
-      <c r="G59" s="305" t="n">
+      <c r="G59" s="319" t="n">
         <v>306</v>
       </c>
-      <c r="H59" s="305" t="n">
+      <c r="H59" s="319" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="305" t="n">
+      <c r="I59" s="319" t="n">
         <v>2</v>
       </c>
-      <c r="J59" s="305" t="n">
+      <c r="J59" s="319" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10725,482 +10767,482 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1" s="63">
-      <c r="C65" s="304" t="n">
+      <c r="C65" s="318" t="n">
         <v>2</v>
       </c>
-      <c r="D65" s="304" t="n">
+      <c r="D65" s="318" t="n">
         <v>48</v>
       </c>
-      <c r="E65" s="306" t="n">
+      <c r="E65" s="320" t="n">
         <v>1460.2</v>
       </c>
-      <c r="F65" s="307">
+      <c r="F65" s="321">
         <f>E65/4375.1-1</f>
         <v/>
       </c>
-      <c r="G65" s="306" t="n">
+      <c r="G65" s="320" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H65" s="306" t="n">
+      <c r="H65" s="320" t="n">
         <v>95.8</v>
       </c>
-      <c r="I65" s="306">
+      <c r="I65" s="320">
         <f>G65+H65</f>
         <v/>
       </c>
-      <c r="J65" s="304" t="n">
+      <c r="J65" s="318" t="n">
         <v>56</v>
       </c>
-      <c r="K65" s="304" t="n">
+      <c r="K65" s="318" t="n">
         <v>5261</v>
       </c>
-      <c r="L65" s="304" t="n">
+      <c r="L65" s="318" t="n">
         <v>4368</v>
       </c>
-      <c r="M65" s="304" t="n">
+      <c r="M65" s="318" t="n">
         <v>349</v>
       </c>
-      <c r="N65" s="304" t="n">
+      <c r="N65" s="318" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1" s="63">
-      <c r="C66" s="305" t="n">
+      <c r="C66" s="319" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="305" t="n">
+      <c r="D66" s="319" t="n">
         <v>43</v>
       </c>
-      <c r="E66" s="308" t="n">
+      <c r="E66" s="322" t="n">
         <v>1476.5</v>
       </c>
-      <c r="F66" s="309">
+      <c r="F66" s="323">
         <f>E66/4375.1-1</f>
         <v/>
       </c>
-      <c r="G66" s="308" t="n">
+      <c r="G66" s="322" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H66" s="308" t="n">
+      <c r="H66" s="322" t="n">
         <v>95.8</v>
       </c>
-      <c r="I66" s="308">
+      <c r="I66" s="322">
         <f>G66+H66</f>
         <v/>
       </c>
-      <c r="J66" s="305" t="n">
+      <c r="J66" s="319" t="n">
         <v>54</v>
       </c>
-      <c r="K66" s="305" t="n">
+      <c r="K66" s="319" t="n">
         <v>5255</v>
       </c>
-      <c r="L66" s="305" t="n">
+      <c r="L66" s="319" t="n">
         <v>4176</v>
       </c>
-      <c r="M66" s="305" t="n">
+      <c r="M66" s="319" t="n">
         <v>358</v>
       </c>
-      <c r="N66" s="305" t="n">
+      <c r="N66" s="319" t="n">
         <v>108</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1" s="63">
-      <c r="C67" s="304" t="n">
+      <c r="C67" s="318" t="n">
         <v>8</v>
       </c>
-      <c r="D67" s="304" t="n">
+      <c r="D67" s="318" t="n">
         <v>39</v>
       </c>
-      <c r="E67" s="306" t="n">
+      <c r="E67" s="320" t="n">
         <v>1500.8</v>
       </c>
-      <c r="F67" s="307">
+      <c r="F67" s="321">
         <f>E67/4375.1-1</f>
         <v/>
       </c>
-      <c r="G67" s="306" t="n">
+      <c r="G67" s="320" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H67" s="306" t="n">
+      <c r="H67" s="320" t="n">
         <v>95.8</v>
       </c>
-      <c r="I67" s="306">
+      <c r="I67" s="320">
         <f>G67+H67</f>
         <v/>
       </c>
-      <c r="J67" s="304" t="n">
+      <c r="J67" s="318" t="n">
         <v>53</v>
       </c>
-      <c r="K67" s="304" t="n">
+      <c r="K67" s="318" t="n">
         <v>5253</v>
       </c>
-      <c r="L67" s="304" t="n">
+      <c r="L67" s="318" t="n">
         <v>3984</v>
       </c>
-      <c r="M67" s="304" t="n">
+      <c r="M67" s="318" t="n">
         <v>368</v>
       </c>
-      <c r="N67" s="304" t="n">
+      <c r="N67" s="318" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="63">
-      <c r="C68" s="305" t="n">
+      <c r="C68" s="319" t="n">
         <v>10</v>
       </c>
-      <c r="D68" s="305" t="n">
+      <c r="D68" s="319" t="n">
         <v>36</v>
       </c>
-      <c r="E68" s="308" t="n">
+      <c r="E68" s="322" t="n">
         <v>1532.5</v>
       </c>
-      <c r="F68" s="309">
+      <c r="F68" s="323">
         <f>E68/4375.1-1</f>
         <v/>
       </c>
-      <c r="G68" s="308" t="n">
+      <c r="G68" s="322" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H68" s="308" t="n">
+      <c r="H68" s="322" t="n">
         <v>95.8</v>
       </c>
-      <c r="I68" s="308">
+      <c r="I68" s="322">
         <f>G68+H68</f>
         <v/>
       </c>
-      <c r="J68" s="305" t="n">
+      <c r="J68" s="319" t="n">
         <v>53</v>
       </c>
-      <c r="K68" s="305" t="n">
+      <c r="K68" s="319" t="n">
         <v>5253</v>
       </c>
-      <c r="L68" s="305" t="n">
+      <c r="L68" s="319" t="n">
         <v>3888</v>
       </c>
-      <c r="M68" s="305" t="n">
+      <c r="M68" s="319" t="n">
         <v>379</v>
       </c>
-      <c r="N68" s="305" t="n">
+      <c r="N68" s="319" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="63">
-      <c r="C69" s="310" t="n">
+      <c r="C69" s="324" t="n">
         <v>15</v>
       </c>
-      <c r="D69" s="310" t="n">
+      <c r="D69" s="324" t="n">
         <v>34</v>
       </c>
-      <c r="E69" s="311" t="n">
+      <c r="E69" s="325" t="n">
         <v>1562.5</v>
       </c>
-      <c r="F69" s="312">
+      <c r="F69" s="326">
         <f>E69/4375.1-1</f>
         <v/>
       </c>
-      <c r="G69" s="311" t="n">
+      <c r="G69" s="325" t="n">
         <v>80.5</v>
       </c>
-      <c r="H69" s="311" t="n">
+      <c r="H69" s="325" t="n">
         <v>95.8</v>
       </c>
-      <c r="I69" s="311">
+      <c r="I69" s="325">
         <f>G69+H69</f>
         <v/>
       </c>
-      <c r="J69" s="310" t="n">
+      <c r="J69" s="324" t="n">
         <v>52</v>
       </c>
-      <c r="K69" s="310" t="n">
+      <c r="K69" s="324" t="n">
         <v>5251</v>
       </c>
-      <c r="L69" s="310" t="n">
+      <c r="L69" s="324" t="n">
         <v>3696</v>
       </c>
-      <c r="M69" s="310" t="n">
+      <c r="M69" s="324" t="n">
         <v>388</v>
       </c>
-      <c r="N69" s="310" t="n">
+      <c r="N69" s="324" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="63">
-      <c r="C70" s="305" t="n">
+      <c r="C70" s="319" t="n">
         <v>20</v>
       </c>
-      <c r="D70" s="305" t="n">
+      <c r="D70" s="319" t="n">
         <v>32</v>
       </c>
-      <c r="E70" s="308" t="n">
+      <c r="E70" s="322" t="n">
         <v>1603.9</v>
       </c>
-      <c r="F70" s="309">
+      <c r="F70" s="323">
         <f>E70/4375.1-1</f>
         <v/>
       </c>
-      <c r="G70" s="308" t="n">
+      <c r="G70" s="322" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="H70" s="308" t="n">
+      <c r="H70" s="322" t="n">
         <v>95.8</v>
       </c>
-      <c r="I70" s="308">
+      <c r="I70" s="322">
         <f>G70+H70</f>
         <v/>
       </c>
-      <c r="J70" s="305" t="n">
+      <c r="J70" s="319" t="n">
         <v>51</v>
       </c>
-      <c r="K70" s="305" t="n">
+      <c r="K70" s="319" t="n">
         <v>5249</v>
       </c>
-      <c r="L70" s="305" t="n">
+      <c r="L70" s="319" t="n">
         <v>3696</v>
       </c>
-      <c r="M70" s="305" t="n">
+      <c r="M70" s="319" t="n">
         <v>403</v>
       </c>
-      <c r="N70" s="305" t="n">
+      <c r="N70" s="319" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="63">
-      <c r="C71" s="304" t="n">
+      <c r="C71" s="318" t="n">
         <v>25</v>
       </c>
-      <c r="D71" s="304" t="n">
+      <c r="D71" s="318" t="n">
         <v>29</v>
       </c>
-      <c r="E71" s="306" t="n">
+      <c r="E71" s="320" t="n">
         <v>1674.7</v>
       </c>
-      <c r="F71" s="307">
+      <c r="F71" s="321">
         <f>E71/4375.1-1</f>
         <v/>
       </c>
-      <c r="G71" s="306" t="n">
+      <c r="G71" s="320" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H71" s="306" t="n">
+      <c r="H71" s="320" t="n">
         <v>95.8</v>
       </c>
-      <c r="I71" s="306">
+      <c r="I71" s="320">
         <f>G71+H71</f>
         <v/>
       </c>
-      <c r="J71" s="304" t="n">
+      <c r="J71" s="318" t="n">
         <v>50</v>
       </c>
-      <c r="K71" s="304" t="n">
+      <c r="K71" s="318" t="n">
         <v>5247</v>
       </c>
-      <c r="L71" s="304" t="n">
+      <c r="L71" s="318" t="n">
         <v>3600</v>
       </c>
-      <c r="M71" s="304" t="n">
+      <c r="M71" s="318" t="n">
         <v>427</v>
       </c>
-      <c r="N71" s="304" t="n">
+      <c r="N71" s="318" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="63">
-      <c r="C72" s="305" t="n">
+      <c r="C72" s="319" t="n">
         <v>30</v>
       </c>
-      <c r="D72" s="305" t="n">
+      <c r="D72" s="319" t="n">
         <v>27</v>
       </c>
-      <c r="E72" s="308" t="n">
+      <c r="E72" s="322" t="n">
         <v>1736.2</v>
       </c>
-      <c r="F72" s="309">
+      <c r="F72" s="323">
         <f>E72/4375.1-1</f>
         <v/>
       </c>
-      <c r="G72" s="308" t="n">
+      <c r="G72" s="322" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="H72" s="308" t="n">
+      <c r="H72" s="322" t="n">
         <v>95.8</v>
       </c>
-      <c r="I72" s="308">
+      <c r="I72" s="322">
         <f>G72+H72</f>
         <v/>
       </c>
-      <c r="J72" s="305" t="n">
+      <c r="J72" s="319" t="n">
         <v>48</v>
       </c>
-      <c r="K72" s="305" t="n">
+      <c r="K72" s="319" t="n">
         <v>5243</v>
       </c>
-      <c r="L72" s="305" t="n">
+      <c r="L72" s="319" t="n">
         <v>3504</v>
       </c>
-      <c r="M72" s="305" t="n">
+      <c r="M72" s="319" t="n">
         <v>448</v>
       </c>
-      <c r="N72" s="305" t="n">
+      <c r="N72" s="319" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="63">
-      <c r="C73" s="304" t="n">
+      <c r="C73" s="318" t="n">
         <v>40</v>
       </c>
-      <c r="D73" s="304" t="n">
+      <c r="D73" s="318" t="n">
         <v>24</v>
       </c>
-      <c r="E73" s="306" t="n">
+      <c r="E73" s="320" t="n">
         <v>1852</v>
       </c>
-      <c r="F73" s="307">
+      <c r="F73" s="321">
         <f>E73/4375.1-1</f>
         <v/>
       </c>
-      <c r="G73" s="306" t="n">
+      <c r="G73" s="320" t="n">
         <v>82.3</v>
       </c>
-      <c r="H73" s="306" t="n">
+      <c r="H73" s="320" t="n">
         <v>95.8</v>
       </c>
-      <c r="I73" s="306">
+      <c r="I73" s="320">
         <f>G73+H73</f>
         <v/>
       </c>
-      <c r="J73" s="304" t="n">
+      <c r="J73" s="318" t="n">
         <v>47</v>
       </c>
-      <c r="K73" s="304" t="n">
+      <c r="K73" s="318" t="n">
         <v>5241</v>
       </c>
-      <c r="L73" s="304" t="n">
+      <c r="L73" s="318" t="n">
         <v>3552</v>
       </c>
-      <c r="M73" s="304" t="n">
+      <c r="M73" s="318" t="n">
         <v>488</v>
       </c>
-      <c r="N73" s="304" t="n">
+      <c r="N73" s="318" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="63">
-      <c r="C74" s="305" t="n">
+      <c r="C74" s="319" t="n">
         <v>50</v>
       </c>
-      <c r="D74" s="305" t="n">
+      <c r="D74" s="319" t="n">
         <v>20</v>
       </c>
-      <c r="E74" s="308" t="n">
+      <c r="E74" s="322" t="n">
         <v>2041.2</v>
       </c>
-      <c r="F74" s="309">
+      <c r="F74" s="323">
         <f>E74/4375.1-1</f>
         <v/>
       </c>
-      <c r="G74" s="308" t="n">
+      <c r="G74" s="322" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="H74" s="308" t="n">
+      <c r="H74" s="322" t="n">
         <v>95.8</v>
       </c>
-      <c r="I74" s="308">
+      <c r="I74" s="322">
         <f>G74+H74</f>
         <v/>
       </c>
-      <c r="J74" s="305" t="n">
+      <c r="J74" s="319" t="n">
         <v>46</v>
       </c>
-      <c r="K74" s="305" t="n">
+      <c r="K74" s="319" t="n">
         <v>5238</v>
       </c>
-      <c r="L74" s="305" t="n">
+      <c r="L74" s="319" t="n">
         <v>3696</v>
       </c>
-      <c r="M74" s="305" t="n">
+      <c r="M74" s="319" t="n">
         <v>554</v>
       </c>
-      <c r="N74" s="305" t="n">
+      <c r="N74" s="319" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="63">
-      <c r="C75" s="304" t="n">
+      <c r="C75" s="318" t="n">
         <v>60</v>
       </c>
-      <c r="D75" s="304" t="n">
+      <c r="D75" s="318" t="n">
         <v>18</v>
       </c>
-      <c r="E75" s="306" t="n">
+      <c r="E75" s="320" t="n">
         <v>2153.9</v>
       </c>
-      <c r="F75" s="307">
+      <c r="F75" s="321">
         <f>E75/4375.1-1</f>
         <v/>
       </c>
-      <c r="G75" s="306" t="n">
+      <c r="G75" s="320" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="H75" s="306" t="n">
+      <c r="H75" s="320" t="n">
         <v>95.8</v>
       </c>
-      <c r="I75" s="306">
+      <c r="I75" s="320">
         <f>G75+H75</f>
         <v/>
       </c>
-      <c r="J75" s="304" t="n">
+      <c r="J75" s="318" t="n">
         <v>45</v>
       </c>
-      <c r="K75" s="304" t="n">
+      <c r="K75" s="318" t="n">
         <v>5236</v>
       </c>
-      <c r="L75" s="304" t="n">
+      <c r="L75" s="318" t="n">
         <v>3744</v>
       </c>
-      <c r="M75" s="304" t="n">
+      <c r="M75" s="318" t="n">
         <v>592</v>
       </c>
-      <c r="N75" s="304" t="n">
+      <c r="N75" s="318" t="n">
         <v>245</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="63">
-      <c r="C76" s="305" t="n">
+      <c r="C76" s="319" t="n">
         <v>80</v>
       </c>
-      <c r="D76" s="305" t="n">
+      <c r="D76" s="319" t="n">
         <v>17</v>
       </c>
-      <c r="E76" s="308" t="n">
+      <c r="E76" s="322" t="n">
         <v>2215.1</v>
       </c>
-      <c r="F76" s="309">
+      <c r="F76" s="323">
         <f>E76/4375.1-1</f>
         <v/>
       </c>
-      <c r="G76" s="308" t="n">
+      <c r="G76" s="322" t="n">
         <v>84.7</v>
       </c>
-      <c r="H76" s="308" t="n">
+      <c r="H76" s="322" t="n">
         <v>95.8</v>
       </c>
-      <c r="I76" s="308">
+      <c r="I76" s="322">
         <f>G76+H76</f>
         <v/>
       </c>
-      <c r="J76" s="305" t="n">
+      <c r="J76" s="319" t="n">
         <v>44</v>
       </c>
-      <c r="K76" s="305" t="n">
+      <c r="K76" s="319" t="n">
         <v>5234</v>
       </c>
-      <c r="L76" s="305" t="n">
+      <c r="L76" s="319" t="n">
         <v>3600</v>
       </c>
-      <c r="M76" s="305" t="n">
+      <c r="M76" s="319" t="n">
         <v>614</v>
       </c>
-      <c r="N76" s="305" t="n">
+      <c r="N76" s="319" t="n">
         <v>245</v>
       </c>
     </row>
@@ -11229,134 +11271,134 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="304" t="n">
+      <c r="B80" s="318" t="n">
         <v>17</v>
       </c>
-      <c r="C80" s="306" t="n">
+      <c r="C80" s="320" t="n">
         <v>2215.1</v>
       </c>
-      <c r="D80" s="306" t="n">
+      <c r="D80" s="320" t="n">
         <v>527.3</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="305" t="n">
+      <c r="B81" s="319" t="n">
         <v>18</v>
       </c>
-      <c r="C81" s="308" t="n">
+      <c r="C81" s="322" t="n">
         <v>2153.9</v>
       </c>
-      <c r="D81" s="308" t="n">
+      <c r="D81" s="322" t="n">
         <v>529.8</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="304" t="n">
+      <c r="B82" s="318" t="n">
         <v>20</v>
       </c>
-      <c r="C82" s="306" t="n">
+      <c r="C82" s="320" t="n">
         <v>2041.2</v>
       </c>
-      <c r="D82" s="306" t="n">
+      <c r="D82" s="320" t="n">
         <v>527.5</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="305" t="n">
+      <c r="B83" s="319" t="n">
         <v>24</v>
       </c>
-      <c r="C83" s="308" t="n">
+      <c r="C83" s="322" t="n">
         <v>1852</v>
       </c>
-      <c r="D83" s="308" t="n">
+      <c r="D83" s="322" t="n">
         <v>524.2</v>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="304" t="n">
+      <c r="B84" s="318" t="n">
         <v>27</v>
       </c>
-      <c r="C84" s="306" t="n">
+      <c r="C84" s="320" t="n">
         <v>1736.2</v>
       </c>
-      <c r="D84" s="306" t="n">
+      <c r="D84" s="320" t="n">
         <v>524.4</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="305" t="n">
+      <c r="B85" s="319" t="n">
         <v>29</v>
       </c>
-      <c r="C85" s="308" t="n">
+      <c r="C85" s="322" t="n">
         <v>1674.7</v>
       </c>
-      <c r="D85" s="308" t="n">
+      <c r="D85" s="322" t="n">
         <v>527.9</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="304" t="n">
+      <c r="B86" s="318" t="n">
         <v>32</v>
       </c>
-      <c r="C86" s="306" t="n">
+      <c r="C86" s="320" t="n">
         <v>1603.9</v>
       </c>
-      <c r="D86" s="306" t="n">
+      <c r="D86" s="320" t="n">
         <v>531.7</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="305" t="n">
+      <c r="B87" s="319" t="n">
         <v>34</v>
       </c>
-      <c r="C87" s="308" t="n">
+      <c r="C87" s="322" t="n">
         <v>1562.5</v>
       </c>
-      <c r="D87" s="308" t="n">
+      <c r="D87" s="322" t="n">
         <v>533.2</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="304" t="n">
+      <c r="B88" s="318" t="n">
         <v>36</v>
       </c>
-      <c r="C88" s="306" t="n">
+      <c r="C88" s="320" t="n">
         <v>1532.5</v>
       </c>
-      <c r="D88" s="306" t="n">
+      <c r="D88" s="320" t="n">
         <v>539.3</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="305" t="n">
+      <c r="B89" s="319" t="n">
         <v>39</v>
       </c>
-      <c r="C89" s="308" t="n">
+      <c r="C89" s="322" t="n">
         <v>1500.8</v>
       </c>
-      <c r="D89" s="308" t="n">
+      <c r="D89" s="322" t="n">
         <v>544.4</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="304" t="n">
+      <c r="B90" s="318" t="n">
         <v>43</v>
       </c>
-      <c r="C90" s="306" t="n">
+      <c r="C90" s="320" t="n">
         <v>1476.5</v>
       </c>
-      <c r="D90" s="306" t="n">
+      <c r="D90" s="320" t="n">
         <v>553</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="305" t="n">
+      <c r="B91" s="319" t="n">
         <v>48</v>
       </c>
-      <c r="C91" s="308" t="n">
+      <c r="C91" s="322" t="n">
         <v>1460.2</v>
       </c>
-      <c r="D91" s="308" t="n">
+      <c r="D91" s="322" t="n">
         <v>563.9</v>
       </c>
     </row>
@@ -11417,19 +11459,19 @@
           <t>Обслужено ДХ, шт</t>
         </is>
       </c>
-      <c r="D95" s="304" t="n">
-        <v>3076</v>
-      </c>
-      <c r="E95" s="304" t="n">
-        <v>3076</v>
-      </c>
-      <c r="F95" s="304" t="n">
-        <v>3076</v>
-      </c>
-      <c r="G95" s="304" t="n">
-        <v>3076</v>
-      </c>
-      <c r="H95" s="313" t="n"/>
+      <c r="D95" s="318" t="n">
+        <v>3087</v>
+      </c>
+      <c r="E95" s="318" t="n">
+        <v>3087</v>
+      </c>
+      <c r="F95" s="318" t="n">
+        <v>3087</v>
+      </c>
+      <c r="G95" s="318" t="n">
+        <v>3087</v>
+      </c>
+      <c r="H95" s="327" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="63">
       <c r="C96" s="114" t="inlineStr">
@@ -11437,19 +11479,19 @@
           <t>Волокно-км</t>
         </is>
       </c>
-      <c r="D96" s="308" t="n">
+      <c r="D96" s="322" t="n">
         <v>4375.1</v>
       </c>
-      <c r="E96" s="308" t="n">
+      <c r="E96" s="322" t="n">
         <v>1256.1</v>
       </c>
-      <c r="F96" s="308" t="n">
+      <c r="F96" s="322" t="n">
         <v>889.2</v>
       </c>
-      <c r="G96" s="308" t="n">
-        <v>1497.1</v>
-      </c>
-      <c r="H96" s="314">
+      <c r="G96" s="322" t="n">
+        <v>1498.3</v>
+      </c>
+      <c r="H96" s="328">
         <f>CHOOSE(MATCH(MIN(D96:G96),D96:G96,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11460,23 +11502,23 @@
           <t>Волокно-км на ДХ, км</t>
         </is>
       </c>
-      <c r="D97" s="315">
-        <f>D96/3076</f>
-        <v/>
-      </c>
-      <c r="E97" s="315">
-        <f>E96/3076</f>
-        <v/>
-      </c>
-      <c r="F97" s="315">
-        <f>F96/3076</f>
-        <v/>
-      </c>
-      <c r="G97" s="315">
-        <f>G96/3076</f>
-        <v/>
-      </c>
-      <c r="H97" s="313">
+      <c r="D97" s="329">
+        <f>D96/3087</f>
+        <v/>
+      </c>
+      <c r="E97" s="329">
+        <f>E96/3087</f>
+        <v/>
+      </c>
+      <c r="F97" s="329">
+        <f>F96/3087</f>
+        <v/>
+      </c>
+      <c r="G97" s="329">
+        <f>G96/3087</f>
+        <v/>
+      </c>
+      <c r="H97" s="327">
         <f>CHOOSE(MATCH(MIN(D97:G97),D97:G97,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11487,19 +11529,19 @@
           <t>Магистральный кабель, км</t>
         </is>
       </c>
-      <c r="D98" s="308" t="n">
+      <c r="D98" s="322" t="n">
         <v>109.4</v>
       </c>
-      <c r="E98" s="308" t="n">
+      <c r="E98" s="322" t="n">
         <v>76.5</v>
       </c>
-      <c r="F98" s="308" t="n">
+      <c r="F98" s="322" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="G98" s="308" t="n">
+      <c r="G98" s="322" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="H98" s="314">
+      <c r="H98" s="328">
         <f>CHOOSE(MATCH(MIN(D98:G98),D98:G98,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11510,19 +11552,19 @@
           <t>в т.ч. 8-волоконный, км</t>
         </is>
       </c>
-      <c r="D99" s="306" t="n">
+      <c r="D99" s="320" t="n">
         <v>35.1</v>
       </c>
-      <c r="E99" s="306" t="n">
+      <c r="E99" s="320" t="n">
         <v>46.7</v>
       </c>
-      <c r="F99" s="306" t="n">
+      <c r="F99" s="320" t="n">
         <v>49.5</v>
       </c>
-      <c r="G99" s="306" t="n">
+      <c r="G99" s="320" t="n">
         <v>42.7</v>
       </c>
-      <c r="H99" s="313" t="n"/>
+      <c r="H99" s="327" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1" s="63">
       <c r="C100" s="114" t="inlineStr">
@@ -11530,19 +11572,19 @@
           <t>в т.ч. 96-волоконный, км</t>
         </is>
       </c>
-      <c r="D100" s="308" t="n">
+      <c r="D100" s="322" t="n">
         <v>33.8</v>
       </c>
-      <c r="E100" s="308" t="n">
+      <c r="E100" s="322" t="n">
         <v>1.5</v>
       </c>
-      <c r="F100" s="308" t="n">
+      <c r="F100" s="322" t="n">
         <v>0.9</v>
       </c>
-      <c r="G100" s="308" t="n">
+      <c r="G100" s="322" t="n">
         <v>0.7</v>
       </c>
-      <c r="H100" s="314" t="n"/>
+      <c r="H100" s="328" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="63">
       <c r="C101" s="112" t="inlineStr">
@@ -11550,19 +11592,19 @@
           <t>Дроп-кабель, км</t>
         </is>
       </c>
-      <c r="D101" s="306" t="n">
+      <c r="D101" s="320" t="n">
         <v>95.8</v>
       </c>
-      <c r="E101" s="306" t="n">
+      <c r="E101" s="320" t="n">
         <v>170.7</v>
       </c>
-      <c r="F101" s="306" t="n">
+      <c r="F101" s="320" t="n">
         <v>244</v>
       </c>
-      <c r="G101" s="306" t="n">
-        <v>126.3</v>
-      </c>
-      <c r="H101" s="313">
+      <c r="G101" s="320" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="H101" s="327">
         <f>CHOOSE(MATCH(MIN(D101:G101),D101:G101,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11573,23 +11615,23 @@
           <t>ВСЕГО кабель + дропы, км</t>
         </is>
       </c>
-      <c r="D102" s="308">
+      <c r="D102" s="322">
         <f>D98+D101</f>
         <v/>
       </c>
-      <c r="E102" s="308">
+      <c r="E102" s="322">
         <f>E98+E101</f>
         <v/>
       </c>
-      <c r="F102" s="308">
+      <c r="F102" s="322">
         <f>F98+F101</f>
         <v/>
       </c>
-      <c r="G102" s="308">
+      <c r="G102" s="322">
         <f>G98+G101</f>
         <v/>
       </c>
-      <c r="H102" s="314">
+      <c r="H102" s="328">
         <f>CHOOSE(MATCH(MIN(D102:G102),D102:G102,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11600,19 +11642,19 @@
           <t>Средний дроп, м</t>
         </is>
       </c>
-      <c r="D103" s="304" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E103" s="304" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="F103" s="304" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="G103" s="304" t="n">
+      <c r="D103" s="318" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E103" s="318" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="F103" s="318" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="G103" s="318" t="n">
         <v>39</v>
       </c>
-      <c r="H103" s="313">
+      <c r="H103" s="327">
         <f>CHOOSE(MATCH(MIN(D103:G103),D103:G103,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11623,19 +11665,19 @@
           <t>Максимальный дроп, м</t>
         </is>
       </c>
-      <c r="D104" s="305" t="n">
+      <c r="D104" s="319" t="n">
         <v>132.5</v>
       </c>
-      <c r="E104" s="305" t="n">
+      <c r="E104" s="319" t="n">
         <v>201</v>
       </c>
-      <c r="F104" s="305" t="n">
+      <c r="F104" s="319" t="n">
         <v>266</v>
       </c>
-      <c r="G104" s="305" t="n">
+      <c r="G104" s="319" t="n">
         <v>132.5</v>
       </c>
-      <c r="H104" s="314">
+      <c r="H104" s="328">
         <f>CHOOSE(MATCH(MIN(D104:G104),D104:G104,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11646,15 +11688,15 @@
           <t>Ср. маршрут волокна ДХ, м</t>
         </is>
       </c>
-      <c r="D105" s="304" t="n">
+      <c r="D105" s="318" t="n">
         <v>1361</v>
       </c>
-      <c r="E105" s="304" t="n"/>
-      <c r="F105" s="304" t="n"/>
-      <c r="G105" s="304" t="n">
-        <v>279</v>
-      </c>
-      <c r="H105" s="313">
+      <c r="E105" s="318" t="n"/>
+      <c r="F105" s="318" t="n"/>
+      <c r="G105" s="318" t="n">
+        <v>278</v>
+      </c>
+      <c r="H105" s="327">
         <f>CHOOSE(MATCH(MIN(D105:G105),D105:G105,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11665,19 +11707,19 @@
           <t>ОРШ, шт</t>
         </is>
       </c>
-      <c r="D106" s="305" t="n">
+      <c r="D106" s="319" t="n">
         <v>6</v>
       </c>
-      <c r="E106" s="305" t="n">
+      <c r="E106" s="319" t="n">
         <v>6</v>
       </c>
-      <c r="F106" s="305" t="n">
+      <c r="F106" s="319" t="n">
         <v>6</v>
       </c>
-      <c r="G106" s="305" t="n">
+      <c r="G106" s="319" t="n">
         <v>42</v>
       </c>
-      <c r="H106" s="314">
+      <c r="H106" s="328">
         <f>CHOOSE(MATCH(MIN(D106:G106),D106:G106,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11688,19 +11730,19 @@
           <t>РОР, шт</t>
         </is>
       </c>
-      <c r="D107" s="304" t="n">
+      <c r="D107" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="304" t="n">
+      <c r="E107" s="318" t="n">
         <v>515</v>
       </c>
-      <c r="F107" s="304" t="n">
+      <c r="F107" s="318" t="n">
         <v>323</v>
       </c>
-      <c r="G107" s="304" t="n">
+      <c r="G107" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="313" t="n"/>
+      <c r="H107" s="327" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="63">
       <c r="C108" s="114" t="inlineStr">
@@ -11708,19 +11750,19 @@
           <t>Сплиттеры 1:64, шт</t>
         </is>
       </c>
-      <c r="D108" s="305" t="n">
+      <c r="D108" s="319" t="n">
         <v>39</v>
       </c>
-      <c r="E108" s="305" t="n">
+      <c r="E108" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="305" t="n">
+      <c r="F108" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="305" t="n">
+      <c r="G108" s="319" t="n">
         <v>65</v>
       </c>
-      <c r="H108" s="314" t="n"/>
+      <c r="H108" s="328" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1" s="63">
       <c r="C109" s="112" t="inlineStr">
@@ -11728,19 +11770,19 @@
           <t>Сплиттеры 1:8, шт</t>
         </is>
       </c>
-      <c r="D109" s="304" t="n">
+      <c r="D109" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="304" t="n">
+      <c r="E109" s="318" t="n">
         <v>581</v>
       </c>
-      <c r="F109" s="304" t="n">
+      <c r="F109" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="304" t="n">
+      <c r="G109" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="313" t="n"/>
+      <c r="H109" s="327" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1" s="63">
       <c r="C110" s="114" t="inlineStr">
@@ -11748,19 +11790,19 @@
           <t>Сплиттеры 1:4, шт</t>
         </is>
       </c>
-      <c r="D110" s="305" t="n">
+      <c r="D110" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="305" t="n">
+      <c r="E110" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="305" t="n">
+      <c r="F110" s="319" t="n">
         <v>83</v>
       </c>
-      <c r="G110" s="305" t="n">
+      <c r="G110" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="314" t="n"/>
+      <c r="H110" s="328" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1" s="63">
       <c r="C111" s="112" t="inlineStr">
@@ -11768,19 +11810,19 @@
           <t>Сплиттеры 1:16, шт</t>
         </is>
       </c>
-      <c r="D111" s="304" t="n">
+      <c r="D111" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="304" t="n">
+      <c r="E111" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="304" t="n">
+      <c r="F111" s="318" t="n">
         <v>323</v>
       </c>
-      <c r="G111" s="304" t="n">
+      <c r="G111" s="318" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="313" t="n"/>
+      <c r="H111" s="327" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1" s="63">
       <c r="C112" s="114" t="inlineStr">
@@ -11788,19 +11830,19 @@
           <t>Муфты, шт</t>
         </is>
       </c>
-      <c r="D112" s="305" t="n">
+      <c r="D112" s="319" t="n">
         <v>1140</v>
       </c>
-      <c r="E112" s="305" t="n">
+      <c r="E112" s="319" t="n">
         <v>115</v>
       </c>
-      <c r="F112" s="305" t="n">
+      <c r="F112" s="319" t="n">
         <v>100</v>
       </c>
-      <c r="G112" s="305" t="n">
+      <c r="G112" s="319" t="n">
         <v>1103</v>
       </c>
-      <c r="H112" s="314">
+      <c r="H112" s="328">
         <f>CHOOSE(MATCH(MIN(D112:G112),D112:G112,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11811,19 +11853,19 @@
           <t>Сварки, шт</t>
         </is>
       </c>
-      <c r="D113" s="304" t="n">
+      <c r="D113" s="318" t="n">
         <v>5136</v>
       </c>
-      <c r="E113" s="304" t="n">
+      <c r="E113" s="318" t="n">
         <v>2585</v>
       </c>
-      <c r="F113" s="304" t="n">
+      <c r="F113" s="318" t="n">
         <v>1552</v>
       </c>
-      <c r="G113" s="304" t="n">
-        <v>6914</v>
-      </c>
-      <c r="H113" s="313">
+      <c r="G113" s="318" t="n">
+        <v>6938</v>
+      </c>
+      <c r="H113" s="327">
         <f>CHOOSE(MATCH(MIN(D113:G113),D113:G113,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11834,19 +11876,19 @@
           <t>Коннекторы FAST, шт</t>
         </is>
       </c>
-      <c r="D114" s="305" t="n">
+      <c r="D114" s="319" t="n">
         <v>2569</v>
       </c>
-      <c r="E114" s="305" t="n">
+      <c r="E114" s="319" t="n">
         <v>5136</v>
       </c>
-      <c r="F114" s="305" t="n">
+      <c r="F114" s="319" t="n">
         <v>5136</v>
       </c>
-      <c r="G114" s="305" t="n">
-        <v>3386</v>
-      </c>
-      <c r="H114" s="314">
+      <c r="G114" s="319" t="n">
+        <v>3398</v>
+      </c>
+      <c r="H114" s="328">
         <f>CHOOSE(MATCH(MIN(D114:G114),D114:G114,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11857,19 +11899,19 @@
           <t>Порты кросса ОРШ, шт</t>
         </is>
       </c>
-      <c r="D115" s="304" t="n">
+      <c r="D115" s="318" t="n">
         <v>3600</v>
       </c>
-      <c r="E115" s="304" t="n">
+      <c r="E115" s="318" t="n">
         <v>1008</v>
       </c>
-      <c r="F115" s="304" t="n">
+      <c r="F115" s="318" t="n">
         <v>864</v>
       </c>
-      <c r="G115" s="304" t="n">
+      <c r="G115" s="318" t="n">
         <v>5184</v>
       </c>
-      <c r="H115" s="313">
+      <c r="H115" s="327">
         <f>CHOOSE(MATCH(MIN(D115:G115),D115:G115,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11880,19 +11922,19 @@
           <t>Порты OLT, шт</t>
         </is>
       </c>
-      <c r="D116" s="305" t="n">
+      <c r="D116" s="319" t="n">
         <v>39</v>
       </c>
-      <c r="E116" s="305" t="n">
+      <c r="E116" s="319" t="n">
         <v>66</v>
       </c>
-      <c r="F116" s="305" t="n">
+      <c r="F116" s="319" t="n">
         <v>83</v>
       </c>
-      <c r="G116" s="305" t="n">
+      <c r="G116" s="319" t="n">
         <v>65</v>
       </c>
-      <c r="H116" s="314">
+      <c r="H116" s="328">
         <f>CHOOSE(MATCH(MIN(D116:G116),D116:G116,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11903,19 +11945,19 @@
           <t>Комплекты подвеса, шт</t>
         </is>
       </c>
-      <c r="D117" s="304" t="n">
+      <c r="D117" s="318" t="n">
         <v>2911</v>
       </c>
-      <c r="E117" s="304" t="n">
+      <c r="E117" s="318" t="n">
         <v>4180</v>
       </c>
-      <c r="F117" s="304" t="n">
+      <c r="F117" s="318" t="n">
         <v>6136</v>
       </c>
-      <c r="G117" s="304" t="n">
+      <c r="G117" s="318" t="n">
         <v>2472</v>
       </c>
-      <c r="H117" s="313">
+      <c r="H117" s="327">
         <f>CHOOSE(MATCH(MIN(D117:G117),D117:G117,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11926,19 +11968,19 @@
           <t>Доп. шкафы ОРШ (сверх 6), шт</t>
         </is>
       </c>
-      <c r="D118" s="305" t="n">
+      <c r="D118" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="305" t="n">
+      <c r="E118" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="305" t="n">
+      <c r="F118" s="319" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="305" t="n">
+      <c r="G118" s="319" t="n">
         <v>36</v>
       </c>
-      <c r="H118" s="314">
+      <c r="H118" s="328">
         <f>CHOOSE(MATCH(MIN(D118:G118),D118:G118,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -12002,17 +12044,17 @@
           <t>Кабельная продукция (магистраль)</t>
         </is>
       </c>
-      <c r="D123" s="306" t="n">
+      <c r="D123" s="320" t="n">
         <v>233</v>
       </c>
-      <c r="E123" s="306" t="n">
+      <c r="E123" s="320" t="n">
         <v>107</v>
       </c>
-      <c r="F123" s="306" t="n">
+      <c r="F123" s="320" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="G123" s="306" t="n">
-        <v>133</v>
+      <c r="G123" s="320" t="n">
+        <v>133.1</v>
       </c>
     </row>
     <row r="124" ht="18" customHeight="1" s="63">
@@ -12021,17 +12063,17 @@
           <t>Дроп-кабели</t>
         </is>
       </c>
-      <c r="D124" s="308" t="n">
+      <c r="D124" s="322" t="n">
         <v>47.9</v>
       </c>
-      <c r="E124" s="308" t="n">
+      <c r="E124" s="322" t="n">
         <v>85.3</v>
       </c>
-      <c r="F124" s="308" t="n">
+      <c r="F124" s="322" t="n">
         <v>122</v>
       </c>
-      <c r="G124" s="308" t="n">
-        <v>63.1</v>
+      <c r="G124" s="322" t="n">
+        <v>63.4</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1" s="63">
@@ -12040,17 +12082,17 @@
           <t>Оборудование и монтаж</t>
         </is>
       </c>
-      <c r="D125" s="306" t="n">
+      <c r="D125" s="320" t="n">
         <v>315</v>
       </c>
-      <c r="E125" s="306" t="n">
+      <c r="E125" s="320" t="n">
         <v>306.2</v>
       </c>
-      <c r="F125" s="306" t="n">
+      <c r="F125" s="320" t="n">
         <v>270.8</v>
       </c>
-      <c r="G125" s="306" t="n">
-        <v>372.7</v>
+      <c r="G125" s="320" t="n">
+        <v>373</v>
       </c>
     </row>
     <row r="126">
@@ -12082,16 +12124,16 @@
           <t>Доп. шкафы ОРШ (сверх базовых 6, по 1,5 у.е.)</t>
         </is>
       </c>
-      <c r="D127" s="308" t="n">
+      <c r="D127" s="322" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="308" t="n">
+      <c r="E127" s="322" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="308" t="n">
+      <c r="F127" s="322" t="n">
         <v>0</v>
       </c>
-      <c r="G127" s="308" t="n">
+      <c r="G127" s="322" t="n">
         <v>54</v>
       </c>
     </row>
@@ -12124,19 +12166,19 @@
           <t>Δ к лучшей схеме</t>
         </is>
       </c>
-      <c r="D129" s="307">
+      <c r="D129" s="321">
         <f>D128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="E129" s="307">
+      <c r="E129" s="321">
         <f>E128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="F129" s="307">
+      <c r="F129" s="321">
         <f>F128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="G129" s="307">
+      <c r="G129" s="321">
         <f>G128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
@@ -12181,106 +12223,106 @@
       </c>
     </row>
     <row r="133" ht="18" customHeight="1" s="63">
-      <c r="C133" s="316" t="n">
+      <c r="C133" s="330" t="n">
         <v>0</v>
       </c>
-      <c r="D133" s="304" t="n">
+      <c r="D133" s="318" t="n">
         <v>520.2</v>
       </c>
-      <c r="E133" s="304" t="n">
+      <c r="E133" s="318" t="n">
         <v>553.4</v>
       </c>
-      <c r="F133" s="304" t="n">
+      <c r="F133" s="318" t="n">
         <v>585.9</v>
       </c>
-      <c r="G133" s="304" t="n">
-        <v>646.1</v>
-      </c>
-      <c r="H133" s="313">
+      <c r="G133" s="318" t="n">
+        <v>646.9</v>
+      </c>
+      <c r="H133" s="327">
         <f>CHOOSE(MATCH(MIN(D133:G133),D133:G133,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1" s="63">
-      <c r="C134" s="317" t="n">
+      <c r="C134" s="331" t="n">
         <v>0.3</v>
       </c>
-      <c r="D134" s="305" t="n">
+      <c r="D134" s="319" t="n">
         <v>545.2</v>
       </c>
-      <c r="E134" s="305" t="n">
+      <c r="E134" s="319" t="n">
         <v>510.5</v>
       </c>
-      <c r="F134" s="305" t="n">
+      <c r="F134" s="319" t="n">
         <v>511.9</v>
       </c>
-      <c r="G134" s="305" t="n">
-        <v>623.6</v>
-      </c>
-      <c r="H134" s="314">
+      <c r="G134" s="319" t="n">
+        <v>624.2</v>
+      </c>
+      <c r="H134" s="328">
         <f>CHOOSE(MATCH(MIN(D134:G134),D134:G134,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1" s="63">
-      <c r="C135" s="316" t="n">
+      <c r="C135" s="330" t="n">
         <v>0.5</v>
       </c>
-      <c r="D135" s="304" t="n">
+      <c r="D135" s="318" t="n">
         <v>595.9</v>
       </c>
-      <c r="E135" s="304" t="n">
+      <c r="E135" s="318" t="n">
         <v>498.6</v>
       </c>
-      <c r="F135" s="304" t="n">
+      <c r="F135" s="318" t="n">
         <v>481.6</v>
       </c>
-      <c r="G135" s="304" t="n">
-        <v>622.9</v>
-      </c>
-      <c r="H135" s="313">
+      <c r="G135" s="318" t="n">
+        <v>623.4</v>
+      </c>
+      <c r="H135" s="327">
         <f>CHOOSE(MATCH(MIN(D135:G135),D135:G135,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1" s="63">
-      <c r="C136" s="317" t="n">
+      <c r="C136" s="331" t="n">
         <v>0.7</v>
       </c>
-      <c r="D136" s="305" t="n">
+      <c r="D136" s="319" t="n">
         <v>688</v>
       </c>
-      <c r="E136" s="305" t="n">
+      <c r="E136" s="319" t="n">
         <v>500.1</v>
       </c>
-      <c r="F136" s="305" t="n">
+      <c r="F136" s="319" t="n">
         <v>464</v>
       </c>
-      <c r="G136" s="305" t="n">
-        <v>633.8</v>
-      </c>
-      <c r="H136" s="314">
+      <c r="G136" s="319" t="n">
+        <v>634.4</v>
+      </c>
+      <c r="H136" s="328">
         <f>CHOOSE(MATCH(MIN(D136:G136),D136:G136,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1" s="63">
-      <c r="C137" s="316" t="n">
+      <c r="C137" s="330" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="304" t="n">
+      <c r="D137" s="318" t="n">
         <v>955</v>
       </c>
-      <c r="E137" s="304" t="n">
+      <c r="E137" s="318" t="n">
         <v>531.4</v>
       </c>
-      <c r="F137" s="304" t="n">
+      <c r="F137" s="318" t="n">
         <v>459.4</v>
       </c>
-      <c r="G137" s="304" t="n">
-        <v>676.2</v>
-      </c>
-      <c r="H137" s="313">
+      <c r="G137" s="318" t="n">
+        <v>676.8</v>
+      </c>
+      <c r="H137" s="327">
         <f>CHOOSE(MATCH(MIN(D137:G137),D137:G137,0),"A","B","C","D")</f>
         <v/>
       </c>

--- a/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
+++ b/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
@@ -255,7 +255,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="332">
+  <cellXfs count="346">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -698,6 +698,48 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4676,7 +4718,7 @@
       <c r="L5" s="108" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1" s="63">
-      <c r="B6" s="327" t="n">
+      <c r="B6" s="341" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -4684,7 +4726,7 @@
           <t>Шкаф оптический распределительный (ОРШ) центральный — в здании ЦУ</t>
         </is>
       </c>
-      <c r="D6" s="327" t="inlineStr">
+      <c r="D6" s="341" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4694,22 +4736,22 @@
           <t>1 на СНП (здание по проекту)</t>
         </is>
       </c>
-      <c r="F6" s="318" t="n">
+      <c r="F6" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="318" t="n">
+      <c r="G6" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="318" t="n">
+      <c r="H6" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="318" t="n">
+      <c r="I6" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="318" t="n">
+      <c r="J6" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="318" t="n">
+      <c r="K6" s="332" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="146">
@@ -4718,7 +4760,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="63">
-      <c r="B7" s="328" t="n">
+      <c r="B7" s="342" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="114" t="inlineStr">
@@ -4726,7 +4768,7 @@
           <t>Шкаф зонный ОРШ уличный (под сплиттеры 1:64)</t>
         </is>
       </c>
-      <c r="D7" s="328" t="inlineStr">
+      <c r="D7" s="342" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4736,20 +4778,20 @@
           <t>1 на зону — в центре сектора (медиана зоны, зона ≥ 48 ДХ)</t>
         </is>
       </c>
-      <c r="F7" s="319" t="n">
+      <c r="F7" s="333" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="319" t="n"/>
-      <c r="H7" s="319" t="n">
+      <c r="G7" s="333" t="n"/>
+      <c r="H7" s="333" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="319" t="n">
+      <c r="I7" s="333" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="319" t="n">
+      <c r="J7" s="333" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="319" t="n">
+      <c r="K7" s="333" t="n">
         <v>6</v>
       </c>
       <c r="L7" s="147">
@@ -4758,7 +4800,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="63">
-      <c r="B8" s="327" t="n">
+      <c r="B8" s="341" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -4766,7 +4808,7 @@
           <t>Сплиттер PLC 1×64 (в ОРШ: ЦУ и зонных)</t>
         </is>
       </c>
-      <c r="D8" s="327" t="inlineStr">
+      <c r="D8" s="341" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4776,22 +4818,22 @@
           <t>ceil(ДХ зоны / 64), заполнение 75-100%</t>
         </is>
       </c>
-      <c r="F8" s="318" t="n">
+      <c r="F8" s="332" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="318" t="n">
+      <c r="G8" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="318" t="n">
+      <c r="H8" s="332" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="318" t="n">
+      <c r="I8" s="332" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="318" t="n">
+      <c r="J8" s="332" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="318" t="n">
+      <c r="K8" s="332" t="n">
         <v>13</v>
       </c>
       <c r="L8" s="146">
@@ -4800,7 +4842,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="63">
-      <c r="B9" s="328" t="n">
+      <c r="B9" s="342" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="114" t="inlineStr">
@@ -4808,7 +4850,7 @@
           <t>Пигтейль SC/UPC для кросса ОРШ</t>
         </is>
       </c>
-      <c r="D9" s="328" t="inlineStr">
+      <c r="D9" s="342" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4818,22 +4860,22 @@
           <t>ДХ + 2 × сплиттеры 1:64</t>
         </is>
       </c>
-      <c r="F9" s="319" t="n">
+      <c r="F9" s="333" t="n">
         <v>1073</v>
       </c>
-      <c r="G9" s="319" t="n">
+      <c r="G9" s="333" t="n">
         <v>128</v>
       </c>
-      <c r="H9" s="319" t="n">
+      <c r="H9" s="333" t="n">
         <v>392</v>
       </c>
-      <c r="I9" s="319" t="n">
+      <c r="I9" s="333" t="n">
         <v>650</v>
       </c>
-      <c r="J9" s="319" t="n">
-        <v>298</v>
-      </c>
-      <c r="K9" s="319" t="n">
+      <c r="J9" s="333" t="n">
+        <v>300</v>
+      </c>
+      <c r="K9" s="333" t="n">
         <v>676</v>
       </c>
       <c r="L9" s="147">
@@ -4842,7 +4884,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="63">
-      <c r="B10" s="327" t="n">
+      <c r="B10" s="341" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="112" t="inlineStr">
@@ -4850,7 +4892,7 @@
           <t>Порт PON OLT — справочно (активное оборудование, единый узел OLT)</t>
         </is>
       </c>
-      <c r="D10" s="327" t="inlineStr">
+      <c r="D10" s="341" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4860,22 +4902,22 @@
           <t>по числу сплиттеров 1:64</t>
         </is>
       </c>
-      <c r="F10" s="318" t="n">
+      <c r="F10" s="332" t="n">
         <v>22</v>
       </c>
-      <c r="G10" s="318" t="n">
+      <c r="G10" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="318" t="n">
+      <c r="H10" s="332" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="318" t="n">
+      <c r="I10" s="332" t="n">
         <v>14</v>
       </c>
-      <c r="J10" s="318" t="n">
+      <c r="J10" s="332" t="n">
         <v>6</v>
       </c>
-      <c r="K10" s="318" t="n">
+      <c r="K10" s="332" t="n">
         <v>13</v>
       </c>
       <c r="L10" s="146">
@@ -4901,7 +4943,7 @@
       <c r="L11" s="108" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="63">
-      <c r="B12" s="327" t="n">
+      <c r="B12" s="341" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="112" t="inlineStr">
@@ -4909,7 +4951,7 @@
           <t>Кабель оптический самонесущий, 8 волокон</t>
         </is>
       </c>
-      <c r="D12" s="327" t="inlineStr">
+      <c r="D12" s="341" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4919,22 +4961,22 @@
           <t>распределение зоны max(8; 1,25 × ДХ потока) + фидер ceil(1,25 × сплиттеры зоны)</t>
         </is>
       </c>
-      <c r="F12" s="320" t="n">
+      <c r="F12" s="334" t="n">
         <v>16.7</v>
       </c>
-      <c r="G12" s="320" t="n">
+      <c r="G12" s="334" t="n">
         <v>2.6</v>
       </c>
-      <c r="H12" s="320" t="n">
+      <c r="H12" s="334" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="320" t="n">
+      <c r="I12" s="334" t="n">
         <v>9.9</v>
       </c>
-      <c r="J12" s="320" t="n">
+      <c r="J12" s="334" t="n">
         <v>4.5</v>
       </c>
-      <c r="K12" s="320" t="n">
+      <c r="K12" s="334" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="148">
@@ -4943,7 +4985,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="63">
-      <c r="B13" s="328" t="n">
+      <c r="B13" s="342" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="114" t="inlineStr">
@@ -4951,7 +4993,7 @@
           <t>Кабель оптический самонесущий, 12 волокон</t>
         </is>
       </c>
-      <c r="D13" s="328" t="inlineStr">
+      <c r="D13" s="342" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4961,22 +5003,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F13" s="322" t="n">
+      <c r="F13" s="336" t="n">
         <v>4.4</v>
       </c>
-      <c r="G13" s="322" t="n">
+      <c r="G13" s="336" t="n">
         <v>0.6</v>
       </c>
-      <c r="H13" s="322" t="n">
+      <c r="H13" s="336" t="n">
         <v>1.5</v>
       </c>
-      <c r="I13" s="322" t="n">
+      <c r="I13" s="336" t="n">
         <v>3.5</v>
       </c>
-      <c r="J13" s="322" t="n">
+      <c r="J13" s="336" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" s="322" t="n">
+      <c r="K13" s="336" t="n">
         <v>0.9</v>
       </c>
       <c r="L13" s="149">
@@ -4985,7 +5027,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="63">
-      <c r="B14" s="327" t="n">
+      <c r="B14" s="341" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="112" t="inlineStr">
@@ -4993,7 +5035,7 @@
           <t>Кабель оптический самонесущий, 16 волокон</t>
         </is>
       </c>
-      <c r="D14" s="327" t="inlineStr">
+      <c r="D14" s="341" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5003,22 +5045,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F14" s="320" t="n">
+      <c r="F14" s="334" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" s="320" t="n">
+      <c r="G14" s="334" t="n">
         <v>0.5</v>
       </c>
-      <c r="H14" s="320" t="n">
+      <c r="H14" s="334" t="n">
         <v>0.5</v>
       </c>
-      <c r="I14" s="320" t="n">
+      <c r="I14" s="334" t="n">
         <v>1.6</v>
       </c>
-      <c r="J14" s="320" t="n">
+      <c r="J14" s="334" t="n">
         <v>1.3</v>
       </c>
-      <c r="K14" s="320" t="n">
+      <c r="K14" s="334" t="n">
         <v>1.1</v>
       </c>
       <c r="L14" s="148">
@@ -5027,7 +5069,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="63">
-      <c r="B15" s="328" t="n">
+      <c r="B15" s="342" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="114" t="inlineStr">
@@ -5035,7 +5077,7 @@
           <t>Кабель оптический самонесущий, 24 волокна</t>
         </is>
       </c>
-      <c r="D15" s="328" t="inlineStr">
+      <c r="D15" s="342" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5045,22 +5087,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F15" s="322" t="n">
+      <c r="F15" s="336" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="322" t="n">
+      <c r="G15" s="336" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="322" t="n">
+      <c r="H15" s="336" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="322" t="n">
+      <c r="I15" s="336" t="n">
         <v>3.1</v>
       </c>
-      <c r="J15" s="322" t="n">
+      <c r="J15" s="336" t="n">
         <v>1.4</v>
       </c>
-      <c r="K15" s="322" t="n">
+      <c r="K15" s="336" t="n">
         <v>1.4</v>
       </c>
       <c r="L15" s="149">
@@ -5069,7 +5111,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="63">
-      <c r="B16" s="327" t="n">
+      <c r="B16" s="341" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="112" t="inlineStr">
@@ -5077,7 +5119,7 @@
           <t>Кабель оптический самонесущий, 32 волокна</t>
         </is>
       </c>
-      <c r="D16" s="327" t="inlineStr">
+      <c r="D16" s="341" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5087,22 +5129,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F16" s="320" t="n">
+      <c r="F16" s="334" t="n">
         <v>2.2</v>
       </c>
-      <c r="G16" s="320" t="n">
+      <c r="G16" s="334" t="n">
         <v>0.4</v>
       </c>
-      <c r="H16" s="320" t="n">
+      <c r="H16" s="334" t="n">
         <v>1.1</v>
       </c>
-      <c r="I16" s="320" t="n">
+      <c r="I16" s="334" t="n">
         <v>1.8</v>
       </c>
-      <c r="J16" s="320" t="n">
+      <c r="J16" s="334" t="n">
         <v>0.8</v>
       </c>
-      <c r="K16" s="320" t="n">
+      <c r="K16" s="334" t="n">
         <v>0.9</v>
       </c>
       <c r="L16" s="148">
@@ -5111,7 +5153,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="63">
-      <c r="B17" s="328" t="n">
+      <c r="B17" s="342" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="114" t="inlineStr">
@@ -5119,7 +5161,7 @@
           <t>Кабель оптический самонесущий, 48 волокон</t>
         </is>
       </c>
-      <c r="D17" s="328" t="inlineStr">
+      <c r="D17" s="342" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5129,22 +5171,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F17" s="322" t="n">
+      <c r="F17" s="336" t="n">
         <v>1.7</v>
       </c>
-      <c r="G17" s="322" t="n">
+      <c r="G17" s="336" t="n">
         <v>0.2</v>
       </c>
-      <c r="H17" s="322" t="n">
+      <c r="H17" s="336" t="n">
         <v>1.1</v>
       </c>
-      <c r="I17" s="322" t="n">
+      <c r="I17" s="336" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" s="322" t="n">
+      <c r="J17" s="336" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="322" t="n">
+      <c r="K17" s="336" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="149">
@@ -5153,7 +5195,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="63">
-      <c r="B18" s="327" t="n">
+      <c r="B18" s="341" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="112" t="inlineStr">
@@ -5161,7 +5203,7 @@
           <t>Кабель оптический самонесущий, 64 волокна</t>
         </is>
       </c>
-      <c r="D18" s="327" t="inlineStr">
+      <c r="D18" s="341" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5171,22 +5213,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F18" s="320" t="n">
+      <c r="F18" s="334" t="n">
         <v>0.7</v>
       </c>
-      <c r="G18" s="320" t="n">
+      <c r="G18" s="334" t="n">
         <v>0.3</v>
       </c>
-      <c r="H18" s="320" t="n">
+      <c r="H18" s="334" t="n">
         <v>0.5</v>
       </c>
-      <c r="I18" s="320" t="n">
+      <c r="I18" s="334" t="n">
         <v>0.4</v>
       </c>
-      <c r="J18" s="320" t="n">
+      <c r="J18" s="334" t="n">
         <v>0.3</v>
       </c>
-      <c r="K18" s="320" t="n">
+      <c r="K18" s="334" t="n">
         <v>0.4</v>
       </c>
       <c r="L18" s="148">
@@ -5195,7 +5237,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="63">
-      <c r="B19" s="328" t="n">
+      <c r="B19" s="342" t="n">
         <v>13</v>
       </c>
       <c r="C19" s="114" t="inlineStr">
@@ -5203,7 +5245,7 @@
           <t>Кабель оптический самонесущий, 72 волокна</t>
         </is>
       </c>
-      <c r="D19" s="328" t="inlineStr">
+      <c r="D19" s="342" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5213,14 +5255,14 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F19" s="322" t="n">
+      <c r="F19" s="336" t="n">
         <v>0.4</v>
       </c>
-      <c r="G19" s="322" t="n"/>
-      <c r="H19" s="322" t="n"/>
-      <c r="I19" s="322" t="n"/>
-      <c r="J19" s="322" t="n"/>
-      <c r="K19" s="322" t="n">
+      <c r="G19" s="336" t="n"/>
+      <c r="H19" s="336" t="n"/>
+      <c r="I19" s="336" t="n"/>
+      <c r="J19" s="336" t="n"/>
+      <c r="K19" s="336" t="n">
         <v>0.3</v>
       </c>
       <c r="L19" s="149">
@@ -5229,7 +5271,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="63">
-      <c r="B20" s="327" t="n">
+      <c r="B20" s="341" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="112" t="inlineStr">
@@ -5237,7 +5279,7 @@
           <t>Кабель оптический самонесущий, 96 волокон</t>
         </is>
       </c>
-      <c r="D20" s="327" t="inlineStr">
+      <c r="D20" s="341" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5247,20 +5289,20 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F20" s="320" t="n">
+      <c r="F20" s="334" t="n">
         <v>0.1</v>
       </c>
-      <c r="G20" s="320" t="n">
+      <c r="G20" s="334" t="n">
         <v>0.1</v>
       </c>
-      <c r="H20" s="320" t="n">
+      <c r="H20" s="334" t="n">
         <v>0.2</v>
       </c>
-      <c r="I20" s="320" t="n"/>
-      <c r="J20" s="320" t="n">
+      <c r="I20" s="334" t="n"/>
+      <c r="J20" s="334" t="n">
         <v>0.1</v>
       </c>
-      <c r="K20" s="320" t="n">
+      <c r="K20" s="334" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="148">
@@ -5269,7 +5311,7 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="63">
-      <c r="B21" s="328" t="n">
+      <c r="B21" s="342" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="114" t="inlineStr">
@@ -5277,7 +5319,7 @@
           <t>Кабель дроп-кабельный самонесущий, 2 волокна (1 раб. + 1 рез.)</t>
         </is>
       </c>
-      <c r="D21" s="328" t="inlineStr">
+      <c r="D21" s="342" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5287,22 +5329,22 @@
           <t>дропы × 1,05 (без подводок — дроп от муфты напрямую)</t>
         </is>
       </c>
-      <c r="F21" s="322" t="n">
+      <c r="F21" s="336" t="n">
         <v>41.7</v>
       </c>
-      <c r="G21" s="322" t="n">
+      <c r="G21" s="336" t="n">
         <v>5.2</v>
       </c>
-      <c r="H21" s="322" t="n">
+      <c r="H21" s="336" t="n">
         <v>15.8</v>
       </c>
-      <c r="I21" s="322" t="n">
+      <c r="I21" s="336" t="n">
         <v>27.2</v>
       </c>
-      <c r="J21" s="322" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="K21" s="322" t="n">
+      <c r="J21" s="336" t="n">
+        <v>13</v>
+      </c>
+      <c r="K21" s="336" t="n">
         <v>24</v>
       </c>
       <c r="L21" s="149">
@@ -5311,7 +5353,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="63">
-      <c r="B22" s="327" t="n">
+      <c r="B22" s="341" t="n">
         <v>16</v>
       </c>
       <c r="C22" s="112" t="inlineStr">
@@ -5319,7 +5361,7 @@
           <t>Справочно: суммарная ёмкость магистрального кабеля</t>
         </is>
       </c>
-      <c r="D22" s="327" t="inlineStr">
+      <c r="D22" s="341" t="inlineStr">
         <is>
           <t>волокно-км</t>
         </is>
@@ -5329,22 +5371,22 @@
           <t>Σ (длина участка × волокна)</t>
         </is>
       </c>
-      <c r="F22" s="320" t="n">
+      <c r="F22" s="334" t="n">
         <v>524.8</v>
       </c>
-      <c r="G22" s="320" t="n">
+      <c r="G22" s="334" t="n">
         <v>90</v>
       </c>
-      <c r="H22" s="320" t="n">
+      <c r="H22" s="334" t="n">
         <v>218.5</v>
       </c>
-      <c r="I22" s="320" t="n">
+      <c r="I22" s="334" t="n">
         <v>329.9</v>
       </c>
-      <c r="J22" s="320" t="n">
+      <c r="J22" s="334" t="n">
         <v>141.2</v>
       </c>
-      <c r="K22" s="320" t="n">
+      <c r="K22" s="334" t="n">
         <v>193.9</v>
       </c>
       <c r="L22" s="148">
@@ -5370,7 +5412,7 @@
       <c r="L23" s="108" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="63">
-      <c r="B24" s="327" t="n">
+      <c r="B24" s="341" t="n">
         <v>17</v>
       </c>
       <c r="C24" s="112" t="inlineStr">
@@ -5378,7 +5420,7 @@
           <t>Муфта оптическая (ветвления магистрали)</t>
         </is>
       </c>
-      <c r="D24" s="327" t="inlineStr">
+      <c r="D24" s="341" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5388,22 +5430,22 @@
           <t>узлы ветвления кроме точек врезов зонных ОРШ; транзит — неразрезным кабелем</t>
         </is>
       </c>
-      <c r="F24" s="318" t="n">
+      <c r="F24" s="332" t="n">
         <v>367</v>
       </c>
-      <c r="G24" s="318" t="n">
+      <c r="G24" s="332" t="n">
         <v>70</v>
       </c>
-      <c r="H24" s="318" t="n">
+      <c r="H24" s="332" t="n">
         <v>158</v>
       </c>
-      <c r="I24" s="318" t="n">
+      <c r="I24" s="332" t="n">
         <v>246</v>
       </c>
-      <c r="J24" s="318" t="n">
+      <c r="J24" s="332" t="n">
         <v>119</v>
       </c>
-      <c r="K24" s="318" t="n">
+      <c r="K24" s="332" t="n">
         <v>143</v>
       </c>
       <c r="L24" s="146">
@@ -5429,7 +5471,7 @@
       <c r="L25" s="108" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="63">
-      <c r="B26" s="327" t="n">
+      <c r="B26" s="341" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="112" t="inlineStr">
@@ -5437,7 +5479,7 @@
           <t>Бокс абонентский оптический с адаптером SC/UPC</t>
         </is>
       </c>
-      <c r="D26" s="327" t="inlineStr">
+      <c r="D26" s="341" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5447,22 +5489,22 @@
           <t>1 на ДХ</t>
         </is>
       </c>
-      <c r="F26" s="318" t="n">
+      <c r="F26" s="332" t="n">
         <v>1029</v>
       </c>
-      <c r="G26" s="318" t="n">
+      <c r="G26" s="332" t="n">
         <v>124</v>
       </c>
-      <c r="H26" s="318" t="n">
+      <c r="H26" s="332" t="n">
         <v>376</v>
       </c>
-      <c r="I26" s="318" t="n">
+      <c r="I26" s="332" t="n">
         <v>622</v>
       </c>
-      <c r="J26" s="318" t="n">
-        <v>286</v>
-      </c>
-      <c r="K26" s="318" t="n">
+      <c r="J26" s="332" t="n">
+        <v>288</v>
+      </c>
+      <c r="K26" s="332" t="n">
         <v>650</v>
       </c>
       <c r="L26" s="146">
@@ -5471,7 +5513,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="63">
-      <c r="B27" s="328" t="n">
+      <c r="B27" s="342" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="114" t="inlineStr">
@@ -5479,7 +5521,7 @@
           <t>Коннектор оптический механический SC/UPC</t>
         </is>
       </c>
-      <c r="D27" s="328" t="inlineStr">
+      <c r="D27" s="342" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5489,22 +5531,22 @@
           <t>ДХ × 1,1 (абонентский бокс)</t>
         </is>
       </c>
-      <c r="F27" s="319" t="n">
+      <c r="F27" s="333" t="n">
         <v>1132</v>
       </c>
-      <c r="G27" s="319" t="n">
+      <c r="G27" s="333" t="n">
         <v>137</v>
       </c>
-      <c r="H27" s="319" t="n">
+      <c r="H27" s="333" t="n">
         <v>414</v>
       </c>
-      <c r="I27" s="319" t="n">
+      <c r="I27" s="333" t="n">
         <v>685</v>
       </c>
-      <c r="J27" s="319" t="n">
-        <v>315</v>
-      </c>
-      <c r="K27" s="319" t="n">
+      <c r="J27" s="333" t="n">
+        <v>317</v>
+      </c>
+      <c r="K27" s="333" t="n">
         <v>715</v>
       </c>
       <c r="L27" s="147">
@@ -5513,7 +5555,7 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="63">
-      <c r="B28" s="327" t="n">
+      <c r="B28" s="341" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="112" t="inlineStr">
@@ -5521,7 +5563,7 @@
           <t>Сварное соединение (оценка объёма работ)</t>
         </is>
       </c>
-      <c r="D28" s="327" t="inlineStr">
+      <c r="D28" s="341" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5531,22 +5573,22 @@
           <t>(2 × ДХ + 2 × сплиттеры 1:64) × 1,1</t>
         </is>
       </c>
-      <c r="F28" s="318" t="n">
+      <c r="F28" s="332" t="n">
         <v>2313</v>
       </c>
-      <c r="G28" s="318" t="n">
+      <c r="G28" s="332" t="n">
         <v>278</v>
       </c>
-      <c r="H28" s="318" t="n">
+      <c r="H28" s="332" t="n">
         <v>845</v>
       </c>
-      <c r="I28" s="318" t="n">
+      <c r="I28" s="332" t="n">
         <v>1400</v>
       </c>
-      <c r="J28" s="318" t="n">
-        <v>643</v>
-      </c>
-      <c r="K28" s="318" t="n">
+      <c r="J28" s="332" t="n">
+        <v>647</v>
+      </c>
+      <c r="K28" s="332" t="n">
         <v>1459</v>
       </c>
       <c r="L28" s="146">
@@ -5555,7 +5597,7 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="63">
-      <c r="B29" s="328" t="n">
+      <c r="B29" s="342" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="114" t="inlineStr">
@@ -5563,7 +5605,7 @@
           <t>Гильза КДЗС, 60 мм</t>
         </is>
       </c>
-      <c r="D29" s="328" t="inlineStr">
+      <c r="D29" s="342" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5573,22 +5615,22 @@
           <t>по числу сварных соединений</t>
         </is>
       </c>
-      <c r="F29" s="319" t="n">
+      <c r="F29" s="333" t="n">
         <v>2313</v>
       </c>
-      <c r="G29" s="319" t="n">
+      <c r="G29" s="333" t="n">
         <v>278</v>
       </c>
-      <c r="H29" s="319" t="n">
+      <c r="H29" s="333" t="n">
         <v>845</v>
       </c>
-      <c r="I29" s="319" t="n">
+      <c r="I29" s="333" t="n">
         <v>1400</v>
       </c>
-      <c r="J29" s="319" t="n">
-        <v>643</v>
-      </c>
-      <c r="K29" s="319" t="n">
+      <c r="J29" s="333" t="n">
+        <v>647</v>
+      </c>
+      <c r="K29" s="333" t="n">
         <v>1459</v>
       </c>
       <c r="L29" s="147">
@@ -5597,7 +5639,7 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="63">
-      <c r="B30" s="327" t="n">
+      <c r="B30" s="341" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="112" t="inlineStr">
@@ -5605,7 +5647,7 @@
           <t>Комплект подвеса магистрального кабеля (кронштейн + спиральный зажим)</t>
         </is>
       </c>
-      <c r="D30" s="327" t="inlineStr">
+      <c r="D30" s="341" t="inlineStr">
         <is>
           <t>компл</t>
         </is>
@@ -5615,22 +5657,22 @@
           <t>30 на 1 км кабеля</t>
         </is>
       </c>
-      <c r="F30" s="318" t="n">
+      <c r="F30" s="332" t="n">
         <v>918</v>
       </c>
-      <c r="G30" s="318" t="n">
+      <c r="G30" s="332" t="n">
         <v>144</v>
       </c>
-      <c r="H30" s="318" t="n">
+      <c r="H30" s="332" t="n">
         <v>316</v>
       </c>
-      <c r="I30" s="318" t="n">
+      <c r="I30" s="332" t="n">
         <v>584</v>
       </c>
-      <c r="J30" s="318" t="n">
+      <c r="J30" s="332" t="n">
         <v>247</v>
       </c>
-      <c r="K30" s="318" t="n">
+      <c r="K30" s="332" t="n">
         <v>263</v>
       </c>
       <c r="L30" s="146">
@@ -5639,7 +5681,7 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" s="63">
-      <c r="B31" s="328" t="n">
+      <c r="B31" s="342" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="114" t="inlineStr">
@@ -5647,7 +5689,7 @@
           <t>Анкерный зажим дроп-кабеля</t>
         </is>
       </c>
-      <c r="D31" s="328" t="inlineStr">
+      <c r="D31" s="342" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5657,22 +5699,22 @@
           <t>2 на ДХ</t>
         </is>
       </c>
-      <c r="F31" s="319" t="n">
+      <c r="F31" s="333" t="n">
         <v>2058</v>
       </c>
-      <c r="G31" s="319" t="n">
+      <c r="G31" s="333" t="n">
         <v>248</v>
       </c>
-      <c r="H31" s="319" t="n">
+      <c r="H31" s="333" t="n">
         <v>752</v>
       </c>
-      <c r="I31" s="319" t="n">
+      <c r="I31" s="333" t="n">
         <v>1244</v>
       </c>
-      <c r="J31" s="319" t="n">
-        <v>572</v>
-      </c>
-      <c r="K31" s="319" t="n">
+      <c r="J31" s="333" t="n">
+        <v>576</v>
+      </c>
+      <c r="K31" s="333" t="n">
         <v>1300</v>
       </c>
       <c r="L31" s="147">
@@ -5681,7 +5723,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" s="63">
-      <c r="B32" s="327" t="n">
+      <c r="B32" s="341" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="112" t="inlineStr">
@@ -5689,7 +5731,7 @@
           <t>Крепёж дроп-кабеля (скобы / хомуты)</t>
         </is>
       </c>
-      <c r="D32" s="327" t="inlineStr">
+      <c r="D32" s="341" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5699,22 +5741,22 @@
           <t>6 на ДХ</t>
         </is>
       </c>
-      <c r="F32" s="318" t="n">
+      <c r="F32" s="332" t="n">
         <v>6174</v>
       </c>
-      <c r="G32" s="318" t="n">
+      <c r="G32" s="332" t="n">
         <v>744</v>
       </c>
-      <c r="H32" s="318" t="n">
+      <c r="H32" s="332" t="n">
         <v>2256</v>
       </c>
-      <c r="I32" s="318" t="n">
+      <c r="I32" s="332" t="n">
         <v>3732</v>
       </c>
-      <c r="J32" s="318" t="n">
-        <v>1716</v>
-      </c>
-      <c r="K32" s="318" t="n">
+      <c r="J32" s="332" t="n">
+        <v>1728</v>
+      </c>
+      <c r="K32" s="332" t="n">
         <v>3900</v>
       </c>
       <c r="L32" s="146">
@@ -9383,7 +9425,7 @@
       </c>
       <c r="D14" s="109" t="inlineStr">
         <is>
-          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1498 (-69% к A); суммарная длина 217.3 км — минимум среди всех схем книги.</t>
+          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1498 (-69% к A); суммарная длина 217.4 км — минимум среди всех схем книги.</t>
         </is>
       </c>
     </row>
@@ -9464,19 +9506,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F18" s="318" t="n">
+      <c r="F18" s="332" t="n">
         <v>69</v>
       </c>
-      <c r="G18" s="318" t="n">
+      <c r="G18" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="318" t="n">
+      <c r="H18" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="318" t="n">
+      <c r="I18" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="318" t="n">
+      <c r="J18" s="332" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9492,19 +9534,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F19" s="319" t="n">
+      <c r="F19" s="333" t="n">
         <v>46</v>
       </c>
-      <c r="G19" s="319" t="n">
+      <c r="G19" s="333" t="n">
         <v>752</v>
       </c>
-      <c r="H19" s="319" t="n">
+      <c r="H19" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="319" t="n">
+      <c r="I19" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="319" t="n">
+      <c r="J19" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9520,19 +9562,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F20" s="318" t="n">
+      <c r="F20" s="332" t="n">
         <v>114</v>
       </c>
-      <c r="G20" s="318" t="n">
+      <c r="G20" s="332" t="n">
         <v>546</v>
       </c>
-      <c r="H20" s="318" t="n">
+      <c r="H20" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="318" t="n">
+      <c r="I20" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="318" t="n">
+      <c r="J20" s="332" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9548,19 +9590,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F21" s="319" t="n">
+      <c r="F21" s="333" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="319" t="n">
+      <c r="G21" s="333" t="n">
         <v>667</v>
       </c>
-      <c r="H21" s="319" t="n">
+      <c r="H21" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="319" t="n">
+      <c r="I21" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="319" t="n">
+      <c r="J21" s="333" t="n">
         <v>48</v>
       </c>
     </row>
@@ -9576,19 +9618,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F22" s="318" t="n">
+      <c r="F22" s="332" t="n">
         <v>132</v>
       </c>
-      <c r="G22" s="318" t="n">
+      <c r="G22" s="332" t="n">
         <v>717</v>
       </c>
-      <c r="H22" s="318" t="n">
+      <c r="H22" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="318" t="n">
+      <c r="I22" s="332" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="318" t="n">
+      <c r="J22" s="332" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9604,19 +9646,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F23" s="319" t="n">
+      <c r="F23" s="333" t="n">
         <v>109</v>
       </c>
-      <c r="G23" s="319" t="n">
+      <c r="G23" s="333" t="n">
         <v>856</v>
       </c>
-      <c r="H23" s="319" t="n">
+      <c r="H23" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="319" t="n">
+      <c r="I23" s="333" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="319" t="n">
+      <c r="J23" s="333" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9632,19 +9674,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F24" s="318" t="n">
+      <c r="F24" s="332" t="n">
         <v>84</v>
       </c>
-      <c r="G24" s="318" t="n">
+      <c r="G24" s="332" t="n">
         <v>908</v>
       </c>
-      <c r="H24" s="318" t="n">
+      <c r="H24" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="318" t="n">
+      <c r="I24" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="318" t="n">
+      <c r="J24" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9660,19 +9702,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F25" s="319" t="n">
+      <c r="F25" s="333" t="n">
         <v>50</v>
       </c>
-      <c r="G25" s="319" t="n">
+      <c r="G25" s="333" t="n">
         <v>1708</v>
       </c>
-      <c r="H25" s="319" t="n">
+      <c r="H25" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="319" t="n">
+      <c r="I25" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="319" t="n">
+      <c r="J25" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9688,19 +9730,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F26" s="318" t="n">
+      <c r="F26" s="332" t="n">
         <v>49</v>
       </c>
-      <c r="G26" s="318" t="n">
+      <c r="G26" s="332" t="n">
         <v>860</v>
       </c>
-      <c r="H26" s="318" t="n">
+      <c r="H26" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="318" t="n">
+      <c r="I26" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="318" t="n">
+      <c r="J26" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9716,19 +9758,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F27" s="319" t="n">
+      <c r="F27" s="333" t="n">
         <v>49</v>
       </c>
-      <c r="G27" s="319" t="n">
+      <c r="G27" s="333" t="n">
         <v>1211</v>
       </c>
-      <c r="H27" s="319" t="n">
+      <c r="H27" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="319" t="n">
+      <c r="I27" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="319" t="n">
+      <c r="J27" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9744,19 +9786,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F28" s="318" t="n">
+      <c r="F28" s="332" t="n">
         <v>88</v>
       </c>
-      <c r="G28" s="318" t="n">
+      <c r="G28" s="332" t="n">
         <v>1175</v>
       </c>
-      <c r="H28" s="318" t="n">
+      <c r="H28" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="318" t="n">
+      <c r="I28" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="318" t="n">
+      <c r="J28" s="332" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9772,19 +9814,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F29" s="319" t="n">
+      <c r="F29" s="333" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="319" t="n">
+      <c r="G29" s="333" t="n">
         <v>1169</v>
       </c>
-      <c r="H29" s="319" t="n">
+      <c r="H29" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="319" t="n">
+      <c r="I29" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="319" t="n">
+      <c r="J29" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9800,19 +9842,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F30" s="318" t="n">
+      <c r="F30" s="332" t="n">
         <v>51</v>
       </c>
-      <c r="G30" s="318" t="n">
+      <c r="G30" s="332" t="n">
         <v>1390</v>
       </c>
-      <c r="H30" s="318" t="n">
+      <c r="H30" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="318" t="n">
+      <c r="I30" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="318" t="n">
+      <c r="J30" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9828,19 +9870,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F31" s="319" t="n">
+      <c r="F31" s="333" t="n">
         <v>49</v>
       </c>
-      <c r="G31" s="319" t="n">
+      <c r="G31" s="333" t="n">
         <v>879</v>
       </c>
-      <c r="H31" s="319" t="n">
+      <c r="H31" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="319" t="n">
+      <c r="I31" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="319" t="n">
+      <c r="J31" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9856,19 +9898,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F32" s="318" t="n">
+      <c r="F32" s="332" t="n">
         <v>59</v>
       </c>
-      <c r="G32" s="318" t="n">
+      <c r="G32" s="332" t="n">
         <v>745</v>
       </c>
-      <c r="H32" s="318" t="n">
+      <c r="H32" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="318" t="n">
+      <c r="I32" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="318" t="n">
+      <c r="J32" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9888,19 +9930,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F33" s="319" t="n">
+      <c r="F33" s="333" t="n">
         <v>124</v>
       </c>
-      <c r="G33" s="319" t="n">
+      <c r="G33" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="319" t="n">
+      <c r="H33" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="319" t="n">
+      <c r="I33" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="319" t="n">
+      <c r="J33" s="333" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9920,19 +9962,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F34" s="318" t="n">
+      <c r="F34" s="332" t="n">
         <v>35</v>
       </c>
-      <c r="G34" s="318" t="n">
+      <c r="G34" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="318" t="n">
+      <c r="H34" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="318" t="n">
+      <c r="I34" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="318" t="n">
+      <c r="J34" s="332" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9948,19 +9990,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F35" s="319" t="n">
+      <c r="F35" s="333" t="n">
         <v>56</v>
       </c>
-      <c r="G35" s="319" t="n">
+      <c r="G35" s="333" t="n">
         <v>805</v>
       </c>
-      <c r="H35" s="319" t="n">
+      <c r="H35" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="319" t="n">
+      <c r="I35" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="319" t="n">
+      <c r="J35" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9976,19 +10018,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F36" s="318" t="n">
+      <c r="F36" s="332" t="n">
         <v>156</v>
       </c>
-      <c r="G36" s="318" t="n">
+      <c r="G36" s="332" t="n">
         <v>295</v>
       </c>
-      <c r="H36" s="318" t="n">
+      <c r="H36" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="318" t="n">
+      <c r="I36" s="332" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="318" t="n">
+      <c r="J36" s="332" t="n">
         <v>288</v>
       </c>
     </row>
@@ -10004,19 +10046,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F37" s="319" t="n">
+      <c r="F37" s="333" t="n">
         <v>69</v>
       </c>
-      <c r="G37" s="319" t="n">
+      <c r="G37" s="333" t="n">
         <v>1394</v>
       </c>
-      <c r="H37" s="319" t="n">
+      <c r="H37" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="319" t="n">
+      <c r="I37" s="333" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="319" t="n">
+      <c r="J37" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10032,19 +10074,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F38" s="318" t="n">
+      <c r="F38" s="332" t="n">
         <v>60</v>
       </c>
-      <c r="G38" s="318" t="n">
+      <c r="G38" s="332" t="n">
         <v>556</v>
       </c>
-      <c r="H38" s="318" t="n">
+      <c r="H38" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="318" t="n">
+      <c r="I38" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="318" t="n">
+      <c r="J38" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10064,19 +10106,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F39" s="319" t="n">
+      <c r="F39" s="333" t="n">
         <v>27</v>
       </c>
-      <c r="G39" s="319" t="n">
+      <c r="G39" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="319" t="n">
+      <c r="H39" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="319" t="n">
+      <c r="I39" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="319" t="n">
+      <c r="J39" s="333" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10092,19 +10134,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F40" s="318" t="n">
+      <c r="F40" s="332" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="318" t="n">
+      <c r="G40" s="332" t="n">
         <v>1298</v>
       </c>
-      <c r="H40" s="318" t="n">
+      <c r="H40" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="318" t="n">
+      <c r="I40" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="318" t="n">
+      <c r="J40" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10120,19 +10162,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F41" s="319" t="n">
+      <c r="F41" s="333" t="n">
         <v>107</v>
       </c>
-      <c r="G41" s="319" t="n">
+      <c r="G41" s="333" t="n">
         <v>418</v>
       </c>
-      <c r="H41" s="319" t="n">
+      <c r="H41" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="319" t="n">
+      <c r="I41" s="333" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="319" t="n">
+      <c r="J41" s="333" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10148,19 +10190,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F42" s="318" t="n">
+      <c r="F42" s="332" t="n">
         <v>53</v>
       </c>
-      <c r="G42" s="318" t="n">
+      <c r="G42" s="332" t="n">
         <v>1329</v>
       </c>
-      <c r="H42" s="318" t="n">
+      <c r="H42" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="318" t="n">
+      <c r="I42" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="318" t="n">
+      <c r="J42" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10176,19 +10218,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F43" s="319" t="n">
+      <c r="F43" s="333" t="n">
         <v>53</v>
       </c>
-      <c r="G43" s="319" t="n">
+      <c r="G43" s="333" t="n">
         <v>937</v>
       </c>
-      <c r="H43" s="319" t="n">
+      <c r="H43" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="319" t="n">
+      <c r="I43" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="319" t="n">
+      <c r="J43" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10204,19 +10246,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F44" s="318" t="n">
+      <c r="F44" s="332" t="n">
         <v>85</v>
       </c>
-      <c r="G44" s="318" t="n">
+      <c r="G44" s="332" t="n">
         <v>368</v>
       </c>
-      <c r="H44" s="318" t="n">
+      <c r="H44" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="318" t="n">
+      <c r="I44" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="318" t="n">
+      <c r="J44" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10232,19 +10274,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F45" s="319" t="n">
+      <c r="F45" s="333" t="n">
         <v>48</v>
       </c>
-      <c r="G45" s="319" t="n">
+      <c r="G45" s="333" t="n">
         <v>1096</v>
       </c>
-      <c r="H45" s="319" t="n">
+      <c r="H45" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="319" t="n">
+      <c r="I45" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="319" t="n">
+      <c r="J45" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10260,19 +10302,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F46" s="318" t="n">
+      <c r="F46" s="332" t="n">
         <v>76</v>
       </c>
-      <c r="G46" s="318" t="n">
+      <c r="G46" s="332" t="n">
         <v>302</v>
       </c>
-      <c r="H46" s="318" t="n">
+      <c r="H46" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="318" t="n">
+      <c r="I46" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="318" t="n">
+      <c r="J46" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10288,19 +10330,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F47" s="319" t="n">
+      <c r="F47" s="333" t="n">
         <v>78</v>
       </c>
-      <c r="G47" s="319" t="n">
+      <c r="G47" s="333" t="n">
         <v>1779</v>
       </c>
-      <c r="H47" s="319" t="n">
+      <c r="H47" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="319" t="n">
+      <c r="I47" s="333" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="319" t="n">
+      <c r="J47" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10316,19 +10358,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F48" s="318" t="n">
+      <c r="F48" s="332" t="n">
         <v>50</v>
       </c>
-      <c r="G48" s="318" t="n">
+      <c r="G48" s="332" t="n">
         <v>476</v>
       </c>
-      <c r="H48" s="318" t="n">
+      <c r="H48" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="318" t="n">
+      <c r="I48" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="318" t="n">
+      <c r="J48" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10348,19 +10390,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F49" s="319" t="n">
+      <c r="F49" s="333" t="n">
         <v>70</v>
       </c>
-      <c r="G49" s="319" t="n">
+      <c r="G49" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="319" t="n">
+      <c r="H49" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="I49" s="319" t="n">
+      <c r="I49" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="319" t="n">
+      <c r="J49" s="333" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10376,19 +10418,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F50" s="318" t="n">
+      <c r="F50" s="332" t="n">
         <v>62</v>
       </c>
-      <c r="G50" s="318" t="n">
+      <c r="G50" s="332" t="n">
         <v>666</v>
       </c>
-      <c r="H50" s="318" t="n">
+      <c r="H50" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="318" t="n">
+      <c r="I50" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="318" t="n">
+      <c r="J50" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10404,19 +10446,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F51" s="319" t="n">
-        <v>93</v>
-      </c>
-      <c r="G51" s="319" t="n">
+      <c r="F51" s="333" t="n">
+        <v>95</v>
+      </c>
+      <c r="G51" s="333" t="n">
         <v>262</v>
       </c>
-      <c r="H51" s="319" t="n">
+      <c r="H51" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="319" t="n">
+      <c r="I51" s="333" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="319" t="n">
+      <c r="J51" s="333" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10432,19 +10474,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F52" s="318" t="n">
+      <c r="F52" s="332" t="n">
         <v>61</v>
       </c>
-      <c r="G52" s="318" t="n">
+      <c r="G52" s="332" t="n">
         <v>367</v>
       </c>
-      <c r="H52" s="318" t="n">
+      <c r="H52" s="332" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="318" t="n">
+      <c r="I52" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="318" t="n">
+      <c r="J52" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10464,19 +10506,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F53" s="319" t="n">
+      <c r="F53" s="333" t="n">
         <v>122</v>
       </c>
-      <c r="G53" s="319" t="n">
+      <c r="G53" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="319" t="n">
+      <c r="H53" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="319" t="n">
+      <c r="I53" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="319" t="n">
+      <c r="J53" s="333" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10492,19 +10534,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F54" s="318" t="n">
+      <c r="F54" s="332" t="n">
         <v>93</v>
       </c>
-      <c r="G54" s="318" t="n">
+      <c r="G54" s="332" t="n">
         <v>274</v>
       </c>
-      <c r="H54" s="318" t="n">
+      <c r="H54" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="318" t="n">
+      <c r="I54" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="318" t="n">
+      <c r="J54" s="332" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10520,19 +10562,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F55" s="319" t="n">
+      <c r="F55" s="333" t="n">
         <v>156</v>
       </c>
-      <c r="G55" s="319" t="n">
+      <c r="G55" s="333" t="n">
         <v>654</v>
       </c>
-      <c r="H55" s="319" t="n">
+      <c r="H55" s="333" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="319" t="n">
+      <c r="I55" s="333" t="n">
         <v>4</v>
       </c>
-      <c r="J55" s="319" t="n">
+      <c r="J55" s="333" t="n">
         <v>288</v>
       </c>
     </row>
@@ -10548,19 +10590,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F56" s="318" t="n">
+      <c r="F56" s="332" t="n">
         <v>91</v>
       </c>
-      <c r="G56" s="318" t="n">
+      <c r="G56" s="332" t="n">
         <v>336</v>
       </c>
-      <c r="H56" s="318" t="n">
+      <c r="H56" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="318" t="n">
+      <c r="I56" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="J56" s="318" t="n">
+      <c r="J56" s="332" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10576,19 +10618,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F57" s="319" t="n">
+      <c r="F57" s="333" t="n">
         <v>59</v>
       </c>
-      <c r="G57" s="319" t="n">
+      <c r="G57" s="333" t="n">
         <v>433</v>
       </c>
-      <c r="H57" s="319" t="n">
+      <c r="H57" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="319" t="n">
+      <c r="I57" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="319" t="n">
+      <c r="J57" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10604,19 +10646,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F58" s="318" t="n">
+      <c r="F58" s="332" t="n">
         <v>73</v>
       </c>
-      <c r="G58" s="318" t="n">
+      <c r="G58" s="332" t="n">
         <v>710</v>
       </c>
-      <c r="H58" s="318" t="n">
+      <c r="H58" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="318" t="n">
+      <c r="I58" s="332" t="n">
         <v>3</v>
       </c>
-      <c r="J58" s="318" t="n">
+      <c r="J58" s="332" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10632,19 +10674,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F59" s="319" t="n">
+      <c r="F59" s="333" t="n">
         <v>56</v>
       </c>
-      <c r="G59" s="319" t="n">
+      <c r="G59" s="333" t="n">
         <v>306</v>
       </c>
-      <c r="H59" s="319" t="n">
+      <c r="H59" s="333" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="319" t="n">
+      <c r="I59" s="333" t="n">
         <v>2</v>
       </c>
-      <c r="J59" s="319" t="n">
+      <c r="J59" s="333" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10767,482 +10809,482 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1" s="63">
-      <c r="C65" s="318" t="n">
+      <c r="C65" s="332" t="n">
         <v>2</v>
       </c>
-      <c r="D65" s="318" t="n">
+      <c r="D65" s="332" t="n">
         <v>48</v>
       </c>
-      <c r="E65" s="320" t="n">
+      <c r="E65" s="334" t="n">
         <v>1460.2</v>
       </c>
-      <c r="F65" s="321">
+      <c r="F65" s="335">
         <f>E65/4375.1-1</f>
         <v/>
       </c>
-      <c r="G65" s="320" t="n">
+      <c r="G65" s="334" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H65" s="320" t="n">
+      <c r="H65" s="334" t="n">
         <v>95.8</v>
       </c>
-      <c r="I65" s="320">
+      <c r="I65" s="334">
         <f>G65+H65</f>
         <v/>
       </c>
-      <c r="J65" s="318" t="n">
+      <c r="J65" s="332" t="n">
         <v>56</v>
       </c>
-      <c r="K65" s="318" t="n">
+      <c r="K65" s="332" t="n">
         <v>5261</v>
       </c>
-      <c r="L65" s="318" t="n">
+      <c r="L65" s="332" t="n">
         <v>4368</v>
       </c>
-      <c r="M65" s="318" t="n">
+      <c r="M65" s="332" t="n">
         <v>349</v>
       </c>
-      <c r="N65" s="318" t="n">
+      <c r="N65" s="332" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1" s="63">
-      <c r="C66" s="319" t="n">
+      <c r="C66" s="333" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="319" t="n">
+      <c r="D66" s="333" t="n">
         <v>43</v>
       </c>
-      <c r="E66" s="322" t="n">
+      <c r="E66" s="336" t="n">
         <v>1476.5</v>
       </c>
-      <c r="F66" s="323">
+      <c r="F66" s="337">
         <f>E66/4375.1-1</f>
         <v/>
       </c>
-      <c r="G66" s="322" t="n">
+      <c r="G66" s="336" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H66" s="322" t="n">
+      <c r="H66" s="336" t="n">
         <v>95.8</v>
       </c>
-      <c r="I66" s="322">
+      <c r="I66" s="336">
         <f>G66+H66</f>
         <v/>
       </c>
-      <c r="J66" s="319" t="n">
+      <c r="J66" s="333" t="n">
         <v>54</v>
       </c>
-      <c r="K66" s="319" t="n">
+      <c r="K66" s="333" t="n">
         <v>5255</v>
       </c>
-      <c r="L66" s="319" t="n">
+      <c r="L66" s="333" t="n">
         <v>4176</v>
       </c>
-      <c r="M66" s="319" t="n">
+      <c r="M66" s="333" t="n">
         <v>358</v>
       </c>
-      <c r="N66" s="319" t="n">
+      <c r="N66" s="333" t="n">
         <v>108</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1" s="63">
-      <c r="C67" s="318" t="n">
+      <c r="C67" s="332" t="n">
         <v>8</v>
       </c>
-      <c r="D67" s="318" t="n">
+      <c r="D67" s="332" t="n">
         <v>39</v>
       </c>
-      <c r="E67" s="320" t="n">
+      <c r="E67" s="334" t="n">
         <v>1500.8</v>
       </c>
-      <c r="F67" s="321">
+      <c r="F67" s="335">
         <f>E67/4375.1-1</f>
         <v/>
       </c>
-      <c r="G67" s="320" t="n">
+      <c r="G67" s="334" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H67" s="320" t="n">
+      <c r="H67" s="334" t="n">
         <v>95.8</v>
       </c>
-      <c r="I67" s="320">
+      <c r="I67" s="334">
         <f>G67+H67</f>
         <v/>
       </c>
-      <c r="J67" s="318" t="n">
+      <c r="J67" s="332" t="n">
         <v>53</v>
       </c>
-      <c r="K67" s="318" t="n">
+      <c r="K67" s="332" t="n">
         <v>5253</v>
       </c>
-      <c r="L67" s="318" t="n">
+      <c r="L67" s="332" t="n">
         <v>3984</v>
       </c>
-      <c r="M67" s="318" t="n">
+      <c r="M67" s="332" t="n">
         <v>368</v>
       </c>
-      <c r="N67" s="318" t="n">
+      <c r="N67" s="332" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="63">
-      <c r="C68" s="319" t="n">
+      <c r="C68" s="333" t="n">
         <v>10</v>
       </c>
-      <c r="D68" s="319" t="n">
+      <c r="D68" s="333" t="n">
         <v>36</v>
       </c>
-      <c r="E68" s="322" t="n">
+      <c r="E68" s="336" t="n">
         <v>1532.5</v>
       </c>
-      <c r="F68" s="323">
+      <c r="F68" s="337">
         <f>E68/4375.1-1</f>
         <v/>
       </c>
-      <c r="G68" s="322" t="n">
+      <c r="G68" s="336" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H68" s="322" t="n">
+      <c r="H68" s="336" t="n">
         <v>95.8</v>
       </c>
-      <c r="I68" s="322">
+      <c r="I68" s="336">
         <f>G68+H68</f>
         <v/>
       </c>
-      <c r="J68" s="319" t="n">
+      <c r="J68" s="333" t="n">
         <v>53</v>
       </c>
-      <c r="K68" s="319" t="n">
+      <c r="K68" s="333" t="n">
         <v>5253</v>
       </c>
-      <c r="L68" s="319" t="n">
+      <c r="L68" s="333" t="n">
         <v>3888</v>
       </c>
-      <c r="M68" s="319" t="n">
+      <c r="M68" s="333" t="n">
         <v>379</v>
       </c>
-      <c r="N68" s="319" t="n">
+      <c r="N68" s="333" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="63">
-      <c r="C69" s="324" t="n">
+      <c r="C69" s="338" t="n">
         <v>15</v>
       </c>
-      <c r="D69" s="324" t="n">
+      <c r="D69" s="338" t="n">
         <v>34</v>
       </c>
-      <c r="E69" s="325" t="n">
+      <c r="E69" s="339" t="n">
         <v>1562.5</v>
       </c>
-      <c r="F69" s="326">
+      <c r="F69" s="340">
         <f>E69/4375.1-1</f>
         <v/>
       </c>
-      <c r="G69" s="325" t="n">
+      <c r="G69" s="339" t="n">
         <v>80.5</v>
       </c>
-      <c r="H69" s="325" t="n">
+      <c r="H69" s="339" t="n">
         <v>95.8</v>
       </c>
-      <c r="I69" s="325">
+      <c r="I69" s="339">
         <f>G69+H69</f>
         <v/>
       </c>
-      <c r="J69" s="324" t="n">
+      <c r="J69" s="338" t="n">
         <v>52</v>
       </c>
-      <c r="K69" s="324" t="n">
+      <c r="K69" s="338" t="n">
         <v>5251</v>
       </c>
-      <c r="L69" s="324" t="n">
+      <c r="L69" s="338" t="n">
         <v>3696</v>
       </c>
-      <c r="M69" s="324" t="n">
+      <c r="M69" s="338" t="n">
         <v>388</v>
       </c>
-      <c r="N69" s="324" t="n">
+      <c r="N69" s="338" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="63">
-      <c r="C70" s="319" t="n">
+      <c r="C70" s="333" t="n">
         <v>20</v>
       </c>
-      <c r="D70" s="319" t="n">
+      <c r="D70" s="333" t="n">
         <v>32</v>
       </c>
-      <c r="E70" s="322" t="n">
+      <c r="E70" s="336" t="n">
         <v>1603.9</v>
       </c>
-      <c r="F70" s="323">
+      <c r="F70" s="337">
         <f>E70/4375.1-1</f>
         <v/>
       </c>
-      <c r="G70" s="322" t="n">
+      <c r="G70" s="336" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="H70" s="322" t="n">
+      <c r="H70" s="336" t="n">
         <v>95.8</v>
       </c>
-      <c r="I70" s="322">
+      <c r="I70" s="336">
         <f>G70+H70</f>
         <v/>
       </c>
-      <c r="J70" s="319" t="n">
+      <c r="J70" s="333" t="n">
         <v>51</v>
       </c>
-      <c r="K70" s="319" t="n">
+      <c r="K70" s="333" t="n">
         <v>5249</v>
       </c>
-      <c r="L70" s="319" t="n">
+      <c r="L70" s="333" t="n">
         <v>3696</v>
       </c>
-      <c r="M70" s="319" t="n">
+      <c r="M70" s="333" t="n">
         <v>403</v>
       </c>
-      <c r="N70" s="319" t="n">
+      <c r="N70" s="333" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="63">
-      <c r="C71" s="318" t="n">
+      <c r="C71" s="332" t="n">
         <v>25</v>
       </c>
-      <c r="D71" s="318" t="n">
+      <c r="D71" s="332" t="n">
         <v>29</v>
       </c>
-      <c r="E71" s="320" t="n">
+      <c r="E71" s="334" t="n">
         <v>1674.7</v>
       </c>
-      <c r="F71" s="321">
+      <c r="F71" s="335">
         <f>E71/4375.1-1</f>
         <v/>
       </c>
-      <c r="G71" s="320" t="n">
+      <c r="G71" s="334" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H71" s="320" t="n">
+      <c r="H71" s="334" t="n">
         <v>95.8</v>
       </c>
-      <c r="I71" s="320">
+      <c r="I71" s="334">
         <f>G71+H71</f>
         <v/>
       </c>
-      <c r="J71" s="318" t="n">
+      <c r="J71" s="332" t="n">
         <v>50</v>
       </c>
-      <c r="K71" s="318" t="n">
+      <c r="K71" s="332" t="n">
         <v>5247</v>
       </c>
-      <c r="L71" s="318" t="n">
+      <c r="L71" s="332" t="n">
         <v>3600</v>
       </c>
-      <c r="M71" s="318" t="n">
+      <c r="M71" s="332" t="n">
         <v>427</v>
       </c>
-      <c r="N71" s="318" t="n">
+      <c r="N71" s="332" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="63">
-      <c r="C72" s="319" t="n">
+      <c r="C72" s="333" t="n">
         <v>30</v>
       </c>
-      <c r="D72" s="319" t="n">
+      <c r="D72" s="333" t="n">
         <v>27</v>
       </c>
-      <c r="E72" s="322" t="n">
+      <c r="E72" s="336" t="n">
         <v>1736.2</v>
       </c>
-      <c r="F72" s="323">
+      <c r="F72" s="337">
         <f>E72/4375.1-1</f>
         <v/>
       </c>
-      <c r="G72" s="322" t="n">
+      <c r="G72" s="336" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="H72" s="322" t="n">
+      <c r="H72" s="336" t="n">
         <v>95.8</v>
       </c>
-      <c r="I72" s="322">
+      <c r="I72" s="336">
         <f>G72+H72</f>
         <v/>
       </c>
-      <c r="J72" s="319" t="n">
+      <c r="J72" s="333" t="n">
         <v>48</v>
       </c>
-      <c r="K72" s="319" t="n">
+      <c r="K72" s="333" t="n">
         <v>5243</v>
       </c>
-      <c r="L72" s="319" t="n">
+      <c r="L72" s="333" t="n">
         <v>3504</v>
       </c>
-      <c r="M72" s="319" t="n">
+      <c r="M72" s="333" t="n">
         <v>448</v>
       </c>
-      <c r="N72" s="319" t="n">
+      <c r="N72" s="333" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="63">
-      <c r="C73" s="318" t="n">
+      <c r="C73" s="332" t="n">
         <v>40</v>
       </c>
-      <c r="D73" s="318" t="n">
+      <c r="D73" s="332" t="n">
         <v>24</v>
       </c>
-      <c r="E73" s="320" t="n">
+      <c r="E73" s="334" t="n">
         <v>1852</v>
       </c>
-      <c r="F73" s="321">
+      <c r="F73" s="335">
         <f>E73/4375.1-1</f>
         <v/>
       </c>
-      <c r="G73" s="320" t="n">
+      <c r="G73" s="334" t="n">
         <v>82.3</v>
       </c>
-      <c r="H73" s="320" t="n">
+      <c r="H73" s="334" t="n">
         <v>95.8</v>
       </c>
-      <c r="I73" s="320">
+      <c r="I73" s="334">
         <f>G73+H73</f>
         <v/>
       </c>
-      <c r="J73" s="318" t="n">
+      <c r="J73" s="332" t="n">
         <v>47</v>
       </c>
-      <c r="K73" s="318" t="n">
+      <c r="K73" s="332" t="n">
         <v>5241</v>
       </c>
-      <c r="L73" s="318" t="n">
+      <c r="L73" s="332" t="n">
         <v>3552</v>
       </c>
-      <c r="M73" s="318" t="n">
+      <c r="M73" s="332" t="n">
         <v>488</v>
       </c>
-      <c r="N73" s="318" t="n">
+      <c r="N73" s="332" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="63">
-      <c r="C74" s="319" t="n">
+      <c r="C74" s="333" t="n">
         <v>50</v>
       </c>
-      <c r="D74" s="319" t="n">
+      <c r="D74" s="333" t="n">
         <v>20</v>
       </c>
-      <c r="E74" s="322" t="n">
+      <c r="E74" s="336" t="n">
         <v>2041.2</v>
       </c>
-      <c r="F74" s="323">
+      <c r="F74" s="337">
         <f>E74/4375.1-1</f>
         <v/>
       </c>
-      <c r="G74" s="322" t="n">
+      <c r="G74" s="336" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="H74" s="322" t="n">
+      <c r="H74" s="336" t="n">
         <v>95.8</v>
       </c>
-      <c r="I74" s="322">
+      <c r="I74" s="336">
         <f>G74+H74</f>
         <v/>
       </c>
-      <c r="J74" s="319" t="n">
+      <c r="J74" s="333" t="n">
         <v>46</v>
       </c>
-      <c r="K74" s="319" t="n">
+      <c r="K74" s="333" t="n">
         <v>5238</v>
       </c>
-      <c r="L74" s="319" t="n">
+      <c r="L74" s="333" t="n">
         <v>3696</v>
       </c>
-      <c r="M74" s="319" t="n">
+      <c r="M74" s="333" t="n">
         <v>554</v>
       </c>
-      <c r="N74" s="319" t="n">
+      <c r="N74" s="333" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="63">
-      <c r="C75" s="318" t="n">
+      <c r="C75" s="332" t="n">
         <v>60</v>
       </c>
-      <c r="D75" s="318" t="n">
+      <c r="D75" s="332" t="n">
         <v>18</v>
       </c>
-      <c r="E75" s="320" t="n">
+      <c r="E75" s="334" t="n">
         <v>2153.9</v>
       </c>
-      <c r="F75" s="321">
+      <c r="F75" s="335">
         <f>E75/4375.1-1</f>
         <v/>
       </c>
-      <c r="G75" s="320" t="n">
+      <c r="G75" s="334" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="H75" s="320" t="n">
+      <c r="H75" s="334" t="n">
         <v>95.8</v>
       </c>
-      <c r="I75" s="320">
+      <c r="I75" s="334">
         <f>G75+H75</f>
         <v/>
       </c>
-      <c r="J75" s="318" t="n">
+      <c r="J75" s="332" t="n">
         <v>45</v>
       </c>
-      <c r="K75" s="318" t="n">
+      <c r="K75" s="332" t="n">
         <v>5236</v>
       </c>
-      <c r="L75" s="318" t="n">
+      <c r="L75" s="332" t="n">
         <v>3744</v>
       </c>
-      <c r="M75" s="318" t="n">
+      <c r="M75" s="332" t="n">
         <v>592</v>
       </c>
-      <c r="N75" s="318" t="n">
+      <c r="N75" s="332" t="n">
         <v>245</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="63">
-      <c r="C76" s="319" t="n">
+      <c r="C76" s="333" t="n">
         <v>80</v>
       </c>
-      <c r="D76" s="319" t="n">
+      <c r="D76" s="333" t="n">
         <v>17</v>
       </c>
-      <c r="E76" s="322" t="n">
+      <c r="E76" s="336" t="n">
         <v>2215.1</v>
       </c>
-      <c r="F76" s="323">
+      <c r="F76" s="337">
         <f>E76/4375.1-1</f>
         <v/>
       </c>
-      <c r="G76" s="322" t="n">
+      <c r="G76" s="336" t="n">
         <v>84.7</v>
       </c>
-      <c r="H76" s="322" t="n">
+      <c r="H76" s="336" t="n">
         <v>95.8</v>
       </c>
-      <c r="I76" s="322">
+      <c r="I76" s="336">
         <f>G76+H76</f>
         <v/>
       </c>
-      <c r="J76" s="319" t="n">
+      <c r="J76" s="333" t="n">
         <v>44</v>
       </c>
-      <c r="K76" s="319" t="n">
+      <c r="K76" s="333" t="n">
         <v>5234</v>
       </c>
-      <c r="L76" s="319" t="n">
+      <c r="L76" s="333" t="n">
         <v>3600</v>
       </c>
-      <c r="M76" s="319" t="n">
+      <c r="M76" s="333" t="n">
         <v>614</v>
       </c>
-      <c r="N76" s="319" t="n">
+      <c r="N76" s="333" t="n">
         <v>245</v>
       </c>
     </row>
@@ -11271,134 +11313,134 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="318" t="n">
+      <c r="B80" s="332" t="n">
         <v>17</v>
       </c>
-      <c r="C80" s="320" t="n">
+      <c r="C80" s="334" t="n">
         <v>2215.1</v>
       </c>
-      <c r="D80" s="320" t="n">
+      <c r="D80" s="334" t="n">
         <v>527.3</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="319" t="n">
+      <c r="B81" s="333" t="n">
         <v>18</v>
       </c>
-      <c r="C81" s="322" t="n">
+      <c r="C81" s="336" t="n">
         <v>2153.9</v>
       </c>
-      <c r="D81" s="322" t="n">
+      <c r="D81" s="336" t="n">
         <v>529.8</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="318" t="n">
+      <c r="B82" s="332" t="n">
         <v>20</v>
       </c>
-      <c r="C82" s="320" t="n">
+      <c r="C82" s="334" t="n">
         <v>2041.2</v>
       </c>
-      <c r="D82" s="320" t="n">
+      <c r="D82" s="334" t="n">
         <v>527.5</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="319" t="n">
+      <c r="B83" s="333" t="n">
         <v>24</v>
       </c>
-      <c r="C83" s="322" t="n">
+      <c r="C83" s="336" t="n">
         <v>1852</v>
       </c>
-      <c r="D83" s="322" t="n">
+      <c r="D83" s="336" t="n">
         <v>524.2</v>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="318" t="n">
+      <c r="B84" s="332" t="n">
         <v>27</v>
       </c>
-      <c r="C84" s="320" t="n">
+      <c r="C84" s="334" t="n">
         <v>1736.2</v>
       </c>
-      <c r="D84" s="320" t="n">
+      <c r="D84" s="334" t="n">
         <v>524.4</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="319" t="n">
+      <c r="B85" s="333" t="n">
         <v>29</v>
       </c>
-      <c r="C85" s="322" t="n">
+      <c r="C85" s="336" t="n">
         <v>1674.7</v>
       </c>
-      <c r="D85" s="322" t="n">
+      <c r="D85" s="336" t="n">
         <v>527.9</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="318" t="n">
+      <c r="B86" s="332" t="n">
         <v>32</v>
       </c>
-      <c r="C86" s="320" t="n">
+      <c r="C86" s="334" t="n">
         <v>1603.9</v>
       </c>
-      <c r="D86" s="320" t="n">
+      <c r="D86" s="334" t="n">
         <v>531.7</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="319" t="n">
+      <c r="B87" s="333" t="n">
         <v>34</v>
       </c>
-      <c r="C87" s="322" t="n">
+      <c r="C87" s="336" t="n">
         <v>1562.5</v>
       </c>
-      <c r="D87" s="322" t="n">
+      <c r="D87" s="336" t="n">
         <v>533.2</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="318" t="n">
+      <c r="B88" s="332" t="n">
         <v>36</v>
       </c>
-      <c r="C88" s="320" t="n">
+      <c r="C88" s="334" t="n">
         <v>1532.5</v>
       </c>
-      <c r="D88" s="320" t="n">
+      <c r="D88" s="334" t="n">
         <v>539.3</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="319" t="n">
+      <c r="B89" s="333" t="n">
         <v>39</v>
       </c>
-      <c r="C89" s="322" t="n">
+      <c r="C89" s="336" t="n">
         <v>1500.8</v>
       </c>
-      <c r="D89" s="322" t="n">
+      <c r="D89" s="336" t="n">
         <v>544.4</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="318" t="n">
+      <c r="B90" s="332" t="n">
         <v>43</v>
       </c>
-      <c r="C90" s="320" t="n">
+      <c r="C90" s="334" t="n">
         <v>1476.5</v>
       </c>
-      <c r="D90" s="320" t="n">
+      <c r="D90" s="334" t="n">
         <v>553</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="319" t="n">
+      <c r="B91" s="333" t="n">
         <v>48</v>
       </c>
-      <c r="C91" s="322" t="n">
+      <c r="C91" s="336" t="n">
         <v>1460.2</v>
       </c>
-      <c r="D91" s="322" t="n">
+      <c r="D91" s="336" t="n">
         <v>563.9</v>
       </c>
     </row>
@@ -11459,19 +11501,19 @@
           <t>Обслужено ДХ, шт</t>
         </is>
       </c>
-      <c r="D95" s="318" t="n">
-        <v>3087</v>
-      </c>
-      <c r="E95" s="318" t="n">
-        <v>3087</v>
-      </c>
-      <c r="F95" s="318" t="n">
-        <v>3087</v>
-      </c>
-      <c r="G95" s="318" t="n">
-        <v>3087</v>
-      </c>
-      <c r="H95" s="327" t="n"/>
+      <c r="D95" s="332" t="n">
+        <v>3089</v>
+      </c>
+      <c r="E95" s="332" t="n">
+        <v>3089</v>
+      </c>
+      <c r="F95" s="332" t="n">
+        <v>3089</v>
+      </c>
+      <c r="G95" s="332" t="n">
+        <v>3089</v>
+      </c>
+      <c r="H95" s="341" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="63">
       <c r="C96" s="114" t="inlineStr">
@@ -11479,19 +11521,19 @@
           <t>Волокно-км</t>
         </is>
       </c>
-      <c r="D96" s="322" t="n">
+      <c r="D96" s="336" t="n">
         <v>4375.1</v>
       </c>
-      <c r="E96" s="322" t="n">
+      <c r="E96" s="336" t="n">
         <v>1256.1</v>
       </c>
-      <c r="F96" s="322" t="n">
+      <c r="F96" s="336" t="n">
         <v>889.2</v>
       </c>
-      <c r="G96" s="322" t="n">
+      <c r="G96" s="336" t="n">
         <v>1498.3</v>
       </c>
-      <c r="H96" s="328">
+      <c r="H96" s="342">
         <f>CHOOSE(MATCH(MIN(D96:G96),D96:G96,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11502,23 +11544,23 @@
           <t>Волокно-км на ДХ, км</t>
         </is>
       </c>
-      <c r="D97" s="329">
-        <f>D96/3087</f>
-        <v/>
-      </c>
-      <c r="E97" s="329">
-        <f>E96/3087</f>
-        <v/>
-      </c>
-      <c r="F97" s="329">
-        <f>F96/3087</f>
-        <v/>
-      </c>
-      <c r="G97" s="329">
-        <f>G96/3087</f>
-        <v/>
-      </c>
-      <c r="H97" s="327">
+      <c r="D97" s="343">
+        <f>D96/3089</f>
+        <v/>
+      </c>
+      <c r="E97" s="343">
+        <f>E96/3089</f>
+        <v/>
+      </c>
+      <c r="F97" s="343">
+        <f>F96/3089</f>
+        <v/>
+      </c>
+      <c r="G97" s="343">
+        <f>G96/3089</f>
+        <v/>
+      </c>
+      <c r="H97" s="341">
         <f>CHOOSE(MATCH(MIN(D97:G97),D97:G97,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11529,19 +11571,19 @@
           <t>Магистральный кабель, км</t>
         </is>
       </c>
-      <c r="D98" s="322" t="n">
+      <c r="D98" s="336" t="n">
         <v>109.4</v>
       </c>
-      <c r="E98" s="322" t="n">
+      <c r="E98" s="336" t="n">
         <v>76.5</v>
       </c>
-      <c r="F98" s="322" t="n">
+      <c r="F98" s="336" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="G98" s="322" t="n">
+      <c r="G98" s="336" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="H98" s="328">
+      <c r="H98" s="342">
         <f>CHOOSE(MATCH(MIN(D98:G98),D98:G98,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11552,19 +11594,19 @@
           <t>в т.ч. 8-волоконный, км</t>
         </is>
       </c>
-      <c r="D99" s="320" t="n">
+      <c r="D99" s="334" t="n">
         <v>35.1</v>
       </c>
-      <c r="E99" s="320" t="n">
+      <c r="E99" s="334" t="n">
         <v>46.7</v>
       </c>
-      <c r="F99" s="320" t="n">
+      <c r="F99" s="334" t="n">
         <v>49.5</v>
       </c>
-      <c r="G99" s="320" t="n">
+      <c r="G99" s="334" t="n">
         <v>42.7</v>
       </c>
-      <c r="H99" s="327" t="n"/>
+      <c r="H99" s="341" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1" s="63">
       <c r="C100" s="114" t="inlineStr">
@@ -11572,19 +11614,19 @@
           <t>в т.ч. 96-волоконный, км</t>
         </is>
       </c>
-      <c r="D100" s="322" t="n">
+      <c r="D100" s="336" t="n">
         <v>33.8</v>
       </c>
-      <c r="E100" s="322" t="n">
+      <c r="E100" s="336" t="n">
         <v>1.5</v>
       </c>
-      <c r="F100" s="322" t="n">
+      <c r="F100" s="336" t="n">
         <v>0.9</v>
       </c>
-      <c r="G100" s="322" t="n">
+      <c r="G100" s="336" t="n">
         <v>0.7</v>
       </c>
-      <c r="H100" s="328" t="n"/>
+      <c r="H100" s="342" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="63">
       <c r="C101" s="112" t="inlineStr">
@@ -11592,19 +11634,19 @@
           <t>Дроп-кабель, км</t>
         </is>
       </c>
-      <c r="D101" s="320" t="n">
+      <c r="D101" s="334" t="n">
         <v>95.8</v>
       </c>
-      <c r="E101" s="320" t="n">
+      <c r="E101" s="334" t="n">
         <v>170.7</v>
       </c>
-      <c r="F101" s="320" t="n">
+      <c r="F101" s="334" t="n">
         <v>244</v>
       </c>
-      <c r="G101" s="320" t="n">
-        <v>126.8</v>
-      </c>
-      <c r="H101" s="327">
+      <c r="G101" s="334" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="H101" s="341">
         <f>CHOOSE(MATCH(MIN(D101:G101),D101:G101,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11615,23 +11657,23 @@
           <t>ВСЕГО кабель + дропы, км</t>
         </is>
       </c>
-      <c r="D102" s="322">
+      <c r="D102" s="336">
         <f>D98+D101</f>
         <v/>
       </c>
-      <c r="E102" s="322">
+      <c r="E102" s="336">
         <f>E98+E101</f>
         <v/>
       </c>
-      <c r="F102" s="322">
+      <c r="F102" s="336">
         <f>F98+F101</f>
         <v/>
       </c>
-      <c r="G102" s="322">
+      <c r="G102" s="336">
         <f>G98+G101</f>
         <v/>
       </c>
-      <c r="H102" s="328">
+      <c r="H102" s="342">
         <f>CHOOSE(MATCH(MIN(D102:G102),D102:G102,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11642,19 +11684,19 @@
           <t>Средний дроп, м</t>
         </is>
       </c>
-      <c r="D103" s="318" t="n">
+      <c r="D103" s="332" t="n">
         <v>29.4</v>
       </c>
-      <c r="E103" s="318" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="F103" s="318" t="n">
+      <c r="E103" s="332" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="F103" s="332" t="n">
         <v>75.2</v>
       </c>
-      <c r="G103" s="318" t="n">
+      <c r="G103" s="332" t="n">
         <v>39</v>
       </c>
-      <c r="H103" s="327">
+      <c r="H103" s="341">
         <f>CHOOSE(MATCH(MIN(D103:G103),D103:G103,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11665,19 +11707,19 @@
           <t>Максимальный дроп, м</t>
         </is>
       </c>
-      <c r="D104" s="319" t="n">
+      <c r="D104" s="333" t="n">
         <v>132.5</v>
       </c>
-      <c r="E104" s="319" t="n">
+      <c r="E104" s="333" t="n">
         <v>201</v>
       </c>
-      <c r="F104" s="319" t="n">
+      <c r="F104" s="333" t="n">
         <v>266</v>
       </c>
-      <c r="G104" s="319" t="n">
+      <c r="G104" s="333" t="n">
         <v>132.5</v>
       </c>
-      <c r="H104" s="328">
+      <c r="H104" s="342">
         <f>CHOOSE(MATCH(MIN(D104:G104),D104:G104,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11688,15 +11730,15 @@
           <t>Ср. маршрут волокна ДХ, м</t>
         </is>
       </c>
-      <c r="D105" s="318" t="n">
+      <c r="D105" s="332" t="n">
         <v>1361</v>
       </c>
-      <c r="E105" s="318" t="n"/>
-      <c r="F105" s="318" t="n"/>
-      <c r="G105" s="318" t="n">
+      <c r="E105" s="332" t="n"/>
+      <c r="F105" s="332" t="n"/>
+      <c r="G105" s="332" t="n">
         <v>278</v>
       </c>
-      <c r="H105" s="327">
+      <c r="H105" s="341">
         <f>CHOOSE(MATCH(MIN(D105:G105),D105:G105,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11707,19 +11749,19 @@
           <t>ОРШ, шт</t>
         </is>
       </c>
-      <c r="D106" s="319" t="n">
+      <c r="D106" s="333" t="n">
         <v>6</v>
       </c>
-      <c r="E106" s="319" t="n">
+      <c r="E106" s="333" t="n">
         <v>6</v>
       </c>
-      <c r="F106" s="319" t="n">
+      <c r="F106" s="333" t="n">
         <v>6</v>
       </c>
-      <c r="G106" s="319" t="n">
+      <c r="G106" s="333" t="n">
         <v>42</v>
       </c>
-      <c r="H106" s="328">
+      <c r="H106" s="342">
         <f>CHOOSE(MATCH(MIN(D106:G106),D106:G106,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11730,19 +11772,19 @@
           <t>РОР, шт</t>
         </is>
       </c>
-      <c r="D107" s="318" t="n">
+      <c r="D107" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="318" t="n">
+      <c r="E107" s="332" t="n">
         <v>515</v>
       </c>
-      <c r="F107" s="318" t="n">
+      <c r="F107" s="332" t="n">
         <v>323</v>
       </c>
-      <c r="G107" s="318" t="n">
+      <c r="G107" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="327" t="n"/>
+      <c r="H107" s="341" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="63">
       <c r="C108" s="114" t="inlineStr">
@@ -11750,19 +11792,19 @@
           <t>Сплиттеры 1:64, шт</t>
         </is>
       </c>
-      <c r="D108" s="319" t="n">
+      <c r="D108" s="333" t="n">
         <v>39</v>
       </c>
-      <c r="E108" s="319" t="n">
+      <c r="E108" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="319" t="n">
+      <c r="F108" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="319" t="n">
+      <c r="G108" s="333" t="n">
         <v>65</v>
       </c>
-      <c r="H108" s="328" t="n"/>
+      <c r="H108" s="342" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1" s="63">
       <c r="C109" s="112" t="inlineStr">
@@ -11770,19 +11812,19 @@
           <t>Сплиттеры 1:8, шт</t>
         </is>
       </c>
-      <c r="D109" s="318" t="n">
+      <c r="D109" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="318" t="n">
+      <c r="E109" s="332" t="n">
         <v>581</v>
       </c>
-      <c r="F109" s="318" t="n">
+      <c r="F109" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="318" t="n">
+      <c r="G109" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="327" t="n"/>
+      <c r="H109" s="341" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1" s="63">
       <c r="C110" s="114" t="inlineStr">
@@ -11790,19 +11832,19 @@
           <t>Сплиттеры 1:4, шт</t>
         </is>
       </c>
-      <c r="D110" s="319" t="n">
+      <c r="D110" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="319" t="n">
+      <c r="E110" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="319" t="n">
+      <c r="F110" s="333" t="n">
         <v>83</v>
       </c>
-      <c r="G110" s="319" t="n">
+      <c r="G110" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="328" t="n"/>
+      <c r="H110" s="342" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1" s="63">
       <c r="C111" s="112" t="inlineStr">
@@ -11810,19 +11852,19 @@
           <t>Сплиттеры 1:16, шт</t>
         </is>
       </c>
-      <c r="D111" s="318" t="n">
+      <c r="D111" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="318" t="n">
+      <c r="E111" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="318" t="n">
+      <c r="F111" s="332" t="n">
         <v>323</v>
       </c>
-      <c r="G111" s="318" t="n">
+      <c r="G111" s="332" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="327" t="n"/>
+      <c r="H111" s="341" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1" s="63">
       <c r="C112" s="114" t="inlineStr">
@@ -11830,19 +11872,19 @@
           <t>Муфты, шт</t>
         </is>
       </c>
-      <c r="D112" s="319" t="n">
+      <c r="D112" s="333" t="n">
         <v>1140</v>
       </c>
-      <c r="E112" s="319" t="n">
+      <c r="E112" s="333" t="n">
         <v>115</v>
       </c>
-      <c r="F112" s="319" t="n">
+      <c r="F112" s="333" t="n">
         <v>100</v>
       </c>
-      <c r="G112" s="319" t="n">
+      <c r="G112" s="333" t="n">
         <v>1103</v>
       </c>
-      <c r="H112" s="328">
+      <c r="H112" s="342">
         <f>CHOOSE(MATCH(MIN(D112:G112),D112:G112,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11853,19 +11895,19 @@
           <t>Сварки, шт</t>
         </is>
       </c>
-      <c r="D113" s="318" t="n">
+      <c r="D113" s="332" t="n">
         <v>5136</v>
       </c>
-      <c r="E113" s="318" t="n">
+      <c r="E113" s="332" t="n">
         <v>2585</v>
       </c>
-      <c r="F113" s="318" t="n">
+      <c r="F113" s="332" t="n">
         <v>1552</v>
       </c>
-      <c r="G113" s="318" t="n">
-        <v>6938</v>
-      </c>
-      <c r="H113" s="327">
+      <c r="G113" s="332" t="n">
+        <v>6942</v>
+      </c>
+      <c r="H113" s="341">
         <f>CHOOSE(MATCH(MIN(D113:G113),D113:G113,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11876,19 +11918,19 @@
           <t>Коннекторы FAST, шт</t>
         </is>
       </c>
-      <c r="D114" s="319" t="n">
+      <c r="D114" s="333" t="n">
         <v>2569</v>
       </c>
-      <c r="E114" s="319" t="n">
+      <c r="E114" s="333" t="n">
         <v>5136</v>
       </c>
-      <c r="F114" s="319" t="n">
+      <c r="F114" s="333" t="n">
         <v>5136</v>
       </c>
-      <c r="G114" s="319" t="n">
-        <v>3398</v>
-      </c>
-      <c r="H114" s="328">
+      <c r="G114" s="333" t="n">
+        <v>3400</v>
+      </c>
+      <c r="H114" s="342">
         <f>CHOOSE(MATCH(MIN(D114:G114),D114:G114,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11899,19 +11941,19 @@
           <t>Порты кросса ОРШ, шт</t>
         </is>
       </c>
-      <c r="D115" s="318" t="n">
+      <c r="D115" s="332" t="n">
         <v>3600</v>
       </c>
-      <c r="E115" s="318" t="n">
+      <c r="E115" s="332" t="n">
         <v>1008</v>
       </c>
-      <c r="F115" s="318" t="n">
+      <c r="F115" s="332" t="n">
         <v>864</v>
       </c>
-      <c r="G115" s="318" t="n">
+      <c r="G115" s="332" t="n">
         <v>5184</v>
       </c>
-      <c r="H115" s="327">
+      <c r="H115" s="341">
         <f>CHOOSE(MATCH(MIN(D115:G115),D115:G115,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11922,19 +11964,19 @@
           <t>Порты OLT, шт</t>
         </is>
       </c>
-      <c r="D116" s="319" t="n">
+      <c r="D116" s="333" t="n">
         <v>39</v>
       </c>
-      <c r="E116" s="319" t="n">
+      <c r="E116" s="333" t="n">
         <v>66</v>
       </c>
-      <c r="F116" s="319" t="n">
+      <c r="F116" s="333" t="n">
         <v>83</v>
       </c>
-      <c r="G116" s="319" t="n">
+      <c r="G116" s="333" t="n">
         <v>65</v>
       </c>
-      <c r="H116" s="328">
+      <c r="H116" s="342">
         <f>CHOOSE(MATCH(MIN(D116:G116),D116:G116,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11945,19 +11987,19 @@
           <t>Комплекты подвеса, шт</t>
         </is>
       </c>
-      <c r="D117" s="318" t="n">
+      <c r="D117" s="332" t="n">
         <v>2911</v>
       </c>
-      <c r="E117" s="318" t="n">
+      <c r="E117" s="332" t="n">
         <v>4180</v>
       </c>
-      <c r="F117" s="318" t="n">
+      <c r="F117" s="332" t="n">
         <v>6136</v>
       </c>
-      <c r="G117" s="318" t="n">
+      <c r="G117" s="332" t="n">
         <v>2472</v>
       </c>
-      <c r="H117" s="327">
+      <c r="H117" s="341">
         <f>CHOOSE(MATCH(MIN(D117:G117),D117:G117,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11968,19 +12010,19 @@
           <t>Доп. шкафы ОРШ (сверх 6), шт</t>
         </is>
       </c>
-      <c r="D118" s="319" t="n">
+      <c r="D118" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="319" t="n">
+      <c r="E118" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="319" t="n">
+      <c r="F118" s="333" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="319" t="n">
+      <c r="G118" s="333" t="n">
         <v>36</v>
       </c>
-      <c r="H118" s="328">
+      <c r="H118" s="342">
         <f>CHOOSE(MATCH(MIN(D118:G118),D118:G118,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -12044,16 +12086,16 @@
           <t>Кабельная продукция (магистраль)</t>
         </is>
       </c>
-      <c r="D123" s="320" t="n">
+      <c r="D123" s="334" t="n">
         <v>233</v>
       </c>
-      <c r="E123" s="320" t="n">
+      <c r="E123" s="334" t="n">
         <v>107</v>
       </c>
-      <c r="F123" s="320" t="n">
+      <c r="F123" s="334" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="G123" s="320" t="n">
+      <c r="G123" s="334" t="n">
         <v>133.1</v>
       </c>
     </row>
@@ -12063,17 +12105,17 @@
           <t>Дроп-кабели</t>
         </is>
       </c>
-      <c r="D124" s="322" t="n">
+      <c r="D124" s="336" t="n">
         <v>47.9</v>
       </c>
-      <c r="E124" s="322" t="n">
+      <c r="E124" s="336" t="n">
         <v>85.3</v>
       </c>
-      <c r="F124" s="322" t="n">
+      <c r="F124" s="336" t="n">
         <v>122</v>
       </c>
-      <c r="G124" s="322" t="n">
-        <v>63.4</v>
+      <c r="G124" s="336" t="n">
+        <v>63.5</v>
       </c>
     </row>
     <row r="125" ht="18" customHeight="1" s="63">
@@ -12082,16 +12124,16 @@
           <t>Оборудование и монтаж</t>
         </is>
       </c>
-      <c r="D125" s="320" t="n">
+      <c r="D125" s="334" t="n">
         <v>315</v>
       </c>
-      <c r="E125" s="320" t="n">
+      <c r="E125" s="334" t="n">
         <v>306.2</v>
       </c>
-      <c r="F125" s="320" t="n">
+      <c r="F125" s="334" t="n">
         <v>270.8</v>
       </c>
-      <c r="G125" s="320" t="n">
+      <c r="G125" s="334" t="n">
         <v>373</v>
       </c>
     </row>
@@ -12124,16 +12166,16 @@
           <t>Доп. шкафы ОРШ (сверх базовых 6, по 1,5 у.е.)</t>
         </is>
       </c>
-      <c r="D127" s="322" t="n">
+      <c r="D127" s="336" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="322" t="n">
+      <c r="E127" s="336" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="322" t="n">
+      <c r="F127" s="336" t="n">
         <v>0</v>
       </c>
-      <c r="G127" s="322" t="n">
+      <c r="G127" s="336" t="n">
         <v>54</v>
       </c>
     </row>
@@ -12166,19 +12208,19 @@
           <t>Δ к лучшей схеме</t>
         </is>
       </c>
-      <c r="D129" s="321">
+      <c r="D129" s="335">
         <f>D128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="E129" s="321">
+      <c r="E129" s="335">
         <f>E128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="F129" s="321">
+      <c r="F129" s="335">
         <f>F128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="G129" s="321">
+      <c r="G129" s="335">
         <f>G128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
@@ -12223,106 +12265,106 @@
       </c>
     </row>
     <row r="133" ht="18" customHeight="1" s="63">
-      <c r="C133" s="330" t="n">
+      <c r="C133" s="344" t="n">
         <v>0</v>
       </c>
-      <c r="D133" s="318" t="n">
+      <c r="D133" s="332" t="n">
         <v>520.2</v>
       </c>
-      <c r="E133" s="318" t="n">
+      <c r="E133" s="332" t="n">
         <v>553.4</v>
       </c>
-      <c r="F133" s="318" t="n">
+      <c r="F133" s="332" t="n">
         <v>585.9</v>
       </c>
-      <c r="G133" s="318" t="n">
-        <v>646.9</v>
-      </c>
-      <c r="H133" s="327">
+      <c r="G133" s="332" t="n">
+        <v>647</v>
+      </c>
+      <c r="H133" s="341">
         <f>CHOOSE(MATCH(MIN(D133:G133),D133:G133,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1" s="63">
-      <c r="C134" s="331" t="n">
+      <c r="C134" s="345" t="n">
         <v>0.3</v>
       </c>
-      <c r="D134" s="319" t="n">
+      <c r="D134" s="333" t="n">
         <v>545.2</v>
       </c>
-      <c r="E134" s="319" t="n">
+      <c r="E134" s="333" t="n">
         <v>510.5</v>
       </c>
-      <c r="F134" s="319" t="n">
+      <c r="F134" s="333" t="n">
         <v>511.9</v>
       </c>
-      <c r="G134" s="319" t="n">
-        <v>624.2</v>
-      </c>
-      <c r="H134" s="328">
+      <c r="G134" s="333" t="n">
+        <v>624.3</v>
+      </c>
+      <c r="H134" s="342">
         <f>CHOOSE(MATCH(MIN(D134:G134),D134:G134,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1" s="63">
-      <c r="C135" s="330" t="n">
+      <c r="C135" s="344" t="n">
         <v>0.5</v>
       </c>
-      <c r="D135" s="318" t="n">
+      <c r="D135" s="332" t="n">
         <v>595.9</v>
       </c>
-      <c r="E135" s="318" t="n">
+      <c r="E135" s="332" t="n">
         <v>498.6</v>
       </c>
-      <c r="F135" s="318" t="n">
+      <c r="F135" s="332" t="n">
         <v>481.6</v>
       </c>
-      <c r="G135" s="318" t="n">
-        <v>623.4</v>
-      </c>
-      <c r="H135" s="327">
+      <c r="G135" s="332" t="n">
+        <v>623.5</v>
+      </c>
+      <c r="H135" s="341">
         <f>CHOOSE(MATCH(MIN(D135:G135),D135:G135,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1" s="63">
-      <c r="C136" s="331" t="n">
+      <c r="C136" s="345" t="n">
         <v>0.7</v>
       </c>
-      <c r="D136" s="319" t="n">
+      <c r="D136" s="333" t="n">
         <v>688</v>
       </c>
-      <c r="E136" s="319" t="n">
+      <c r="E136" s="333" t="n">
         <v>500.1</v>
       </c>
-      <c r="F136" s="319" t="n">
+      <c r="F136" s="333" t="n">
         <v>464</v>
       </c>
-      <c r="G136" s="319" t="n">
-        <v>634.4</v>
-      </c>
-      <c r="H136" s="328">
+      <c r="G136" s="333" t="n">
+        <v>634.5</v>
+      </c>
+      <c r="H136" s="342">
         <f>CHOOSE(MATCH(MIN(D136:G136),D136:G136,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1" s="63">
-      <c r="C137" s="330" t="n">
+      <c r="C137" s="344" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="318" t="n">
+      <c r="D137" s="332" t="n">
         <v>955</v>
       </c>
-      <c r="E137" s="318" t="n">
+      <c r="E137" s="332" t="n">
         <v>531.4</v>
       </c>
-      <c r="F137" s="318" t="n">
+      <c r="F137" s="332" t="n">
         <v>459.4</v>
       </c>
-      <c r="G137" s="318" t="n">
+      <c r="G137" s="332" t="n">
         <v>676.8</v>
       </c>
-      <c r="H137" s="327">
+      <c r="H137" s="341">
         <f>CHOOSE(MATCH(MIN(D137:G137),D137:G137,0),"A","B","C","D")</f>
         <v/>
       </c>

--- a/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
+++ b/download/Сводная_таблица_материалов_FTTH_ВКО_каскад.xlsx
@@ -255,7 +255,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="346">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -698,6 +698,48 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="15" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -4718,7 +4760,7 @@
       <c r="L5" s="108" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1" s="63">
-      <c r="B6" s="341" t="n">
+      <c r="B6" s="355" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -4726,7 +4768,7 @@
           <t>Шкаф оптический распределительный (ОРШ) центральный — в здании ЦУ</t>
         </is>
       </c>
-      <c r="D6" s="341" t="inlineStr">
+      <c r="D6" s="355" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4736,22 +4778,22 @@
           <t>1 на СНП (здание по проекту)</t>
         </is>
       </c>
-      <c r="F6" s="332" t="n">
+      <c r="F6" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="332" t="n">
+      <c r="G6" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="332" t="n">
+      <c r="H6" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="332" t="n">
+      <c r="I6" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="332" t="n">
+      <c r="J6" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="K6" s="332" t="n">
+      <c r="K6" s="346" t="n">
         <v>1</v>
       </c>
       <c r="L6" s="146">
@@ -4760,7 +4802,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" s="63">
-      <c r="B7" s="342" t="n">
+      <c r="B7" s="356" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="114" t="inlineStr">
@@ -4768,7 +4810,7 @@
           <t>Шкаф зонный ОРШ уличный (под сплиттеры 1:64)</t>
         </is>
       </c>
-      <c r="D7" s="342" t="inlineStr">
+      <c r="D7" s="356" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4778,20 +4820,20 @@
           <t>1 на зону — в центре сектора (медиана зоны, зона ≥ 48 ДХ)</t>
         </is>
       </c>
-      <c r="F7" s="333" t="n">
+      <c r="F7" s="347" t="n">
         <v>14</v>
       </c>
-      <c r="G7" s="333" t="n"/>
-      <c r="H7" s="333" t="n">
+      <c r="G7" s="347" t="n"/>
+      <c r="H7" s="347" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="333" t="n">
+      <c r="I7" s="347" t="n">
         <v>9</v>
       </c>
-      <c r="J7" s="333" t="n">
+      <c r="J7" s="347" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="333" t="n">
+      <c r="K7" s="347" t="n">
         <v>6</v>
       </c>
       <c r="L7" s="147">
@@ -4800,7 +4842,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="63">
-      <c r="B8" s="341" t="n">
+      <c r="B8" s="355" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -4808,7 +4850,7 @@
           <t>Сплиттер PLC 1×64 (в ОРШ: ЦУ и зонных)</t>
         </is>
       </c>
-      <c r="D8" s="341" t="inlineStr">
+      <c r="D8" s="355" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4818,22 +4860,22 @@
           <t>ceil(ДХ зоны / 64), заполнение 75-100%</t>
         </is>
       </c>
-      <c r="F8" s="332" t="n">
+      <c r="F8" s="346" t="n">
         <v>22</v>
       </c>
-      <c r="G8" s="332" t="n">
+      <c r="G8" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="H8" s="332" t="n">
+      <c r="H8" s="346" t="n">
         <v>8</v>
       </c>
-      <c r="I8" s="332" t="n">
+      <c r="I8" s="346" t="n">
         <v>14</v>
       </c>
-      <c r="J8" s="332" t="n">
+      <c r="J8" s="346" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="332" t="n">
+      <c r="K8" s="346" t="n">
         <v>13</v>
       </c>
       <c r="L8" s="146">
@@ -4842,7 +4884,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" s="63">
-      <c r="B9" s="342" t="n">
+      <c r="B9" s="356" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="114" t="inlineStr">
@@ -4850,7 +4892,7 @@
           <t>Пигтейль SC/UPC для кросса ОРШ</t>
         </is>
       </c>
-      <c r="D9" s="342" t="inlineStr">
+      <c r="D9" s="356" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4860,23 +4902,23 @@
           <t>ДХ + 2 × сплиттеры 1:64</t>
         </is>
       </c>
-      <c r="F9" s="333" t="n">
+      <c r="F9" s="347" t="n">
         <v>1073</v>
       </c>
-      <c r="G9" s="333" t="n">
+      <c r="G9" s="347" t="n">
         <v>128</v>
       </c>
-      <c r="H9" s="333" t="n">
+      <c r="H9" s="347" t="n">
         <v>392</v>
       </c>
-      <c r="I9" s="333" t="n">
+      <c r="I9" s="347" t="n">
         <v>650</v>
       </c>
-      <c r="J9" s="333" t="n">
-        <v>300</v>
-      </c>
-      <c r="K9" s="333" t="n">
-        <v>676</v>
+      <c r="J9" s="347" t="n">
+        <v>298</v>
+      </c>
+      <c r="K9" s="347" t="n">
+        <v>678</v>
       </c>
       <c r="L9" s="147">
         <f>SUM(F9:K9)</f>
@@ -4884,7 +4926,7 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" s="63">
-      <c r="B10" s="341" t="n">
+      <c r="B10" s="355" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="112" t="inlineStr">
@@ -4892,7 +4934,7 @@
           <t>Порт PON OLT — справочно (активное оборудование, единый узел OLT)</t>
         </is>
       </c>
-      <c r="D10" s="341" t="inlineStr">
+      <c r="D10" s="355" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -4902,22 +4944,22 @@
           <t>по числу сплиттеров 1:64</t>
         </is>
       </c>
-      <c r="F10" s="332" t="n">
+      <c r="F10" s="346" t="n">
         <v>22</v>
       </c>
-      <c r="G10" s="332" t="n">
+      <c r="G10" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="332" t="n">
+      <c r="H10" s="346" t="n">
         <v>8</v>
       </c>
-      <c r="I10" s="332" t="n">
+      <c r="I10" s="346" t="n">
         <v>14</v>
       </c>
-      <c r="J10" s="332" t="n">
+      <c r="J10" s="346" t="n">
         <v>6</v>
       </c>
-      <c r="K10" s="332" t="n">
+      <c r="K10" s="346" t="n">
         <v>13</v>
       </c>
       <c r="L10" s="146">
@@ -4943,7 +4985,7 @@
       <c r="L11" s="108" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="63">
-      <c r="B12" s="341" t="n">
+      <c r="B12" s="355" t="n">
         <v>6</v>
       </c>
       <c r="C12" s="112" t="inlineStr">
@@ -4951,7 +4993,7 @@
           <t>Кабель оптический самонесущий, 8 волокон</t>
         </is>
       </c>
-      <c r="D12" s="341" t="inlineStr">
+      <c r="D12" s="355" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -4961,22 +5003,22 @@
           <t>распределение зоны max(8; 1,25 × ДХ потока) + фидер ceil(1,25 × сплиттеры зоны)</t>
         </is>
       </c>
-      <c r="F12" s="334" t="n">
+      <c r="F12" s="348" t="n">
         <v>16.7</v>
       </c>
-      <c r="G12" s="334" t="n">
+      <c r="G12" s="348" t="n">
         <v>2.6</v>
       </c>
-      <c r="H12" s="334" t="n">
+      <c r="H12" s="348" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="334" t="n">
+      <c r="I12" s="348" t="n">
         <v>9.9</v>
       </c>
-      <c r="J12" s="334" t="n">
+      <c r="J12" s="348" t="n">
         <v>4.5</v>
       </c>
-      <c r="K12" s="334" t="n">
+      <c r="K12" s="348" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="148">
@@ -4985,7 +5027,7 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" s="63">
-      <c r="B13" s="342" t="n">
+      <c r="B13" s="356" t="n">
         <v>7</v>
       </c>
       <c r="C13" s="114" t="inlineStr">
@@ -4993,7 +5035,7 @@
           <t>Кабель оптический самонесущий, 12 волокон</t>
         </is>
       </c>
-      <c r="D13" s="342" t="inlineStr">
+      <c r="D13" s="356" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5003,22 +5045,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F13" s="336" t="n">
+      <c r="F13" s="350" t="n">
         <v>4.4</v>
       </c>
-      <c r="G13" s="336" t="n">
+      <c r="G13" s="350" t="n">
         <v>0.6</v>
       </c>
-      <c r="H13" s="336" t="n">
+      <c r="H13" s="350" t="n">
         <v>1.5</v>
       </c>
-      <c r="I13" s="336" t="n">
+      <c r="I13" s="350" t="n">
         <v>3.5</v>
       </c>
-      <c r="J13" s="336" t="n">
+      <c r="J13" s="350" t="n">
         <v>0.7</v>
       </c>
-      <c r="K13" s="336" t="n">
+      <c r="K13" s="350" t="n">
         <v>0.9</v>
       </c>
       <c r="L13" s="149">
@@ -5027,7 +5069,7 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" s="63">
-      <c r="B14" s="341" t="n">
+      <c r="B14" s="355" t="n">
         <v>8</v>
       </c>
       <c r="C14" s="112" t="inlineStr">
@@ -5035,7 +5077,7 @@
           <t>Кабель оптический самонесущий, 16 волокон</t>
         </is>
       </c>
-      <c r="D14" s="341" t="inlineStr">
+      <c r="D14" s="355" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5045,23 +5087,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F14" s="334" t="n">
+      <c r="F14" s="348" t="n">
         <v>1.8</v>
       </c>
-      <c r="G14" s="334" t="n">
+      <c r="G14" s="348" t="n">
         <v>0.5</v>
       </c>
-      <c r="H14" s="334" t="n">
+      <c r="H14" s="348" t="n">
         <v>0.5</v>
       </c>
-      <c r="I14" s="334" t="n">
+      <c r="I14" s="348" t="n">
         <v>1.6</v>
       </c>
-      <c r="J14" s="334" t="n">
+      <c r="J14" s="348" t="n">
         <v>1.3</v>
       </c>
-      <c r="K14" s="334" t="n">
-        <v>1.1</v>
+      <c r="K14" s="348" t="n">
+        <v>0.9</v>
       </c>
       <c r="L14" s="148">
         <f>SUM(F14:K14)</f>
@@ -5069,7 +5111,7 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" s="63">
-      <c r="B15" s="342" t="n">
+      <c r="B15" s="356" t="n">
         <v>9</v>
       </c>
       <c r="C15" s="114" t="inlineStr">
@@ -5077,7 +5119,7 @@
           <t>Кабель оптический самонесущий, 24 волокна</t>
         </is>
       </c>
-      <c r="D15" s="342" t="inlineStr">
+      <c r="D15" s="356" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5087,23 +5129,23 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F15" s="336" t="n">
+      <c r="F15" s="350" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="336" t="n">
+      <c r="G15" s="350" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="336" t="n">
+      <c r="H15" s="350" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="336" t="n">
+      <c r="I15" s="350" t="n">
         <v>3.1</v>
       </c>
-      <c r="J15" s="336" t="n">
+      <c r="J15" s="350" t="n">
         <v>1.4</v>
       </c>
-      <c r="K15" s="336" t="n">
-        <v>1.4</v>
+      <c r="K15" s="350" t="n">
+        <v>1.6</v>
       </c>
       <c r="L15" s="149">
         <f>SUM(F15:K15)</f>
@@ -5111,7 +5153,7 @@
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" s="63">
-      <c r="B16" s="341" t="n">
+      <c r="B16" s="355" t="n">
         <v>10</v>
       </c>
       <c r="C16" s="112" t="inlineStr">
@@ -5119,7 +5161,7 @@
           <t>Кабель оптический самонесущий, 32 волокна</t>
         </is>
       </c>
-      <c r="D16" s="341" t="inlineStr">
+      <c r="D16" s="355" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5129,22 +5171,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F16" s="334" t="n">
+      <c r="F16" s="348" t="n">
         <v>2.2</v>
       </c>
-      <c r="G16" s="334" t="n">
+      <c r="G16" s="348" t="n">
         <v>0.4</v>
       </c>
-      <c r="H16" s="334" t="n">
+      <c r="H16" s="348" t="n">
         <v>1.1</v>
       </c>
-      <c r="I16" s="334" t="n">
+      <c r="I16" s="348" t="n">
         <v>1.8</v>
       </c>
-      <c r="J16" s="334" t="n">
+      <c r="J16" s="348" t="n">
         <v>0.8</v>
       </c>
-      <c r="K16" s="334" t="n">
+      <c r="K16" s="348" t="n">
         <v>0.9</v>
       </c>
       <c r="L16" s="148">
@@ -5153,7 +5195,7 @@
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" s="63">
-      <c r="B17" s="342" t="n">
+      <c r="B17" s="356" t="n">
         <v>11</v>
       </c>
       <c r="C17" s="114" t="inlineStr">
@@ -5161,7 +5203,7 @@
           <t>Кабель оптический самонесущий, 48 волокон</t>
         </is>
       </c>
-      <c r="D17" s="342" t="inlineStr">
+      <c r="D17" s="356" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5171,22 +5213,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F17" s="336" t="n">
+      <c r="F17" s="350" t="n">
         <v>1.7</v>
       </c>
-      <c r="G17" s="336" t="n">
+      <c r="G17" s="350" t="n">
         <v>0.2</v>
       </c>
-      <c r="H17" s="336" t="n">
+      <c r="H17" s="350" t="n">
         <v>1.1</v>
       </c>
-      <c r="I17" s="336" t="n">
+      <c r="I17" s="350" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" s="336" t="n">
+      <c r="J17" s="350" t="n">
         <v>0.4</v>
       </c>
-      <c r="K17" s="336" t="n">
+      <c r="K17" s="350" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="149">
@@ -5195,7 +5237,7 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" s="63">
-      <c r="B18" s="341" t="n">
+      <c r="B18" s="355" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="112" t="inlineStr">
@@ -5203,7 +5245,7 @@
           <t>Кабель оптический самонесущий, 64 волокна</t>
         </is>
       </c>
-      <c r="D18" s="341" t="inlineStr">
+      <c r="D18" s="355" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5213,22 +5255,22 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F18" s="334" t="n">
+      <c r="F18" s="348" t="n">
         <v>0.7</v>
       </c>
-      <c r="G18" s="334" t="n">
+      <c r="G18" s="348" t="n">
         <v>0.3</v>
       </c>
-      <c r="H18" s="334" t="n">
+      <c r="H18" s="348" t="n">
         <v>0.5</v>
       </c>
-      <c r="I18" s="334" t="n">
+      <c r="I18" s="348" t="n">
         <v>0.4</v>
       </c>
-      <c r="J18" s="334" t="n">
+      <c r="J18" s="348" t="n">
         <v>0.3</v>
       </c>
-      <c r="K18" s="334" t="n">
+      <c r="K18" s="348" t="n">
         <v>0.4</v>
       </c>
       <c r="L18" s="148">
@@ -5237,7 +5279,7 @@
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="63">
-      <c r="B19" s="342" t="n">
+      <c r="B19" s="356" t="n">
         <v>13</v>
       </c>
       <c r="C19" s="114" t="inlineStr">
@@ -5245,7 +5287,7 @@
           <t>Кабель оптический самонесущий, 72 волокна</t>
         </is>
       </c>
-      <c r="D19" s="342" t="inlineStr">
+      <c r="D19" s="356" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5255,14 +5297,14 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F19" s="336" t="n">
+      <c r="F19" s="350" t="n">
         <v>0.4</v>
       </c>
-      <c r="G19" s="336" t="n"/>
-      <c r="H19" s="336" t="n"/>
-      <c r="I19" s="336" t="n"/>
-      <c r="J19" s="336" t="n"/>
-      <c r="K19" s="336" t="n">
+      <c r="G19" s="350" t="n"/>
+      <c r="H19" s="350" t="n"/>
+      <c r="I19" s="350" t="n"/>
+      <c r="J19" s="350" t="n"/>
+      <c r="K19" s="350" t="n">
         <v>0.3</v>
       </c>
       <c r="L19" s="149">
@@ -5271,7 +5313,7 @@
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" s="63">
-      <c r="B20" s="341" t="n">
+      <c r="B20" s="355" t="n">
         <v>14</v>
       </c>
       <c r="C20" s="112" t="inlineStr">
@@ -5279,7 +5321,7 @@
           <t>Кабель оптический самонесущий, 96 волокон</t>
         </is>
       </c>
-      <c r="D20" s="341" t="inlineStr">
+      <c r="D20" s="355" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5289,20 +5331,20 @@
           <t>то же</t>
         </is>
       </c>
-      <c r="F20" s="334" t="n">
+      <c r="F20" s="348" t="n">
         <v>0.1</v>
       </c>
-      <c r="G20" s="334" t="n">
+      <c r="G20" s="348" t="n">
         <v>0.1</v>
       </c>
-      <c r="H20" s="334" t="n">
+      <c r="H20" s="348" t="n">
         <v>0.2</v>
       </c>
-      <c r="I20" s="334" t="n"/>
-      <c r="J20" s="334" t="n">
+      <c r="I20" s="348" t="n"/>
+      <c r="J20" s="348" t="n">
         <v>0.1</v>
       </c>
-      <c r="K20" s="334" t="n">
+      <c r="K20" s="348" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="148">
@@ -5311,7 +5353,7 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" s="63">
-      <c r="B21" s="342" t="n">
+      <c r="B21" s="356" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="114" t="inlineStr">
@@ -5319,7 +5361,7 @@
           <t>Кабель дроп-кабельный самонесущий, 2 волокна (1 раб. + 1 рез.)</t>
         </is>
       </c>
-      <c r="D21" s="342" t="inlineStr">
+      <c r="D21" s="356" t="inlineStr">
         <is>
           <t>км</t>
         </is>
@@ -5329,23 +5371,23 @@
           <t>дропы × 1,05 (без подводок — дроп от муфты напрямую)</t>
         </is>
       </c>
-      <c r="F21" s="336" t="n">
+      <c r="F21" s="350" t="n">
         <v>41.7</v>
       </c>
-      <c r="G21" s="336" t="n">
+      <c r="G21" s="350" t="n">
         <v>5.2</v>
       </c>
-      <c r="H21" s="336" t="n">
+      <c r="H21" s="350" t="n">
         <v>15.8</v>
       </c>
-      <c r="I21" s="336" t="n">
+      <c r="I21" s="350" t="n">
         <v>27.2</v>
       </c>
-      <c r="J21" s="336" t="n">
-        <v>13</v>
-      </c>
-      <c r="K21" s="336" t="n">
-        <v>24</v>
+      <c r="J21" s="350" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="K21" s="350" t="n">
+        <v>24.1</v>
       </c>
       <c r="L21" s="149">
         <f>SUM(F21:K21)</f>
@@ -5353,7 +5395,7 @@
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" s="63">
-      <c r="B22" s="341" t="n">
+      <c r="B22" s="355" t="n">
         <v>16</v>
       </c>
       <c r="C22" s="112" t="inlineStr">
@@ -5361,7 +5403,7 @@
           <t>Справочно: суммарная ёмкость магистрального кабеля</t>
         </is>
       </c>
-      <c r="D22" s="341" t="inlineStr">
+      <c r="D22" s="355" t="inlineStr">
         <is>
           <t>волокно-км</t>
         </is>
@@ -5371,23 +5413,23 @@
           <t>Σ (длина участка × волокна)</t>
         </is>
       </c>
-      <c r="F22" s="334" t="n">
+      <c r="F22" s="348" t="n">
         <v>524.8</v>
       </c>
-      <c r="G22" s="334" t="n">
+      <c r="G22" s="348" t="n">
         <v>90</v>
       </c>
-      <c r="H22" s="334" t="n">
+      <c r="H22" s="348" t="n">
         <v>218.5</v>
       </c>
-      <c r="I22" s="334" t="n">
+      <c r="I22" s="348" t="n">
         <v>329.9</v>
       </c>
-      <c r="J22" s="334" t="n">
+      <c r="J22" s="348" t="n">
         <v>141.2</v>
       </c>
-      <c r="K22" s="334" t="n">
-        <v>193.9</v>
+      <c r="K22" s="348" t="n">
+        <v>194.8</v>
       </c>
       <c r="L22" s="148">
         <f>SUM(F22:K22)</f>
@@ -5412,7 +5454,7 @@
       <c r="L23" s="108" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1" s="63">
-      <c r="B24" s="341" t="n">
+      <c r="B24" s="355" t="n">
         <v>17</v>
       </c>
       <c r="C24" s="112" t="inlineStr">
@@ -5420,7 +5462,7 @@
           <t>Муфта оптическая (ветвления магистрали)</t>
         </is>
       </c>
-      <c r="D24" s="341" t="inlineStr">
+      <c r="D24" s="355" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5430,22 +5472,22 @@
           <t>узлы ветвления кроме точек врезов зонных ОРШ; транзит — неразрезным кабелем</t>
         </is>
       </c>
-      <c r="F24" s="332" t="n">
+      <c r="F24" s="346" t="n">
         <v>367</v>
       </c>
-      <c r="G24" s="332" t="n">
+      <c r="G24" s="346" t="n">
         <v>70</v>
       </c>
-      <c r="H24" s="332" t="n">
+      <c r="H24" s="346" t="n">
         <v>158</v>
       </c>
-      <c r="I24" s="332" t="n">
+      <c r="I24" s="346" t="n">
         <v>246</v>
       </c>
-      <c r="J24" s="332" t="n">
+      <c r="J24" s="346" t="n">
         <v>119</v>
       </c>
-      <c r="K24" s="332" t="n">
+      <c r="K24" s="346" t="n">
         <v>143</v>
       </c>
       <c r="L24" s="146">
@@ -5471,7 +5513,7 @@
       <c r="L25" s="108" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="63">
-      <c r="B26" s="341" t="n">
+      <c r="B26" s="355" t="n">
         <v>18</v>
       </c>
       <c r="C26" s="112" t="inlineStr">
@@ -5479,7 +5521,7 @@
           <t>Бокс абонентский оптический с адаптером SC/UPC</t>
         </is>
       </c>
-      <c r="D26" s="341" t="inlineStr">
+      <c r="D26" s="355" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5489,23 +5531,23 @@
           <t>1 на ДХ</t>
         </is>
       </c>
-      <c r="F26" s="332" t="n">
+      <c r="F26" s="346" t="n">
         <v>1029</v>
       </c>
-      <c r="G26" s="332" t="n">
+      <c r="G26" s="346" t="n">
         <v>124</v>
       </c>
-      <c r="H26" s="332" t="n">
+      <c r="H26" s="346" t="n">
         <v>376</v>
       </c>
-      <c r="I26" s="332" t="n">
+      <c r="I26" s="346" t="n">
         <v>622</v>
       </c>
-      <c r="J26" s="332" t="n">
-        <v>288</v>
-      </c>
-      <c r="K26" s="332" t="n">
-        <v>650</v>
+      <c r="J26" s="346" t="n">
+        <v>286</v>
+      </c>
+      <c r="K26" s="346" t="n">
+        <v>652</v>
       </c>
       <c r="L26" s="146">
         <f>SUM(F26:K26)</f>
@@ -5513,7 +5555,7 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" s="63">
-      <c r="B27" s="342" t="n">
+      <c r="B27" s="356" t="n">
         <v>19</v>
       </c>
       <c r="C27" s="114" t="inlineStr">
@@ -5521,7 +5563,7 @@
           <t>Коннектор оптический механический SC/UPC</t>
         </is>
       </c>
-      <c r="D27" s="342" t="inlineStr">
+      <c r="D27" s="356" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5531,23 +5573,23 @@
           <t>ДХ × 1,1 (абонентский бокс)</t>
         </is>
       </c>
-      <c r="F27" s="333" t="n">
+      <c r="F27" s="347" t="n">
         <v>1132</v>
       </c>
-      <c r="G27" s="333" t="n">
+      <c r="G27" s="347" t="n">
         <v>137</v>
       </c>
-      <c r="H27" s="333" t="n">
+      <c r="H27" s="347" t="n">
         <v>414</v>
       </c>
-      <c r="I27" s="333" t="n">
+      <c r="I27" s="347" t="n">
         <v>685</v>
       </c>
-      <c r="J27" s="333" t="n">
-        <v>317</v>
-      </c>
-      <c r="K27" s="333" t="n">
-        <v>715</v>
+      <c r="J27" s="347" t="n">
+        <v>315</v>
+      </c>
+      <c r="K27" s="347" t="n">
+        <v>718</v>
       </c>
       <c r="L27" s="147">
         <f>SUM(F27:K27)</f>
@@ -5555,7 +5597,7 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="63">
-      <c r="B28" s="341" t="n">
+      <c r="B28" s="355" t="n">
         <v>20</v>
       </c>
       <c r="C28" s="112" t="inlineStr">
@@ -5563,7 +5605,7 @@
           <t>Сварное соединение (оценка объёма работ)</t>
         </is>
       </c>
-      <c r="D28" s="341" t="inlineStr">
+      <c r="D28" s="355" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5573,23 +5615,23 @@
           <t>(2 × ДХ + 2 × сплиттеры 1:64) × 1,1</t>
         </is>
       </c>
-      <c r="F28" s="332" t="n">
+      <c r="F28" s="346" t="n">
         <v>2313</v>
       </c>
-      <c r="G28" s="332" t="n">
+      <c r="G28" s="346" t="n">
         <v>278</v>
       </c>
-      <c r="H28" s="332" t="n">
+      <c r="H28" s="346" t="n">
         <v>845</v>
       </c>
-      <c r="I28" s="332" t="n">
+      <c r="I28" s="346" t="n">
         <v>1400</v>
       </c>
-      <c r="J28" s="332" t="n">
-        <v>647</v>
-      </c>
-      <c r="K28" s="332" t="n">
-        <v>1459</v>
+      <c r="J28" s="346" t="n">
+        <v>643</v>
+      </c>
+      <c r="K28" s="346" t="n">
+        <v>1463</v>
       </c>
       <c r="L28" s="146">
         <f>SUM(F28:K28)</f>
@@ -5597,7 +5639,7 @@
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" s="63">
-      <c r="B29" s="342" t="n">
+      <c r="B29" s="356" t="n">
         <v>21</v>
       </c>
       <c r="C29" s="114" t="inlineStr">
@@ -5605,7 +5647,7 @@
           <t>Гильза КДЗС, 60 мм</t>
         </is>
       </c>
-      <c r="D29" s="342" t="inlineStr">
+      <c r="D29" s="356" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5615,23 +5657,23 @@
           <t>по числу сварных соединений</t>
         </is>
       </c>
-      <c r="F29" s="333" t="n">
+      <c r="F29" s="347" t="n">
         <v>2313</v>
       </c>
-      <c r="G29" s="333" t="n">
+      <c r="G29" s="347" t="n">
         <v>278</v>
       </c>
-      <c r="H29" s="333" t="n">
+      <c r="H29" s="347" t="n">
         <v>845</v>
       </c>
-      <c r="I29" s="333" t="n">
+      <c r="I29" s="347" t="n">
         <v>1400</v>
       </c>
-      <c r="J29" s="333" t="n">
-        <v>647</v>
-      </c>
-      <c r="K29" s="333" t="n">
-        <v>1459</v>
+      <c r="J29" s="347" t="n">
+        <v>643</v>
+      </c>
+      <c r="K29" s="347" t="n">
+        <v>1463</v>
       </c>
       <c r="L29" s="147">
         <f>SUM(F29:K29)</f>
@@ -5639,7 +5681,7 @@
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" s="63">
-      <c r="B30" s="341" t="n">
+      <c r="B30" s="355" t="n">
         <v>22</v>
       </c>
       <c r="C30" s="112" t="inlineStr">
@@ -5647,7 +5689,7 @@
           <t>Комплект подвеса магистрального кабеля (кронштейн + спиральный зажим)</t>
         </is>
       </c>
-      <c r="D30" s="341" t="inlineStr">
+      <c r="D30" s="355" t="inlineStr">
         <is>
           <t>компл</t>
         </is>
@@ -5657,22 +5699,22 @@
           <t>30 на 1 км кабеля</t>
         </is>
       </c>
-      <c r="F30" s="332" t="n">
+      <c r="F30" s="346" t="n">
         <v>918</v>
       </c>
-      <c r="G30" s="332" t="n">
+      <c r="G30" s="346" t="n">
         <v>144</v>
       </c>
-      <c r="H30" s="332" t="n">
+      <c r="H30" s="346" t="n">
         <v>316</v>
       </c>
-      <c r="I30" s="332" t="n">
+      <c r="I30" s="346" t="n">
         <v>584</v>
       </c>
-      <c r="J30" s="332" t="n">
+      <c r="J30" s="346" t="n">
         <v>247</v>
       </c>
-      <c r="K30" s="332" t="n">
+      <c r="K30" s="346" t="n">
         <v>263</v>
       </c>
       <c r="L30" s="146">
@@ -5681,7 +5723,7 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" s="63">
-      <c r="B31" s="342" t="n">
+      <c r="B31" s="356" t="n">
         <v>23</v>
       </c>
       <c r="C31" s="114" t="inlineStr">
@@ -5689,7 +5731,7 @@
           <t>Анкерный зажим дроп-кабеля</t>
         </is>
       </c>
-      <c r="D31" s="342" t="inlineStr">
+      <c r="D31" s="356" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5699,23 +5741,23 @@
           <t>2 на ДХ</t>
         </is>
       </c>
-      <c r="F31" s="333" t="n">
+      <c r="F31" s="347" t="n">
         <v>2058</v>
       </c>
-      <c r="G31" s="333" t="n">
+      <c r="G31" s="347" t="n">
         <v>248</v>
       </c>
-      <c r="H31" s="333" t="n">
+      <c r="H31" s="347" t="n">
         <v>752</v>
       </c>
-      <c r="I31" s="333" t="n">
+      <c r="I31" s="347" t="n">
         <v>1244</v>
       </c>
-      <c r="J31" s="333" t="n">
-        <v>576</v>
-      </c>
-      <c r="K31" s="333" t="n">
-        <v>1300</v>
+      <c r="J31" s="347" t="n">
+        <v>572</v>
+      </c>
+      <c r="K31" s="347" t="n">
+        <v>1304</v>
       </c>
       <c r="L31" s="147">
         <f>SUM(F31:K31)</f>
@@ -5723,7 +5765,7 @@
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" s="63">
-      <c r="B32" s="341" t="n">
+      <c r="B32" s="355" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="112" t="inlineStr">
@@ -5731,7 +5773,7 @@
           <t>Крепёж дроп-кабеля (скобы / хомуты)</t>
         </is>
       </c>
-      <c r="D32" s="341" t="inlineStr">
+      <c r="D32" s="355" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
@@ -5741,23 +5783,23 @@
           <t>6 на ДХ</t>
         </is>
       </c>
-      <c r="F32" s="332" t="n">
+      <c r="F32" s="346" t="n">
         <v>6174</v>
       </c>
-      <c r="G32" s="332" t="n">
+      <c r="G32" s="346" t="n">
         <v>744</v>
       </c>
-      <c r="H32" s="332" t="n">
+      <c r="H32" s="346" t="n">
         <v>2256</v>
       </c>
-      <c r="I32" s="332" t="n">
+      <c r="I32" s="346" t="n">
         <v>3732</v>
       </c>
-      <c r="J32" s="332" t="n">
-        <v>1728</v>
-      </c>
-      <c r="K32" s="332" t="n">
-        <v>3900</v>
+      <c r="J32" s="346" t="n">
+        <v>1716</v>
+      </c>
+      <c r="K32" s="346" t="n">
+        <v>3912</v>
       </c>
       <c r="L32" s="146">
         <f>SUM(F32:K32)</f>
@@ -9425,7 +9467,7 @@
       </c>
       <c r="D14" s="109" t="inlineStr">
         <is>
-          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1498 (-69% к A); суммарная длина 217.4 км — минимум среди всех схем книги.</t>
+          <t>S_MIN = 15 волокно-км на доп. ОРШ: 36 зон + 6 ЦУ = 42 ОРШ; волокно-км 1499 (-69% к A); суммарная длина 217.4 км — минимум среди всех схем книги.</t>
         </is>
       </c>
     </row>
@@ -9506,19 +9548,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F18" s="332" t="n">
+      <c r="F18" s="346" t="n">
         <v>69</v>
       </c>
-      <c r="G18" s="332" t="n">
+      <c r="G18" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="332" t="n">
+      <c r="H18" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I18" s="332" t="n">
+      <c r="I18" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="332" t="n">
+      <c r="J18" s="346" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9534,19 +9576,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F19" s="333" t="n">
+      <c r="F19" s="347" t="n">
         <v>46</v>
       </c>
-      <c r="G19" s="333" t="n">
+      <c r="G19" s="347" t="n">
         <v>752</v>
       </c>
-      <c r="H19" s="333" t="n">
+      <c r="H19" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="333" t="n">
+      <c r="I19" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="333" t="n">
+      <c r="J19" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9562,19 +9604,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F20" s="332" t="n">
+      <c r="F20" s="346" t="n">
         <v>114</v>
       </c>
-      <c r="G20" s="332" t="n">
+      <c r="G20" s="346" t="n">
         <v>546</v>
       </c>
-      <c r="H20" s="332" t="n">
+      <c r="H20" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="332" t="n">
+      <c r="I20" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="332" t="n">
+      <c r="J20" s="346" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9590,19 +9632,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F21" s="333" t="n">
+      <c r="F21" s="347" t="n">
         <v>30</v>
       </c>
-      <c r="G21" s="333" t="n">
+      <c r="G21" s="347" t="n">
         <v>667</v>
       </c>
-      <c r="H21" s="333" t="n">
+      <c r="H21" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="333" t="n">
+      <c r="I21" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J21" s="333" t="n">
+      <c r="J21" s="347" t="n">
         <v>48</v>
       </c>
     </row>
@@ -9618,19 +9660,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F22" s="332" t="n">
+      <c r="F22" s="346" t="n">
         <v>132</v>
       </c>
-      <c r="G22" s="332" t="n">
+      <c r="G22" s="346" t="n">
         <v>717</v>
       </c>
-      <c r="H22" s="332" t="n">
+      <c r="H22" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="I22" s="332" t="n">
+      <c r="I22" s="346" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="332" t="n">
+      <c r="J22" s="346" t="n">
         <v>288</v>
       </c>
     </row>
@@ -9646,19 +9688,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F23" s="333" t="n">
+      <c r="F23" s="347" t="n">
         <v>109</v>
       </c>
-      <c r="G23" s="333" t="n">
+      <c r="G23" s="347" t="n">
         <v>856</v>
       </c>
-      <c r="H23" s="333" t="n">
+      <c r="H23" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="333" t="n">
+      <c r="I23" s="347" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="333" t="n">
+      <c r="J23" s="347" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9674,19 +9716,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F24" s="332" t="n">
+      <c r="F24" s="346" t="n">
         <v>84</v>
       </c>
-      <c r="G24" s="332" t="n">
+      <c r="G24" s="346" t="n">
         <v>908</v>
       </c>
-      <c r="H24" s="332" t="n">
+      <c r="H24" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="332" t="n">
+      <c r="I24" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="J24" s="332" t="n">
+      <c r="J24" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9702,19 +9744,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F25" s="333" t="n">
+      <c r="F25" s="347" t="n">
         <v>50</v>
       </c>
-      <c r="G25" s="333" t="n">
+      <c r="G25" s="347" t="n">
         <v>1708</v>
       </c>
-      <c r="H25" s="333" t="n">
+      <c r="H25" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="333" t="n">
+      <c r="I25" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="333" t="n">
+      <c r="J25" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9730,19 +9772,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F26" s="332" t="n">
+      <c r="F26" s="346" t="n">
         <v>49</v>
       </c>
-      <c r="G26" s="332" t="n">
+      <c r="G26" s="346" t="n">
         <v>860</v>
       </c>
-      <c r="H26" s="332" t="n">
+      <c r="H26" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="332" t="n">
+      <c r="I26" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="332" t="n">
+      <c r="J26" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9758,19 +9800,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F27" s="333" t="n">
+      <c r="F27" s="347" t="n">
         <v>49</v>
       </c>
-      <c r="G27" s="333" t="n">
+      <c r="G27" s="347" t="n">
         <v>1211</v>
       </c>
-      <c r="H27" s="333" t="n">
+      <c r="H27" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="333" t="n">
+      <c r="I27" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="333" t="n">
+      <c r="J27" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9786,19 +9828,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F28" s="332" t="n">
+      <c r="F28" s="346" t="n">
         <v>88</v>
       </c>
-      <c r="G28" s="332" t="n">
+      <c r="G28" s="346" t="n">
         <v>1175</v>
       </c>
-      <c r="H28" s="332" t="n">
+      <c r="H28" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I28" s="332" t="n">
+      <c r="I28" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="332" t="n">
+      <c r="J28" s="346" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9814,19 +9856,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F29" s="333" t="n">
+      <c r="F29" s="347" t="n">
         <v>50</v>
       </c>
-      <c r="G29" s="333" t="n">
+      <c r="G29" s="347" t="n">
         <v>1169</v>
       </c>
-      <c r="H29" s="333" t="n">
+      <c r="H29" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I29" s="333" t="n">
+      <c r="I29" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="333" t="n">
+      <c r="J29" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9842,19 +9884,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F30" s="332" t="n">
+      <c r="F30" s="346" t="n">
         <v>51</v>
       </c>
-      <c r="G30" s="332" t="n">
+      <c r="G30" s="346" t="n">
         <v>1390</v>
       </c>
-      <c r="H30" s="332" t="n">
+      <c r="H30" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I30" s="332" t="n">
+      <c r="I30" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="332" t="n">
+      <c r="J30" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9870,19 +9912,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F31" s="333" t="n">
+      <c r="F31" s="347" t="n">
         <v>49</v>
       </c>
-      <c r="G31" s="333" t="n">
+      <c r="G31" s="347" t="n">
         <v>879</v>
       </c>
-      <c r="H31" s="333" t="n">
+      <c r="H31" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="333" t="n">
+      <c r="I31" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="333" t="n">
+      <c r="J31" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9898,19 +9940,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F32" s="332" t="n">
+      <c r="F32" s="346" t="n">
         <v>59</v>
       </c>
-      <c r="G32" s="332" t="n">
+      <c r="G32" s="346" t="n">
         <v>745</v>
       </c>
-      <c r="H32" s="332" t="n">
+      <c r="H32" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="332" t="n">
+      <c r="I32" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="332" t="n">
+      <c r="J32" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -9930,19 +9972,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F33" s="333" t="n">
+      <c r="F33" s="347" t="n">
         <v>124</v>
       </c>
-      <c r="G33" s="333" t="n">
+      <c r="G33" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="333" t="n">
+      <c r="H33" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="333" t="n">
+      <c r="I33" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="333" t="n">
+      <c r="J33" s="347" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9962,19 +10004,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F34" s="332" t="n">
+      <c r="F34" s="346" t="n">
         <v>35</v>
       </c>
-      <c r="G34" s="332" t="n">
+      <c r="G34" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="332" t="n">
+      <c r="H34" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="332" t="n">
+      <c r="I34" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="332" t="n">
+      <c r="J34" s="346" t="n">
         <v>144</v>
       </c>
     </row>
@@ -9990,19 +10032,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F35" s="333" t="n">
+      <c r="F35" s="347" t="n">
         <v>56</v>
       </c>
-      <c r="G35" s="333" t="n">
+      <c r="G35" s="347" t="n">
         <v>805</v>
       </c>
-      <c r="H35" s="333" t="n">
+      <c r="H35" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="333" t="n">
+      <c r="I35" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="333" t="n">
+      <c r="J35" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10018,19 +10060,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F36" s="332" t="n">
+      <c r="F36" s="346" t="n">
         <v>156</v>
       </c>
-      <c r="G36" s="332" t="n">
+      <c r="G36" s="346" t="n">
         <v>295</v>
       </c>
-      <c r="H36" s="332" t="n">
+      <c r="H36" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="332" t="n">
+      <c r="I36" s="346" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="332" t="n">
+      <c r="J36" s="346" t="n">
         <v>288</v>
       </c>
     </row>
@@ -10046,19 +10088,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F37" s="333" t="n">
+      <c r="F37" s="347" t="n">
         <v>69</v>
       </c>
-      <c r="G37" s="333" t="n">
+      <c r="G37" s="347" t="n">
         <v>1394</v>
       </c>
-      <c r="H37" s="333" t="n">
+      <c r="H37" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="333" t="n">
+      <c r="I37" s="347" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="333" t="n">
+      <c r="J37" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10074,19 +10116,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F38" s="332" t="n">
+      <c r="F38" s="346" t="n">
         <v>60</v>
       </c>
-      <c r="G38" s="332" t="n">
+      <c r="G38" s="346" t="n">
         <v>556</v>
       </c>
-      <c r="H38" s="332" t="n">
+      <c r="H38" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="332" t="n">
+      <c r="I38" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="332" t="n">
+      <c r="J38" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10106,19 +10148,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F39" s="333" t="n">
+      <c r="F39" s="347" t="n">
         <v>27</v>
       </c>
-      <c r="G39" s="333" t="n">
+      <c r="G39" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="H39" s="333" t="n">
+      <c r="H39" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="333" t="n">
+      <c r="I39" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="333" t="n">
+      <c r="J39" s="347" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10134,19 +10176,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F40" s="332" t="n">
+      <c r="F40" s="346" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="332" t="n">
+      <c r="G40" s="346" t="n">
         <v>1298</v>
       </c>
-      <c r="H40" s="332" t="n">
+      <c r="H40" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I40" s="332" t="n">
+      <c r="I40" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="332" t="n">
+      <c r="J40" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10162,19 +10204,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F41" s="333" t="n">
+      <c r="F41" s="347" t="n">
         <v>107</v>
       </c>
-      <c r="G41" s="333" t="n">
+      <c r="G41" s="347" t="n">
         <v>418</v>
       </c>
-      <c r="H41" s="333" t="n">
+      <c r="H41" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="I41" s="333" t="n">
+      <c r="I41" s="347" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="333" t="n">
+      <c r="J41" s="347" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10190,19 +10232,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F42" s="332" t="n">
+      <c r="F42" s="346" t="n">
         <v>53</v>
       </c>
-      <c r="G42" s="332" t="n">
+      <c r="G42" s="346" t="n">
         <v>1329</v>
       </c>
-      <c r="H42" s="332" t="n">
+      <c r="H42" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="332" t="n">
+      <c r="I42" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="332" t="n">
+      <c r="J42" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10218,19 +10260,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F43" s="333" t="n">
+      <c r="F43" s="347" t="n">
         <v>53</v>
       </c>
-      <c r="G43" s="333" t="n">
+      <c r="G43" s="347" t="n">
         <v>937</v>
       </c>
-      <c r="H43" s="333" t="n">
+      <c r="H43" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="333" t="n">
+      <c r="I43" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="333" t="n">
+      <c r="J43" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10246,19 +10288,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F44" s="332" t="n">
+      <c r="F44" s="346" t="n">
         <v>85</v>
       </c>
-      <c r="G44" s="332" t="n">
+      <c r="G44" s="346" t="n">
         <v>368</v>
       </c>
-      <c r="H44" s="332" t="n">
+      <c r="H44" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="332" t="n">
+      <c r="I44" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="332" t="n">
+      <c r="J44" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10274,19 +10316,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F45" s="333" t="n">
+      <c r="F45" s="347" t="n">
         <v>48</v>
       </c>
-      <c r="G45" s="333" t="n">
+      <c r="G45" s="347" t="n">
         <v>1096</v>
       </c>
-      <c r="H45" s="333" t="n">
+      <c r="H45" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="333" t="n">
+      <c r="I45" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="333" t="n">
+      <c r="J45" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10302,19 +10344,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F46" s="332" t="n">
+      <c r="F46" s="346" t="n">
         <v>76</v>
       </c>
-      <c r="G46" s="332" t="n">
+      <c r="G46" s="346" t="n">
         <v>302</v>
       </c>
-      <c r="H46" s="332" t="n">
+      <c r="H46" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I46" s="332" t="n">
+      <c r="I46" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="332" t="n">
+      <c r="J46" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10330,19 +10372,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F47" s="333" t="n">
+      <c r="F47" s="347" t="n">
         <v>78</v>
       </c>
-      <c r="G47" s="333" t="n">
+      <c r="G47" s="347" t="n">
         <v>1779</v>
       </c>
-      <c r="H47" s="333" t="n">
+      <c r="H47" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="I47" s="333" t="n">
+      <c r="I47" s="347" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="333" t="n">
+      <c r="J47" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10358,19 +10400,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F48" s="332" t="n">
+      <c r="F48" s="346" t="n">
         <v>50</v>
       </c>
-      <c r="G48" s="332" t="n">
+      <c r="G48" s="346" t="n">
         <v>476</v>
       </c>
-      <c r="H48" s="332" t="n">
+      <c r="H48" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I48" s="332" t="n">
+      <c r="I48" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="332" t="n">
+      <c r="J48" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10390,19 +10432,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F49" s="333" t="n">
+      <c r="F49" s="347" t="n">
         <v>70</v>
       </c>
-      <c r="G49" s="333" t="n">
+      <c r="G49" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="333" t="n">
+      <c r="H49" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="I49" s="333" t="n">
+      <c r="I49" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="J49" s="333" t="n">
+      <c r="J49" s="347" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10418,19 +10460,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F50" s="332" t="n">
+      <c r="F50" s="346" t="n">
         <v>62</v>
       </c>
-      <c r="G50" s="332" t="n">
+      <c r="G50" s="346" t="n">
         <v>666</v>
       </c>
-      <c r="H50" s="332" t="n">
+      <c r="H50" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="332" t="n">
+      <c r="I50" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="332" t="n">
+      <c r="J50" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10446,19 +10488,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F51" s="333" t="n">
-        <v>95</v>
-      </c>
-      <c r="G51" s="333" t="n">
+      <c r="F51" s="347" t="n">
+        <v>93</v>
+      </c>
+      <c r="G51" s="347" t="n">
         <v>262</v>
       </c>
-      <c r="H51" s="333" t="n">
+      <c r="H51" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="I51" s="333" t="n">
+      <c r="I51" s="347" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="333" t="n">
+      <c r="J51" s="347" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10474,19 +10516,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F52" s="332" t="n">
+      <c r="F52" s="346" t="n">
         <v>61</v>
       </c>
-      <c r="G52" s="332" t="n">
+      <c r="G52" s="346" t="n">
         <v>367</v>
       </c>
-      <c r="H52" s="332" t="n">
+      <c r="H52" s="346" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="332" t="n">
+      <c r="I52" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="332" t="n">
+      <c r="J52" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10506,19 +10548,19 @@
           <t>ЦУ (корневая)</t>
         </is>
       </c>
-      <c r="F53" s="333" t="n">
+      <c r="F53" s="347" t="n">
         <v>122</v>
       </c>
-      <c r="G53" s="333" t="n">
+      <c r="G53" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="333" t="n">
+      <c r="H53" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="I53" s="333" t="n">
+      <c r="I53" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="333" t="n">
+      <c r="J53" s="347" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10534,19 +10576,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F54" s="332" t="n">
+      <c r="F54" s="346" t="n">
         <v>93</v>
       </c>
-      <c r="G54" s="332" t="n">
+      <c r="G54" s="346" t="n">
         <v>274</v>
       </c>
-      <c r="H54" s="332" t="n">
+      <c r="H54" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="332" t="n">
+      <c r="I54" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="332" t="n">
+      <c r="J54" s="346" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10562,19 +10604,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F55" s="333" t="n">
-        <v>156</v>
-      </c>
-      <c r="G55" s="333" t="n">
+      <c r="F55" s="347" t="n">
+        <v>158</v>
+      </c>
+      <c r="G55" s="347" t="n">
         <v>654</v>
       </c>
-      <c r="H55" s="333" t="n">
+      <c r="H55" s="347" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="333" t="n">
+      <c r="I55" s="347" t="n">
         <v>4</v>
       </c>
-      <c r="J55" s="333" t="n">
+      <c r="J55" s="347" t="n">
         <v>288</v>
       </c>
     </row>
@@ -10590,19 +10632,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F56" s="332" t="n">
+      <c r="F56" s="346" t="n">
         <v>91</v>
       </c>
-      <c r="G56" s="332" t="n">
+      <c r="G56" s="346" t="n">
         <v>336</v>
       </c>
-      <c r="H56" s="332" t="n">
+      <c r="H56" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="332" t="n">
+      <c r="I56" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="J56" s="332" t="n">
+      <c r="J56" s="346" t="n">
         <v>144</v>
       </c>
     </row>
@@ -10618,19 +10660,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F57" s="333" t="n">
+      <c r="F57" s="347" t="n">
         <v>59</v>
       </c>
-      <c r="G57" s="333" t="n">
+      <c r="G57" s="347" t="n">
         <v>433</v>
       </c>
-      <c r="H57" s="333" t="n">
+      <c r="H57" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="333" t="n">
+      <c r="I57" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="333" t="n">
+      <c r="J57" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10646,19 +10688,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F58" s="332" t="n">
+      <c r="F58" s="346" t="n">
         <v>73</v>
       </c>
-      <c r="G58" s="332" t="n">
+      <c r="G58" s="346" t="n">
         <v>710</v>
       </c>
-      <c r="H58" s="332" t="n">
+      <c r="H58" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="332" t="n">
+      <c r="I58" s="346" t="n">
         <v>3</v>
       </c>
-      <c r="J58" s="332" t="n">
+      <c r="J58" s="346" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10674,19 +10716,19 @@
           <t>зонный шкаф</t>
         </is>
       </c>
-      <c r="F59" s="333" t="n">
+      <c r="F59" s="347" t="n">
         <v>56</v>
       </c>
-      <c r="G59" s="333" t="n">
+      <c r="G59" s="347" t="n">
         <v>306</v>
       </c>
-      <c r="H59" s="333" t="n">
+      <c r="H59" s="347" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="333" t="n">
+      <c r="I59" s="347" t="n">
         <v>2</v>
       </c>
-      <c r="J59" s="333" t="n">
+      <c r="J59" s="347" t="n">
         <v>96</v>
       </c>
     </row>
@@ -10809,482 +10851,482 @@
       </c>
     </row>
     <row r="65" ht="18" customHeight="1" s="63">
-      <c r="C65" s="332" t="n">
+      <c r="C65" s="346" t="n">
         <v>2</v>
       </c>
-      <c r="D65" s="332" t="n">
+      <c r="D65" s="346" t="n">
         <v>48</v>
       </c>
-      <c r="E65" s="334" t="n">
+      <c r="E65" s="348" t="n">
         <v>1460.2</v>
       </c>
-      <c r="F65" s="335">
+      <c r="F65" s="349">
         <f>E65/4375.1-1</f>
         <v/>
       </c>
-      <c r="G65" s="334" t="n">
+      <c r="G65" s="348" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H65" s="334" t="n">
+      <c r="H65" s="348" t="n">
         <v>95.8</v>
       </c>
-      <c r="I65" s="334">
+      <c r="I65" s="348">
         <f>G65+H65</f>
         <v/>
       </c>
-      <c r="J65" s="332" t="n">
+      <c r="J65" s="346" t="n">
         <v>56</v>
       </c>
-      <c r="K65" s="332" t="n">
+      <c r="K65" s="346" t="n">
         <v>5261</v>
       </c>
-      <c r="L65" s="332" t="n">
+      <c r="L65" s="346" t="n">
         <v>4368</v>
       </c>
-      <c r="M65" s="332" t="n">
+      <c r="M65" s="346" t="n">
         <v>349</v>
       </c>
-      <c r="N65" s="332" t="n">
+      <c r="N65" s="346" t="n">
         <v>74</v>
       </c>
     </row>
     <row r="66" ht="18" customHeight="1" s="63">
-      <c r="C66" s="333" t="n">
+      <c r="C66" s="347" t="n">
         <v>5</v>
       </c>
-      <c r="D66" s="333" t="n">
+      <c r="D66" s="347" t="n">
         <v>43</v>
       </c>
-      <c r="E66" s="336" t="n">
+      <c r="E66" s="350" t="n">
         <v>1476.5</v>
       </c>
-      <c r="F66" s="337">
+      <c r="F66" s="351">
         <f>E66/4375.1-1</f>
         <v/>
       </c>
-      <c r="G66" s="336" t="n">
+      <c r="G66" s="350" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H66" s="336" t="n">
+      <c r="H66" s="350" t="n">
         <v>95.8</v>
       </c>
-      <c r="I66" s="336">
+      <c r="I66" s="350">
         <f>G66+H66</f>
         <v/>
       </c>
-      <c r="J66" s="333" t="n">
+      <c r="J66" s="347" t="n">
         <v>54</v>
       </c>
-      <c r="K66" s="333" t="n">
+      <c r="K66" s="347" t="n">
         <v>5255</v>
       </c>
-      <c r="L66" s="333" t="n">
+      <c r="L66" s="347" t="n">
         <v>4176</v>
       </c>
-      <c r="M66" s="333" t="n">
+      <c r="M66" s="347" t="n">
         <v>358</v>
       </c>
-      <c r="N66" s="333" t="n">
+      <c r="N66" s="347" t="n">
         <v>108</v>
       </c>
     </row>
     <row r="67" ht="18" customHeight="1" s="63">
-      <c r="C67" s="332" t="n">
+      <c r="C67" s="346" t="n">
         <v>8</v>
       </c>
-      <c r="D67" s="332" t="n">
+      <c r="D67" s="346" t="n">
         <v>39</v>
       </c>
-      <c r="E67" s="334" t="n">
+      <c r="E67" s="348" t="n">
         <v>1500.8</v>
       </c>
-      <c r="F67" s="335">
+      <c r="F67" s="349">
         <f>E67/4375.1-1</f>
         <v/>
       </c>
-      <c r="G67" s="334" t="n">
+      <c r="G67" s="348" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H67" s="334" t="n">
+      <c r="H67" s="348" t="n">
         <v>95.8</v>
       </c>
-      <c r="I67" s="334">
+      <c r="I67" s="348">
         <f>G67+H67</f>
         <v/>
       </c>
-      <c r="J67" s="332" t="n">
+      <c r="J67" s="346" t="n">
         <v>53</v>
       </c>
-      <c r="K67" s="332" t="n">
+      <c r="K67" s="346" t="n">
         <v>5253</v>
       </c>
-      <c r="L67" s="332" t="n">
+      <c r="L67" s="346" t="n">
         <v>3984</v>
       </c>
-      <c r="M67" s="332" t="n">
+      <c r="M67" s="346" t="n">
         <v>368</v>
       </c>
-      <c r="N67" s="332" t="n">
+      <c r="N67" s="346" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="63">
-      <c r="C68" s="333" t="n">
+      <c r="C68" s="347" t="n">
         <v>10</v>
       </c>
-      <c r="D68" s="333" t="n">
+      <c r="D68" s="347" t="n">
         <v>36</v>
       </c>
-      <c r="E68" s="336" t="n">
+      <c r="E68" s="350" t="n">
         <v>1532.5</v>
       </c>
-      <c r="F68" s="337">
+      <c r="F68" s="351">
         <f>E68/4375.1-1</f>
         <v/>
       </c>
-      <c r="G68" s="336" t="n">
+      <c r="G68" s="350" t="n">
         <v>80.40000000000001</v>
       </c>
-      <c r="H68" s="336" t="n">
+      <c r="H68" s="350" t="n">
         <v>95.8</v>
       </c>
-      <c r="I68" s="336">
+      <c r="I68" s="350">
         <f>G68+H68</f>
         <v/>
       </c>
-      <c r="J68" s="333" t="n">
+      <c r="J68" s="347" t="n">
         <v>53</v>
       </c>
-      <c r="K68" s="333" t="n">
+      <c r="K68" s="347" t="n">
         <v>5253</v>
       </c>
-      <c r="L68" s="333" t="n">
+      <c r="L68" s="347" t="n">
         <v>3888</v>
       </c>
-      <c r="M68" s="333" t="n">
+      <c r="M68" s="347" t="n">
         <v>379</v>
       </c>
-      <c r="N68" s="333" t="n">
+      <c r="N68" s="347" t="n">
         <v>119</v>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="63">
-      <c r="C69" s="338" t="n">
+      <c r="C69" s="352" t="n">
         <v>15</v>
       </c>
-      <c r="D69" s="338" t="n">
+      <c r="D69" s="352" t="n">
         <v>34</v>
       </c>
-      <c r="E69" s="339" t="n">
+      <c r="E69" s="353" t="n">
         <v>1562.5</v>
       </c>
-      <c r="F69" s="340">
+      <c r="F69" s="354">
         <f>E69/4375.1-1</f>
         <v/>
       </c>
-      <c r="G69" s="339" t="n">
+      <c r="G69" s="353" t="n">
         <v>80.5</v>
       </c>
-      <c r="H69" s="339" t="n">
+      <c r="H69" s="353" t="n">
         <v>95.8</v>
       </c>
-      <c r="I69" s="339">
+      <c r="I69" s="353">
         <f>G69+H69</f>
         <v/>
       </c>
-      <c r="J69" s="338" t="n">
+      <c r="J69" s="352" t="n">
         <v>52</v>
       </c>
-      <c r="K69" s="338" t="n">
+      <c r="K69" s="352" t="n">
         <v>5251</v>
       </c>
-      <c r="L69" s="338" t="n">
+      <c r="L69" s="352" t="n">
         <v>3696</v>
       </c>
-      <c r="M69" s="338" t="n">
+      <c r="M69" s="352" t="n">
         <v>388</v>
       </c>
-      <c r="N69" s="338" t="n">
+      <c r="N69" s="352" t="n">
         <v>128</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="63">
-      <c r="C70" s="333" t="n">
+      <c r="C70" s="347" t="n">
         <v>20</v>
       </c>
-      <c r="D70" s="333" t="n">
+      <c r="D70" s="347" t="n">
         <v>32</v>
       </c>
-      <c r="E70" s="336" t="n">
+      <c r="E70" s="350" t="n">
         <v>1603.9</v>
       </c>
-      <c r="F70" s="337">
+      <c r="F70" s="351">
         <f>E70/4375.1-1</f>
         <v/>
       </c>
-      <c r="G70" s="336" t="n">
+      <c r="G70" s="350" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="H70" s="336" t="n">
+      <c r="H70" s="350" t="n">
         <v>95.8</v>
       </c>
-      <c r="I70" s="336">
+      <c r="I70" s="350">
         <f>G70+H70</f>
         <v/>
       </c>
-      <c r="J70" s="333" t="n">
+      <c r="J70" s="347" t="n">
         <v>51</v>
       </c>
-      <c r="K70" s="333" t="n">
+      <c r="K70" s="347" t="n">
         <v>5249</v>
       </c>
-      <c r="L70" s="333" t="n">
+      <c r="L70" s="347" t="n">
         <v>3696</v>
       </c>
-      <c r="M70" s="333" t="n">
+      <c r="M70" s="347" t="n">
         <v>403</v>
       </c>
-      <c r="N70" s="333" t="n">
+      <c r="N70" s="347" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="63">
-      <c r="C71" s="332" t="n">
+      <c r="C71" s="346" t="n">
         <v>25</v>
       </c>
-      <c r="D71" s="332" t="n">
+      <c r="D71" s="346" t="n">
         <v>29</v>
       </c>
-      <c r="E71" s="334" t="n">
+      <c r="E71" s="348" t="n">
         <v>1674.7</v>
       </c>
-      <c r="F71" s="335">
+      <c r="F71" s="349">
         <f>E71/4375.1-1</f>
         <v/>
       </c>
-      <c r="G71" s="334" t="n">
+      <c r="G71" s="348" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H71" s="334" t="n">
+      <c r="H71" s="348" t="n">
         <v>95.8</v>
       </c>
-      <c r="I71" s="334">
+      <c r="I71" s="348">
         <f>G71+H71</f>
         <v/>
       </c>
-      <c r="J71" s="332" t="n">
+      <c r="J71" s="346" t="n">
         <v>50</v>
       </c>
-      <c r="K71" s="332" t="n">
+      <c r="K71" s="346" t="n">
         <v>5247</v>
       </c>
-      <c r="L71" s="332" t="n">
+      <c r="L71" s="346" t="n">
         <v>3600</v>
       </c>
-      <c r="M71" s="332" t="n">
+      <c r="M71" s="346" t="n">
         <v>427</v>
       </c>
-      <c r="N71" s="332" t="n">
+      <c r="N71" s="346" t="n">
         <v>148</v>
       </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="63">
-      <c r="C72" s="333" t="n">
+      <c r="C72" s="347" t="n">
         <v>30</v>
       </c>
-      <c r="D72" s="333" t="n">
+      <c r="D72" s="347" t="n">
         <v>27</v>
       </c>
-      <c r="E72" s="336" t="n">
+      <c r="E72" s="350" t="n">
         <v>1736.2</v>
       </c>
-      <c r="F72" s="337">
+      <c r="F72" s="351">
         <f>E72/4375.1-1</f>
         <v/>
       </c>
-      <c r="G72" s="336" t="n">
+      <c r="G72" s="350" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="H72" s="336" t="n">
+      <c r="H72" s="350" t="n">
         <v>95.8</v>
       </c>
-      <c r="I72" s="336">
+      <c r="I72" s="350">
         <f>G72+H72</f>
         <v/>
       </c>
-      <c r="J72" s="333" t="n">
+      <c r="J72" s="347" t="n">
         <v>48</v>
       </c>
-      <c r="K72" s="333" t="n">
+      <c r="K72" s="347" t="n">
         <v>5243</v>
       </c>
-      <c r="L72" s="333" t="n">
+      <c r="L72" s="347" t="n">
         <v>3504</v>
       </c>
-      <c r="M72" s="333" t="n">
+      <c r="M72" s="347" t="n">
         <v>448</v>
       </c>
-      <c r="N72" s="333" t="n">
+      <c r="N72" s="347" t="n">
         <v>154</v>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="63">
-      <c r="C73" s="332" t="n">
+      <c r="C73" s="346" t="n">
         <v>40</v>
       </c>
-      <c r="D73" s="332" t="n">
+      <c r="D73" s="346" t="n">
         <v>24</v>
       </c>
-      <c r="E73" s="334" t="n">
+      <c r="E73" s="348" t="n">
         <v>1852</v>
       </c>
-      <c r="F73" s="335">
+      <c r="F73" s="349">
         <f>E73/4375.1-1</f>
         <v/>
       </c>
-      <c r="G73" s="334" t="n">
+      <c r="G73" s="348" t="n">
         <v>82.3</v>
       </c>
-      <c r="H73" s="334" t="n">
+      <c r="H73" s="348" t="n">
         <v>95.8</v>
       </c>
-      <c r="I73" s="334">
+      <c r="I73" s="348">
         <f>G73+H73</f>
         <v/>
       </c>
-      <c r="J73" s="332" t="n">
+      <c r="J73" s="346" t="n">
         <v>47</v>
       </c>
-      <c r="K73" s="332" t="n">
+      <c r="K73" s="346" t="n">
         <v>5241</v>
       </c>
-      <c r="L73" s="332" t="n">
+      <c r="L73" s="346" t="n">
         <v>3552</v>
       </c>
-      <c r="M73" s="332" t="n">
+      <c r="M73" s="346" t="n">
         <v>488</v>
       </c>
-      <c r="N73" s="332" t="n">
+      <c r="N73" s="346" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="63">
-      <c r="C74" s="333" t="n">
+      <c r="C74" s="347" t="n">
         <v>50</v>
       </c>
-      <c r="D74" s="333" t="n">
+      <c r="D74" s="347" t="n">
         <v>20</v>
       </c>
-      <c r="E74" s="336" t="n">
+      <c r="E74" s="350" t="n">
         <v>2041.2</v>
       </c>
-      <c r="F74" s="337">
+      <c r="F74" s="351">
         <f>E74/4375.1-1</f>
         <v/>
       </c>
-      <c r="G74" s="336" t="n">
+      <c r="G74" s="350" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="H74" s="336" t="n">
+      <c r="H74" s="350" t="n">
         <v>95.8</v>
       </c>
-      <c r="I74" s="336">
+      <c r="I74" s="350">
         <f>G74+H74</f>
         <v/>
       </c>
-      <c r="J74" s="333" t="n">
+      <c r="J74" s="347" t="n">
         <v>46</v>
       </c>
-      <c r="K74" s="333" t="n">
+      <c r="K74" s="347" t="n">
         <v>5238</v>
       </c>
-      <c r="L74" s="333" t="n">
+      <c r="L74" s="347" t="n">
         <v>3696</v>
       </c>
-      <c r="M74" s="333" t="n">
+      <c r="M74" s="347" t="n">
         <v>554</v>
       </c>
-      <c r="N74" s="333" t="n">
+      <c r="N74" s="347" t="n">
         <v>164</v>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="63">
-      <c r="C75" s="332" t="n">
+      <c r="C75" s="346" t="n">
         <v>60</v>
       </c>
-      <c r="D75" s="332" t="n">
+      <c r="D75" s="346" t="n">
         <v>18</v>
       </c>
-      <c r="E75" s="334" t="n">
+      <c r="E75" s="348" t="n">
         <v>2153.9</v>
       </c>
-      <c r="F75" s="335">
+      <c r="F75" s="349">
         <f>E75/4375.1-1</f>
         <v/>
       </c>
-      <c r="G75" s="334" t="n">
+      <c r="G75" s="348" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="H75" s="334" t="n">
+      <c r="H75" s="348" t="n">
         <v>95.8</v>
       </c>
-      <c r="I75" s="334">
+      <c r="I75" s="348">
         <f>G75+H75</f>
         <v/>
       </c>
-      <c r="J75" s="332" t="n">
+      <c r="J75" s="346" t="n">
         <v>45</v>
       </c>
-      <c r="K75" s="332" t="n">
+      <c r="K75" s="346" t="n">
         <v>5236</v>
       </c>
-      <c r="L75" s="332" t="n">
+      <c r="L75" s="346" t="n">
         <v>3744</v>
       </c>
-      <c r="M75" s="332" t="n">
+      <c r="M75" s="346" t="n">
         <v>592</v>
       </c>
-      <c r="N75" s="332" t="n">
+      <c r="N75" s="346" t="n">
         <v>245</v>
       </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="63">
-      <c r="C76" s="333" t="n">
+      <c r="C76" s="347" t="n">
         <v>80</v>
       </c>
-      <c r="D76" s="333" t="n">
+      <c r="D76" s="347" t="n">
         <v>17</v>
       </c>
-      <c r="E76" s="336" t="n">
+      <c r="E76" s="350" t="n">
         <v>2215.1</v>
       </c>
-      <c r="F76" s="337">
+      <c r="F76" s="351">
         <f>E76/4375.1-1</f>
         <v/>
       </c>
-      <c r="G76" s="336" t="n">
+      <c r="G76" s="350" t="n">
         <v>84.7</v>
       </c>
-      <c r="H76" s="336" t="n">
+      <c r="H76" s="350" t="n">
         <v>95.8</v>
       </c>
-      <c r="I76" s="336">
+      <c r="I76" s="350">
         <f>G76+H76</f>
         <v/>
       </c>
-      <c r="J76" s="333" t="n">
+      <c r="J76" s="347" t="n">
         <v>44</v>
       </c>
-      <c r="K76" s="333" t="n">
+      <c r="K76" s="347" t="n">
         <v>5234</v>
       </c>
-      <c r="L76" s="333" t="n">
+      <c r="L76" s="347" t="n">
         <v>3600</v>
       </c>
-      <c r="M76" s="333" t="n">
+      <c r="M76" s="347" t="n">
         <v>614</v>
       </c>
-      <c r="N76" s="333" t="n">
+      <c r="N76" s="347" t="n">
         <v>245</v>
       </c>
     </row>
@@ -11313,134 +11355,134 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="332" t="n">
+      <c r="B80" s="346" t="n">
         <v>17</v>
       </c>
-      <c r="C80" s="334" t="n">
+      <c r="C80" s="348" t="n">
         <v>2215.1</v>
       </c>
-      <c r="D80" s="334" t="n">
+      <c r="D80" s="348" t="n">
         <v>527.3</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="333" t="n">
+      <c r="B81" s="347" t="n">
         <v>18</v>
       </c>
-      <c r="C81" s="336" t="n">
+      <c r="C81" s="350" t="n">
         <v>2153.9</v>
       </c>
-      <c r="D81" s="336" t="n">
+      <c r="D81" s="350" t="n">
         <v>529.8</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="332" t="n">
+      <c r="B82" s="346" t="n">
         <v>20</v>
       </c>
-      <c r="C82" s="334" t="n">
+      <c r="C82" s="348" t="n">
         <v>2041.2</v>
       </c>
-      <c r="D82" s="334" t="n">
+      <c r="D82" s="348" t="n">
         <v>527.5</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="333" t="n">
+      <c r="B83" s="347" t="n">
         <v>24</v>
       </c>
-      <c r="C83" s="336" t="n">
+      <c r="C83" s="350" t="n">
         <v>1852</v>
       </c>
-      <c r="D83" s="336" t="n">
+      <c r="D83" s="350" t="n">
         <v>524.2</v>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="332" t="n">
+      <c r="B84" s="346" t="n">
         <v>27</v>
       </c>
-      <c r="C84" s="334" t="n">
+      <c r="C84" s="348" t="n">
         <v>1736.2</v>
       </c>
-      <c r="D84" s="334" t="n">
+      <c r="D84" s="348" t="n">
         <v>524.4</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="333" t="n">
+      <c r="B85" s="347" t="n">
         <v>29</v>
       </c>
-      <c r="C85" s="336" t="n">
+      <c r="C85" s="350" t="n">
         <v>1674.7</v>
       </c>
-      <c r="D85" s="336" t="n">
+      <c r="D85" s="350" t="n">
         <v>527.9</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="332" t="n">
+      <c r="B86" s="346" t="n">
         <v>32</v>
       </c>
-      <c r="C86" s="334" t="n">
+      <c r="C86" s="348" t="n">
         <v>1603.9</v>
       </c>
-      <c r="D86" s="334" t="n">
+      <c r="D86" s="348" t="n">
         <v>531.7</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="333" t="n">
+      <c r="B87" s="347" t="n">
         <v>34</v>
       </c>
-      <c r="C87" s="336" t="n">
+      <c r="C87" s="350" t="n">
         <v>1562.5</v>
       </c>
-      <c r="D87" s="336" t="n">
+      <c r="D87" s="350" t="n">
         <v>533.2</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="332" t="n">
+      <c r="B88" s="346" t="n">
         <v>36</v>
       </c>
-      <c r="C88" s="334" t="n">
+      <c r="C88" s="348" t="n">
         <v>1532.5</v>
       </c>
-      <c r="D88" s="334" t="n">
+      <c r="D88" s="348" t="n">
         <v>539.3</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="333" t="n">
+      <c r="B89" s="347" t="n">
         <v>39</v>
       </c>
-      <c r="C89" s="336" t="n">
+      <c r="C89" s="350" t="n">
         <v>1500.8</v>
       </c>
-      <c r="D89" s="336" t="n">
+      <c r="D89" s="350" t="n">
         <v>544.4</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="332" t="n">
+      <c r="B90" s="346" t="n">
         <v>43</v>
       </c>
-      <c r="C90" s="334" t="n">
+      <c r="C90" s="348" t="n">
         <v>1476.5</v>
       </c>
-      <c r="D90" s="334" t="n">
+      <c r="D90" s="348" t="n">
         <v>553</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="333" t="n">
+      <c r="B91" s="347" t="n">
         <v>48</v>
       </c>
-      <c r="C91" s="336" t="n">
+      <c r="C91" s="350" t="n">
         <v>1460.2</v>
       </c>
-      <c r="D91" s="336" t="n">
+      <c r="D91" s="350" t="n">
         <v>563.9</v>
       </c>
     </row>
@@ -11501,19 +11543,19 @@
           <t>Обслужено ДХ, шт</t>
         </is>
       </c>
-      <c r="D95" s="332" t="n">
+      <c r="D95" s="346" t="n">
         <v>3089</v>
       </c>
-      <c r="E95" s="332" t="n">
+      <c r="E95" s="346" t="n">
         <v>3089</v>
       </c>
-      <c r="F95" s="332" t="n">
+      <c r="F95" s="346" t="n">
         <v>3089</v>
       </c>
-      <c r="G95" s="332" t="n">
+      <c r="G95" s="346" t="n">
         <v>3089</v>
       </c>
-      <c r="H95" s="341" t="n"/>
+      <c r="H95" s="355" t="n"/>
     </row>
     <row r="96" ht="18" customHeight="1" s="63">
       <c r="C96" s="114" t="inlineStr">
@@ -11521,19 +11563,19 @@
           <t>Волокно-км</t>
         </is>
       </c>
-      <c r="D96" s="336" t="n">
+      <c r="D96" s="350" t="n">
         <v>4375.1</v>
       </c>
-      <c r="E96" s="336" t="n">
+      <c r="E96" s="350" t="n">
         <v>1256.1</v>
       </c>
-      <c r="F96" s="336" t="n">
+      <c r="F96" s="350" t="n">
         <v>889.2</v>
       </c>
-      <c r="G96" s="336" t="n">
-        <v>1498.3</v>
-      </c>
-      <c r="H96" s="342">
+      <c r="G96" s="350" t="n">
+        <v>1499.2</v>
+      </c>
+      <c r="H96" s="356">
         <f>CHOOSE(MATCH(MIN(D96:G96),D96:G96,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11544,23 +11586,23 @@
           <t>Волокно-км на ДХ, км</t>
         </is>
       </c>
-      <c r="D97" s="343">
+      <c r="D97" s="357">
         <f>D96/3089</f>
         <v/>
       </c>
-      <c r="E97" s="343">
+      <c r="E97" s="357">
         <f>E96/3089</f>
         <v/>
       </c>
-      <c r="F97" s="343">
+      <c r="F97" s="357">
         <f>F96/3089</f>
         <v/>
       </c>
-      <c r="G97" s="343">
+      <c r="G97" s="357">
         <f>G96/3089</f>
         <v/>
       </c>
-      <c r="H97" s="341">
+      <c r="H97" s="355">
         <f>CHOOSE(MATCH(MIN(D97:G97),D97:G97,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11571,19 +11613,19 @@
           <t>Магистральный кабель, км</t>
         </is>
       </c>
-      <c r="D98" s="336" t="n">
+      <c r="D98" s="350" t="n">
         <v>109.4</v>
       </c>
-      <c r="E98" s="336" t="n">
+      <c r="E98" s="350" t="n">
         <v>76.5</v>
       </c>
-      <c r="F98" s="336" t="n">
+      <c r="F98" s="350" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="G98" s="336" t="n">
+      <c r="G98" s="350" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="H98" s="342">
+      <c r="H98" s="356">
         <f>CHOOSE(MATCH(MIN(D98:G98),D98:G98,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11594,19 +11636,19 @@
           <t>в т.ч. 8-волоконный, км</t>
         </is>
       </c>
-      <c r="D99" s="334" t="n">
+      <c r="D99" s="348" t="n">
         <v>35.1</v>
       </c>
-      <c r="E99" s="334" t="n">
+      <c r="E99" s="348" t="n">
         <v>46.7</v>
       </c>
-      <c r="F99" s="334" t="n">
+      <c r="F99" s="348" t="n">
         <v>49.5</v>
       </c>
-      <c r="G99" s="334" t="n">
+      <c r="G99" s="348" t="n">
         <v>42.7</v>
       </c>
-      <c r="H99" s="341" t="n"/>
+      <c r="H99" s="355" t="n"/>
     </row>
     <row r="100" ht="18" customHeight="1" s="63">
       <c r="C100" s="114" t="inlineStr">
@@ -11614,19 +11656,19 @@
           <t>в т.ч. 96-волоконный, км</t>
         </is>
       </c>
-      <c r="D100" s="336" t="n">
+      <c r="D100" s="350" t="n">
         <v>33.8</v>
       </c>
-      <c r="E100" s="336" t="n">
+      <c r="E100" s="350" t="n">
         <v>1.5</v>
       </c>
-      <c r="F100" s="336" t="n">
+      <c r="F100" s="350" t="n">
         <v>0.9</v>
       </c>
-      <c r="G100" s="336" t="n">
+      <c r="G100" s="350" t="n">
         <v>0.7</v>
       </c>
-      <c r="H100" s="342" t="n"/>
+      <c r="H100" s="356" t="n"/>
     </row>
     <row r="101" ht="18" customHeight="1" s="63">
       <c r="C101" s="112" t="inlineStr">
@@ -11634,19 +11676,19 @@
           <t>Дроп-кабель, км</t>
         </is>
       </c>
-      <c r="D101" s="334" t="n">
+      <c r="D101" s="348" t="n">
         <v>95.8</v>
       </c>
-      <c r="E101" s="334" t="n">
+      <c r="E101" s="348" t="n">
         <v>170.7</v>
       </c>
-      <c r="F101" s="334" t="n">
+      <c r="F101" s="348" t="n">
         <v>244</v>
       </c>
-      <c r="G101" s="334" t="n">
+      <c r="G101" s="348" t="n">
         <v>126.9</v>
       </c>
-      <c r="H101" s="341">
+      <c r="H101" s="355">
         <f>CHOOSE(MATCH(MIN(D101:G101),D101:G101,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11657,23 +11699,23 @@
           <t>ВСЕГО кабель + дропы, км</t>
         </is>
       </c>
-      <c r="D102" s="336">
+      <c r="D102" s="350">
         <f>D98+D101</f>
         <v/>
       </c>
-      <c r="E102" s="336">
+      <c r="E102" s="350">
         <f>E98+E101</f>
         <v/>
       </c>
-      <c r="F102" s="336">
+      <c r="F102" s="350">
         <f>F98+F101</f>
         <v/>
       </c>
-      <c r="G102" s="336">
+      <c r="G102" s="350">
         <f>G98+G101</f>
         <v/>
       </c>
-      <c r="H102" s="342">
+      <c r="H102" s="356">
         <f>CHOOSE(MATCH(MIN(D102:G102),D102:G102,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11684,19 +11726,19 @@
           <t>Средний дроп, м</t>
         </is>
       </c>
-      <c r="D103" s="332" t="n">
+      <c r="D103" s="346" t="n">
         <v>29.4</v>
       </c>
-      <c r="E103" s="332" t="n">
+      <c r="E103" s="346" t="n">
         <v>52.5</v>
       </c>
-      <c r="F103" s="332" t="n">
+      <c r="F103" s="346" t="n">
         <v>75.2</v>
       </c>
-      <c r="G103" s="332" t="n">
+      <c r="G103" s="346" t="n">
         <v>39</v>
       </c>
-      <c r="H103" s="341">
+      <c r="H103" s="355">
         <f>CHOOSE(MATCH(MIN(D103:G103),D103:G103,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11707,19 +11749,19 @@
           <t>Максимальный дроп, м</t>
         </is>
       </c>
-      <c r="D104" s="333" t="n">
+      <c r="D104" s="347" t="n">
         <v>132.5</v>
       </c>
-      <c r="E104" s="333" t="n">
+      <c r="E104" s="347" t="n">
         <v>201</v>
       </c>
-      <c r="F104" s="333" t="n">
+      <c r="F104" s="347" t="n">
         <v>266</v>
       </c>
-      <c r="G104" s="333" t="n">
+      <c r="G104" s="347" t="n">
         <v>132.5</v>
       </c>
-      <c r="H104" s="342">
+      <c r="H104" s="356">
         <f>CHOOSE(MATCH(MIN(D104:G104),D104:G104,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11730,15 +11772,15 @@
           <t>Ср. маршрут волокна ДХ, м</t>
         </is>
       </c>
-      <c r="D105" s="332" t="n">
+      <c r="D105" s="346" t="n">
         <v>1361</v>
       </c>
-      <c r="E105" s="332" t="n"/>
-      <c r="F105" s="332" t="n"/>
-      <c r="G105" s="332" t="n">
+      <c r="E105" s="346" t="n"/>
+      <c r="F105" s="346" t="n"/>
+      <c r="G105" s="346" t="n">
         <v>278</v>
       </c>
-      <c r="H105" s="341">
+      <c r="H105" s="355">
         <f>CHOOSE(MATCH(MIN(D105:G105),D105:G105,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11749,19 +11791,19 @@
           <t>ОРШ, шт</t>
         </is>
       </c>
-      <c r="D106" s="333" t="n">
+      <c r="D106" s="347" t="n">
         <v>6</v>
       </c>
-      <c r="E106" s="333" t="n">
+      <c r="E106" s="347" t="n">
         <v>6</v>
       </c>
-      <c r="F106" s="333" t="n">
+      <c r="F106" s="347" t="n">
         <v>6</v>
       </c>
-      <c r="G106" s="333" t="n">
+      <c r="G106" s="347" t="n">
         <v>42</v>
       </c>
-      <c r="H106" s="342">
+      <c r="H106" s="356">
         <f>CHOOSE(MATCH(MIN(D106:G106),D106:G106,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11772,19 +11814,19 @@
           <t>РОР, шт</t>
         </is>
       </c>
-      <c r="D107" s="332" t="n">
+      <c r="D107" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="332" t="n">
+      <c r="E107" s="346" t="n">
         <v>515</v>
       </c>
-      <c r="F107" s="332" t="n">
+      <c r="F107" s="346" t="n">
         <v>323</v>
       </c>
-      <c r="G107" s="332" t="n">
+      <c r="G107" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="341" t="n"/>
+      <c r="H107" s="355" t="n"/>
     </row>
     <row r="108" ht="18" customHeight="1" s="63">
       <c r="C108" s="114" t="inlineStr">
@@ -11792,19 +11834,19 @@
           <t>Сплиттеры 1:64, шт</t>
         </is>
       </c>
-      <c r="D108" s="333" t="n">
+      <c r="D108" s="347" t="n">
         <v>39</v>
       </c>
-      <c r="E108" s="333" t="n">
+      <c r="E108" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="333" t="n">
+      <c r="F108" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="333" t="n">
+      <c r="G108" s="347" t="n">
         <v>65</v>
       </c>
-      <c r="H108" s="342" t="n"/>
+      <c r="H108" s="356" t="n"/>
     </row>
     <row r="109" ht="18" customHeight="1" s="63">
       <c r="C109" s="112" t="inlineStr">
@@ -11812,19 +11854,19 @@
           <t>Сплиттеры 1:8, шт</t>
         </is>
       </c>
-      <c r="D109" s="332" t="n">
+      <c r="D109" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="332" t="n">
+      <c r="E109" s="346" t="n">
         <v>581</v>
       </c>
-      <c r="F109" s="332" t="n">
+      <c r="F109" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="332" t="n">
+      <c r="G109" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="341" t="n"/>
+      <c r="H109" s="355" t="n"/>
     </row>
     <row r="110" ht="18" customHeight="1" s="63">
       <c r="C110" s="114" t="inlineStr">
@@ -11832,19 +11874,19 @@
           <t>Сплиттеры 1:4, шт</t>
         </is>
       </c>
-      <c r="D110" s="333" t="n">
+      <c r="D110" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="333" t="n">
+      <c r="E110" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="333" t="n">
+      <c r="F110" s="347" t="n">
         <v>83</v>
       </c>
-      <c r="G110" s="333" t="n">
+      <c r="G110" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="H110" s="342" t="n"/>
+      <c r="H110" s="356" t="n"/>
     </row>
     <row r="111" ht="18" customHeight="1" s="63">
       <c r="C111" s="112" t="inlineStr">
@@ -11852,19 +11894,19 @@
           <t>Сплиттеры 1:16, шт</t>
         </is>
       </c>
-      <c r="D111" s="332" t="n">
+      <c r="D111" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="332" t="n">
+      <c r="E111" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="332" t="n">
+      <c r="F111" s="346" t="n">
         <v>323</v>
       </c>
-      <c r="G111" s="332" t="n">
+      <c r="G111" s="346" t="n">
         <v>0</v>
       </c>
-      <c r="H111" s="341" t="n"/>
+      <c r="H111" s="355" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1" s="63">
       <c r="C112" s="114" t="inlineStr">
@@ -11872,19 +11914,19 @@
           <t>Муфты, шт</t>
         </is>
       </c>
-      <c r="D112" s="333" t="n">
+      <c r="D112" s="347" t="n">
         <v>1140</v>
       </c>
-      <c r="E112" s="333" t="n">
+      <c r="E112" s="347" t="n">
         <v>115</v>
       </c>
-      <c r="F112" s="333" t="n">
+      <c r="F112" s="347" t="n">
         <v>100</v>
       </c>
-      <c r="G112" s="333" t="n">
+      <c r="G112" s="347" t="n">
         <v>1103</v>
       </c>
-      <c r="H112" s="342">
+      <c r="H112" s="356">
         <f>CHOOSE(MATCH(MIN(D112:G112),D112:G112,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11895,19 +11937,19 @@
           <t>Сварки, шт</t>
         </is>
       </c>
-      <c r="D113" s="332" t="n">
+      <c r="D113" s="346" t="n">
         <v>5136</v>
       </c>
-      <c r="E113" s="332" t="n">
+      <c r="E113" s="346" t="n">
         <v>2585</v>
       </c>
-      <c r="F113" s="332" t="n">
+      <c r="F113" s="346" t="n">
         <v>1552</v>
       </c>
-      <c r="G113" s="332" t="n">
+      <c r="G113" s="346" t="n">
         <v>6942</v>
       </c>
-      <c r="H113" s="341">
+      <c r="H113" s="355">
         <f>CHOOSE(MATCH(MIN(D113:G113),D113:G113,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11918,19 +11960,19 @@
           <t>Коннекторы FAST, шт</t>
         </is>
       </c>
-      <c r="D114" s="333" t="n">
+      <c r="D114" s="347" t="n">
         <v>2569</v>
       </c>
-      <c r="E114" s="333" t="n">
+      <c r="E114" s="347" t="n">
         <v>5136</v>
       </c>
-      <c r="F114" s="333" t="n">
+      <c r="F114" s="347" t="n">
         <v>5136</v>
       </c>
-      <c r="G114" s="333" t="n">
-        <v>3400</v>
-      </c>
-      <c r="H114" s="342">
+      <c r="G114" s="347" t="n">
+        <v>3401</v>
+      </c>
+      <c r="H114" s="356">
         <f>CHOOSE(MATCH(MIN(D114:G114),D114:G114,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11941,19 +11983,19 @@
           <t>Порты кросса ОРШ, шт</t>
         </is>
       </c>
-      <c r="D115" s="332" t="n">
+      <c r="D115" s="346" t="n">
         <v>3600</v>
       </c>
-      <c r="E115" s="332" t="n">
+      <c r="E115" s="346" t="n">
         <v>1008</v>
       </c>
-      <c r="F115" s="332" t="n">
+      <c r="F115" s="346" t="n">
         <v>864</v>
       </c>
-      <c r="G115" s="332" t="n">
+      <c r="G115" s="346" t="n">
         <v>5184</v>
       </c>
-      <c r="H115" s="341">
+      <c r="H115" s="355">
         <f>CHOOSE(MATCH(MIN(D115:G115),D115:G115,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11964,19 +12006,19 @@
           <t>Порты OLT, шт</t>
         </is>
       </c>
-      <c r="D116" s="333" t="n">
+      <c r="D116" s="347" t="n">
         <v>39</v>
       </c>
-      <c r="E116" s="333" t="n">
+      <c r="E116" s="347" t="n">
         <v>66</v>
       </c>
-      <c r="F116" s="333" t="n">
+      <c r="F116" s="347" t="n">
         <v>83</v>
       </c>
-      <c r="G116" s="333" t="n">
+      <c r="G116" s="347" t="n">
         <v>65</v>
       </c>
-      <c r="H116" s="342">
+      <c r="H116" s="356">
         <f>CHOOSE(MATCH(MIN(D116:G116),D116:G116,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -11987,19 +12029,19 @@
           <t>Комплекты подвеса, шт</t>
         </is>
       </c>
-      <c r="D117" s="332" t="n">
+      <c r="D117" s="346" t="n">
         <v>2911</v>
       </c>
-      <c r="E117" s="332" t="n">
+      <c r="E117" s="346" t="n">
         <v>4180</v>
       </c>
-      <c r="F117" s="332" t="n">
+      <c r="F117" s="346" t="n">
         <v>6136</v>
       </c>
-      <c r="G117" s="332" t="n">
+      <c r="G117" s="346" t="n">
         <v>2472</v>
       </c>
-      <c r="H117" s="341">
+      <c r="H117" s="355">
         <f>CHOOSE(MATCH(MIN(D117:G117),D117:G117,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -12010,19 +12052,19 @@
           <t>Доп. шкафы ОРШ (сверх 6), шт</t>
         </is>
       </c>
-      <c r="D118" s="333" t="n">
+      <c r="D118" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="333" t="n">
+      <c r="E118" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="333" t="n">
+      <c r="F118" s="347" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="333" t="n">
+      <c r="G118" s="347" t="n">
         <v>36</v>
       </c>
-      <c r="H118" s="342">
+      <c r="H118" s="356">
         <f>CHOOSE(MATCH(MIN(D118:G118),D118:G118,0),"A","B","C","D")</f>
         <v/>
       </c>
@@ -12086,16 +12128,16 @@
           <t>Кабельная продукция (магистраль)</t>
         </is>
       </c>
-      <c r="D123" s="334" t="n">
+      <c r="D123" s="348" t="n">
         <v>233</v>
       </c>
-      <c r="E123" s="334" t="n">
+      <c r="E123" s="348" t="n">
         <v>107</v>
       </c>
-      <c r="F123" s="334" t="n">
+      <c r="F123" s="348" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="G123" s="334" t="n">
+      <c r="G123" s="348" t="n">
         <v>133.1</v>
       </c>
     </row>
@@ -12105,16 +12147,16 @@
           <t>Дроп-кабели</t>
         </is>
       </c>
-      <c r="D124" s="336" t="n">
+      <c r="D124" s="350" t="n">
         <v>47.9</v>
       </c>
-      <c r="E124" s="336" t="n">
+      <c r="E124" s="350" t="n">
         <v>85.3</v>
       </c>
-      <c r="F124" s="336" t="n">
+      <c r="F124" s="350" t="n">
         <v>122</v>
       </c>
-      <c r="G124" s="336" t="n">
+      <c r="G124" s="350" t="n">
         <v>63.5</v>
       </c>
     </row>
@@ -12124,16 +12166,16 @@
           <t>Оборудование и монтаж</t>
         </is>
       </c>
-      <c r="D125" s="334" t="n">
+      <c r="D125" s="348" t="n">
         <v>315</v>
       </c>
-      <c r="E125" s="334" t="n">
+      <c r="E125" s="348" t="n">
         <v>306.2</v>
       </c>
-      <c r="F125" s="334" t="n">
+      <c r="F125" s="348" t="n">
         <v>270.8</v>
       </c>
-      <c r="G125" s="334" t="n">
+      <c r="G125" s="348" t="n">
         <v>373</v>
       </c>
     </row>
@@ -12166,16 +12208,16 @@
           <t>Доп. шкафы ОРШ (сверх базовых 6, по 1,5 у.е.)</t>
         </is>
       </c>
-      <c r="D127" s="336" t="n">
+      <c r="D127" s="350" t="n">
         <v>0</v>
       </c>
-      <c r="E127" s="336" t="n">
+      <c r="E127" s="350" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="336" t="n">
+      <c r="F127" s="350" t="n">
         <v>0</v>
       </c>
-      <c r="G127" s="336" t="n">
+      <c r="G127" s="350" t="n">
         <v>54</v>
       </c>
     </row>
@@ -12208,19 +12250,19 @@
           <t>Δ к лучшей схеме</t>
         </is>
       </c>
-      <c r="D129" s="335">
+      <c r="D129" s="349">
         <f>D128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="E129" s="335">
+      <c r="E129" s="349">
         <f>E128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="F129" s="335">
+      <c r="F129" s="349">
         <f>F128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
-      <c r="G129" s="335">
+      <c r="G129" s="349">
         <f>G128/MIN($D$128:$G$128)-1</f>
         <v/>
       </c>
@@ -12265,106 +12307,106 @@
       </c>
     </row>
     <row r="133" ht="18" customHeight="1" s="63">
-      <c r="C133" s="344" t="n">
+      <c r="C133" s="358" t="n">
         <v>0</v>
       </c>
-      <c r="D133" s="332" t="n">
+      <c r="D133" s="346" t="n">
         <v>520.2</v>
       </c>
-      <c r="E133" s="332" t="n">
+      <c r="E133" s="346" t="n">
         <v>553.4</v>
       </c>
-      <c r="F133" s="332" t="n">
+      <c r="F133" s="346" t="n">
         <v>585.9</v>
       </c>
-      <c r="G133" s="332" t="n">
+      <c r="G133" s="346" t="n">
         <v>647</v>
       </c>
-      <c r="H133" s="341">
+      <c r="H133" s="355">
         <f>CHOOSE(MATCH(MIN(D133:G133),D133:G133,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="134" ht="18" customHeight="1" s="63">
-      <c r="C134" s="345" t="n">
+      <c r="C134" s="359" t="n">
         <v>0.3</v>
       </c>
-      <c r="D134" s="333" t="n">
+      <c r="D134" s="347" t="n">
         <v>545.2</v>
       </c>
-      <c r="E134" s="333" t="n">
+      <c r="E134" s="347" t="n">
         <v>510.5</v>
       </c>
-      <c r="F134" s="333" t="n">
+      <c r="F134" s="347" t="n">
         <v>511.9</v>
       </c>
-      <c r="G134" s="333" t="n">
-        <v>624.3</v>
-      </c>
-      <c r="H134" s="342">
+      <c r="G134" s="347" t="n">
+        <v>624.4</v>
+      </c>
+      <c r="H134" s="356">
         <f>CHOOSE(MATCH(MIN(D134:G134),D134:G134,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="135" ht="18" customHeight="1" s="63">
-      <c r="C135" s="344" t="n">
+      <c r="C135" s="358" t="n">
         <v>0.5</v>
       </c>
-      <c r="D135" s="332" t="n">
+      <c r="D135" s="346" t="n">
         <v>595.9</v>
       </c>
-      <c r="E135" s="332" t="n">
+      <c r="E135" s="346" t="n">
         <v>498.6</v>
       </c>
-      <c r="F135" s="332" t="n">
+      <c r="F135" s="346" t="n">
         <v>481.6</v>
       </c>
-      <c r="G135" s="332" t="n">
-        <v>623.5</v>
-      </c>
-      <c r="H135" s="341">
+      <c r="G135" s="346" t="n">
+        <v>623.6</v>
+      </c>
+      <c r="H135" s="355">
         <f>CHOOSE(MATCH(MIN(D135:G135),D135:G135,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="136" ht="18" customHeight="1" s="63">
-      <c r="C136" s="345" t="n">
+      <c r="C136" s="359" t="n">
         <v>0.7</v>
       </c>
-      <c r="D136" s="333" t="n">
+      <c r="D136" s="347" t="n">
         <v>688</v>
       </c>
-      <c r="E136" s="333" t="n">
+      <c r="E136" s="347" t="n">
         <v>500.1</v>
       </c>
-      <c r="F136" s="333" t="n">
+      <c r="F136" s="347" t="n">
         <v>464</v>
       </c>
-      <c r="G136" s="333" t="n">
-        <v>634.5</v>
-      </c>
-      <c r="H136" s="342">
+      <c r="G136" s="347" t="n">
+        <v>634.6</v>
+      </c>
+      <c r="H136" s="356">
         <f>CHOOSE(MATCH(MIN(D136:G136),D136:G136,0),"A","B","C","D")</f>
         <v/>
       </c>
     </row>
     <row r="137" ht="18" customHeight="1" s="63">
-      <c r="C137" s="344" t="n">
+      <c r="C137" s="358" t="n">
         <v>1</v>
       </c>
-      <c r="D137" s="332" t="n">
+      <c r="D137" s="346" t="n">
         <v>955</v>
       </c>
-      <c r="E137" s="332" t="n">
+      <c r="E137" s="346" t="n">
         <v>531.4</v>
       </c>
-      <c r="F137" s="332" t="n">
+      <c r="F137" s="346" t="n">
         <v>459.4</v>
       </c>
-      <c r="G137" s="332" t="n">
-        <v>676.8</v>
-      </c>
-      <c r="H137" s="341">
+      <c r="G137" s="346" t="n">
+        <v>677</v>
+      </c>
+      <c r="H137" s="355">
         <f>CHOOSE(MATCH(MIN(D137:G137),D137:G137,0),"A","B","C","D")</f>
         <v/>
       </c>
